--- a/docs/NTCSWEB-Modules.xlsx
+++ b/docs/NTCSWEB-Modules.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Back office" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Website" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Public School Menu" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Back office'!$A$1:$K$39</definedName>
@@ -74,7 +75,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -96,8 +97,20 @@
         <fgColor rgb="FFF3F5FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -135,11 +148,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9DCE3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9DCE3"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9DCE3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -219,6 +245,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2039,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K208"/>
+  <dimension ref="A1:K211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4116,12 +4175,12 @@
       </c>
       <c r="I54" s="20" t="inlineStr">
         <is>
-          <t>Exams</t>
+          <t>Academic Transcript</t>
         </is>
       </c>
       <c r="J54" s="20" t="inlineStr">
         <is>
-          <t>ការប្រឡង</t>
+          <t>ប្រវត្តិពិន្ទុ</t>
         </is>
       </c>
       <c r="K54" s="24" t="n"/>
@@ -4155,12 +4214,12 @@
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>Grades</t>
+          <t>Student Progress</t>
         </is>
       </c>
       <c r="J55" s="20" t="inlineStr">
         <is>
-          <t>និទ្ទេស</t>
+          <t>វឌ្ឍនភាពសិស្ស</t>
         </is>
       </c>
       <c r="K55" s="24" t="n"/>
@@ -4194,12 +4253,12 @@
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
-          <t>Make-up Exam</t>
+          <t>Result Export</t>
         </is>
       </c>
       <c r="J56" s="20" t="inlineStr">
         <is>
-          <t>ប្រឡងសង</t>
+          <t>នាំចេញលទ្ធផល</t>
         </is>
       </c>
       <c r="K56" s="24" t="n"/>
@@ -4233,286 +4292,286 @@
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
+          <t>Exams</t>
+        </is>
+      </c>
+      <c r="J57" s="20" t="inlineStr">
+        <is>
+          <t>ការប្រឡង</t>
+        </is>
+      </c>
+      <c r="K57" s="24" t="n"/>
+    </row>
+    <row r="58" ht="21.6" customHeight="1">
+      <c r="A58" s="19" t="n"/>
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>B4.9</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr">
+        <is>
+          <t>Examination</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>ការប្រឡងនិងលទ្ធផល</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr">
+        <is>
+          <t>/examination</t>
+        </is>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I58" s="20" t="inlineStr">
+        <is>
+          <t>Grades</t>
+        </is>
+      </c>
+      <c r="J58" s="20" t="inlineStr">
+        <is>
+          <t>និទ្ទេស</t>
+        </is>
+      </c>
+      <c r="K58" s="24" t="n"/>
+    </row>
+    <row r="59" ht="21.6" customHeight="1">
+      <c r="A59" s="19" t="n"/>
+      <c r="B59" s="20" t="n"/>
+      <c r="C59" s="20" t="n"/>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>B4.9</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>Examination</t>
+        </is>
+      </c>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>ការប្រឡងនិងលទ្ធផល</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>/examination</t>
+        </is>
+      </c>
+      <c r="H59" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="I59" s="20" t="inlineStr">
+        <is>
+          <t>Make-up Exam</t>
+        </is>
+      </c>
+      <c r="J59" s="20" t="inlineStr">
+        <is>
+          <t>ប្រឡងសង</t>
+        </is>
+      </c>
+      <c r="K59" s="24" t="n"/>
+    </row>
+    <row r="60" ht="21.6" customHeight="1">
+      <c r="A60" s="19" t="n"/>
+      <c r="B60" s="20" t="n"/>
+      <c r="C60" s="20" t="n"/>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>B4.9</t>
+        </is>
+      </c>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>Examination</t>
+        </is>
+      </c>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>ការប្រឡងនិងលទ្ធផល</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr">
+        <is>
+          <t>/examination</t>
+        </is>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I60" s="20" t="inlineStr">
+        <is>
           <t>Certificate</t>
         </is>
       </c>
-      <c r="J57" s="20" t="inlineStr">
+      <c r="J60" s="20" t="inlineStr">
         <is>
           <t>វិញ្ញាបនបត្រ</t>
         </is>
       </c>
-      <c r="K57" s="24" t="n"/>
-    </row>
-    <row r="58" ht="21.6" customHeight="1">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="K60" s="24" t="n"/>
+    </row>
+    <row r="61" ht="21.6" customHeight="1">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>សិស្សានុសិស្ស</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="D61" s="1" t="inlineStr">
         <is>
           <t>B5.1</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>សិស្សានុសិស្ស</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>/students</t>
         </is>
       </c>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="3" t="n"/>
-      <c r="J58" s="3" t="n"/>
-      <c r="K58" s="6" t="n"/>
-    </row>
-    <row r="59" ht="21.6" customHeight="1">
-      <c r="A59" s="7" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="3" t="n"/>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="6" t="n"/>
+    </row>
+    <row r="62" ht="21.6" customHeight="1">
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>B5.2</t>
         </is>
       </c>
-      <c r="E59" s="10" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>Import Students</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>នាំចូលទិន្នន័យសិស្ស</t>
         </is>
       </c>
-      <c r="G59" s="11" t="inlineStr">
+      <c r="G62" s="11" t="inlineStr">
         <is>
           <t>/student-imports</t>
         </is>
       </c>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="12" t="n"/>
-    </row>
-    <row r="60" ht="21.6" customHeight="1">
-      <c r="A60" s="7" t="n"/>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="12" t="n"/>
+    </row>
+    <row r="63" ht="21.6" customHeight="1">
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>B5.3</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>Enrollments</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>ការចុះឈ្មោះចូលរៀន</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>/enrollments</t>
         </is>
       </c>
-      <c r="H60" s="7" t="n"/>
-      <c r="I60" s="8" t="n"/>
-      <c r="J60" s="8" t="n"/>
-      <c r="K60" s="12" t="n"/>
-    </row>
-    <row r="61" ht="21.6" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="12" t="n"/>
+    </row>
+    <row r="64" ht="21.6" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>HRM</t>
         </is>
       </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>ធនធានមនុស្ស</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
         <is>
           <t>B6.1</t>
         </is>
       </c>
-      <c r="E61" s="14" t="inlineStr">
+      <c r="E64" s="14" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="F61" s="15" t="inlineStr">
+      <c r="F64" s="15" t="inlineStr">
         <is>
           <t>បុគ្គលិក</t>
         </is>
       </c>
-      <c r="G61" s="16" t="inlineStr">
+      <c r="G64" s="16" t="inlineStr">
         <is>
           <t>/staff</t>
         </is>
       </c>
-      <c r="H61" s="17" t="n">
+      <c r="H64" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I61" s="15" t="inlineStr">
+      <c r="I64" s="15" t="inlineStr">
         <is>
           <t>Current Info</t>
         </is>
       </c>
-      <c r="J61" s="15" t="inlineStr">
+      <c r="J64" s="15" t="inlineStr">
         <is>
           <t>ព័ត៌មានបច្ចុប្បន្ន</t>
         </is>
       </c>
-      <c r="K61" s="18" t="inlineStr">
+      <c r="K64" s="18" t="inlineStr">
         <is>
           <t>Tabs on the staff form</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="21.6" customHeight="1">
-      <c r="A62" s="19" t="n"/>
-      <c r="B62" s="20" t="n"/>
-      <c r="C62" s="20" t="n"/>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>B6.1</t>
-        </is>
-      </c>
-      <c r="E62" s="20" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="F62" s="20" t="inlineStr">
-        <is>
-          <t>បុគ្គលិក</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr">
-        <is>
-          <t>/staff</t>
-        </is>
-      </c>
-      <c r="H62" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" s="20" t="inlineStr">
-        <is>
-          <t>Emergency Contacts</t>
-        </is>
-      </c>
-      <c r="J62" s="20" t="inlineStr">
-        <is>
-          <t>ទំនាក់ទំនងបន្ទាន់</t>
-        </is>
-      </c>
-      <c r="K62" s="24" t="n"/>
-    </row>
-    <row r="63" ht="21.6" customHeight="1">
-      <c r="A63" s="19" t="n"/>
-      <c r="B63" s="20" t="n"/>
-      <c r="C63" s="20" t="n"/>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>B6.1</t>
-        </is>
-      </c>
-      <c r="E63" s="20" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="F63" s="20" t="inlineStr">
-        <is>
-          <t>បុគ្គលិក</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="inlineStr">
-        <is>
-          <t>/staff</t>
-        </is>
-      </c>
-      <c r="H63" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I63" s="20" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="J63" s="20" t="inlineStr">
-        <is>
-          <t>ការសិក្សា</t>
-        </is>
-      </c>
-      <c r="K63" s="24" t="n"/>
-    </row>
-    <row r="64" ht="21.6" customHeight="1">
-      <c r="A64" s="19" t="n"/>
-      <c r="B64" s="20" t="n"/>
-      <c r="C64" s="20" t="n"/>
-      <c r="D64" s="19" t="inlineStr">
-        <is>
-          <t>B6.1</t>
-        </is>
-      </c>
-      <c r="E64" s="20" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="F64" s="20" t="inlineStr">
-        <is>
-          <t>បុគ្គលិក</t>
-        </is>
-      </c>
-      <c r="G64" s="23" t="inlineStr">
-        <is>
-          <t>/staff</t>
-        </is>
-      </c>
-      <c r="H64" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I64" s="20" t="inlineStr">
-        <is>
-          <t>Family Members</t>
-        </is>
-      </c>
-      <c r="J64" s="20" t="inlineStr">
-        <is>
-          <t>សមាជិកគ្រួសារ</t>
-        </is>
-      </c>
-      <c r="K64" s="24" t="n"/>
     </row>
     <row r="65" ht="21.6" customHeight="1">
       <c r="A65" s="19" t="n"/>
@@ -4539,16 +4598,16 @@
         </is>
       </c>
       <c r="H65" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I65" s="20" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Emergency Contacts</t>
         </is>
       </c>
       <c r="J65" s="20" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>ទំនាក់ទំនងបន្ទាន់</t>
         </is>
       </c>
       <c r="K65" s="24" t="n"/>
@@ -4578,16 +4637,16 @@
         </is>
       </c>
       <c r="H66" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
-          <t>Previous Work</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="J66" s="20" t="inlineStr">
         <is>
-          <t>បទពិសោធន៍ការងារពីមុន</t>
+          <t>ការសិក្សា</t>
         </is>
       </c>
       <c r="K66" s="24" t="n"/>
@@ -4596,37 +4655,37 @@
       <c r="A67" s="19" t="n"/>
       <c r="B67" s="20" t="n"/>
       <c r="C67" s="20" t="n"/>
-      <c r="D67" s="21" t="inlineStr">
-        <is>
-          <t>B6.2</t>
-        </is>
-      </c>
-      <c r="E67" s="22" t="inlineStr">
-        <is>
-          <t>Teachers</t>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>B6.1</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>Staff</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>គ្រូ</t>
+          <t>បុគ្គលិក</t>
         </is>
       </c>
       <c r="G67" s="23" t="inlineStr">
         <is>
-          <t>/teachers</t>
+          <t>/staff</t>
         </is>
       </c>
       <c r="H67" s="19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Family Members</t>
         </is>
       </c>
       <c r="J67" s="20" t="inlineStr">
         <is>
-          <t>គុណវុឌ្ឍិ</t>
+          <t>សមាជិកគ្រួសារ</t>
         </is>
       </c>
       <c r="K67" s="24" t="n"/>
@@ -4637,35 +4696,35 @@
       <c r="C68" s="20" t="n"/>
       <c r="D68" s="19" t="inlineStr">
         <is>
-          <t>B6.2</t>
+          <t>B6.1</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Teachers</t>
+          <t>Staff</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>គ្រូ</t>
+          <t>បុគ្គលិក</t>
         </is>
       </c>
       <c r="G68" s="23" t="inlineStr">
         <is>
-          <t>/teachers</t>
+          <t>/staff</t>
         </is>
       </c>
       <c r="H68" s="19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="J68" s="20" t="inlineStr">
         <is>
-          <t>ការចាត់តាំង</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="K68" s="24" t="n"/>
@@ -4676,35 +4735,35 @@
       <c r="C69" s="20" t="n"/>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t>B6.2</t>
+          <t>B6.1</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>Teachers</t>
+          <t>Staff</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>គ្រូ</t>
+          <t>បុគ្គលិក</t>
         </is>
       </c>
       <c r="G69" s="23" t="inlineStr">
         <is>
-          <t>/teachers</t>
+          <t>/staff</t>
         </is>
       </c>
       <c r="H69" s="19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>Homeroom</t>
+          <t>Previous Work</t>
         </is>
       </c>
       <c r="J69" s="20" t="inlineStr">
         <is>
-          <t>គ្រូប្រចាំថ្នាក់</t>
+          <t>បទពិសោធន៍ការងារពីមុន</t>
         </is>
       </c>
       <c r="K69" s="24" t="n"/>
@@ -4713,12 +4772,12 @@
       <c r="A70" s="19" t="n"/>
       <c r="B70" s="20" t="n"/>
       <c r="C70" s="20" t="n"/>
-      <c r="D70" s="19" t="inlineStr">
+      <c r="D70" s="21" t="inlineStr">
         <is>
           <t>B6.2</t>
         </is>
       </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="E70" s="22" t="inlineStr">
         <is>
           <t>Teachers</t>
         </is>
@@ -4734,16 +4793,16 @@
         </is>
       </c>
       <c r="H70" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>Teaching load</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="J70" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបង្រៀន</t>
+          <t>គុណវុឌ្ឍិ</t>
         </is>
       </c>
       <c r="K70" s="24" t="n"/>
@@ -4773,16 +4832,16 @@
         </is>
       </c>
       <c r="H71" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
-          <t>ពេលទំនេរ</t>
+          <t>ការចាត់តាំង</t>
         </is>
       </c>
       <c r="K71" s="24" t="n"/>
@@ -4812,16 +4871,16 @@
         </is>
       </c>
       <c r="H72" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>Substitute</t>
+          <t>Homeroom</t>
         </is>
       </c>
       <c r="J72" s="20" t="inlineStr">
         <is>
-          <t>គ្រូជំនួស</t>
+          <t>គ្រូប្រចាំថ្នាក់</t>
         </is>
       </c>
       <c r="K72" s="24" t="n"/>
@@ -4851,16 +4910,16 @@
         </is>
       </c>
       <c r="H73" s="19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Teaching load</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
         <is>
-          <t>ឯកសារ</t>
+          <t>ម៉ោងបង្រៀន</t>
         </is>
       </c>
       <c r="K73" s="24" t="n"/>
@@ -4869,66 +4928,76 @@
       <c r="A74" s="19" t="n"/>
       <c r="B74" s="20" t="n"/>
       <c r="C74" s="20" t="n"/>
-      <c r="D74" s="21" t="inlineStr">
-        <is>
-          <t>B6.3</t>
-        </is>
-      </c>
-      <c r="E74" s="22" t="inlineStr">
-        <is>
-          <t>Staff Status History</t>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>B6.2</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>Teachers</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
+          <t>គ្រូ</t>
         </is>
       </c>
       <c r="G74" s="23" t="inlineStr">
         <is>
-          <t>/staff-status-history</t>
-        </is>
-      </c>
-      <c r="H74" s="19" t="n"/>
-      <c r="I74" s="20" t="n"/>
-      <c r="J74" s="20" t="n"/>
+          <t>/teachers</t>
+        </is>
+      </c>
+      <c r="H74" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I74" s="20" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="J74" s="20" t="inlineStr">
+        <is>
+          <t>ពេលទំនេរ</t>
+        </is>
+      </c>
       <c r="K74" s="24" t="n"/>
     </row>
     <row r="75" ht="21.6" customHeight="1">
       <c r="A75" s="19" t="n"/>
       <c r="B75" s="20" t="n"/>
       <c r="C75" s="20" t="n"/>
-      <c r="D75" s="21" t="inlineStr">
-        <is>
-          <t>B6.4</t>
-        </is>
-      </c>
-      <c r="E75" s="22" t="inlineStr">
-        <is>
-          <t>Organization Management</t>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>B6.2</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>Teachers</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងអង្គភាព</t>
+          <t>គ្រូ</t>
         </is>
       </c>
       <c r="G75" s="23" t="inlineStr">
         <is>
-          <t>/organization</t>
+          <t>/teachers</t>
         </is>
       </c>
       <c r="H75" s="19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Substitute</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>សាលា</t>
+          <t>គ្រូជំនួស</t>
         </is>
       </c>
       <c r="K75" s="24" t="n"/>
@@ -4939,35 +5008,35 @@
       <c r="C76" s="20" t="n"/>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>B6.4</t>
+          <t>B6.2</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Organization Management</t>
+          <t>Teachers</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងអង្គភាព</t>
+          <t>គ្រូ</t>
         </is>
       </c>
       <c r="G76" s="23" t="inlineStr">
         <is>
-          <t>/organization</t>
+          <t>/teachers</t>
         </is>
       </c>
       <c r="H76" s="19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="J76" s="20" t="inlineStr">
         <is>
-          <t>សាខា</t>
+          <t>ឯកសារ</t>
         </is>
       </c>
       <c r="K76" s="24" t="n"/>
@@ -4976,51 +5045,41 @@
       <c r="A77" s="19" t="n"/>
       <c r="B77" s="20" t="n"/>
       <c r="C77" s="20" t="n"/>
-      <c r="D77" s="19" t="inlineStr">
-        <is>
-          <t>B6.4</t>
-        </is>
-      </c>
-      <c r="E77" s="20" t="inlineStr">
-        <is>
-          <t>Organization Management</t>
+      <c r="D77" s="21" t="inlineStr">
+        <is>
+          <t>B6.3</t>
+        </is>
+      </c>
+      <c r="E77" s="22" t="inlineStr">
+        <is>
+          <t>Staff Status History</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងអង្គភាព</t>
+          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
         <is>
-          <t>/organization</t>
-        </is>
-      </c>
-      <c r="H77" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I77" s="20" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="J77" s="20" t="inlineStr">
-        <is>
-          <t>នាយកដ្ឋាន</t>
-        </is>
-      </c>
+          <t>/staff-status-history</t>
+        </is>
+      </c>
+      <c r="H77" s="19" t="n"/>
+      <c r="I77" s="20" t="n"/>
+      <c r="J77" s="20" t="n"/>
       <c r="K77" s="24" t="n"/>
     </row>
     <row r="78" ht="21.6" customHeight="1">
       <c r="A78" s="19" t="n"/>
       <c r="B78" s="20" t="n"/>
       <c r="C78" s="20" t="n"/>
-      <c r="D78" s="19" t="inlineStr">
+      <c r="D78" s="21" t="inlineStr">
         <is>
           <t>B6.4</t>
         </is>
       </c>
-      <c r="E78" s="20" t="inlineStr">
+      <c r="E78" s="22" t="inlineStr">
         <is>
           <t>Organization Management</t>
         </is>
@@ -5036,16 +5095,16 @@
         </is>
       </c>
       <c r="H78" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>School</t>
         </is>
       </c>
       <c r="J78" s="20" t="inlineStr">
         <is>
-          <t>ក្រុម</t>
+          <t>សាលា</t>
         </is>
       </c>
       <c r="K78" s="24" t="n"/>
@@ -5075,16 +5134,16 @@
         </is>
       </c>
       <c r="H79" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="J79" s="20" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>សាខា</t>
         </is>
       </c>
       <c r="K79" s="24" t="n"/>
@@ -5114,16 +5173,16 @@
         </is>
       </c>
       <c r="H80" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>Job grade</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="J80" s="20" t="inlineStr">
         <is>
-          <t>ថ្នាក់ការងារ</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="K80" s="24" t="n"/>
@@ -5153,16 +5212,16 @@
         </is>
       </c>
       <c r="H81" s="19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Job level</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
-          <t>កម្រិតការងារ</t>
+          <t>ក្រុម</t>
         </is>
       </c>
       <c r="K81" s="24" t="n"/>
@@ -5192,16 +5251,16 @@
         </is>
       </c>
       <c r="H82" s="19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>Reporting manager</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="J82" s="20" t="inlineStr">
         <is>
-          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="K82" s="24" t="n"/>
@@ -5231,16 +5290,16 @@
         </is>
       </c>
       <c r="H83" s="19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Organization hierarchy</t>
+          <t>Job grade</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
+          <t>ថ្នាក់ការងារ</t>
         </is>
       </c>
       <c r="K83" s="24" t="n"/>
@@ -5249,37 +5308,37 @@
       <c r="A84" s="19" t="n"/>
       <c r="B84" s="20" t="n"/>
       <c r="C84" s="20" t="n"/>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>B6.5</t>
-        </is>
-      </c>
-      <c r="E84" s="22" t="inlineStr">
-        <is>
-          <t>Recruitment</t>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>B6.4</t>
+        </is>
+      </c>
+      <c r="E84" s="20" t="inlineStr">
+        <is>
+          <t>Organization Management</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបុគ្គលិក</t>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
         </is>
       </c>
       <c r="G84" s="23" t="inlineStr">
         <is>
-          <t>/recruitment</t>
+          <t>/organization</t>
         </is>
       </c>
       <c r="H84" s="19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>Manpower request</t>
+          <t>Job level</t>
         </is>
       </c>
       <c r="J84" s="20" t="inlineStr">
         <is>
-          <t>សំណើបុគ្គលិក</t>
+          <t>កម្រិតការងារ</t>
         </is>
       </c>
       <c r="K84" s="24" t="n"/>
@@ -5290,35 +5349,35 @@
       <c r="C85" s="20" t="n"/>
       <c r="D85" s="19" t="inlineStr">
         <is>
-          <t>B6.5</t>
+          <t>B6.4</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Organization Management</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបុគ្គលិក</t>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
         </is>
       </c>
       <c r="G85" s="23" t="inlineStr">
         <is>
-          <t>/recruitment</t>
+          <t>/organization</t>
         </is>
       </c>
       <c r="H85" s="19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Job positions</t>
+          <t>Reporting manager</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>មុខតំណែងការងារ</t>
+          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
         </is>
       </c>
       <c r="K85" s="24" t="n"/>
@@ -5329,35 +5388,35 @@
       <c r="C86" s="20" t="n"/>
       <c r="D86" s="19" t="inlineStr">
         <is>
-          <t>B6.5</t>
+          <t>B6.4</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Organization Management</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបុគ្គលិក</t>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
         </is>
       </c>
       <c r="G86" s="23" t="inlineStr">
         <is>
-          <t>/recruitment</t>
+          <t>/organization</t>
         </is>
       </c>
       <c r="H86" s="19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Job postings</t>
+          <t>Organization hierarchy</t>
         </is>
       </c>
       <c r="J86" s="20" t="inlineStr">
         <is>
-          <t>ការផ្សព្វផ្សាយការងារ</t>
+          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
         </is>
       </c>
       <c r="K86" s="24" t="n"/>
@@ -5366,12 +5425,12 @@
       <c r="A87" s="19" t="n"/>
       <c r="B87" s="20" t="n"/>
       <c r="C87" s="20" t="n"/>
-      <c r="D87" s="19" t="inlineStr">
+      <c r="D87" s="21" t="inlineStr">
         <is>
           <t>B6.5</t>
         </is>
       </c>
-      <c r="E87" s="20" t="inlineStr">
+      <c r="E87" s="22" t="inlineStr">
         <is>
           <t>Recruitment</t>
         </is>
@@ -5387,16 +5446,16 @@
         </is>
       </c>
       <c r="H87" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Applicant management</t>
+          <t>Manpower request</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងបេក្ខជន</t>
+          <t>សំណើបុគ្គលិក</t>
         </is>
       </c>
       <c r="K87" s="24" t="n"/>
@@ -5426,16 +5485,16 @@
         </is>
       </c>
       <c r="H88" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>CV/resume</t>
+          <t>Job positions</t>
         </is>
       </c>
       <c r="J88" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិរូប (CV)</t>
+          <t>មុខតំណែងការងារ</t>
         </is>
       </c>
       <c r="K88" s="24" t="n"/>
@@ -5465,16 +5524,16 @@
         </is>
       </c>
       <c r="H89" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Job postings</t>
         </is>
       </c>
       <c r="J89" s="20" t="inlineStr">
         <is>
-          <t>សម្ភាសន៍</t>
+          <t>ការផ្សព្វផ្សាយការងារ</t>
         </is>
       </c>
       <c r="K89" s="24" t="n"/>
@@ -5504,16 +5563,16 @@
         </is>
       </c>
       <c r="H90" s="19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Interview evaluation</t>
+          <t>Applicant management</t>
         </is>
       </c>
       <c r="J90" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃសម្ភាសន៍</t>
+          <t>គ្រប់គ្រងបេក្ខជន</t>
         </is>
       </c>
       <c r="K90" s="24" t="n"/>
@@ -5543,16 +5602,16 @@
         </is>
       </c>
       <c r="H91" s="19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>Candidate selection</t>
+          <t>CV/resume</t>
         </is>
       </c>
       <c r="J91" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបេក្ខជន</t>
+          <t>ប្រវត្តិរូប (CV)</t>
         </is>
       </c>
       <c r="K91" s="24" t="n"/>
@@ -5582,16 +5641,16 @@
         </is>
       </c>
       <c r="H92" s="19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
-          <t>Offer letter</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J92" s="20" t="inlineStr">
         <is>
-          <t>លិខិតផ្តល់ការងារ</t>
+          <t>សម្ភាសន៍</t>
         </is>
       </c>
       <c r="K92" s="24" t="n"/>
@@ -5621,16 +5680,16 @@
         </is>
       </c>
       <c r="H93" s="19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I93" s="20" t="inlineStr">
         <is>
-          <t>Recruitment pipeline</t>
+          <t>Interview evaluation</t>
         </is>
       </c>
       <c r="J93" s="20" t="inlineStr">
         <is>
-          <t>ដំណើរការជ្រើសរើស</t>
+          <t>ការវាយតម្លៃសម្ភាសន៍</t>
         </is>
       </c>
       <c r="K93" s="24" t="n"/>
@@ -5639,37 +5698,37 @@
       <c r="A94" s="19" t="n"/>
       <c r="B94" s="20" t="n"/>
       <c r="C94" s="20" t="n"/>
-      <c r="D94" s="21" t="inlineStr">
-        <is>
-          <t>B6.6</t>
-        </is>
-      </c>
-      <c r="E94" s="22" t="inlineStr">
-        <is>
-          <t>Attendance &amp; Time</t>
+      <c r="D94" s="19" t="inlineStr">
+        <is>
+          <t>B6.5</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+          <t>ការជ្រើសរើសបុគ្គលិក</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
         <is>
-          <t>/time-attendance</t>
+          <t>/recruitment</t>
         </is>
       </c>
       <c r="H94" s="19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
-          <t>Employee attendance</t>
+          <t>Candidate selection</t>
         </is>
       </c>
       <c r="J94" s="20" t="inlineStr">
         <is>
-          <t>វត្តមានបុគ្គលិក</t>
+          <t>ការជ្រើសរើសបេក្ខជន</t>
         </is>
       </c>
       <c r="K94" s="24" t="n"/>
@@ -5680,35 +5739,35 @@
       <c r="C95" s="20" t="n"/>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t>B6.6</t>
+          <t>B6.5</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>Attendance &amp; Time</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+          <t>ការជ្រើសរើសបុគ្គលិក</t>
         </is>
       </c>
       <c r="G95" s="23" t="inlineStr">
         <is>
-          <t>/time-attendance</t>
+          <t>/recruitment</t>
         </is>
       </c>
       <c r="H95" s="19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I95" s="20" t="inlineStr">
         <is>
-          <t>Check-in / check-out</t>
+          <t>Offer letter</t>
         </is>
       </c>
       <c r="J95" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>លិខិតផ្តល់ការងារ</t>
         </is>
       </c>
       <c r="K95" s="24" t="n"/>
@@ -5719,35 +5778,35 @@
       <c r="C96" s="20" t="n"/>
       <c r="D96" s="19" t="inlineStr">
         <is>
-          <t>B6.6</t>
+          <t>B6.5</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Attendance &amp; Time</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
         <is>
-          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+          <t>ការជ្រើសរើសបុគ្គលិក</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
         <is>
-          <t>/time-attendance</t>
+          <t>/recruitment</t>
         </is>
       </c>
       <c r="H96" s="19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
-          <t>Late</t>
+          <t>Recruitment pipeline</t>
         </is>
       </c>
       <c r="J96" s="20" t="inlineStr">
         <is>
-          <t>មកយឺត</t>
+          <t>ដំណើរការជ្រើសរើស</t>
         </is>
       </c>
       <c r="K96" s="24" t="n"/>
@@ -5756,12 +5815,12 @@
       <c r="A97" s="19" t="n"/>
       <c r="B97" s="20" t="n"/>
       <c r="C97" s="20" t="n"/>
-      <c r="D97" s="19" t="inlineStr">
+      <c r="D97" s="21" t="inlineStr">
         <is>
           <t>B6.6</t>
         </is>
       </c>
-      <c r="E97" s="20" t="inlineStr">
+      <c r="E97" s="22" t="inlineStr">
         <is>
           <t>Attendance &amp; Time</t>
         </is>
@@ -5777,16 +5836,16 @@
         </is>
       </c>
       <c r="H97" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>Early leave</t>
+          <t>Employee attendance</t>
         </is>
       </c>
       <c r="J97" s="20" t="inlineStr">
         <is>
-          <t>ចេញមុន</t>
+          <t>វត្តមានបុគ្គលិក</t>
         </is>
       </c>
       <c r="K97" s="24" t="n"/>
@@ -5816,16 +5875,16 @@
         </is>
       </c>
       <c r="H98" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
-          <t>Absence</t>
+          <t>Check-in / check-out</t>
         </is>
       </c>
       <c r="J98" s="20" t="inlineStr">
         <is>
-          <t>អវត្តមាន</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="K98" s="24" t="n"/>
@@ -5855,16 +5914,16 @@
         </is>
       </c>
       <c r="H99" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I99" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Late</t>
         </is>
       </c>
       <c r="J99" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>មកយឺត</t>
         </is>
       </c>
       <c r="K99" s="24" t="n"/>
@@ -5894,16 +5953,16 @@
         </is>
       </c>
       <c r="H100" s="19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Early leave</t>
         </is>
       </c>
       <c r="J100" s="20" t="inlineStr">
         <is>
-          <t>វេនការងារ</t>
+          <t>ចេញមុន</t>
         </is>
       </c>
       <c r="K100" s="24" t="n"/>
@@ -5933,16 +5992,16 @@
         </is>
       </c>
       <c r="H101" s="19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I101" s="20" t="inlineStr">
         <is>
-          <t>Staff shift</t>
+          <t>Absence</t>
         </is>
       </c>
       <c r="J101" s="20" t="inlineStr">
         <is>
-          <t>វេនបុគ្គលិក</t>
+          <t>អវត្តមាន</t>
         </is>
       </c>
       <c r="K101" s="24" t="n"/>
@@ -5972,16 +6031,16 @@
         </is>
       </c>
       <c r="H102" s="19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="J102" s="20" t="inlineStr">
         <is>
-          <t>ថ្ងៃឈប់សម្រាក</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="K102" s="24" t="n"/>
@@ -6011,16 +6070,16 @@
         </is>
       </c>
       <c r="H103" s="19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>Attendance correction</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
         <is>
-          <t>ការកែវត្តមាន</t>
+          <t>វេនការងារ</t>
         </is>
       </c>
       <c r="K103" s="24" t="n"/>
@@ -6050,16 +6109,16 @@
         </is>
       </c>
       <c r="H104" s="19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
-          <t>Attendance approval</t>
+          <t>Staff shift</t>
         </is>
       </c>
       <c r="J104" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តវត្តមាន</t>
+          <t>វេនបុគ្គលិក</t>
         </is>
       </c>
       <c r="K104" s="24" t="n"/>
@@ -6068,37 +6127,37 @@
       <c r="A105" s="19" t="n"/>
       <c r="B105" s="20" t="n"/>
       <c r="C105" s="20" t="n"/>
-      <c r="D105" s="21" t="inlineStr">
-        <is>
-          <t>B6.7</t>
-        </is>
-      </c>
-      <c r="E105" s="22" t="inlineStr">
-        <is>
-          <t>Leave Management</t>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t>B6.6</t>
+        </is>
+      </c>
+      <c r="E105" s="20" t="inlineStr">
+        <is>
+          <t>Attendance &amp; Time</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
         <is>
-          <t>/leave-management</t>
+          <t>/time-attendance</t>
         </is>
       </c>
       <c r="H105" s="19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I105" s="20" t="inlineStr">
         <is>
-          <t>Leave types</t>
+          <t>Holidays</t>
         </is>
       </c>
       <c r="J105" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
+          <t>ថ្ងៃឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K105" s="24" t="n"/>
@@ -6109,35 +6168,35 @@
       <c r="C106" s="20" t="n"/>
       <c r="D106" s="19" t="inlineStr">
         <is>
-          <t>B6.7</t>
+          <t>B6.6</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Leave Management</t>
+          <t>Attendance &amp; Time</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
         </is>
       </c>
       <c r="G106" s="23" t="inlineStr">
         <is>
-          <t>/leave-management</t>
+          <t>/time-attendance</t>
         </is>
       </c>
       <c r="H106" s="19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
-          <t>Leave policies</t>
+          <t>Attendance correction</t>
         </is>
       </c>
       <c r="J106" s="20" t="inlineStr">
         <is>
-          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
+          <t>ការកែវត្តមាន</t>
         </is>
       </c>
       <c r="K106" s="24" t="n"/>
@@ -6148,35 +6207,35 @@
       <c r="C107" s="20" t="n"/>
       <c r="D107" s="19" t="inlineStr">
         <is>
-          <t>B6.7</t>
+          <t>B6.6</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>Leave Management</t>
+          <t>Attendance &amp; Time</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
         <is>
-          <t>/leave-management</t>
+          <t>/time-attendance</t>
         </is>
       </c>
       <c r="H107" s="19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>Leave balance</t>
+          <t>Attendance approval</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
         <is>
-          <t>សមតុល្យច្បាប់</t>
+          <t>ការអនុម័តវត្តមាន</t>
         </is>
       </c>
       <c r="K107" s="24" t="n"/>
@@ -6185,12 +6244,12 @@
       <c r="A108" s="19" t="n"/>
       <c r="B108" s="20" t="n"/>
       <c r="C108" s="20" t="n"/>
-      <c r="D108" s="19" t="inlineStr">
+      <c r="D108" s="21" t="inlineStr">
         <is>
           <t>B6.7</t>
         </is>
       </c>
-      <c r="E108" s="20" t="inlineStr">
+      <c r="E108" s="22" t="inlineStr">
         <is>
           <t>Leave Management</t>
         </is>
@@ -6206,16 +6265,16 @@
         </is>
       </c>
       <c r="H108" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
-          <t>Leave request</t>
+          <t>Leave types</t>
         </is>
       </c>
       <c r="J108" s="20" t="inlineStr">
         <is>
-          <t>សំណើច្បាប់ឈប់សម្រាក</t>
+          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K108" s="24" t="n"/>
@@ -6245,16 +6304,16 @@
         </is>
       </c>
       <c r="H109" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I109" s="20" t="inlineStr">
         <is>
-          <t>Approval workflow</t>
+          <t>Leave policies</t>
         </is>
       </c>
       <c r="J109" s="20" t="inlineStr">
         <is>
-          <t>លំហូរការអនុម័ត</t>
+          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K109" s="24" t="n"/>
@@ -6284,16 +6343,16 @@
         </is>
       </c>
       <c r="H110" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
-          <t>Leave calendar</t>
+          <t>Leave balance</t>
         </is>
       </c>
       <c r="J110" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិទិនច្បាប់</t>
+          <t>សមតុល្យច្បាប់</t>
         </is>
       </c>
       <c r="K110" s="24" t="n"/>
@@ -6323,16 +6382,16 @@
         </is>
       </c>
       <c r="H111" s="19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I111" s="20" t="inlineStr">
         <is>
-          <t>Carry forward</t>
+          <t>Leave request</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
         <is>
-          <t>យោងទៅឆ្នាំបន្ទាប់</t>
+          <t>សំណើច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K111" s="24" t="n"/>
@@ -6362,16 +6421,16 @@
         </is>
       </c>
       <c r="H112" s="19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
-          <t>Leave reports</t>
+          <t>Approval workflow</t>
         </is>
       </c>
       <c r="J112" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ច្បាប់</t>
+          <t>លំហូរការអនុម័ត</t>
         </is>
       </c>
       <c r="K112" s="24" t="n"/>
@@ -6380,37 +6439,37 @@
       <c r="A113" s="19" t="n"/>
       <c r="B113" s="20" t="n"/>
       <c r="C113" s="20" t="n"/>
-      <c r="D113" s="21" t="inlineStr">
-        <is>
-          <t>B6.8</t>
-        </is>
-      </c>
-      <c r="E113" s="22" t="inlineStr">
-        <is>
-          <t>Payroll</t>
+      <c r="D113" s="19" t="inlineStr">
+        <is>
+          <t>B6.7</t>
+        </is>
+      </c>
+      <c r="E113" s="20" t="inlineStr">
+        <is>
+          <t>Leave Management</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
         <is>
-          <t>បញ្ជីប្រាក់ខែ</t>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
         <is>
-          <t>/payroll</t>
+          <t>/leave-management</t>
         </is>
       </c>
       <c r="H113" s="19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>Salary structure</t>
+          <t>Leave calendar</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធប្រាក់ខែ</t>
+          <t>ប្រតិទិនច្បាប់</t>
         </is>
       </c>
       <c r="K113" s="24" t="n"/>
@@ -6421,35 +6480,35 @@
       <c r="C114" s="20" t="n"/>
       <c r="D114" s="19" t="inlineStr">
         <is>
-          <t>B6.8</t>
+          <t>B6.7</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Leave Management</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
         <is>
-          <t>បញ្ជីប្រាក់ខែ</t>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
         <is>
-          <t>/payroll</t>
+          <t>/leave-management</t>
         </is>
       </c>
       <c r="H114" s="19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
-          <t>Basic salary</t>
+          <t>Carry forward</t>
         </is>
       </c>
       <c r="J114" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ខែគោល</t>
+          <t>យោងទៅឆ្នាំបន្ទាប់</t>
         </is>
       </c>
       <c r="K114" s="24" t="n"/>
@@ -6460,35 +6519,35 @@
       <c r="C115" s="20" t="n"/>
       <c r="D115" s="19" t="inlineStr">
         <is>
-          <t>B6.8</t>
+          <t>B6.7</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Leave Management</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
         <is>
-          <t>បញ្ជីប្រាក់ខែ</t>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
         <is>
-          <t>/payroll</t>
+          <t>/leave-management</t>
         </is>
       </c>
       <c r="H115" s="19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>Allowances</t>
+          <t>Leave reports</t>
         </is>
       </c>
       <c r="J115" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ឧបត្ថម្ភ</t>
+          <t>របាយការណ៍ច្បាប់</t>
         </is>
       </c>
       <c r="K115" s="24" t="n"/>
@@ -6497,12 +6556,12 @@
       <c r="A116" s="19" t="n"/>
       <c r="B116" s="20" t="n"/>
       <c r="C116" s="20" t="n"/>
-      <c r="D116" s="19" t="inlineStr">
+      <c r="D116" s="21" t="inlineStr">
         <is>
           <t>B6.8</t>
         </is>
       </c>
-      <c r="E116" s="20" t="inlineStr">
+      <c r="E116" s="22" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
@@ -6518,16 +6577,16 @@
         </is>
       </c>
       <c r="H116" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
-          <t>Bonuses</t>
+          <t>Salary structure</t>
         </is>
       </c>
       <c r="J116" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់រង្វាន់</t>
+          <t>រចនាសម្ព័ន្ធប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K116" s="24" t="n"/>
@@ -6557,16 +6616,16 @@
         </is>
       </c>
       <c r="H117" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I117" s="20" t="inlineStr">
         <is>
-          <t>Deductions</t>
+          <t>Basic salary</t>
         </is>
       </c>
       <c r="J117" s="20" t="inlineStr">
         <is>
-          <t>ការកាត់ប្រាក់</t>
+          <t>ប្រាក់ខែគោល</t>
         </is>
       </c>
       <c r="K117" s="24" t="n"/>
@@ -6596,16 +6655,16 @@
         </is>
       </c>
       <c r="H118" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I118" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Allowances</t>
         </is>
       </c>
       <c r="J118" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>ប្រាក់ឧបត្ថម្ភ</t>
         </is>
       </c>
       <c r="K118" s="24" t="n"/>
@@ -6635,16 +6694,16 @@
         </is>
       </c>
       <c r="H119" s="19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
-          <t>Attendance deduction</t>
+          <t>Bonuses</t>
         </is>
       </c>
       <c r="J119" s="20" t="inlineStr">
         <is>
-          <t>ការកាត់ប្រាក់តាមវត្តមាន</t>
+          <t>ប្រាក់រង្វាន់</t>
         </is>
       </c>
       <c r="K119" s="24" t="n"/>
@@ -6674,16 +6733,16 @@
         </is>
       </c>
       <c r="H120" s="19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I120" s="20" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Deductions</t>
         </is>
       </c>
       <c r="J120" s="20" t="inlineStr">
         <is>
-          <t>ពន្ធ</t>
+          <t>ការកាត់ប្រាក់</t>
         </is>
       </c>
       <c r="K120" s="24" t="n"/>
@@ -6713,16 +6772,16 @@
         </is>
       </c>
       <c r="H121" s="19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I121" s="20" t="inlineStr">
         <is>
-          <t>Social security</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="J121" s="20" t="inlineStr">
         <is>
-          <t>សន្តិសុខសង្គម</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="K121" s="24" t="n"/>
@@ -6752,16 +6811,16 @@
         </is>
       </c>
       <c r="H122" s="19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I122" s="20" t="inlineStr">
         <is>
-          <t>Loan/advance</t>
+          <t>Attendance deduction</t>
         </is>
       </c>
       <c r="J122" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់កម្ចី/ប្រាក់បុរេប្រទាន</t>
+          <t>ការកាត់ប្រាក់តាមវត្តមាន</t>
         </is>
       </c>
       <c r="K122" s="24" t="n"/>
@@ -6791,16 +6850,16 @@
         </is>
       </c>
       <c r="H123" s="19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I123" s="20" t="inlineStr">
         <is>
-          <t>Payroll calculation</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="J123" s="20" t="inlineStr">
         <is>
-          <t>ការគណនាប្រាក់ខែ</t>
+          <t>ពន្ធ</t>
         </is>
       </c>
       <c r="K123" s="24" t="n"/>
@@ -6830,16 +6889,16 @@
         </is>
       </c>
       <c r="H124" s="19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I124" s="20" t="inlineStr">
         <is>
-          <t>Payslip</t>
+          <t>Social security</t>
         </is>
       </c>
       <c r="J124" s="20" t="inlineStr">
         <is>
-          <t>បង្កាន់ដៃប្រាក់ខែ</t>
+          <t>សន្តិសុខសង្គម</t>
         </is>
       </c>
       <c r="K124" s="24" t="n"/>
@@ -6869,16 +6928,16 @@
         </is>
       </c>
       <c r="H125" s="19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I125" s="20" t="inlineStr">
         <is>
-          <t>Payroll approval</t>
+          <t>Loan/advance</t>
         </is>
       </c>
       <c r="J125" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តប្រាក់ខែ</t>
+          <t>ប្រាក់កម្ចី/ប្រាក់បុរេប្រទាន</t>
         </is>
       </c>
       <c r="K125" s="24" t="n"/>
@@ -6908,16 +6967,16 @@
         </is>
       </c>
       <c r="H126" s="19" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
-          <t>Payroll history</t>
+          <t>Payroll calculation</t>
         </is>
       </c>
       <c r="J126" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិប្រាក់ខែ</t>
+          <t>ការគណនាប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K126" s="24" t="n"/>
@@ -6926,35 +6985,39 @@
       <c r="A127" s="19" t="n"/>
       <c r="B127" s="20" t="n"/>
       <c r="C127" s="20" t="n"/>
-      <c r="D127" s="21" t="inlineStr">
-        <is>
-          <t>B6.9</t>
-        </is>
-      </c>
-      <c r="E127" s="22" t="inlineStr">
-        <is>
-          <t>Performance Management</t>
+      <c r="D127" s="19" t="inlineStr">
+        <is>
+          <t>B6.8</t>
+        </is>
+      </c>
+      <c r="E127" s="20" t="inlineStr">
+        <is>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងការងារ</t>
+          <t>បញ្ជីប្រាក់ខែ</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
         <is>
-          <t>/performance</t>
+          <t>/payroll</t>
         </is>
       </c>
       <c r="H127" s="19" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I127" s="20" t="inlineStr">
         <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="J127" s="20" t="n"/>
+          <t>Payslip</t>
+        </is>
+      </c>
+      <c r="J127" s="20" t="inlineStr">
+        <is>
+          <t>បង្កាន់ដៃប្រាក់ខែ</t>
+        </is>
+      </c>
       <c r="K127" s="24" t="n"/>
     </row>
     <row r="128" ht="21.6" customHeight="1">
@@ -6963,35 +7026,35 @@
       <c r="C128" s="20" t="n"/>
       <c r="D128" s="19" t="inlineStr">
         <is>
-          <t>B6.9</t>
+          <t>B6.8</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>Performance Management</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងការងារ</t>
+          <t>បញ្ជីប្រាក់ខែ</t>
         </is>
       </c>
       <c r="G128" s="23" t="inlineStr">
         <is>
-          <t>/performance</t>
+          <t>/payroll</t>
         </is>
       </c>
       <c r="H128" s="19" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I128" s="20" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Payroll approval</t>
         </is>
       </c>
       <c r="J128" s="20" t="inlineStr">
         <is>
-          <t>គោលដៅ</t>
+          <t>ការអនុម័តប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K128" s="24" t="n"/>
@@ -7002,35 +7065,35 @@
       <c r="C129" s="20" t="n"/>
       <c r="D129" s="19" t="inlineStr">
         <is>
-          <t>B6.9</t>
+          <t>B6.8</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
         <is>
-          <t>Performance Management</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងការងារ</t>
+          <t>បញ្ជីប្រាក់ខែ</t>
         </is>
       </c>
       <c r="G129" s="23" t="inlineStr">
         <is>
-          <t>/performance</t>
+          <t>/payroll</t>
         </is>
       </c>
       <c r="H129" s="19" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I129" s="20" t="inlineStr">
         <is>
-          <t>Performance review</t>
+          <t>Payroll history</t>
         </is>
       </c>
       <c r="J129" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃការងារ</t>
+          <t>ប្រវត្តិប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K129" s="24" t="n"/>
@@ -7039,12 +7102,12 @@
       <c r="A130" s="19" t="n"/>
       <c r="B130" s="20" t="n"/>
       <c r="C130" s="20" t="n"/>
-      <c r="D130" s="19" t="inlineStr">
+      <c r="D130" s="21" t="inlineStr">
         <is>
           <t>B6.9</t>
         </is>
       </c>
-      <c r="E130" s="20" t="inlineStr">
+      <c r="E130" s="22" t="inlineStr">
         <is>
           <t>Performance Management</t>
         </is>
@@ -7060,18 +7123,14 @@
         </is>
       </c>
       <c r="H130" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I130" s="20" t="inlineStr">
         <is>
-          <t>Evaluation forms</t>
-        </is>
-      </c>
-      <c r="J130" s="20" t="inlineStr">
-        <is>
-          <t>ទម្រង់វាយតម្លៃ</t>
-        </is>
-      </c>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="J130" s="20" t="n"/>
       <c r="K130" s="24" t="n"/>
     </row>
     <row r="131" ht="21.6" customHeight="1">
@@ -7099,16 +7158,16 @@
         </is>
       </c>
       <c r="H131" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I131" s="20" t="inlineStr">
         <is>
-          <t>Employee self-assessment</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="J131" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃខ្លួនឯង</t>
+          <t>គោលដៅ</t>
         </is>
       </c>
       <c r="K131" s="24" t="n"/>
@@ -7138,16 +7197,16 @@
         </is>
       </c>
       <c r="H132" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I132" s="20" t="inlineStr">
         <is>
-          <t>Manager assessment</t>
+          <t>Performance review</t>
         </is>
       </c>
       <c r="J132" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃដោយអ្នកគ្រប់គ្រង</t>
+          <t>ការវាយតម្លៃការងារ</t>
         </is>
       </c>
       <c r="K132" s="24" t="n"/>
@@ -7177,16 +7236,16 @@
         </is>
       </c>
       <c r="H133" s="19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I133" s="20" t="inlineStr">
         <is>
-          <t>Performance score</t>
+          <t>Evaluation forms</t>
         </is>
       </c>
       <c r="J133" s="20" t="inlineStr">
         <is>
-          <t>ពិន្ទុការងារ</t>
+          <t>ទម្រង់វាយតម្លៃ</t>
         </is>
       </c>
       <c r="K133" s="24" t="n"/>
@@ -7216,16 +7275,16 @@
         </is>
       </c>
       <c r="H134" s="19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I134" s="20" t="inlineStr">
         <is>
-          <t>Promotion recommendation</t>
+          <t>Employee self-assessment</t>
         </is>
       </c>
       <c r="J134" s="20" t="inlineStr">
         <is>
-          <t>ការណែនាំដំឡើងតំណែង</t>
+          <t>ការវាយតម្លៃខ្លួនឯង</t>
         </is>
       </c>
       <c r="K134" s="24" t="n"/>
@@ -7234,66 +7293,76 @@
       <c r="A135" s="19" t="n"/>
       <c r="B135" s="20" t="n"/>
       <c r="C135" s="20" t="n"/>
-      <c r="D135" s="21" t="inlineStr">
-        <is>
-          <t>B6.10</t>
-        </is>
-      </c>
-      <c r="E135" s="22" t="inlineStr">
-        <is>
-          <t>Check in / Check out</t>
+      <c r="D135" s="19" t="inlineStr">
+        <is>
+          <t>B6.9</t>
+        </is>
+      </c>
+      <c r="E135" s="20" t="inlineStr">
+        <is>
+          <t>Performance Management</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>ការគ្រប់គ្រងការងារ</t>
         </is>
       </c>
       <c r="G135" s="23" t="inlineStr">
         <is>
-          <t>/my-check-in</t>
-        </is>
-      </c>
-      <c r="H135" s="19" t="n"/>
-      <c r="I135" s="20" t="n"/>
-      <c r="J135" s="20" t="n"/>
+          <t>/performance</t>
+        </is>
+      </c>
+      <c r="H135" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I135" s="20" t="inlineStr">
+        <is>
+          <t>Manager assessment</t>
+        </is>
+      </c>
+      <c r="J135" s="20" t="inlineStr">
+        <is>
+          <t>ការវាយតម្លៃដោយអ្នកគ្រប់គ្រង</t>
+        </is>
+      </c>
       <c r="K135" s="24" t="n"/>
     </row>
     <row r="136" ht="21.6" customHeight="1">
       <c r="A136" s="19" t="n"/>
       <c r="B136" s="20" t="n"/>
       <c r="C136" s="20" t="n"/>
-      <c r="D136" s="21" t="inlineStr">
-        <is>
-          <t>B6.11</t>
-        </is>
-      </c>
-      <c r="E136" s="22" t="inlineStr">
-        <is>
-          <t>Request Leave</t>
+      <c r="D136" s="19" t="inlineStr">
+        <is>
+          <t>B6.9</t>
+        </is>
+      </c>
+      <c r="E136" s="20" t="inlineStr">
+        <is>
+          <t>Performance Management</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
         <is>
-          <t>ស្នើសុំច្បាប់</t>
+          <t>ការគ្រប់គ្រងការងារ</t>
         </is>
       </c>
       <c r="G136" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests</t>
+          <t>/performance</t>
         </is>
       </c>
       <c r="H136" s="19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I136" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Performance score</t>
         </is>
       </c>
       <c r="J136" s="20" t="inlineStr">
         <is>
-          <t>កំពុងរង់ចាំ</t>
+          <t>ពិន្ទុការងារ</t>
         </is>
       </c>
       <c r="K136" s="24" t="n"/>
@@ -7304,35 +7373,35 @@
       <c r="C137" s="20" t="n"/>
       <c r="D137" s="19" t="inlineStr">
         <is>
-          <t>B6.11</t>
+          <t>B6.9</t>
         </is>
       </c>
       <c r="E137" s="20" t="inlineStr">
         <is>
-          <t>Request Leave</t>
+          <t>Performance Management</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
         <is>
-          <t>ស្នើសុំច្បាប់</t>
+          <t>ការគ្រប់គ្រងការងារ</t>
         </is>
       </c>
       <c r="G137" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests</t>
+          <t>/performance</t>
         </is>
       </c>
       <c r="H137" s="19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I137" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>Promotion recommendation</t>
         </is>
       </c>
       <c r="J137" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>ការណែនាំដំឡើងតំណែង</t>
         </is>
       </c>
       <c r="K137" s="24" t="n"/>
@@ -7341,51 +7410,41 @@
       <c r="A138" s="19" t="n"/>
       <c r="B138" s="20" t="n"/>
       <c r="C138" s="20" t="n"/>
-      <c r="D138" s="19" t="inlineStr">
-        <is>
-          <t>B6.11</t>
-        </is>
-      </c>
-      <c r="E138" s="20" t="inlineStr">
-        <is>
-          <t>Request Leave</t>
+      <c r="D138" s="21" t="inlineStr">
+        <is>
+          <t>B6.10</t>
+        </is>
+      </c>
+      <c r="E138" s="22" t="inlineStr">
+        <is>
+          <t>Check in / Check out</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
         <is>
-          <t>ស្នើសុំច្បាប់</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H138" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I138" s="20" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J138" s="20" t="inlineStr">
-        <is>
-          <t>បានអនុម័ត</t>
-        </is>
-      </c>
+          <t>/my-check-in</t>
+        </is>
+      </c>
+      <c r="H138" s="19" t="n"/>
+      <c r="I138" s="20" t="n"/>
+      <c r="J138" s="20" t="n"/>
       <c r="K138" s="24" t="n"/>
     </row>
     <row r="139" ht="21.6" customHeight="1">
       <c r="A139" s="19" t="n"/>
       <c r="B139" s="20" t="n"/>
       <c r="C139" s="20" t="n"/>
-      <c r="D139" s="19" t="inlineStr">
+      <c r="D139" s="21" t="inlineStr">
         <is>
           <t>B6.11</t>
         </is>
       </c>
-      <c r="E139" s="20" t="inlineStr">
+      <c r="E139" s="22" t="inlineStr">
         <is>
           <t>Request Leave</t>
         </is>
@@ -7401,16 +7460,16 @@
         </is>
       </c>
       <c r="H139" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I139" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J139" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="K139" s="24" t="n"/>
@@ -7440,16 +7499,16 @@
         </is>
       </c>
       <c r="H140" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I140" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J140" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K140" s="24" t="n"/>
@@ -7458,182 +7517,192 @@
       <c r="A141" s="19" t="n"/>
       <c r="B141" s="20" t="n"/>
       <c r="C141" s="20" t="n"/>
-      <c r="D141" s="21" t="inlineStr">
+      <c r="D141" s="19" t="inlineStr">
+        <is>
+          <t>B6.11</t>
+        </is>
+      </c>
+      <c r="E141" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="F141" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="G141" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="H141" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I141" s="20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J141" s="20" t="inlineStr">
+        <is>
+          <t>បានអនុម័ត</t>
+        </is>
+      </c>
+      <c r="K141" s="24" t="n"/>
+    </row>
+    <row r="142" ht="21.6" customHeight="1">
+      <c r="A142" s="19" t="n"/>
+      <c r="B142" s="20" t="n"/>
+      <c r="C142" s="20" t="n"/>
+      <c r="D142" s="19" t="inlineStr">
+        <is>
+          <t>B6.11</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="F142" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="G142" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="H142" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I142" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="J142" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
+      <c r="K142" s="24" t="n"/>
+    </row>
+    <row r="143" ht="21.6" customHeight="1">
+      <c r="A143" s="19" t="n"/>
+      <c r="B143" s="20" t="n"/>
+      <c r="C143" s="20" t="n"/>
+      <c r="D143" s="19" t="inlineStr">
+        <is>
+          <t>B6.11</t>
+        </is>
+      </c>
+      <c r="E143" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="F143" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="G143" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="H143" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I143" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="J143" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="K143" s="24" t="n"/>
+    </row>
+    <row r="144" ht="21.6" customHeight="1">
+      <c r="A144" s="19" t="n"/>
+      <c r="B144" s="20" t="n"/>
+      <c r="C144" s="20" t="n"/>
+      <c r="D144" s="21" t="inlineStr">
         <is>
           <t>B6.12</t>
         </is>
       </c>
-      <c r="E141" s="22" t="inlineStr">
+      <c r="E144" s="22" t="inlineStr">
         <is>
           <t>Form</t>
         </is>
       </c>
-      <c r="F141" s="20" t="inlineStr">
+      <c r="F144" s="20" t="inlineStr">
         <is>
           <t>ទម្រង់</t>
         </is>
       </c>
-      <c r="G141" s="23" t="inlineStr">
+      <c r="G144" s="23" t="inlineStr">
         <is>
           <t>/approvals/my-requests?tab=resignation</t>
         </is>
       </c>
-      <c r="H141" s="19" t="n"/>
-      <c r="I141" s="20" t="n"/>
-      <c r="J141" s="20" t="n"/>
-      <c r="K141" s="24" t="inlineStr">
+      <c r="H144" s="19" t="n"/>
+      <c r="I144" s="20" t="n"/>
+      <c r="J144" s="20" t="n"/>
+      <c r="K144" s="24" t="inlineStr">
         <is>
           <t>Resignation form</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="21.6" customHeight="1">
-      <c r="A142" s="1" t="inlineStr">
+    <row r="145" ht="21.6" customHeight="1">
+      <c r="A145" s="1" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>វិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="D142" s="1" t="inlineStr">
+      <c r="D145" s="1" t="inlineStr">
         <is>
           <t>B7.1</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Billing Dashboard</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងវិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="G142" s="4" t="inlineStr">
+      <c r="G145" s="4" t="inlineStr">
         <is>
           <t>/billing</t>
         </is>
       </c>
-      <c r="H142" s="5" t="n"/>
-      <c r="I142" s="3" t="n"/>
-      <c r="J142" s="3" t="n"/>
-      <c r="K142" s="6" t="n"/>
-    </row>
-    <row r="143" ht="21.6" customHeight="1">
-      <c r="A143" s="7" t="n"/>
-      <c r="B143" s="8" t="n"/>
-      <c r="C143" s="8" t="n"/>
-      <c r="D143" s="9" t="inlineStr">
-        <is>
-          <t>B7.2</t>
-        </is>
-      </c>
-      <c r="E143" s="10" t="inlineStr">
-        <is>
-          <t>Products</t>
-        </is>
-      </c>
-      <c r="F143" s="8" t="inlineStr">
-        <is>
-          <t>ផលិតផល</t>
-        </is>
-      </c>
-      <c r="G143" s="11" t="inlineStr">
-        <is>
-          <t>/products</t>
-        </is>
-      </c>
-      <c r="H143" s="7" t="n"/>
-      <c r="I143" s="8" t="n"/>
-      <c r="J143" s="8" t="n"/>
-      <c r="K143" s="12" t="n"/>
-    </row>
-    <row r="144" ht="21.6" customHeight="1">
-      <c r="A144" s="7" t="n"/>
-      <c r="B144" s="8" t="n"/>
-      <c r="C144" s="8" t="n"/>
-      <c r="D144" s="9" t="inlineStr">
-        <is>
-          <t>B7.3</t>
-        </is>
-      </c>
-      <c r="E144" s="10" t="inlineStr">
-        <is>
-          <t>Invoices</t>
-        </is>
-      </c>
-      <c r="F144" s="8" t="inlineStr">
-        <is>
-          <t>វិក្កយបត្រ</t>
-        </is>
-      </c>
-      <c r="G144" s="11" t="inlineStr">
-        <is>
-          <t>/invoices</t>
-        </is>
-      </c>
-      <c r="H144" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I144" s="8" t="inlineStr">
-        <is>
-          <t>Invoices</t>
-        </is>
-      </c>
-      <c r="J144" s="8" t="inlineStr">
-        <is>
-          <t>វិក្កយបត្រ</t>
-        </is>
-      </c>
-      <c r="K144" s="12" t="n"/>
-    </row>
-    <row r="145" ht="21.6" customHeight="1">
-      <c r="A145" s="7" t="n"/>
-      <c r="B145" s="8" t="n"/>
-      <c r="C145" s="8" t="n"/>
-      <c r="D145" s="7" t="inlineStr">
-        <is>
-          <t>B7.3</t>
-        </is>
-      </c>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t>Invoices</t>
-        </is>
-      </c>
-      <c r="F145" s="8" t="inlineStr">
-        <is>
-          <t>វិក្កយបត្រ</t>
-        </is>
-      </c>
-      <c r="G145" s="11" t="inlineStr">
-        <is>
-          <t>/invoices</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I145" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Invoice</t>
-        </is>
-      </c>
-      <c r="J145" s="8" t="inlineStr">
-        <is>
-          <t>វិក្កយបត្រប្រចាំខែ</t>
-        </is>
-      </c>
-      <c r="K145" s="12" t="n"/>
+      <c r="H145" s="5" t="n"/>
+      <c r="I145" s="3" t="n"/>
+      <c r="J145" s="3" t="n"/>
+      <c r="K145" s="6" t="n"/>
     </row>
     <row r="146" ht="21.6" customHeight="1">
       <c r="A146" s="7" t="n"/>
@@ -7641,22 +7710,22 @@
       <c r="C146" s="8" t="n"/>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>B7.4</t>
+          <t>B7.2</t>
         </is>
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
         <is>
-          <t>ការទូទាត់</t>
+          <t>ផលិតផល</t>
         </is>
       </c>
       <c r="G146" s="11" t="inlineStr">
         <is>
-          <t>/payments</t>
+          <t>/products</t>
         </is>
       </c>
       <c r="H146" s="7" t="n"/>
@@ -7670,156 +7739,176 @@
       <c r="C147" s="8" t="n"/>
       <c r="D147" s="9" t="inlineStr">
         <is>
+          <t>B7.3</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>វិក្កយបត្រ</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>/invoices</t>
+        </is>
+      </c>
+      <c r="H147" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="8" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="J147" s="8" t="inlineStr">
+        <is>
+          <t>វិក្កយបត្រ</t>
+        </is>
+      </c>
+      <c r="K147" s="12" t="n"/>
+    </row>
+    <row r="148" ht="21.6" customHeight="1">
+      <c r="A148" s="7" t="n"/>
+      <c r="B148" s="8" t="n"/>
+      <c r="C148" s="8" t="n"/>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>B7.3</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t>វិក្កយបត្រ</t>
+        </is>
+      </c>
+      <c r="G148" s="11" t="inlineStr">
+        <is>
+          <t>/invoices</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I148" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Invoice</t>
+        </is>
+      </c>
+      <c r="J148" s="8" t="inlineStr">
+        <is>
+          <t>វិក្កយបត្រប្រចាំខែ</t>
+        </is>
+      </c>
+      <c r="K148" s="12" t="n"/>
+    </row>
+    <row r="149" ht="21.6" customHeight="1">
+      <c r="A149" s="7" t="n"/>
+      <c r="B149" s="8" t="n"/>
+      <c r="C149" s="8" t="n"/>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>B7.4</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="F149" s="8" t="inlineStr">
+        <is>
+          <t>ការទូទាត់</t>
+        </is>
+      </c>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>/payments</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="n"/>
+      <c r="I149" s="8" t="n"/>
+      <c r="J149" s="8" t="n"/>
+      <c r="K149" s="12" t="n"/>
+    </row>
+    <row r="150" ht="21.6" customHeight="1">
+      <c r="A150" s="7" t="n"/>
+      <c r="B150" s="8" t="n"/>
+      <c r="C150" s="8" t="n"/>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
           <t>B7.5</t>
         </is>
       </c>
-      <c r="E147" s="10" t="inlineStr">
+      <c r="E150" s="10" t="inlineStr">
         <is>
           <t>Currency Rates</t>
         </is>
       </c>
-      <c r="F147" s="8" t="inlineStr">
+      <c r="F150" s="8" t="inlineStr">
         <is>
           <t>អត្រាប្តូរប្រាក់</t>
         </is>
       </c>
-      <c r="G147" s="11" t="inlineStr">
+      <c r="G150" s="11" t="inlineStr">
         <is>
           <t>/currency-rates</t>
         </is>
       </c>
-      <c r="H147" s="7" t="n"/>
-      <c r="I147" s="8" t="n"/>
-      <c r="J147" s="8" t="n"/>
-      <c r="K147" s="12" t="n"/>
-    </row>
-    <row r="148" ht="21.6" customHeight="1">
-      <c r="A148" s="13" t="inlineStr">
+      <c r="H150" s="7" t="n"/>
+      <c r="I150" s="8" t="n"/>
+      <c r="J150" s="8" t="n"/>
+      <c r="K150" s="12" t="n"/>
+    </row>
+    <row r="151" ht="21.6" customHeight="1">
+      <c r="A151" s="13" t="inlineStr">
         <is>
           <t>B8</t>
         </is>
       </c>
-      <c r="B148" s="14" t="inlineStr">
+      <c r="B151" s="14" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="C148" s="15" t="inlineStr">
+      <c r="C151" s="15" t="inlineStr">
         <is>
           <t>គណនេយ្យ</t>
         </is>
       </c>
-      <c r="D148" s="13" t="inlineStr">
+      <c r="D151" s="13" t="inlineStr">
         <is>
           <t>B8.1</t>
         </is>
       </c>
-      <c r="E148" s="14" t="inlineStr">
+      <c r="E151" s="14" t="inlineStr">
         <is>
           <t>Accounting Dashboard</t>
         </is>
       </c>
-      <c r="F148" s="15" t="inlineStr">
+      <c r="F151" s="15" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងគណនេយ្យ</t>
         </is>
       </c>
-      <c r="G148" s="16" t="inlineStr">
+      <c r="G151" s="16" t="inlineStr">
         <is>
           <t>/accounting</t>
         </is>
       </c>
-      <c r="H148" s="17" t="n"/>
-      <c r="I148" s="15" t="n"/>
-      <c r="J148" s="15" t="n"/>
-      <c r="K148" s="18" t="n"/>
-    </row>
-    <row r="149" ht="21.6" customHeight="1">
-      <c r="A149" s="19" t="n"/>
-      <c r="B149" s="20" t="n"/>
-      <c r="C149" s="20" t="n"/>
-      <c r="D149" s="21" t="inlineStr">
-        <is>
-          <t>B8.2</t>
-        </is>
-      </c>
-      <c r="E149" s="22" t="inlineStr">
-        <is>
-          <t>Chart of Accounts</t>
-        </is>
-      </c>
-      <c r="F149" s="20" t="inlineStr">
-        <is>
-          <t>តារាងគណនី</t>
-        </is>
-      </c>
-      <c r="G149" s="23" t="inlineStr">
-        <is>
-          <t>/accounts</t>
-        </is>
-      </c>
-      <c r="H149" s="19" t="n"/>
-      <c r="I149" s="20" t="n"/>
-      <c r="J149" s="20" t="n"/>
-      <c r="K149" s="24" t="n"/>
-    </row>
-    <row r="150" ht="21.6" customHeight="1">
-      <c r="A150" s="19" t="n"/>
-      <c r="B150" s="20" t="n"/>
-      <c r="C150" s="20" t="n"/>
-      <c r="D150" s="21" t="inlineStr">
-        <is>
-          <t>B8.3</t>
-        </is>
-      </c>
-      <c r="E150" s="22" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="F150" s="20" t="inlineStr">
-        <is>
-          <t>ចំណូល</t>
-        </is>
-      </c>
-      <c r="G150" s="23" t="inlineStr">
-        <is>
-          <t>/income</t>
-        </is>
-      </c>
-      <c r="H150" s="19" t="n"/>
-      <c r="I150" s="20" t="n"/>
-      <c r="J150" s="20" t="n"/>
-      <c r="K150" s="24" t="n"/>
-    </row>
-    <row r="151" ht="21.6" customHeight="1">
-      <c r="A151" s="19" t="n"/>
-      <c r="B151" s="20" t="n"/>
-      <c r="C151" s="20" t="n"/>
-      <c r="D151" s="21" t="inlineStr">
-        <is>
-          <t>B8.4</t>
-        </is>
-      </c>
-      <c r="E151" s="22" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="F151" s="20" t="inlineStr">
-        <is>
-          <t>ចំណាយ</t>
-        </is>
-      </c>
-      <c r="G151" s="23" t="inlineStr">
-        <is>
-          <t>/expenses</t>
-        </is>
-      </c>
-      <c r="H151" s="19" t="n"/>
-      <c r="I151" s="20" t="n"/>
-      <c r="J151" s="20" t="n"/>
-      <c r="K151" s="24" t="n"/>
+      <c r="H151" s="17" t="n"/>
+      <c r="I151" s="15" t="n"/>
+      <c r="J151" s="15" t="n"/>
+      <c r="K151" s="18" t="n"/>
     </row>
     <row r="152" ht="21.6" customHeight="1">
       <c r="A152" s="19" t="n"/>
@@ -7827,22 +7916,22 @@
       <c r="C152" s="20" t="n"/>
       <c r="D152" s="21" t="inlineStr">
         <is>
-          <t>B8.5</t>
+          <t>B8.2</t>
         </is>
       </c>
       <c r="E152" s="22" t="inlineStr">
         <is>
-          <t>Transactions</t>
+          <t>Chart of Accounts</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិបត្តិការ</t>
+          <t>តារាងគណនី</t>
         </is>
       </c>
       <c r="G152" s="23" t="inlineStr">
         <is>
-          <t>/transactions</t>
+          <t>/accounts</t>
         </is>
       </c>
       <c r="H152" s="19" t="n"/>
@@ -7856,127 +7945,97 @@
       <c r="C153" s="20" t="n"/>
       <c r="D153" s="21" t="inlineStr">
         <is>
-          <t>B8.6</t>
+          <t>B8.3</t>
         </is>
       </c>
       <c r="E153" s="22" t="inlineStr">
         <is>
-          <t>Financial Reports</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+          <t>ចំណូល</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
         <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H153" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I153" s="20" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="J153" s="20" t="inlineStr">
-        <is>
-          <t>ចំណូល</t>
-        </is>
-      </c>
+          <t>/income</t>
+        </is>
+      </c>
+      <c r="H153" s="19" t="n"/>
+      <c r="I153" s="20" t="n"/>
+      <c r="J153" s="20" t="n"/>
       <c r="K153" s="24" t="n"/>
     </row>
     <row r="154" ht="21.6" customHeight="1">
       <c r="A154" s="19" t="n"/>
       <c r="B154" s="20" t="n"/>
       <c r="C154" s="20" t="n"/>
-      <c r="D154" s="19" t="inlineStr">
-        <is>
-          <t>B8.6</t>
-        </is>
-      </c>
-      <c r="E154" s="20" t="inlineStr">
-        <is>
-          <t>Financial Reports</t>
+      <c r="D154" s="21" t="inlineStr">
+        <is>
+          <t>B8.4</t>
+        </is>
+      </c>
+      <c r="E154" s="22" t="inlineStr">
+        <is>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+          <t>ចំណាយ</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
         <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H154" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I154" s="20" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="J154" s="20" t="inlineStr">
-        <is>
-          <t>ចំណាយ</t>
-        </is>
-      </c>
+          <t>/expenses</t>
+        </is>
+      </c>
+      <c r="H154" s="19" t="n"/>
+      <c r="I154" s="20" t="n"/>
+      <c r="J154" s="20" t="n"/>
       <c r="K154" s="24" t="n"/>
     </row>
     <row r="155" ht="21.6" customHeight="1">
       <c r="A155" s="19" t="n"/>
       <c r="B155" s="20" t="n"/>
       <c r="C155" s="20" t="n"/>
-      <c r="D155" s="19" t="inlineStr">
-        <is>
-          <t>B8.6</t>
-        </is>
-      </c>
-      <c r="E155" s="20" t="inlineStr">
-        <is>
-          <t>Financial Reports</t>
+      <c r="D155" s="21" t="inlineStr">
+        <is>
+          <t>B8.5</t>
+        </is>
+      </c>
+      <c r="E155" s="22" t="inlineStr">
+        <is>
+          <t>Transactions</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+          <t>ប្រតិបត្តិការ</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
         <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H155" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I155" s="20" t="inlineStr">
-        <is>
-          <t>Profit &amp; Loss</t>
-        </is>
-      </c>
-      <c r="J155" s="20" t="inlineStr">
-        <is>
-          <t>ប្រាក់ចំណេញ និងខាត</t>
-        </is>
-      </c>
+          <t>/transactions</t>
+        </is>
+      </c>
+      <c r="H155" s="19" t="n"/>
+      <c r="I155" s="20" t="n"/>
+      <c r="J155" s="20" t="n"/>
       <c r="K155" s="24" t="n"/>
     </row>
     <row r="156" ht="21.6" customHeight="1">
       <c r="A156" s="19" t="n"/>
       <c r="B156" s="20" t="n"/>
       <c r="C156" s="20" t="n"/>
-      <c r="D156" s="19" t="inlineStr">
+      <c r="D156" s="21" t="inlineStr">
         <is>
           <t>B8.6</t>
         </is>
       </c>
-      <c r="E156" s="20" t="inlineStr">
+      <c r="E156" s="22" t="inlineStr">
         <is>
           <t>Financial Reports</t>
         </is>
@@ -7992,192 +8051,188 @@
         </is>
       </c>
       <c r="H156" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" s="20" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="J156" s="20" t="inlineStr">
+        <is>
+          <t>ចំណូល</t>
+        </is>
+      </c>
+      <c r="K156" s="24" t="n"/>
+    </row>
+    <row r="157" ht="21.6" customHeight="1">
+      <c r="A157" s="19" t="n"/>
+      <c r="B157" s="20" t="n"/>
+      <c r="C157" s="20" t="n"/>
+      <c r="D157" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E157" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F157" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G157" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H157" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" s="20" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="J157" s="20" t="inlineStr">
+        <is>
+          <t>ចំណាយ</t>
+        </is>
+      </c>
+      <c r="K157" s="24" t="n"/>
+    </row>
+    <row r="158" ht="21.6" customHeight="1">
+      <c r="A158" s="19" t="n"/>
+      <c r="B158" s="20" t="n"/>
+      <c r="C158" s="20" t="n"/>
+      <c r="D158" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E158" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F158" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G158" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H158" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I158" s="20" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss</t>
+        </is>
+      </c>
+      <c r="J158" s="20" t="inlineStr">
+        <is>
+          <t>ប្រាក់ចំណេញ និងខាត</t>
+        </is>
+      </c>
+      <c r="K158" s="24" t="n"/>
+    </row>
+    <row r="159" ht="21.6" customHeight="1">
+      <c r="A159" s="19" t="n"/>
+      <c r="B159" s="20" t="n"/>
+      <c r="C159" s="20" t="n"/>
+      <c r="D159" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E159" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F159" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G159" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H159" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I156" s="20" t="inlineStr">
+      <c r="I159" s="20" t="inlineStr">
         <is>
           <t>Cash Flow</t>
         </is>
       </c>
-      <c r="J156" s="20" t="inlineStr">
+      <c r="J159" s="20" t="inlineStr">
         <is>
           <t>លំហូរសាច់ប្រាក់</t>
         </is>
       </c>
-      <c r="K156" s="24" t="n"/>
-    </row>
-    <row r="157" ht="21.6" customHeight="1">
-      <c r="A157" s="1" t="inlineStr">
+      <c r="K159" s="24" t="n"/>
+    </row>
+    <row r="160" ht="21.6" customHeight="1">
+      <c r="A160" s="1" t="inlineStr">
         <is>
           <t>B9</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>ទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="D157" s="1" t="inlineStr">
+      <c r="D160" s="1" t="inlineStr">
         <is>
           <t>B9.1</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Asset Dashboard</t>
         </is>
       </c>
-      <c r="F157" s="3" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="G157" s="4" t="inlineStr">
+      <c r="G160" s="4" t="inlineStr">
         <is>
           <t>/assets/dashboard</t>
         </is>
       </c>
-      <c r="H157" s="5" t="n"/>
-      <c r="I157" s="3" t="n"/>
-      <c r="J157" s="3" t="n"/>
-      <c r="K157" s="6" t="n"/>
-    </row>
-    <row r="158" ht="21.6" customHeight="1">
-      <c r="A158" s="7" t="n"/>
-      <c r="B158" s="8" t="n"/>
-      <c r="C158" s="8" t="n"/>
-      <c r="D158" s="9" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E158" s="10" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F158" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G158" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H158" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I158" s="8" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="J158" s="8" t="inlineStr">
-        <is>
-          <t>ទិដ្ឋភាពទូទៅ</t>
-        </is>
-      </c>
-      <c r="K158" s="12" t="inlineStr">
-        <is>
-          <t>Tabs on one asset</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="21.6" customHeight="1">
-      <c r="A159" s="7" t="n"/>
-      <c r="B159" s="8" t="n"/>
-      <c r="C159" s="8" t="n"/>
-      <c r="D159" s="7" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E159" s="8" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F159" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G159" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H159" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I159" s="8" t="inlineStr">
-        <is>
-          <t>Assignment</t>
-        </is>
-      </c>
-      <c r="J159" s="8" t="inlineStr">
-        <is>
-          <t>ការចាត់ចែង</t>
-        </is>
-      </c>
-      <c r="K159" s="12" t="n"/>
-    </row>
-    <row r="160" ht="21.6" customHeight="1">
-      <c r="A160" s="7" t="n"/>
-      <c r="B160" s="8" t="n"/>
-      <c r="C160" s="8" t="n"/>
-      <c r="D160" s="7" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E160" s="8" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F160" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G160" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H160" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I160" s="8" t="inlineStr">
-        <is>
-          <t>Transfers</t>
-        </is>
-      </c>
-      <c r="J160" s="8" t="inlineStr">
-        <is>
-          <t>ការផ្ទេរ</t>
-        </is>
-      </c>
-      <c r="K160" s="12" t="n"/>
+      <c r="H160" s="5" t="n"/>
+      <c r="I160" s="3" t="n"/>
+      <c r="J160" s="3" t="n"/>
+      <c r="K160" s="6" t="n"/>
     </row>
     <row r="161" ht="21.6" customHeight="1">
       <c r="A161" s="7" t="n"/>
       <c r="B161" s="8" t="n"/>
       <c r="C161" s="8" t="n"/>
-      <c r="D161" s="7" t="inlineStr">
+      <c r="D161" s="9" t="inlineStr">
         <is>
           <t>B9.2</t>
         </is>
       </c>
-      <c r="E161" s="8" t="inlineStr">
+      <c r="E161" s="10" t="inlineStr">
         <is>
           <t>All Assets</t>
         </is>
@@ -8193,19 +8248,23 @@
         </is>
       </c>
       <c r="H161" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I161" s="8" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>បញ្ហា</t>
-        </is>
-      </c>
-      <c r="K161" s="12" t="n"/>
+          <t>ទិដ្ឋភាពទូទៅ</t>
+        </is>
+      </c>
+      <c r="K161" s="12" t="inlineStr">
+        <is>
+          <t>Tabs on one asset</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="21.6" customHeight="1">
       <c r="A162" s="7" t="n"/>
@@ -8232,16 +8291,16 @@
         </is>
       </c>
       <c r="H162" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>ការចាត់ចែង</t>
         </is>
       </c>
       <c r="K162" s="12" t="n"/>
@@ -8271,16 +8330,16 @@
         </is>
       </c>
       <c r="H163" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Transfers</t>
         </is>
       </c>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ការផ្ទេរ</t>
         </is>
       </c>
       <c r="K163" s="12" t="n"/>
@@ -8289,87 +8348,117 @@
       <c r="A164" s="7" t="n"/>
       <c r="B164" s="8" t="n"/>
       <c r="C164" s="8" t="n"/>
-      <c r="D164" s="9" t="inlineStr">
-        <is>
-          <t>B9.3</t>
-        </is>
-      </c>
-      <c r="E164" s="10" t="inlineStr">
-        <is>
-          <t>My Assets</t>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E164" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr">
         <is>
-          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G164" s="11" t="inlineStr">
         <is>
-          <t>/my-assets</t>
-        </is>
-      </c>
-      <c r="H164" s="7" t="n"/>
-      <c r="I164" s="8" t="n"/>
-      <c r="J164" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I164" s="8" t="inlineStr">
+        <is>
+          <t>Issues</t>
+        </is>
+      </c>
+      <c r="J164" s="8" t="inlineStr">
+        <is>
+          <t>បញ្ហា</t>
+        </is>
+      </c>
       <c r="K164" s="12" t="n"/>
     </row>
     <row r="165" ht="21.6" customHeight="1">
       <c r="A165" s="7" t="n"/>
       <c r="B165" s="8" t="n"/>
       <c r="C165" s="8" t="n"/>
-      <c r="D165" s="9" t="inlineStr">
-        <is>
-          <t>B9.4</t>
-        </is>
-      </c>
-      <c r="E165" s="10" t="inlineStr">
-        <is>
-          <t>Issues</t>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr">
         <is>
-          <t>បញ្ហា</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G165" s="11" t="inlineStr">
         <is>
-          <t>/asset-issues</t>
-        </is>
-      </c>
-      <c r="H165" s="7" t="n"/>
-      <c r="I165" s="8" t="n"/>
-      <c r="J165" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I165" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="J165" s="8" t="inlineStr">
+        <is>
+          <t>ការជួសជុល</t>
+        </is>
+      </c>
       <c r="K165" s="12" t="n"/>
     </row>
     <row r="166" ht="21.6" customHeight="1">
       <c r="A166" s="7" t="n"/>
       <c r="B166" s="8" t="n"/>
       <c r="C166" s="8" t="n"/>
-      <c r="D166" s="9" t="inlineStr">
-        <is>
-          <t>B9.5</t>
-        </is>
-      </c>
-      <c r="E166" s="10" t="inlineStr">
-        <is>
-          <t>Repairs</t>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E166" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G166" s="11" t="inlineStr">
         <is>
-          <t>/asset-repairs</t>
-        </is>
-      </c>
-      <c r="H166" s="7" t="n"/>
-      <c r="I166" s="8" t="n"/>
-      <c r="J166" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I166" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="J166" s="8" t="inlineStr">
+        <is>
+          <t>ការថែទាំ</t>
+        </is>
+      </c>
       <c r="K166" s="12" t="n"/>
     </row>
     <row r="167" ht="21.6" customHeight="1">
@@ -8378,22 +8467,22 @@
       <c r="C167" s="8" t="n"/>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>B9.6</t>
+          <t>B9.3</t>
         </is>
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>Repair Shops</t>
+          <t>My Assets</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr">
         <is>
-          <t>ហាងជួសជុល</t>
+          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
-          <t>/repair-shops</t>
+          <t>/my-assets</t>
         </is>
       </c>
       <c r="H167" s="7" t="n"/>
@@ -8407,22 +8496,22 @@
       <c r="C168" s="8" t="n"/>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>B9.7</t>
+          <t>B9.4</t>
         </is>
       </c>
       <c r="E168" s="10" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>បញ្ហា</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr">
         <is>
-          <t>/asset-maintenance</t>
+          <t>/asset-issues</t>
         </is>
       </c>
       <c r="H168" s="7" t="n"/>
@@ -8436,22 +8525,22 @@
       <c r="C169" s="8" t="n"/>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>B9.8</t>
+          <t>B9.5</t>
         </is>
       </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
-          <t>Asset Categories</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
-          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
-          <t>/asset-categories</t>
+          <t>/asset-repairs</t>
         </is>
       </c>
       <c r="H169" s="7" t="n"/>
@@ -8465,22 +8554,22 @@
       <c r="C170" s="8" t="n"/>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>B9.9</t>
+          <t>B9.6</t>
         </is>
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>Asset Locations</t>
+          <t>Repair Shops</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
+          <t>ហាងជួសជុល</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>/asset-locations</t>
+          <t>/repair-shops</t>
         </is>
       </c>
       <c r="H170" s="7" t="n"/>
@@ -8494,22 +8583,22 @@
       <c r="C171" s="8" t="n"/>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>B9.10</t>
+          <t>B9.7</t>
         </is>
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>Departments</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>ការថែទាំ</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>/departments</t>
+          <t>/asset-maintenance</t>
         </is>
       </c>
       <c r="H171" s="7" t="n"/>
@@ -8523,22 +8612,22 @@
       <c r="C172" s="8" t="n"/>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>B9.11</t>
+          <t>B9.8</t>
         </is>
       </c>
       <c r="E172" s="10" t="inlineStr">
         <is>
-          <t>Suppliers</t>
+          <t>Asset Categories</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>អ្នកផ្គត់ផ្គង់</t>
+          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
-          <t>/suppliers</t>
+          <t>/asset-categories</t>
         </is>
       </c>
       <c r="H172" s="7" t="n"/>
@@ -8552,127 +8641,97 @@
       <c r="C173" s="8" t="n"/>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>B9.12</t>
+          <t>B9.9</t>
         </is>
       </c>
       <c r="E173" s="10" t="inlineStr">
         <is>
-          <t>Asset Reports</t>
+          <t>Asset Locations</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H173" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I173" s="8" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="J173" s="8" t="inlineStr">
-        <is>
-          <t>ស្តុក</t>
-        </is>
-      </c>
+          <t>/asset-locations</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="n"/>
+      <c r="I173" s="8" t="n"/>
+      <c r="J173" s="8" t="n"/>
       <c r="K173" s="12" t="n"/>
     </row>
     <row r="174" ht="21.6" customHeight="1">
       <c r="A174" s="7" t="n"/>
       <c r="B174" s="8" t="n"/>
       <c r="C174" s="8" t="n"/>
-      <c r="D174" s="7" t="inlineStr">
-        <is>
-          <t>B9.12</t>
-        </is>
-      </c>
-      <c r="E174" s="8" t="inlineStr">
-        <is>
-          <t>Asset Reports</t>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>B9.10</t>
+        </is>
+      </c>
+      <c r="E174" s="10" t="inlineStr">
+        <is>
+          <t>Departments</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H174" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I174" s="8" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="J174" s="8" t="inlineStr">
-        <is>
-          <t>ស្ថានភាព</t>
-        </is>
-      </c>
+          <t>/departments</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="n"/>
+      <c r="I174" s="8" t="n"/>
+      <c r="J174" s="8" t="n"/>
       <c r="K174" s="12" t="n"/>
     </row>
     <row r="175" ht="21.6" customHeight="1">
       <c r="A175" s="7" t="n"/>
       <c r="B175" s="8" t="n"/>
       <c r="C175" s="8" t="n"/>
-      <c r="D175" s="7" t="inlineStr">
-        <is>
-          <t>B9.12</t>
-        </is>
-      </c>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t>Asset Reports</t>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>B9.11</t>
+        </is>
+      </c>
+      <c r="E175" s="10" t="inlineStr">
+        <is>
+          <t>Suppliers</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>អ្នកផ្គត់ផ្គង់</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H175" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I175" s="8" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="J175" s="8" t="inlineStr">
-        <is>
-          <t>ការជួសជុល</t>
-        </is>
-      </c>
+          <t>/suppliers</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="n"/>
+      <c r="I175" s="8" t="n"/>
+      <c r="J175" s="8" t="n"/>
       <c r="K175" s="12" t="n"/>
     </row>
     <row r="176" ht="21.6" customHeight="1">
       <c r="A176" s="7" t="n"/>
       <c r="B176" s="8" t="n"/>
       <c r="C176" s="8" t="n"/>
-      <c r="D176" s="7" t="inlineStr">
+      <c r="D176" s="9" t="inlineStr">
         <is>
           <t>B9.12</t>
         </is>
       </c>
-      <c r="E176" s="8" t="inlineStr">
+      <c r="E176" s="10" t="inlineStr">
         <is>
           <t>Asset Reports</t>
         </is>
@@ -8688,16 +8747,16 @@
         </is>
       </c>
       <c r="H176" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I176" s="8" t="inlineStr">
         <is>
-          <t>Repair Cost</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>ថ្លៃជួសជុល</t>
+          <t>ស្តុក</t>
         </is>
       </c>
       <c r="K176" s="12" t="n"/>
@@ -8727,16 +8786,16 @@
         </is>
       </c>
       <c r="H177" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ស្ថានភាព</t>
         </is>
       </c>
       <c r="K177" s="12" t="n"/>
@@ -8766,16 +8825,16 @@
         </is>
       </c>
       <c r="H178" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>Assignments</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
-          <t>ការចាត់ចែង</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="K178" s="12" t="n"/>
@@ -8805,295 +8864,325 @@
         </is>
       </c>
       <c r="H179" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I179" s="8" t="inlineStr">
+        <is>
+          <t>Repair Cost</t>
+        </is>
+      </c>
+      <c r="J179" s="8" t="inlineStr">
+        <is>
+          <t>ថ្លៃជួសជុល</t>
+        </is>
+      </c>
+      <c r="K179" s="12" t="n"/>
+    </row>
+    <row r="180" ht="21.6" customHeight="1">
+      <c r="A180" s="7" t="n"/>
+      <c r="B180" s="8" t="n"/>
+      <c r="C180" s="8" t="n"/>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E180" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F180" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G180" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I180" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="J180" s="8" t="inlineStr">
+        <is>
+          <t>ការថែទាំ</t>
+        </is>
+      </c>
+      <c r="K180" s="12" t="n"/>
+    </row>
+    <row r="181" ht="21.6" customHeight="1">
+      <c r="A181" s="7" t="n"/>
+      <c r="B181" s="8" t="n"/>
+      <c r="C181" s="8" t="n"/>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E181" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G181" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I181" s="8" t="inlineStr">
+        <is>
+          <t>Assignments</t>
+        </is>
+      </c>
+      <c r="J181" s="8" t="inlineStr">
+        <is>
+          <t>ការចាត់ចែង</t>
+        </is>
+      </c>
+      <c r="K181" s="12" t="n"/>
+    </row>
+    <row r="182" ht="21.6" customHeight="1">
+      <c r="A182" s="7" t="n"/>
+      <c r="B182" s="8" t="n"/>
+      <c r="C182" s="8" t="n"/>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E182" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F182" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G182" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H182" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I179" s="8" t="inlineStr">
+      <c r="I182" s="8" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="J179" s="8" t="inlineStr">
+      <c r="J182" s="8" t="inlineStr">
         <is>
           <t>ប្រវត្តិ</t>
         </is>
       </c>
-      <c r="K179" s="12" t="n"/>
-    </row>
-    <row r="180" ht="21.6" customHeight="1">
-      <c r="A180" s="13" t="inlineStr">
+      <c r="K182" s="12" t="n"/>
+    </row>
+    <row r="183" ht="21.6" customHeight="1">
+      <c r="A183" s="13" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="B180" s="14" t="inlineStr">
+      <c r="B183" s="14" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="C180" s="15" t="inlineStr">
+      <c r="C183" s="15" t="inlineStr">
         <is>
           <t>ការទំនាក់ទំនង</t>
         </is>
       </c>
-      <c r="D180" s="13" t="inlineStr">
+      <c r="D183" s="13" t="inlineStr">
         <is>
           <t>B10.1</t>
         </is>
       </c>
-      <c r="E180" s="14" t="inlineStr">
+      <c r="E183" s="14" t="inlineStr">
         <is>
           <t>Contact Messages</t>
         </is>
       </c>
-      <c r="F180" s="15" t="inlineStr">
+      <c r="F183" s="15" t="inlineStr">
         <is>
           <t>សារទំនាក់ទំនង</t>
         </is>
       </c>
-      <c r="G180" s="16" t="inlineStr">
+      <c r="G183" s="16" t="inlineStr">
         <is>
           <t>/contact-messages</t>
         </is>
       </c>
-      <c r="H180" s="17" t="n"/>
-      <c r="I180" s="15" t="n"/>
-      <c r="J180" s="15" t="n"/>
-      <c r="K180" s="18" t="n"/>
-    </row>
-    <row r="181" ht="21.6" customHeight="1">
-      <c r="A181" s="19" t="n"/>
-      <c r="B181" s="20" t="n"/>
-      <c r="C181" s="20" t="n"/>
-      <c r="D181" s="21" t="inlineStr">
+      <c r="H183" s="17" t="n"/>
+      <c r="I183" s="15" t="n"/>
+      <c r="J183" s="15" t="n"/>
+      <c r="K183" s="18" t="n"/>
+    </row>
+    <row r="184" ht="21.6" customHeight="1">
+      <c r="A184" s="19" t="n"/>
+      <c r="B184" s="20" t="n"/>
+      <c r="C184" s="20" t="n"/>
+      <c r="D184" s="21" t="inlineStr">
         <is>
           <t>B10.2</t>
         </is>
       </c>
-      <c r="E181" s="22" t="inlineStr">
+      <c r="E184" s="22" t="inlineStr">
         <is>
           <t>Notifications</t>
         </is>
       </c>
-      <c r="F181" s="20" t="inlineStr">
+      <c r="F184" s="20" t="inlineStr">
         <is>
           <t>ការជូនដំណឹង</t>
         </is>
       </c>
-      <c r="G181" s="23" t="inlineStr">
+      <c r="G184" s="23" t="inlineStr">
         <is>
           <t>/notifications</t>
         </is>
       </c>
-      <c r="H181" s="19" t="n"/>
-      <c r="I181" s="20" t="n"/>
-      <c r="J181" s="20" t="n"/>
-      <c r="K181" s="24" t="n"/>
-    </row>
-    <row r="182" ht="21.6" customHeight="1">
-      <c r="A182" s="19" t="n"/>
-      <c r="B182" s="20" t="n"/>
-      <c r="C182" s="20" t="n"/>
-      <c r="D182" s="21" t="inlineStr">
+      <c r="H184" s="19" t="n"/>
+      <c r="I184" s="20" t="n"/>
+      <c r="J184" s="20" t="n"/>
+      <c r="K184" s="24" t="n"/>
+    </row>
+    <row r="185" ht="21.6" customHeight="1">
+      <c r="A185" s="19" t="n"/>
+      <c r="B185" s="20" t="n"/>
+      <c r="C185" s="20" t="n"/>
+      <c r="D185" s="21" t="inlineStr">
         <is>
           <t>B10.3</t>
         </is>
       </c>
-      <c r="E182" s="22" t="inlineStr">
+      <c r="E185" s="22" t="inlineStr">
         <is>
           <t>Student Feedback</t>
         </is>
       </c>
-      <c r="F182" s="20" t="inlineStr">
+      <c r="F185" s="20" t="inlineStr">
         <is>
           <t>មតិកែលម្អសិស្ស</t>
         </is>
       </c>
-      <c r="G182" s="23" t="inlineStr">
+      <c r="G185" s="23" t="inlineStr">
         <is>
           <t>/student-feedback</t>
         </is>
       </c>
-      <c r="H182" s="19" t="n">
+      <c r="H185" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I182" s="20" t="inlineStr">
+      <c r="I185" s="20" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="J182" s="20" t="inlineStr">
+      <c r="J185" s="20" t="inlineStr">
         <is>
           <t>កំពុងបើក</t>
         </is>
       </c>
-      <c r="K182" s="24" t="n"/>
-    </row>
-    <row r="183" ht="21.6" customHeight="1">
-      <c r="A183" s="19" t="n"/>
-      <c r="B183" s="20" t="n"/>
-      <c r="C183" s="20" t="n"/>
-      <c r="D183" s="19" t="inlineStr">
+      <c r="K185" s="24" t="n"/>
+    </row>
+    <row r="186" ht="21.6" customHeight="1">
+      <c r="A186" s="19" t="n"/>
+      <c r="B186" s="20" t="n"/>
+      <c r="C186" s="20" t="n"/>
+      <c r="D186" s="19" t="inlineStr">
         <is>
           <t>B10.3</t>
         </is>
       </c>
-      <c r="E183" s="20" t="inlineStr">
+      <c r="E186" s="20" t="inlineStr">
         <is>
           <t>Student Feedback</t>
         </is>
       </c>
-      <c r="F183" s="20" t="inlineStr">
+      <c r="F186" s="20" t="inlineStr">
         <is>
           <t>មតិកែលម្អសិស្ស</t>
         </is>
       </c>
-      <c r="G183" s="23" t="inlineStr">
+      <c r="G186" s="23" t="inlineStr">
         <is>
           <t>/student-feedback</t>
         </is>
       </c>
-      <c r="H183" s="19" t="n">
+      <c r="H186" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="I183" s="20" t="inlineStr">
+      <c r="I186" s="20" t="inlineStr">
         <is>
           <t>Replied</t>
         </is>
       </c>
-      <c r="J183" s="20" t="inlineStr">
+      <c r="J186" s="20" t="inlineStr">
         <is>
           <t>បានឆ្លើយតប</t>
         </is>
       </c>
-      <c r="K183" s="24" t="n"/>
-    </row>
-    <row r="184" ht="21.6" customHeight="1">
-      <c r="A184" s="1" t="inlineStr">
+      <c r="K186" s="24" t="n"/>
+    </row>
+    <row r="187" ht="21.6" customHeight="1">
+      <c r="A187" s="1" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t>ការកំណត់</t>
         </is>
       </c>
-      <c r="D184" s="1" t="inlineStr">
+      <c r="D187" s="1" t="inlineStr">
         <is>
           <t>B11.1</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="F184" s="3" t="inlineStr">
+      <c r="F187" s="3" t="inlineStr">
         <is>
           <t>ឯកសារ</t>
         </is>
       </c>
-      <c r="G184" s="4" t="inlineStr">
+      <c r="G187" s="4" t="inlineStr">
         <is>
           <t>/school-documents</t>
         </is>
       </c>
-      <c r="H184" s="5" t="n"/>
-      <c r="I184" s="3" t="n"/>
-      <c r="J184" s="3" t="n"/>
-      <c r="K184" s="6" t="n"/>
-    </row>
-    <row r="185" ht="21.6" customHeight="1">
-      <c r="A185" s="7" t="n"/>
-      <c r="B185" s="8" t="n"/>
-      <c r="C185" s="8" t="n"/>
-      <c r="D185" s="9" t="inlineStr">
-        <is>
-          <t>B11.2</t>
-        </is>
-      </c>
-      <c r="E185" s="10" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F185" s="8" t="inlineStr">
-        <is>
-          <t>ទូទៅ</t>
-        </is>
-      </c>
-      <c r="G185" s="11" t="inlineStr">
-        <is>
-          <t>/settings</t>
-        </is>
-      </c>
-      <c r="H185" s="7" t="n"/>
-      <c r="I185" s="8" t="n"/>
-      <c r="J185" s="8" t="n"/>
-      <c r="K185" s="12" t="n"/>
-    </row>
-    <row r="186" ht="21.6" customHeight="1">
-      <c r="A186" s="7" t="n"/>
-      <c r="B186" s="8" t="n"/>
-      <c r="C186" s="8" t="n"/>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>B11.3</t>
-        </is>
-      </c>
-      <c r="E186" s="10" t="inlineStr">
-        <is>
-          <t>Telegram notifications</t>
-        </is>
-      </c>
-      <c r="F186" s="8" t="inlineStr">
-        <is>
-          <t>ការជូនដំណឹង Telegram</t>
-        </is>
-      </c>
-      <c r="G186" s="11" t="inlineStr">
-        <is>
-          <t>/telegram-notifications</t>
-        </is>
-      </c>
-      <c r="H186" s="7" t="n"/>
-      <c r="I186" s="8" t="n"/>
-      <c r="J186" s="8" t="n"/>
-      <c r="K186" s="12" t="n"/>
-    </row>
-    <row r="187" ht="21.6" customHeight="1">
-      <c r="A187" s="7" t="n"/>
-      <c r="B187" s="8" t="n"/>
-      <c r="C187" s="8" t="n"/>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>B11.4</t>
-        </is>
-      </c>
-      <c r="E187" s="10" t="inlineStr">
-        <is>
-          <t>Users</t>
-        </is>
-      </c>
-      <c r="F187" s="8" t="inlineStr">
-        <is>
-          <t>អ្នកប្រើប្រាស់</t>
-        </is>
-      </c>
-      <c r="G187" s="11" t="inlineStr">
-        <is>
-          <t>/users</t>
-        </is>
-      </c>
-      <c r="H187" s="7" t="n"/>
-      <c r="I187" s="8" t="n"/>
-      <c r="J187" s="8" t="n"/>
-      <c r="K187" s="12" t="n"/>
+      <c r="H187" s="5" t="n"/>
+      <c r="I187" s="3" t="n"/>
+      <c r="J187" s="3" t="n"/>
+      <c r="K187" s="6" t="n"/>
     </row>
     <row r="188" ht="21.6" customHeight="1">
       <c r="A188" s="7" t="n"/>
@@ -9101,22 +9190,22 @@
       <c r="C188" s="8" t="n"/>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>B11.5</t>
+          <t>B11.2</t>
         </is>
       </c>
       <c r="E188" s="10" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F188" s="8" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>ទូទៅ</t>
         </is>
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/settings</t>
         </is>
       </c>
       <c r="H188" s="7" t="n"/>
@@ -9130,22 +9219,22 @@
       <c r="C189" s="8" t="n"/>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>B11.6</t>
+          <t>B11.3</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>Audit Logs</t>
+          <t>Telegram notifications</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr">
         <is>
-          <t>កំណត់ហេតុសវនកម្ម</t>
+          <t>ការជូនដំណឹង Telegram</t>
         </is>
       </c>
       <c r="G189" s="11" t="inlineStr">
         <is>
-          <t>/audit-logs</t>
+          <t>/telegram-notifications</t>
         </is>
       </c>
       <c r="H189" s="7" t="n"/>
@@ -9159,76 +9248,56 @@
       <c r="C190" s="8" t="n"/>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>B11.7</t>
+          <t>B11.4</t>
         </is>
       </c>
       <c r="E190" s="10" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="F190" s="8" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>អ្នកប្រើប្រាស់</t>
         </is>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="H190" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I190" s="8" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="J190" s="8" t="inlineStr">
-        <is>
-          <t>ភាសា</t>
-        </is>
-      </c>
+          <t>/users</t>
+        </is>
+      </c>
+      <c r="H190" s="7" t="n"/>
+      <c r="I190" s="8" t="n"/>
+      <c r="J190" s="8" t="n"/>
       <c r="K190" s="12" t="n"/>
     </row>
     <row r="191" ht="21.6" customHeight="1">
       <c r="A191" s="7" t="n"/>
       <c r="B191" s="8" t="n"/>
       <c r="C191" s="8" t="n"/>
-      <c r="D191" s="7" t="inlineStr">
-        <is>
-          <t>B11.7</t>
-        </is>
-      </c>
-      <c r="E191" s="8" t="inlineStr">
-        <is>
-          <t>Languages</t>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>B11.5</t>
+        </is>
+      </c>
+      <c r="E191" s="10" t="inlineStr">
+        <is>
+          <t>Roles</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="H191" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I191" s="8" t="inlineStr">
-        <is>
-          <t>Translation</t>
-        </is>
-      </c>
-      <c r="J191" s="8" t="inlineStr">
-        <is>
-          <t>ការបកប្រែ</t>
-        </is>
-      </c>
+          <t>/roles</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="n"/>
+      <c r="I191" s="8" t="n"/>
+      <c r="J191" s="8" t="n"/>
       <c r="K191" s="12" t="n"/>
     </row>
     <row r="192" ht="21.6" customHeight="1">
@@ -9237,22 +9306,22 @@
       <c r="C192" s="8" t="n"/>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>B11.8</t>
+          <t>B11.6</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>Base Data</t>
+          <t>Audit Logs</t>
         </is>
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>ទិន្នន័យមូលដ្ឋាន</t>
+          <t>កំណត់ហេតុសវនកម្ម</t>
         </is>
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
-          <t>/lookup-categories</t>
+          <t>/audit-logs</t>
         </is>
       </c>
       <c r="H192" s="7" t="n"/>
@@ -9266,193 +9335,183 @@
       <c r="C193" s="8" t="n"/>
       <c r="D193" s="9" t="inlineStr">
         <is>
+          <t>B11.7</t>
+        </is>
+      </c>
+      <c r="E193" s="10" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="G193" s="11" t="inlineStr">
+        <is>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I193" s="8" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="J193" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="K193" s="12" t="n"/>
+    </row>
+    <row r="194" ht="21.6" customHeight="1">
+      <c r="A194" s="7" t="n"/>
+      <c r="B194" s="8" t="n"/>
+      <c r="C194" s="8" t="n"/>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>B11.7</t>
+        </is>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="G194" s="11" t="inlineStr">
+        <is>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" s="8" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="J194" s="8" t="inlineStr">
+        <is>
+          <t>ការបកប្រែ</t>
+        </is>
+      </c>
+      <c r="K194" s="12" t="n"/>
+    </row>
+    <row r="195" ht="21.6" customHeight="1">
+      <c r="A195" s="7" t="n"/>
+      <c r="B195" s="8" t="n"/>
+      <c r="C195" s="8" t="n"/>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>B11.8</t>
+        </is>
+      </c>
+      <c r="E195" s="10" t="inlineStr">
+        <is>
+          <t>Base Data</t>
+        </is>
+      </c>
+      <c r="F195" s="8" t="inlineStr">
+        <is>
+          <t>ទិន្នន័យមូលដ្ឋាន</t>
+        </is>
+      </c>
+      <c r="G195" s="11" t="inlineStr">
+        <is>
+          <t>/lookup-categories</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="n"/>
+      <c r="I195" s="8" t="n"/>
+      <c r="J195" s="8" t="n"/>
+      <c r="K195" s="12" t="n"/>
+    </row>
+    <row r="196" ht="21.6" customHeight="1">
+      <c r="A196" s="7" t="n"/>
+      <c r="B196" s="8" t="n"/>
+      <c r="C196" s="8" t="n"/>
+      <c r="D196" s="9" t="inlineStr">
+        <is>
           <t>B11.9</t>
         </is>
       </c>
-      <c r="E193" s="10" t="inlineStr">
+      <c r="E196" s="10" t="inlineStr">
         <is>
           <t>Backup</t>
         </is>
       </c>
-      <c r="F193" s="8" t="inlineStr">
+      <c r="F196" s="8" t="inlineStr">
         <is>
           <t>បម្រុងទុក</t>
         </is>
       </c>
-      <c r="G193" s="11" t="inlineStr">
+      <c r="G196" s="11" t="inlineStr">
         <is>
           <t>/database-backups</t>
         </is>
       </c>
-      <c r="H193" s="7" t="n"/>
-      <c r="I193" s="8" t="n"/>
-      <c r="J193" s="8" t="n"/>
-      <c r="K193" s="12" t="n"/>
-    </row>
-    <row r="194" ht="21.6" customHeight="1">
-      <c r="A194" s="13" t="inlineStr">
+      <c r="H196" s="7" t="n"/>
+      <c r="I196" s="8" t="n"/>
+      <c r="J196" s="8" t="n"/>
+      <c r="K196" s="12" t="n"/>
+    </row>
+    <row r="197" ht="21.6" customHeight="1">
+      <c r="A197" s="13" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B194" s="14" t="inlineStr">
+      <c r="B197" s="14" t="inlineStr">
         <is>
           <t>eApprovals</t>
         </is>
       </c>
-      <c r="C194" s="15" t="n"/>
-      <c r="D194" s="13" t="inlineStr">
+      <c r="C197" s="15" t="n"/>
+      <c r="D197" s="13" t="inlineStr">
         <is>
           <t>B12.1</t>
         </is>
       </c>
-      <c r="E194" s="14" t="inlineStr">
+      <c r="E197" s="14" t="inlineStr">
         <is>
           <t>Forms</t>
         </is>
       </c>
-      <c r="F194" s="15" t="inlineStr">
+      <c r="F197" s="15" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="G194" s="16" t="inlineStr">
+      <c r="G197" s="16" t="inlineStr">
         <is>
           <t>/approvals/forms</t>
         </is>
       </c>
-      <c r="H194" s="17" t="n"/>
-      <c r="I194" s="15" t="n"/>
-      <c r="J194" s="15" t="n"/>
-      <c r="K194" s="18" t="n"/>
-    </row>
-    <row r="195" ht="21.6" customHeight="1">
-      <c r="A195" s="19" t="n"/>
-      <c r="B195" s="20" t="n"/>
-      <c r="C195" s="20" t="n"/>
-      <c r="D195" s="21" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E195" s="22" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F195" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G195" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H195" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I195" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J195" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
-      <c r="K195" s="24" t="n"/>
-    </row>
-    <row r="196" ht="21.6" customHeight="1">
-      <c r="A196" s="19" t="n"/>
-      <c r="B196" s="20" t="n"/>
-      <c r="C196" s="20" t="n"/>
-      <c r="D196" s="19" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E196" s="20" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F196" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G196" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H196" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I196" s="20" t="inlineStr">
-        <is>
-          <t>Approved to study</t>
-        </is>
-      </c>
-      <c r="J196" s="20" t="inlineStr">
-        <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
-        </is>
-      </c>
-      <c r="K196" s="24" t="n"/>
-    </row>
-    <row r="197" ht="21.6" customHeight="1">
-      <c r="A197" s="19" t="n"/>
-      <c r="B197" s="20" t="n"/>
-      <c r="C197" s="20" t="n"/>
-      <c r="D197" s="19" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E197" s="20" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F197" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G197" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H197" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I197" s="20" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J197" s="20" t="inlineStr">
-        <is>
-          <t>បានអនុម័ត</t>
-        </is>
-      </c>
-      <c r="K197" s="24" t="n"/>
+      <c r="H197" s="17" t="n"/>
+      <c r="I197" s="15" t="n"/>
+      <c r="J197" s="15" t="n"/>
+      <c r="K197" s="18" t="n"/>
     </row>
     <row r="198" ht="21.6" customHeight="1">
       <c r="A198" s="19" t="n"/>
       <c r="B198" s="20" t="n"/>
       <c r="C198" s="20" t="n"/>
-      <c r="D198" s="19" t="inlineStr">
+      <c r="D198" s="21" t="inlineStr">
         <is>
           <t>B12.2</t>
         </is>
       </c>
-      <c r="E198" s="20" t="inlineStr">
+      <c r="E198" s="22" t="inlineStr">
         <is>
           <t>My Request</t>
         </is>
@@ -9468,16 +9527,16 @@
         </is>
       </c>
       <c r="H198" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I198" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J198" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="K198" s="24" t="n"/>
@@ -9507,16 +9566,16 @@
         </is>
       </c>
       <c r="H199" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I199" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J199" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K199" s="24" t="n"/>
@@ -9525,37 +9584,37 @@
       <c r="A200" s="19" t="n"/>
       <c r="B200" s="20" t="n"/>
       <c r="C200" s="20" t="n"/>
-      <c r="D200" s="21" t="inlineStr">
-        <is>
-          <t>B12.3</t>
-        </is>
-      </c>
-      <c r="E200" s="22" t="inlineStr">
-        <is>
-          <t>Approvals</t>
+      <c r="D200" s="19" t="inlineStr">
+        <is>
+          <t>B12.2</t>
+        </is>
+      </c>
+      <c r="E200" s="20" t="inlineStr">
+        <is>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G200" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H200" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I200" s="20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J200" s="20" t="inlineStr">
         <is>
-          <t>ថ្មី</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K200" s="24" t="n"/>
@@ -9566,88 +9625,88 @@
       <c r="C201" s="20" t="n"/>
       <c r="D201" s="19" t="inlineStr">
         <is>
-          <t>B12.3</t>
+          <t>B12.2</t>
         </is>
       </c>
       <c r="E201" s="20" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G201" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H201" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I201" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="J201" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="K201" s="24" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" ht="21.6" customHeight="1">
       <c r="A202" s="19" t="n"/>
       <c r="B202" s="20" t="n"/>
       <c r="C202" s="20" t="n"/>
       <c r="D202" s="19" t="inlineStr">
         <is>
-          <t>B12.3</t>
+          <t>B12.2</t>
         </is>
       </c>
       <c r="E202" s="20" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F202" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G202" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H202" s="19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I202" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="J202" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>បានលុបចោល</t>
         </is>
       </c>
       <c r="K202" s="24" t="n"/>
     </row>
-    <row r="203">
+    <row r="203" ht="21.6" customHeight="1">
       <c r="A203" s="19" t="n"/>
       <c r="B203" s="20" t="n"/>
       <c r="C203" s="20" t="n"/>
-      <c r="D203" s="19" t="inlineStr">
+      <c r="D203" s="21" t="inlineStr">
         <is>
           <t>B12.3</t>
         </is>
       </c>
-      <c r="E203" s="20" t="inlineStr">
+      <c r="E203" s="22" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
@@ -9663,21 +9722,21 @@
         </is>
       </c>
       <c r="H203" s="19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I203" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>New</t>
         </is>
       </c>
       <c r="J203" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>ថ្មី</t>
         </is>
       </c>
       <c r="K203" s="24" t="n"/>
     </row>
-    <row r="204">
+    <row r="204" ht="21.6" customHeight="1">
       <c r="A204" s="19" t="n"/>
       <c r="B204" s="20" t="n"/>
       <c r="C204" s="20" t="n"/>
@@ -9702,159 +9761,276 @@
         </is>
       </c>
       <c r="H204" s="19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I204" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J204" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K204" s="24" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" ht="21.6" customHeight="1">
       <c r="A205" s="19" t="n"/>
       <c r="B205" s="20" t="n"/>
       <c r="C205" s="20" t="n"/>
-      <c r="D205" s="21" t="inlineStr">
-        <is>
-          <t>B12.4</t>
-        </is>
-      </c>
-      <c r="E205" s="22" t="inlineStr">
-        <is>
-          <t>Form Categories</t>
+      <c r="D205" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E205" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="F205" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទទម្រង់បែបបទ</t>
+          <t>ការអនុម័ត</t>
         </is>
       </c>
       <c r="G205" s="23" t="inlineStr">
         <is>
-          <t>/form-categories</t>
-        </is>
-      </c>
-      <c r="H205" s="19" t="n"/>
-      <c r="I205" s="20" t="n"/>
-      <c r="J205" s="20" t="n"/>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H205" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I205" s="20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J205" s="20" t="inlineStr">
+        <is>
+          <t>បានអនុម័ត</t>
+        </is>
+      </c>
       <c r="K205" s="24" t="n"/>
     </row>
-    <row r="206">
+    <row r="206" ht="21.6" customHeight="1">
       <c r="A206" s="19" t="n"/>
       <c r="B206" s="20" t="n"/>
       <c r="C206" s="20" t="n"/>
-      <c r="D206" s="21" t="inlineStr">
+      <c r="D206" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E206" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
+        </is>
+      </c>
+      <c r="F206" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័ត</t>
+        </is>
+      </c>
+      <c r="G206" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H206" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I206" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="J206" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
+      <c r="K206" s="24" t="n"/>
+    </row>
+    <row r="207" ht="21.6" customHeight="1">
+      <c r="A207" s="19" t="n"/>
+      <c r="B207" s="20" t="n"/>
+      <c r="C207" s="20" t="n"/>
+      <c r="D207" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E207" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
+        </is>
+      </c>
+      <c r="F207" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័ត</t>
+        </is>
+      </c>
+      <c r="G207" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H207" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I207" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="J207" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="K207" s="24" t="n"/>
+    </row>
+    <row r="208" ht="21.6" customHeight="1">
+      <c r="A208" s="19" t="n"/>
+      <c r="B208" s="20" t="n"/>
+      <c r="C208" s="20" t="n"/>
+      <c r="D208" s="21" t="inlineStr">
+        <is>
+          <t>B12.4</t>
+        </is>
+      </c>
+      <c r="E208" s="22" t="inlineStr">
+        <is>
+          <t>Form Categories</t>
+        </is>
+      </c>
+      <c r="F208" s="20" t="inlineStr">
+        <is>
+          <t>ប្រភេទទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="G208" s="23" t="inlineStr">
+        <is>
+          <t>/form-categories</t>
+        </is>
+      </c>
+      <c r="H208" s="19" t="n"/>
+      <c r="I208" s="20" t="n"/>
+      <c r="J208" s="20" t="n"/>
+      <c r="K208" s="24" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="19" t="n"/>
+      <c r="B209" s="20" t="n"/>
+      <c r="C209" s="20" t="n"/>
+      <c r="D209" s="21" t="inlineStr">
         <is>
           <t>B12.5</t>
         </is>
       </c>
-      <c r="E206" s="22" t="inlineStr">
+      <c r="E209" s="22" t="inlineStr">
         <is>
           <t>Form Templates</t>
         </is>
       </c>
-      <c r="F206" s="20" t="inlineStr">
+      <c r="F209" s="20" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="G206" s="23" t="inlineStr">
+      <c r="G209" s="23" t="inlineStr">
         <is>
           <t>/form-templates</t>
         </is>
       </c>
-      <c r="H206" s="19" t="n"/>
-      <c r="I206" s="20" t="n"/>
-      <c r="J206" s="20" t="n"/>
-      <c r="K206" s="24" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="1" t="inlineStr">
+      <c r="H209" s="19" t="n"/>
+      <c r="I209" s="20" t="n"/>
+      <c r="J209" s="20" t="n"/>
+      <c r="K209" s="24" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C207" s="3" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D207" s="1" t="inlineStr">
+      <c r="D210" s="1" t="inlineStr">
         <is>
           <t>B13.1</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Groups</t>
         </is>
       </c>
-      <c r="F207" s="3" t="inlineStr">
+      <c r="F210" s="3" t="inlineStr">
         <is>
           <t>ក្រុម</t>
         </is>
       </c>
-      <c r="G207" s="4" t="inlineStr">
+      <c r="G210" s="4" t="inlineStr">
         <is>
           <t>/approval-flow/groups</t>
         </is>
       </c>
-      <c r="H207" s="5" t="n"/>
-      <c r="I207" s="3" t="n"/>
-      <c r="J207" s="3" t="n"/>
-      <c r="K207" s="6" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="7" t="inlineStr">
+      <c r="H210" s="5" t="n"/>
+      <c r="I210" s="3" t="n"/>
+      <c r="J210" s="3" t="n"/>
+      <c r="K210" s="6" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B208" s="8" t="inlineStr">
+      <c r="B211" s="8" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C208" s="8" t="inlineStr">
+      <c r="C211" s="8" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D208" s="9" t="inlineStr">
+      <c r="D211" s="9" t="inlineStr">
         <is>
           <t>B13.2</t>
         </is>
       </c>
-      <c r="E208" s="10" t="inlineStr">
+      <c r="E211" s="10" t="inlineStr">
         <is>
           <t>Flow Setting</t>
         </is>
       </c>
-      <c r="F208" s="8" t="inlineStr">
+      <c r="F211" s="8" t="inlineStr">
         <is>
           <t>កំណត់លំហូរ</t>
         </is>
       </c>
-      <c r="G208" s="11" t="inlineStr">
+      <c r="G211" s="11" t="inlineStr">
         <is>
           <t>/approval-flow/settings</t>
         </is>
       </c>
-      <c r="H208" s="7" t="n"/>
-      <c r="I208" s="8" t="n"/>
-      <c r="J208" s="8" t="n"/>
-      <c r="K208" s="12" t="n"/>
+      <c r="H211" s="7" t="n"/>
+      <c r="I211" s="8" t="n"/>
+      <c r="J211" s="8" t="n"/>
+      <c r="K211" s="12" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K208"/>
@@ -9880,7 +10056,8 @@
     <col width="10.5546875" bestFit="1" customWidth="1" style="27" min="8" max="8"/>
     <col width="28" customWidth="1" style="27" min="9" max="10"/>
     <col width="44" customWidth="1" style="27" min="11" max="11"/>
-    <col width="8.88671875" customWidth="1" style="27" min="12" max="16384"/>
+    <col width="8.88671875" customWidth="1" style="27" min="12" max="12"/>
+    <col width="8.88671875" customWidth="1" style="27" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customFormat="1" customHeight="1" s="28">
@@ -11216,4 +11393,3069 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="13.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="3"/>
+    <col width="28" customWidth="1" min="4" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10.5546875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customFormat="1" customHeight="1" s="26" thickBot="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Module No.</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
+        <is>
+          <t>Module (ខ្មែរ)</t>
+        </is>
+      </c>
+      <c r="D1" s="25" t="inlineStr">
+        <is>
+          <t>Sub module</t>
+        </is>
+      </c>
+      <c r="E1" s="25" t="inlineStr">
+        <is>
+          <t>Sub module (ខ្មែរ)</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G1" s="25" t="inlineStr">
+        <is>
+          <t>Tab No.</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="I1" s="25" t="inlineStr">
+        <is>
+          <t>Tab (ខ្មែរ)</t>
+        </is>
+      </c>
+      <c r="J1" s="25" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21.6" customHeight="1" thickBot="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>ទិដ្ឋភាពទូទៅ</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>ផ្ទាំងគ្រប់គ្រង</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="21.6" customHeight="1" thickBot="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ការគ្រប់គ្រងគម្រោង</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>ការគ្រប់គ្រងគម្រោង</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="21.6" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>ការសិក្សា</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Programs</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>កម្មវិធីសិក្សា</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>/academic-programs</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H4" s="39" t="inlineStr">
+        <is>
+          <t>Academic Programs</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>កម្មវិធីសិក្សា</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="n"/>
+    </row>
+    <row r="5" ht="21.6" customHeight="1">
+      <c r="A5" s="19" t="n"/>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="36" t="inlineStr">
+        <is>
+          <t>3Academic Years</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>ឆ្នាំសិក្សា</t>
+        </is>
+      </c>
+      <c r="J5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="21.6" customHeight="1">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>Course</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>វគ្គសិក្សា</t>
+        </is>
+      </c>
+      <c r="J6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="21.6" customHeight="1">
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H7" s="36" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>សៀវភៅ</t>
+        </is>
+      </c>
+      <c r="J7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="21.6" customHeight="1">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>Book Categories</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>ប្រភេទសៀវភៅ</t>
+        </is>
+      </c>
+      <c r="J8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="21.6" customHeight="1">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>School Setup</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>ការរៀបចំសាលា</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>/school-setup</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>3Terms / Semesters</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>ឆមាស</t>
+        </is>
+      </c>
+      <c r="J9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="21.6" customHeight="1">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>Grade levels</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>កម្រិតថ្នាក់</t>
+        </is>
+      </c>
+      <c r="J10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="21.6" customHeight="1">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>Curriculum</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>កម្មវិធីសិក្សា</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="21.6" customHeight="1">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H12" s="36" t="inlineStr">
+        <is>
+          <t>3School calendar</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>ប្រតិទិនសាលា</t>
+        </is>
+      </c>
+      <c r="J12" s="24" t="n"/>
+    </row>
+    <row r="13" ht="21.6" customHeight="1">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>Promotion rules</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>លក្ខខណ្ឌឡើងថ្នាក់</t>
+        </is>
+      </c>
+      <c r="J13" s="24" t="n"/>
+    </row>
+    <row r="14" ht="21.6" customHeight="1">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>Promote students</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>ដំឡើងថ្នាក់សិស្ស</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="21.6" customHeight="1">
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>Video Lesson</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>មេរៀនវីដេអូ</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>/videos</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="21.6" customHeight="1">
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Study Building</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>អគារសិក្សា</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>/buildings</t>
+        </is>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H16" s="36" t="inlineStr">
+        <is>
+          <t>Buildings</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>អគារ</t>
+        </is>
+      </c>
+      <c r="J16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="21.6" customHeight="1">
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H17" s="36" t="inlineStr">
+        <is>
+          <t>Classrooms</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>បន្ទប់រៀន</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="21.6" customHeight="1">
+      <c r="A18" s="19" t="n"/>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Classes</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>ថ្នាក់រៀន</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>/classes</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="21.6" customHeight="1">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>Timetable</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>កាលវិភាគ</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>/timetable</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>ថ្នាក់</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="21.6" customHeight="1">
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>Teacher</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>គ្រូ</t>
+        </is>
+      </c>
+      <c r="J20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="21.6" customHeight="1">
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>បន្ទប់</t>
+        </is>
+      </c>
+      <c r="J21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="21.6" customHeight="1">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>Subject hours</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>ម៉ោងតាមមុខវិជ្ជា</t>
+        </is>
+      </c>
+      <c r="J22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="21.6" customHeight="1">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>Conflicts</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>ម៉ោងជាន់គ្នា</t>
+        </is>
+      </c>
+      <c r="J23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="21.6" customHeight="1">
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>Schedule changes</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>សំណើប្តូរកាលវិភាគ</t>
+        </is>
+      </c>
+      <c r="J24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="21.6" customHeight="1">
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Lesson Plans</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>ផែនការបង្រៀន</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>/lessons</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>Lesson plans</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>ផែនការមេរៀន</t>
+        </is>
+      </c>
+      <c r="J25" s="24" t="n"/>
+    </row>
+    <row r="26" ht="21.6" customHeight="1">
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>Weekly plan</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>ផែនការប្រចាំសប្តាហ៍</t>
+        </is>
+      </c>
+      <c r="J26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="21.6" customHeight="1">
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>Teaching log</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>កំណត់ត្រាបង្រៀន</t>
+        </is>
+      </c>
+      <c r="J27" s="24" t="n"/>
+    </row>
+    <row r="28" ht="21.6" customHeight="1">
+      <c r="A28" s="19" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>ពិនិត្យ</t>
+        </is>
+      </c>
+      <c r="J28" s="24" t="n"/>
+    </row>
+    <row r="29" ht="21.6" customHeight="1">
+      <c r="A29" s="19" t="n"/>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>Curriculum progress</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>វឌ្ឍនភាពកម្មវិធីសិក្សា</t>
+        </is>
+      </c>
+      <c r="J29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="21.6" customHeight="1">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>Delays</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>យឺតពេល</t>
+        </is>
+      </c>
+      <c r="J30" s="24" t="n"/>
+    </row>
+    <row r="31" ht="21.6" customHeight="1">
+      <c r="A31" s="19" t="n"/>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Student Attendance</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>វត្តមានសិស្ស</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>/attendance</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>Student Attendance</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>វត្តមានសិស្ស</t>
+        </is>
+      </c>
+      <c r="J31" s="24" t="n"/>
+    </row>
+    <row r="32" ht="21.6" customHeight="1">
+      <c r="A32" s="19" t="n"/>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>Attendance Summary</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>សរុបវត្តមាន</t>
+        </is>
+      </c>
+      <c r="J32" s="24" t="n"/>
+    </row>
+    <row r="33" ht="21.6" customHeight="1">
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>Examination</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>ការប្រឡងនិងលទ្ធផល</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>/examination</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>Assessment Setup</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>ការកំណត់ការវាយតម្លៃ</t>
+        </is>
+      </c>
+      <c r="J33" s="24" t="n"/>
+    </row>
+    <row r="34" ht="21.6" customHeight="1">
+      <c r="A34" s="19" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="20" t="inlineStr">
+        <is>
+          <t>Exam Schedule</t>
+        </is>
+      </c>
+      <c r="I34" s="20" t="inlineStr">
+        <is>
+          <t>កាលវិភាគប្រឡង</t>
+        </is>
+      </c>
+      <c r="J34" s="24" t="n"/>
+    </row>
+    <row r="35" ht="21.6" customHeight="1">
+      <c r="A35" s="19" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>Grade Entry</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>បញ្ចូលពិន្ទុ</t>
+        </is>
+      </c>
+      <c r="J35" s="24" t="n"/>
+    </row>
+    <row r="36" ht="21.6" customHeight="1">
+      <c r="A36" s="19" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>Grade Validation</t>
+        </is>
+      </c>
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>ពិនិត្យពិន្ទុ</t>
+        </is>
+      </c>
+      <c r="J36" s="24" t="n"/>
+    </row>
+    <row r="37" ht="21.6" customHeight="1">
+      <c r="A37" s="19" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
+        <is>
+          <t>Score Calculation</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>គណនាពិន្ទុ</t>
+        </is>
+      </c>
+      <c r="J37" s="24" t="n"/>
+    </row>
+    <row r="38" ht="21.6" customHeight="1">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>Result Approval</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>អនុម័តលទ្ធផល</t>
+        </is>
+      </c>
+      <c r="J38" s="24" t="n"/>
+    </row>
+    <row r="39" ht="21.6" customHeight="1">
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
+        <is>
+          <t>Grade Correction</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>កែពិន្ទុ</t>
+        </is>
+      </c>
+      <c r="J39" s="24" t="n"/>
+    </row>
+    <row r="40" ht="21.6" customHeight="1">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>Academic Transcript</t>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>ប្រវត្តិពិន្ទុ</t>
+        </is>
+      </c>
+      <c r="J40" s="24" t="n"/>
+    </row>
+    <row r="41" ht="21.6" customHeight="1">
+      <c r="A41" s="19" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>Student Progress</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>វឌ្ឍនភាពសិស្ស</t>
+        </is>
+      </c>
+      <c r="J41" s="24" t="n"/>
+    </row>
+    <row r="42" ht="21.6" customHeight="1">
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="23" t="n"/>
+      <c r="G42" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>Result Export</t>
+        </is>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t>នាំចេញលទ្ធផល</t>
+        </is>
+      </c>
+      <c r="J42" s="24" t="n"/>
+    </row>
+    <row r="43" ht="21.6" customHeight="1" thickBot="1">
+      <c r="A43" s="19" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="23" t="n"/>
+      <c r="G43" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>Exams</t>
+        </is>
+      </c>
+      <c r="I43" s="20" t="inlineStr">
+        <is>
+          <t>ការប្រឡង</t>
+        </is>
+      </c>
+      <c r="J43" s="24" t="n"/>
+    </row>
+    <row r="44" ht="21.6" customHeight="1">
+      <c r="A44" s="19" t="n"/>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="23" t="n"/>
+      <c r="G44" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
+        <is>
+          <t>Grades</t>
+        </is>
+      </c>
+      <c r="I44" s="20" t="inlineStr">
+        <is>
+          <t>និទ្ទេស</t>
+        </is>
+      </c>
+      <c r="J44" s="24" t="n"/>
+    </row>
+    <row r="45" ht="21.6" customHeight="1">
+      <c r="A45" s="19" t="n"/>
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="20" t="n"/>
+      <c r="F45" s="23" t="n"/>
+      <c r="G45" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
+        <is>
+          <t>Make-up Exam</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>ប្រឡងសង</t>
+        </is>
+      </c>
+      <c r="J45" s="24" t="n"/>
+    </row>
+    <row r="46" ht="21.6" customHeight="1" thickBot="1">
+      <c r="A46" s="19" t="n"/>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="n"/>
+      <c r="F46" s="23" t="n"/>
+      <c r="G46" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>Certificate</t>
+        </is>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>វិញ្ញាបនបត្រ</t>
+        </is>
+      </c>
+      <c r="J46" s="24" t="n"/>
+    </row>
+    <row r="47" ht="21.6" customHeight="1">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>សិស្សានុសិស្ស</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Students</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>សិស្សានុសិស្ស</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>/students</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="6" t="n"/>
+    </row>
+    <row r="48" ht="21.6" customHeight="1">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Import Students</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>នាំចូលទិន្នន័យសិស្ស</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>/student-imports</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="12" t="n"/>
+    </row>
+    <row r="49" ht="21.6" customHeight="1">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Enrollments</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>ការចុះឈ្មោះចូលរៀន</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>/enrollments</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="12" t="n"/>
+    </row>
+    <row r="50" ht="21.6" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>HRM</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>ធនធានមនុស្ស</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Staff</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>បុគ្គលិក</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>/staff</t>
+        </is>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>Current Info</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>ព័ត៌មានបច្ចុប្បន្ន</t>
+        </is>
+      </c>
+      <c r="J50" s="18" t="inlineStr">
+        <is>
+          <t>Tabs on the staff form</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="21.6" customHeight="1">
+      <c r="A51" s="19" t="n"/>
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="23" t="n"/>
+      <c r="G51" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>Emergency Contacts</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
+        <is>
+          <t>ទំនាក់ទំនងបន្ទាន់</t>
+        </is>
+      </c>
+      <c r="J51" s="24" t="n"/>
+    </row>
+    <row r="52" ht="21.6" customHeight="1">
+      <c r="A52" s="19" t="n"/>
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="23" t="n"/>
+      <c r="G52" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="38" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="I52" s="20" t="inlineStr">
+        <is>
+          <t>ការសិក្សា</t>
+        </is>
+      </c>
+      <c r="J52" s="24" t="n"/>
+    </row>
+    <row r="53" ht="21.6" customHeight="1">
+      <c r="A53" s="19" t="n"/>
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="23" t="n"/>
+      <c r="G53" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>Family Members</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>សមាជិកគ្រួសារ</t>
+        </is>
+      </c>
+      <c r="J53" s="24" t="n"/>
+    </row>
+    <row r="54" ht="21.6" customHeight="1">
+      <c r="A54" s="19" t="n"/>
+      <c r="B54" s="20" t="n"/>
+      <c r="C54" s="20" t="n"/>
+      <c r="D54" s="20" t="n"/>
+      <c r="E54" s="20" t="n"/>
+      <c r="F54" s="23" t="n"/>
+      <c r="G54" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="I54" s="20" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="J54" s="24" t="n"/>
+    </row>
+    <row r="55" ht="21.6" customHeight="1">
+      <c r="A55" s="19" t="n"/>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="23" t="n"/>
+      <c r="G55" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>Previous Work</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
+        <is>
+          <t>បទពិសោធន៍ការងារពីមុន</t>
+        </is>
+      </c>
+      <c r="J55" s="24" t="n"/>
+    </row>
+    <row r="56" ht="21.6" customHeight="1">
+      <c r="A56" s="19" t="n"/>
+      <c r="B56" s="20" t="n"/>
+      <c r="C56" s="20" t="n"/>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>Teachers</t>
+        </is>
+      </c>
+      <c r="E56" s="20" t="inlineStr">
+        <is>
+          <t>គ្រូ</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>/teachers</t>
+        </is>
+      </c>
+      <c r="G56" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="38" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I56" s="20" t="inlineStr">
+        <is>
+          <t>គុណវុឌ្ឍិ</t>
+        </is>
+      </c>
+      <c r="J56" s="24" t="n"/>
+    </row>
+    <row r="57" ht="21.6" customHeight="1">
+      <c r="A57" s="19" t="n"/>
+      <c r="B57" s="20" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="23" t="n"/>
+      <c r="G57" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="I57" s="20" t="inlineStr">
+        <is>
+          <t>ការចាត់តាំង</t>
+        </is>
+      </c>
+      <c r="J57" s="24" t="n"/>
+    </row>
+    <row r="58" ht="21.6" customHeight="1">
+      <c r="A58" s="19" t="n"/>
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="20" t="n"/>
+      <c r="E58" s="20" t="n"/>
+      <c r="F58" s="23" t="n"/>
+      <c r="G58" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" s="20" t="inlineStr">
+        <is>
+          <t>Homeroom</t>
+        </is>
+      </c>
+      <c r="I58" s="20" t="inlineStr">
+        <is>
+          <t>គ្រូប្រចាំថ្នាក់</t>
+        </is>
+      </c>
+      <c r="J58" s="24" t="n"/>
+    </row>
+    <row r="59" ht="21.6" customHeight="1">
+      <c r="A59" s="19" t="n"/>
+      <c r="B59" s="20" t="n"/>
+      <c r="C59" s="20" t="n"/>
+      <c r="D59" s="20" t="n"/>
+      <c r="E59" s="20" t="n"/>
+      <c r="F59" s="23" t="n"/>
+      <c r="G59" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" s="20" t="inlineStr">
+        <is>
+          <t>Teaching load</t>
+        </is>
+      </c>
+      <c r="I59" s="20" t="inlineStr">
+        <is>
+          <t>ម៉ោងបង្រៀន</t>
+        </is>
+      </c>
+      <c r="J59" s="24" t="n"/>
+    </row>
+    <row r="60" ht="21.6" customHeight="1">
+      <c r="A60" s="19" t="n"/>
+      <c r="B60" s="20" t="n"/>
+      <c r="C60" s="20" t="n"/>
+      <c r="D60" s="20" t="n"/>
+      <c r="E60" s="20" t="n"/>
+      <c r="F60" s="23" t="n"/>
+      <c r="G60" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" s="20" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="I60" s="20" t="inlineStr">
+        <is>
+          <t>ពេលទំនេរ</t>
+        </is>
+      </c>
+      <c r="J60" s="24" t="n"/>
+    </row>
+    <row r="61" ht="21.6" customHeight="1">
+      <c r="A61" s="19" t="n"/>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+      <c r="E61" s="20" t="n"/>
+      <c r="F61" s="23" t="n"/>
+      <c r="G61" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>Substitute</t>
+        </is>
+      </c>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
+          <t>គ្រូជំនួស</t>
+        </is>
+      </c>
+      <c r="J61" s="24" t="n"/>
+    </row>
+    <row r="62" ht="21.6" customHeight="1">
+      <c r="A62" s="19" t="n"/>
+      <c r="B62" s="20" t="n"/>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="20" t="n"/>
+      <c r="E62" s="20" t="n"/>
+      <c r="F62" s="23" t="n"/>
+      <c r="G62" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H62" s="20" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="I62" s="20" t="inlineStr">
+        <is>
+          <t>ឯកសារ</t>
+        </is>
+      </c>
+      <c r="J62" s="24" t="n"/>
+    </row>
+    <row r="63" ht="21.6" customHeight="1">
+      <c r="A63" s="19" t="n"/>
+      <c r="B63" s="20" t="n"/>
+      <c r="C63" s="20" t="n"/>
+      <c r="D63" s="22" t="inlineStr">
+        <is>
+          <t>Staff Status History</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>/staff-status-history</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="n"/>
+      <c r="H63" s="20" t="n"/>
+      <c r="I63" s="20" t="n"/>
+      <c r="J63" s="24" t="n"/>
+    </row>
+    <row r="64" ht="21.6" customHeight="1">
+      <c r="A64" s="19" t="n"/>
+      <c r="B64" s="20" t="n"/>
+      <c r="C64" s="20" t="n"/>
+      <c r="D64" s="22" t="inlineStr">
+        <is>
+          <t>Organization Management</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>/organization</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" s="36" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="I64" s="20" t="inlineStr">
+        <is>
+          <t>សាលា</t>
+        </is>
+      </c>
+      <c r="J64" s="24" t="n"/>
+    </row>
+    <row r="65" ht="21.6" customHeight="1">
+      <c r="A65" s="19" t="n"/>
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="20" t="n"/>
+      <c r="E65" s="20" t="n"/>
+      <c r="F65" s="23" t="n"/>
+      <c r="G65" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H65" s="36" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="I65" s="20" t="inlineStr">
+        <is>
+          <t>សាខា</t>
+        </is>
+      </c>
+      <c r="J65" s="24" t="n"/>
+    </row>
+    <row r="66" ht="21.6" customHeight="1">
+      <c r="A66" s="19" t="n"/>
+      <c r="B66" s="20" t="n"/>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="20" t="n"/>
+      <c r="E66" s="20" t="n"/>
+      <c r="F66" s="23" t="n"/>
+      <c r="G66" s="19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H66" s="36" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="I66" s="20" t="inlineStr">
+        <is>
+          <t>នាយកដ្ឋាន</t>
+        </is>
+      </c>
+      <c r="J66" s="24" t="n"/>
+    </row>
+    <row r="67" ht="21.6" customHeight="1">
+      <c r="A67" s="19" t="n"/>
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="20" t="n"/>
+      <c r="F67" s="23" t="n"/>
+      <c r="G67" s="19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H67" s="36" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="I67" s="20" t="inlineStr">
+        <is>
+          <t>ក្រុម</t>
+        </is>
+      </c>
+      <c r="J67" s="24" t="n"/>
+    </row>
+    <row r="68" ht="21.6" customHeight="1">
+      <c r="A68" s="19" t="n"/>
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="20" t="n"/>
+      <c r="F68" s="23" t="n"/>
+      <c r="G68" s="19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="I68" s="20" t="inlineStr">
+        <is>
+          <t>តួនាទី</t>
+        </is>
+      </c>
+      <c r="J68" s="24" t="n"/>
+    </row>
+    <row r="69" ht="21.6" customHeight="1">
+      <c r="A69" s="19" t="n"/>
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="20" t="n"/>
+      <c r="F69" s="23" t="n"/>
+      <c r="G69" s="19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t>Job grade</t>
+        </is>
+      </c>
+      <c r="I69" s="20" t="inlineStr">
+        <is>
+          <t>ថ្នាក់ការងារ</t>
+        </is>
+      </c>
+      <c r="J69" s="24" t="n"/>
+    </row>
+    <row r="70" ht="21.6" customHeight="1">
+      <c r="A70" s="19" t="n"/>
+      <c r="B70" s="20" t="n"/>
+      <c r="C70" s="20" t="n"/>
+      <c r="D70" s="20" t="n"/>
+      <c r="E70" s="20" t="n"/>
+      <c r="F70" s="23" t="n"/>
+      <c r="G70" s="19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H70" s="36" t="inlineStr">
+        <is>
+          <t>Job level</t>
+        </is>
+      </c>
+      <c r="I70" s="20" t="inlineStr">
+        <is>
+          <t>កម្រិតការងារ</t>
+        </is>
+      </c>
+      <c r="J70" s="24" t="n"/>
+    </row>
+    <row r="71" ht="21.6" customHeight="1">
+      <c r="A71" s="19" t="n"/>
+      <c r="B71" s="20" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="20" t="n"/>
+      <c r="F71" s="23" t="n"/>
+      <c r="G71" s="19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>Reporting manager</t>
+        </is>
+      </c>
+      <c r="I71" s="20" t="inlineStr">
+        <is>
+          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
+        </is>
+      </c>
+      <c r="J71" s="24" t="n"/>
+    </row>
+    <row r="72" ht="21.6" customHeight="1">
+      <c r="A72" s="19" t="n"/>
+      <c r="B72" s="20" t="n"/>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="20" t="n"/>
+      <c r="E72" s="20" t="n"/>
+      <c r="F72" s="23" t="n"/>
+      <c r="G72" s="19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="H72" s="36" t="inlineStr">
+        <is>
+          <t>Organization hierarchy</t>
+        </is>
+      </c>
+      <c r="I72" s="20" t="inlineStr">
+        <is>
+          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
+        </is>
+      </c>
+      <c r="J72" s="24" t="n"/>
+    </row>
+    <row r="73" ht="21.6" customHeight="1">
+      <c r="A73" s="19" t="n"/>
+      <c r="B73" s="20" t="n"/>
+      <c r="C73" s="20" t="n"/>
+      <c r="D73" s="22" t="inlineStr">
+        <is>
+          <t>Attendance &amp; Time</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>/time-attendance</t>
+        </is>
+      </c>
+      <c r="G73" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>Employee attendance</t>
+        </is>
+      </c>
+      <c r="I73" s="20" t="inlineStr">
+        <is>
+          <t>វត្តមានបុគ្គលិក</t>
+        </is>
+      </c>
+      <c r="J73" s="24" t="n"/>
+    </row>
+    <row r="74" ht="21.6" customHeight="1">
+      <c r="A74" s="19" t="n"/>
+      <c r="B74" s="20" t="n"/>
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="20" t="n"/>
+      <c r="F74" s="23" t="n"/>
+      <c r="G74" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>Check-in / check-out</t>
+        </is>
+      </c>
+      <c r="I74" s="20" t="inlineStr">
+        <is>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+        </is>
+      </c>
+      <c r="J74" s="24" t="n"/>
+    </row>
+    <row r="75" ht="21.6" customHeight="1">
+      <c r="A75" s="19" t="n"/>
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="20" t="n"/>
+      <c r="F75" s="23" t="n"/>
+      <c r="G75" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" s="20" t="inlineStr">
+        <is>
+          <t>Late</t>
+        </is>
+      </c>
+      <c r="I75" s="20" t="inlineStr">
+        <is>
+          <t>មកយឺត</t>
+        </is>
+      </c>
+      <c r="J75" s="24" t="n"/>
+    </row>
+    <row r="76" ht="21.6" customHeight="1">
+      <c r="A76" s="19" t="n"/>
+      <c r="B76" s="20" t="n"/>
+      <c r="C76" s="20" t="n"/>
+      <c r="D76" s="20" t="n"/>
+      <c r="E76" s="20" t="n"/>
+      <c r="F76" s="23" t="n"/>
+      <c r="G76" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="20" t="inlineStr">
+        <is>
+          <t>Early leave</t>
+        </is>
+      </c>
+      <c r="I76" s="20" t="inlineStr">
+        <is>
+          <t>ចេញមុន</t>
+        </is>
+      </c>
+      <c r="J76" s="24" t="n"/>
+    </row>
+    <row r="77" ht="21.6" customHeight="1">
+      <c r="A77" s="19" t="n"/>
+      <c r="B77" s="20" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="20" t="n"/>
+      <c r="F77" s="23" t="n"/>
+      <c r="G77" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H77" s="20" t="inlineStr">
+        <is>
+          <t>Absence</t>
+        </is>
+      </c>
+      <c r="I77" s="20" t="inlineStr">
+        <is>
+          <t>អវត្តមាន</t>
+        </is>
+      </c>
+      <c r="J77" s="24" t="n"/>
+    </row>
+    <row r="78" ht="21.6" customHeight="1">
+      <c r="A78" s="19" t="n"/>
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="20" t="n"/>
+      <c r="E78" s="20" t="n"/>
+      <c r="F78" s="23" t="n"/>
+      <c r="G78" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H78" s="20" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>ម៉ោងបន្ថែម</t>
+        </is>
+      </c>
+      <c r="J78" s="24" t="n"/>
+    </row>
+    <row r="79" ht="21.6" customHeight="1">
+      <c r="A79" s="19" t="n"/>
+      <c r="B79" s="20" t="n"/>
+      <c r="C79" s="20" t="n"/>
+      <c r="D79" s="20" t="n"/>
+      <c r="E79" s="20" t="n"/>
+      <c r="F79" s="23" t="n"/>
+      <c r="G79" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H79" s="20" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+      <c r="I79" s="20" t="inlineStr">
+        <is>
+          <t>វេនការងារ</t>
+        </is>
+      </c>
+      <c r="J79" s="24" t="n"/>
+    </row>
+    <row r="80" ht="21.6" customHeight="1">
+      <c r="A80" s="19" t="n"/>
+      <c r="B80" s="20" t="n"/>
+      <c r="C80" s="20" t="n"/>
+      <c r="D80" s="20" t="n"/>
+      <c r="E80" s="20" t="n"/>
+      <c r="F80" s="23" t="n"/>
+      <c r="G80" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H80" s="20" t="inlineStr">
+        <is>
+          <t>Staff shift</t>
+        </is>
+      </c>
+      <c r="I80" s="20" t="inlineStr">
+        <is>
+          <t>វេនបុគ្គលិក</t>
+        </is>
+      </c>
+      <c r="J80" s="24" t="n"/>
+    </row>
+    <row r="81" ht="21.6" customHeight="1">
+      <c r="A81" s="19" t="n"/>
+      <c r="B81" s="20" t="n"/>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="20" t="n"/>
+      <c r="E81" s="20" t="n"/>
+      <c r="F81" s="23" t="n"/>
+      <c r="G81" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H81" s="20" t="inlineStr">
+        <is>
+          <t>Holidays</t>
+        </is>
+      </c>
+      <c r="I81" s="20" t="inlineStr">
+        <is>
+          <t>ថ្ងៃឈប់សម្រាក</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="n"/>
+    </row>
+    <row r="82" ht="21.6" customHeight="1">
+      <c r="A82" s="19" t="n"/>
+      <c r="B82" s="20" t="n"/>
+      <c r="C82" s="20" t="n"/>
+      <c r="D82" s="20" t="n"/>
+      <c r="E82" s="20" t="n"/>
+      <c r="F82" s="23" t="n"/>
+      <c r="G82" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H82" s="20" t="inlineStr">
+        <is>
+          <t>Attendance correction</t>
+        </is>
+      </c>
+      <c r="I82" s="20" t="inlineStr">
+        <is>
+          <t>ការកែវត្តមាន</t>
+        </is>
+      </c>
+      <c r="J82" s="24" t="n"/>
+    </row>
+    <row r="83" ht="21.6" customHeight="1">
+      <c r="A83" s="19" t="n"/>
+      <c r="B83" s="20" t="n"/>
+      <c r="C83" s="20" t="n"/>
+      <c r="D83" s="20" t="n"/>
+      <c r="E83" s="20" t="n"/>
+      <c r="F83" s="23" t="n"/>
+      <c r="G83" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="H83" s="20" t="inlineStr">
+        <is>
+          <t>Attendance approval</t>
+        </is>
+      </c>
+      <c r="I83" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័តវត្តមាន</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="n"/>
+    </row>
+    <row r="84" ht="21.6" customHeight="1">
+      <c r="A84" s="19" t="n"/>
+      <c r="B84" s="20" t="n"/>
+      <c r="C84" s="20" t="n"/>
+      <c r="D84" s="22" t="inlineStr">
+        <is>
+          <t>Leave Management</t>
+        </is>
+      </c>
+      <c r="E84" s="20" t="inlineStr">
+        <is>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+        </is>
+      </c>
+      <c r="F84" s="23" t="inlineStr">
+        <is>
+          <t>/leave-management</t>
+        </is>
+      </c>
+      <c r="G84" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="20" t="inlineStr">
+        <is>
+          <t>Leave types</t>
+        </is>
+      </c>
+      <c r="I84" s="20" t="inlineStr">
+        <is>
+          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
+        </is>
+      </c>
+      <c r="J84" s="24" t="n"/>
+    </row>
+    <row r="85" ht="21.6" customHeight="1">
+      <c r="A85" s="19" t="n"/>
+      <c r="B85" s="20" t="n"/>
+      <c r="C85" s="20" t="n"/>
+      <c r="D85" s="20" t="n"/>
+      <c r="E85" s="20" t="n"/>
+      <c r="F85" s="23" t="n"/>
+      <c r="G85" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" s="20" t="inlineStr">
+        <is>
+          <t>Leave policies</t>
+        </is>
+      </c>
+      <c r="I85" s="20" t="inlineStr">
+        <is>
+          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="n"/>
+    </row>
+    <row r="86" ht="21.6" customHeight="1">
+      <c r="A86" s="19" t="n"/>
+      <c r="B86" s="20" t="n"/>
+      <c r="C86" s="20" t="n"/>
+      <c r="D86" s="20" t="n"/>
+      <c r="E86" s="20" t="n"/>
+      <c r="F86" s="23" t="n"/>
+      <c r="G86" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>Leave balance</t>
+        </is>
+      </c>
+      <c r="I86" s="20" t="inlineStr">
+        <is>
+          <t>សមតុល្យច្បាប់</t>
+        </is>
+      </c>
+      <c r="J86" s="24" t="n"/>
+    </row>
+    <row r="87" ht="21.6" customHeight="1">
+      <c r="A87" s="19" t="n"/>
+      <c r="B87" s="20" t="n"/>
+      <c r="C87" s="20" t="n"/>
+      <c r="D87" s="20" t="n"/>
+      <c r="E87" s="20" t="n"/>
+      <c r="F87" s="23" t="n"/>
+      <c r="G87" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H87" s="20" t="inlineStr">
+        <is>
+          <t>Leave request</t>
+        </is>
+      </c>
+      <c r="I87" s="20" t="inlineStr">
+        <is>
+          <t>សំណើច្បាប់ឈប់សម្រាក</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="n"/>
+    </row>
+    <row r="88" ht="21.6" customHeight="1">
+      <c r="A88" s="19" t="n"/>
+      <c r="B88" s="20" t="n"/>
+      <c r="C88" s="20" t="n"/>
+      <c r="D88" s="20" t="n"/>
+      <c r="E88" s="20" t="n"/>
+      <c r="F88" s="23" t="n"/>
+      <c r="G88" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H88" s="20" t="inlineStr">
+        <is>
+          <t>Approval workflow</t>
+        </is>
+      </c>
+      <c r="I88" s="20" t="inlineStr">
+        <is>
+          <t>លំហូរការអនុម័ត</t>
+        </is>
+      </c>
+      <c r="J88" s="24" t="n"/>
+    </row>
+    <row r="89" ht="21.6" customHeight="1">
+      <c r="A89" s="19" t="n"/>
+      <c r="B89" s="20" t="n"/>
+      <c r="C89" s="20" t="n"/>
+      <c r="D89" s="20" t="n"/>
+      <c r="E89" s="20" t="n"/>
+      <c r="F89" s="23" t="n"/>
+      <c r="G89" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H89" s="20" t="inlineStr">
+        <is>
+          <t>Leave calendar</t>
+        </is>
+      </c>
+      <c r="I89" s="20" t="inlineStr">
+        <is>
+          <t>ប្រតិទិនច្បាប់</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="n"/>
+    </row>
+    <row r="90" ht="21.6" customHeight="1">
+      <c r="A90" s="19" t="n"/>
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
+      <c r="F90" s="23" t="n"/>
+      <c r="G90" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H90" s="20" t="inlineStr">
+        <is>
+          <t>Carry forward</t>
+        </is>
+      </c>
+      <c r="I90" s="20" t="inlineStr">
+        <is>
+          <t>យោងទៅឆ្នាំបន្ទាប់</t>
+        </is>
+      </c>
+      <c r="J90" s="24" t="n"/>
+    </row>
+    <row r="91" ht="21.6" customHeight="1">
+      <c r="A91" s="19" t="n"/>
+      <c r="B91" s="20" t="n"/>
+      <c r="C91" s="20" t="n"/>
+      <c r="D91" s="20" t="n"/>
+      <c r="E91" s="20" t="n"/>
+      <c r="F91" s="23" t="n"/>
+      <c r="G91" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" s="20" t="inlineStr">
+        <is>
+          <t>Leave reports</t>
+        </is>
+      </c>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ច្បាប់</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="n"/>
+    </row>
+    <row r="92" ht="21.6" customHeight="1">
+      <c r="A92" s="19" t="n"/>
+      <c r="B92" s="20" t="n"/>
+      <c r="C92" s="20" t="n"/>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>Check in / Check out</t>
+        </is>
+      </c>
+      <c r="E92" s="20" t="inlineStr">
+        <is>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+        </is>
+      </c>
+      <c r="F92" s="23" t="inlineStr">
+        <is>
+          <t>/my-check-in</t>
+        </is>
+      </c>
+      <c r="G92" s="19" t="n"/>
+      <c r="H92" s="20" t="n"/>
+      <c r="I92" s="20" t="n"/>
+      <c r="J92" s="24" t="n"/>
+    </row>
+    <row r="93" ht="21.6" customHeight="1">
+      <c r="A93" s="19" t="n"/>
+      <c r="B93" s="20" t="n"/>
+      <c r="C93" s="20" t="n"/>
+      <c r="D93" s="22" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="G93" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I93" s="20" t="inlineStr">
+        <is>
+          <t>កំពុងរង់ចាំ</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="n"/>
+    </row>
+    <row r="94" ht="21.6" customHeight="1">
+      <c r="A94" s="19" t="n"/>
+      <c r="B94" s="20" t="n"/>
+      <c r="C94" s="20" t="n"/>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="F94" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="G94" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" s="20" t="inlineStr">
+        <is>
+          <t>Approved to study</t>
+        </is>
+      </c>
+      <c r="I94" s="20" t="inlineStr">
+        <is>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
+        </is>
+      </c>
+      <c r="J94" s="24" t="n"/>
+    </row>
+    <row r="95" ht="21.6" customHeight="1" thickBot="1">
+      <c r="A95" s="19" t="n"/>
+      <c r="B95" s="20" t="n"/>
+      <c r="C95" s="20" t="n"/>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="G95" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H95" s="20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I95" s="20" t="inlineStr">
+        <is>
+          <t>បានអនុម័ត</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="n"/>
+    </row>
+    <row r="96" ht="21.6" customHeight="1">
+      <c r="A96" s="19" t="n"/>
+      <c r="B96" s="20" t="n"/>
+      <c r="C96" s="20" t="n"/>
+      <c r="D96" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="G96" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H96" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I96" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
+      <c r="J96" s="24" t="n"/>
+    </row>
+    <row r="97" ht="21.6" customHeight="1">
+      <c r="A97" s="19" t="n"/>
+      <c r="B97" s="20" t="n"/>
+      <c r="C97" s="20" t="n"/>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="F97" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="G97" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H97" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="I97" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="J97" s="24" t="n"/>
+    </row>
+    <row r="98" ht="21.6" customHeight="1">
+      <c r="A98" s="19" t="n"/>
+      <c r="B98" s="20" t="n"/>
+      <c r="C98" s="20" t="n"/>
+      <c r="D98" s="22" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>ទម្រង់</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests?tab=resignation</t>
+        </is>
+      </c>
+      <c r="G98" s="19" t="n"/>
+      <c r="H98" s="20" t="n"/>
+      <c r="I98" s="20" t="n"/>
+      <c r="J98" s="24" t="inlineStr">
+        <is>
+          <t>Resignation form</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="21.6" customHeight="1">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>ការកំណត់</t>
+        </is>
+      </c>
+      <c r="D99" s="35" t="n"/>
+      <c r="E99" s="3" t="n"/>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="5" t="n"/>
+      <c r="H99" s="3" t="n"/>
+      <c r="I99" s="3" t="n"/>
+      <c r="J99" s="6" t="n"/>
+    </row>
+    <row r="100" ht="21.6" customHeight="1">
+      <c r="A100" s="29" t="n"/>
+      <c r="B100" s="30" t="n"/>
+      <c r="C100" s="31" t="n"/>
+      <c r="D100" s="30" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="E100" s="31" t="inlineStr">
+        <is>
+          <t>ឯកសារ</t>
+        </is>
+      </c>
+      <c r="F100" s="32" t="inlineStr">
+        <is>
+          <t>/school-documents</t>
+        </is>
+      </c>
+      <c r="G100" s="33" t="n"/>
+      <c r="H100" s="31" t="n"/>
+      <c r="I100" s="31" t="n"/>
+      <c r="J100" s="34" t="n"/>
+    </row>
+    <row r="101" ht="21.6" customHeight="1">
+      <c r="A101" s="7" t="n"/>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="8" t="n"/>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>ទូទៅ</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>/settings</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="n"/>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="8" t="n"/>
+      <c r="J101" s="12" t="n"/>
+    </row>
+    <row r="102" ht="21.6" customHeight="1">
+      <c r="A102" s="7" t="n"/>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="8" t="n"/>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>Telegram notifications</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>ការជូនដំណឹង Telegram</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>/telegram-notifications</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="n"/>
+      <c r="H102" s="8" t="n"/>
+      <c r="I102" s="8" t="n"/>
+      <c r="J102" s="12" t="n"/>
+    </row>
+    <row r="103" ht="21.6" customHeight="1">
+      <c r="A103" s="7" t="n"/>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>អ្នកប្រើប្រាស់</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>/users</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="n"/>
+      <c r="H103" s="8" t="n"/>
+      <c r="I103" s="8" t="n"/>
+      <c r="J103" s="12" t="n"/>
+    </row>
+    <row r="104" ht="21.6" customHeight="1">
+      <c r="A104" s="7" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D104" s="37" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>តួនាទី</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>/roles</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="n"/>
+      <c r="H104" s="8" t="n"/>
+      <c r="I104" s="8" t="n"/>
+      <c r="J104" s="12" t="n"/>
+    </row>
+    <row r="105" ht="21.6" customHeight="1">
+      <c r="A105" s="7" t="n"/>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>Audit Logs</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>កំណត់ហេតុសវនកម្ម</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>/audit-logs</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="n"/>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="12" t="n"/>
+    </row>
+    <row r="106" ht="21.6" customHeight="1" thickBot="1">
+      <c r="A106" s="7" t="n"/>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="8" t="n"/>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="J106" s="12" t="n"/>
+    </row>
+    <row r="107" ht="21.6" customHeight="1">
+      <c r="A107" s="7" t="n"/>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="8" t="n"/>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>ការបកប្រែ</t>
+        </is>
+      </c>
+      <c r="J107" s="12" t="n"/>
+    </row>
+    <row r="108" ht="21.6" customHeight="1">
+      <c r="A108" s="7" t="n"/>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="8" t="n"/>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Base Data</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>ទិន្នន័យមូលដ្ឋាន</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>/lookup-categories</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="n"/>
+      <c r="H108" s="8" t="n"/>
+      <c r="I108" s="8" t="n"/>
+      <c r="J108" s="12" t="n"/>
+    </row>
+    <row r="109" ht="21.6" customHeight="1">
+      <c r="A109" s="7" t="n"/>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="8" t="n"/>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>Backup</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>បម្រុងទុក</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>/database-backups</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="n"/>
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="8" t="n"/>
+      <c r="J109" s="12" t="n"/>
+    </row>
+    <row r="110" ht="21.6" customHeight="1">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>eApprovals</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="n"/>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>ទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="F110" s="16" t="inlineStr">
+        <is>
+          <t>/approvals/forms</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="n"/>
+      <c r="H110" s="15" t="n"/>
+      <c r="I110" s="15" t="n"/>
+      <c r="J110" s="18" t="n"/>
+    </row>
+    <row r="111" ht="21.6" customHeight="1">
+      <c r="A111" s="19" t="n"/>
+      <c r="B111" s="20" t="n"/>
+      <c r="C111" s="20" t="n"/>
+      <c r="D111" s="22" t="inlineStr">
+        <is>
+          <t>My Request</t>
+        </is>
+      </c>
+      <c r="E111" s="20" t="inlineStr">
+        <is>
+          <t>សំណើរបស់ខ្ញុំ</t>
+        </is>
+      </c>
+      <c r="F111" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="G111" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I111" s="20" t="inlineStr">
+        <is>
+          <t>កំពុងរង់ចាំ</t>
+        </is>
+      </c>
+      <c r="J111" s="24" t="n"/>
+    </row>
+    <row r="112" ht="21.6" customHeight="1">
+      <c r="A112" s="19" t="n"/>
+      <c r="B112" s="20" t="n"/>
+      <c r="C112" s="20" t="n"/>
+      <c r="D112" s="20" t="n"/>
+      <c r="E112" s="20" t="n"/>
+      <c r="F112" s="23" t="n"/>
+      <c r="G112" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" s="20" t="inlineStr">
+        <is>
+          <t>Approved to study</t>
+        </is>
+      </c>
+      <c r="I112" s="20" t="inlineStr">
+        <is>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
+        </is>
+      </c>
+      <c r="J112" s="24" t="n"/>
+    </row>
+    <row r="113" ht="21.6" customHeight="1">
+      <c r="A113" s="19" t="n"/>
+      <c r="B113" s="20" t="n"/>
+      <c r="C113" s="20" t="n"/>
+      <c r="D113" s="20" t="n"/>
+      <c r="E113" s="20" t="n"/>
+      <c r="F113" s="23" t="n"/>
+      <c r="G113" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" s="20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I113" s="20" t="inlineStr">
+        <is>
+          <t>បានអនុម័ត</t>
+        </is>
+      </c>
+      <c r="J113" s="24" t="n"/>
+    </row>
+    <row r="114" ht="22.2" customHeight="1" thickBot="1">
+      <c r="A114" s="19" t="n"/>
+      <c r="B114" s="20" t="n"/>
+      <c r="C114" s="20" t="n"/>
+      <c r="D114" s="20" t="n"/>
+      <c r="E114" s="20" t="n"/>
+      <c r="F114" s="23" t="n"/>
+      <c r="G114" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H114" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I114" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
+      <c r="J114" s="24" t="n"/>
+    </row>
+    <row r="115" ht="21.6" customHeight="1">
+      <c r="A115" s="19" t="n"/>
+      <c r="B115" s="20" t="n"/>
+      <c r="C115" s="20" t="n"/>
+      <c r="D115" s="20" t="n"/>
+      <c r="E115" s="20" t="n"/>
+      <c r="F115" s="23" t="n"/>
+      <c r="G115" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H115" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="I115" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="J115" s="24" t="n"/>
+    </row>
+    <row r="116" ht="21.6" customHeight="1">
+      <c r="A116" s="19" t="n"/>
+      <c r="B116" s="20" t="n"/>
+      <c r="C116" s="20" t="n"/>
+      <c r="D116" s="22" t="inlineStr">
+        <is>
+          <t>Form Categories</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>ប្រភេទទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="F116" s="23" t="inlineStr">
+        <is>
+          <t>/form-categories</t>
+        </is>
+      </c>
+      <c r="G116" s="19" t="n"/>
+      <c r="H116" s="20" t="n"/>
+      <c r="I116" s="20" t="n"/>
+      <c r="J116" s="24" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="19" t="n"/>
+      <c r="B117" s="20" t="n"/>
+      <c r="C117" s="20" t="n"/>
+      <c r="D117" s="22" t="inlineStr">
+        <is>
+          <t>Form Templates</t>
+        </is>
+      </c>
+      <c r="E117" s="20" t="inlineStr">
+        <is>
+          <t>ទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t>/form-templates</t>
+        </is>
+      </c>
+      <c r="G117" s="19" t="n"/>
+      <c r="H117" s="20" t="n"/>
+      <c r="I117" s="20" t="n"/>
+      <c r="J117" s="24" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Approval Flow</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>លំហូរអនុម័ត</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>ក្រុម</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>/approval-flow/groups</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="n"/>
+      <c r="H118" s="3" t="n"/>
+      <c r="I118" s="3" t="n"/>
+      <c r="J118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>Approval Flow</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>លំហូរអនុម័ត</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>Flow Setting</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>កំណត់លំហូរ</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>/approval-flow/settings</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="n"/>
+      <c r="H119" s="8" t="n"/>
+      <c r="I119" s="8" t="n"/>
+      <c r="J119" s="12" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/NTCSWEB-Modules.xlsx
+++ b/docs/NTCSWEB-Modules.xlsx
@@ -2098,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K211"/>
+  <dimension ref="A1:K212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
-          <t>Result Export</t>
+          <t>Remedial Teaching</t>
         </is>
       </c>
       <c r="J56" s="20" t="inlineStr">
         <is>
-          <t>នាំចេញលទ្ធផល</t>
+          <t>ការបង្រៀនបំប៉ន</t>
         </is>
       </c>
       <c r="K56" s="24" t="n"/>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
-          <t>Exams</t>
+          <t>Result Export</t>
         </is>
       </c>
       <c r="J57" s="20" t="inlineStr">
         <is>
-          <t>ការប្រឡង</t>
+          <t>នាំចេញលទ្ធផល</t>
         </is>
       </c>
       <c r="K57" s="24" t="n"/>
@@ -4331,12 +4331,12 @@
       </c>
       <c r="I58" s="20" t="inlineStr">
         <is>
-          <t>Grades</t>
+          <t>Exams</t>
         </is>
       </c>
       <c r="J58" s="20" t="inlineStr">
         <is>
-          <t>និទ្ទេស</t>
+          <t>ការប្រឡង</t>
         </is>
       </c>
       <c r="K58" s="24" t="n"/>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
-          <t>Make-up Exam</t>
+          <t>Grades</t>
         </is>
       </c>
       <c r="J59" s="20" t="inlineStr">
         <is>
-          <t>ប្រឡងសង</t>
+          <t>និទ្ទេស</t>
         </is>
       </c>
       <c r="K59" s="24" t="n"/>
@@ -4409,85 +4409,95 @@
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
+          <t>Make-up Exam</t>
+        </is>
+      </c>
+      <c r="J60" s="20" t="inlineStr">
+        <is>
+          <t>ប្រឡងសង</t>
+        </is>
+      </c>
+      <c r="K60" s="24" t="n"/>
+    </row>
+    <row r="61" ht="21.6" customHeight="1">
+      <c r="A61" s="19" t="n"/>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>B4.9</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>Examination</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>ការប្រឡងនិងលទ្ធផល</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t>/examination</t>
+        </is>
+      </c>
+      <c r="H61" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
           <t>Certificate</t>
         </is>
       </c>
-      <c r="J60" s="20" t="inlineStr">
+      <c r="J61" s="20" t="inlineStr">
         <is>
           <t>វិញ្ញាបនបត្រ</t>
         </is>
       </c>
-      <c r="K60" s="24" t="n"/>
-    </row>
-    <row r="61" ht="21.6" customHeight="1">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="K61" s="24" t="n"/>
+    </row>
+    <row r="62" ht="21.6" customHeight="1">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>សិស្សានុសិស្ស</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr">
+      <c r="D62" s="1" t="inlineStr">
         <is>
           <t>B5.1</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>សិស្សានុសិស្ស</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>/students</t>
         </is>
       </c>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="3" t="n"/>
-      <c r="J61" s="3" t="n"/>
-      <c r="K61" s="6" t="n"/>
-    </row>
-    <row r="62" ht="21.6" customHeight="1">
-      <c r="A62" s="7" t="n"/>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>B5.2</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Import Students</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>នាំចូលទិន្នន័យសិស្ស</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
-        <is>
-          <t>/student-imports</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="12" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="6" t="n"/>
     </row>
     <row r="63" ht="21.6" customHeight="1">
       <c r="A63" s="7" t="n"/>
@@ -4495,22 +4505,22 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>B5.3</t>
+          <t>B5.2</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Enrollments</t>
+          <t>Import Students</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>ការចុះឈ្មោះចូលរៀន</t>
+          <t>នាំចូលទិន្នន័យសិស្ស</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>/enrollments</t>
+          <t>/student-imports</t>
         </is>
       </c>
       <c r="H63" s="7" t="n"/>
@@ -4519,98 +4529,88 @@
       <c r="K63" s="12" t="n"/>
     </row>
     <row r="64" ht="21.6" customHeight="1">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>B5.3</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Enrollments</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>ការចុះឈ្មោះចូលរៀន</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>/enrollments</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="12" t="n"/>
+    </row>
+    <row r="65" ht="21.6" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>HRM</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr">
         <is>
           <t>ធនធានមនុស្ស</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>B6.1</t>
         </is>
       </c>
-      <c r="E64" s="14" t="inlineStr">
+      <c r="E65" s="14" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="F64" s="15" t="inlineStr">
+      <c r="F65" s="15" t="inlineStr">
         <is>
           <t>បុគ្គលិក</t>
         </is>
       </c>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="G65" s="16" t="inlineStr">
         <is>
           <t>/staff</t>
         </is>
       </c>
-      <c r="H64" s="17" t="n">
+      <c r="H65" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I64" s="15" t="inlineStr">
+      <c r="I65" s="15" t="inlineStr">
         <is>
           <t>Current Info</t>
         </is>
       </c>
-      <c r="J64" s="15" t="inlineStr">
+      <c r="J65" s="15" t="inlineStr">
         <is>
           <t>ព័ត៌មានបច្ចុប្បន្ន</t>
         </is>
       </c>
-      <c r="K64" s="18" t="inlineStr">
+      <c r="K65" s="18" t="inlineStr">
         <is>
           <t>Tabs on the staff form</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="21.6" customHeight="1">
-      <c r="A65" s="19" t="n"/>
-      <c r="B65" s="20" t="n"/>
-      <c r="C65" s="20" t="n"/>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>B6.1</t>
-        </is>
-      </c>
-      <c r="E65" s="20" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="F65" s="20" t="inlineStr">
-        <is>
-          <t>បុគ្គលិក</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr">
-        <is>
-          <t>/staff</t>
-        </is>
-      </c>
-      <c r="H65" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I65" s="20" t="inlineStr">
-        <is>
-          <t>Emergency Contacts</t>
-        </is>
-      </c>
-      <c r="J65" s="20" t="inlineStr">
-        <is>
-          <t>ទំនាក់ទំនងបន្ទាន់</t>
-        </is>
-      </c>
-      <c r="K65" s="24" t="n"/>
     </row>
     <row r="66" ht="21.6" customHeight="1">
       <c r="A66" s="19" t="n"/>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="H66" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Emergency Contacts</t>
         </is>
       </c>
       <c r="J66" s="20" t="inlineStr">
         <is>
-          <t>ការសិក្សា</t>
+          <t>ទំនាក់ទំនងបន្ទាន់</t>
         </is>
       </c>
       <c r="K66" s="24" t="n"/>
@@ -4676,16 +4676,16 @@
         </is>
       </c>
       <c r="H67" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>Family Members</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="J67" s="20" t="inlineStr">
         <is>
-          <t>សមាជិកគ្រួសារ</t>
+          <t>ការសិក្សា</t>
         </is>
       </c>
       <c r="K67" s="24" t="n"/>
@@ -4715,16 +4715,16 @@
         </is>
       </c>
       <c r="H68" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Family Members</t>
         </is>
       </c>
       <c r="J68" s="20" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>សមាជិកគ្រួសារ</t>
         </is>
       </c>
       <c r="K68" s="24" t="n"/>
@@ -4754,16 +4754,16 @@
         </is>
       </c>
       <c r="H69" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>Previous Work</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="J69" s="20" t="inlineStr">
         <is>
-          <t>បទពិសោធន៍ការងារពីមុន</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="K69" s="24" t="n"/>
@@ -4772,37 +4772,37 @@
       <c r="A70" s="19" t="n"/>
       <c r="B70" s="20" t="n"/>
       <c r="C70" s="20" t="n"/>
-      <c r="D70" s="21" t="inlineStr">
-        <is>
-          <t>B6.2</t>
-        </is>
-      </c>
-      <c r="E70" s="22" t="inlineStr">
-        <is>
-          <t>Teachers</t>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>B6.1</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>Staff</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>គ្រូ</t>
+          <t>បុគ្គលិក</t>
         </is>
       </c>
       <c r="G70" s="23" t="inlineStr">
         <is>
-          <t>/teachers</t>
+          <t>/staff</t>
         </is>
       </c>
       <c r="H70" s="19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Previous Work</t>
         </is>
       </c>
       <c r="J70" s="20" t="inlineStr">
         <is>
-          <t>គុណវុឌ្ឍិ</t>
+          <t>បទពិសោធន៍ការងារពីមុន</t>
         </is>
       </c>
       <c r="K70" s="24" t="n"/>
@@ -4811,12 +4811,12 @@
       <c r="A71" s="19" t="n"/>
       <c r="B71" s="20" t="n"/>
       <c r="C71" s="20" t="n"/>
-      <c r="D71" s="19" t="inlineStr">
+      <c r="D71" s="21" t="inlineStr">
         <is>
           <t>B6.2</t>
         </is>
       </c>
-      <c r="E71" s="20" t="inlineStr">
+      <c r="E71" s="22" t="inlineStr">
         <is>
           <t>Teachers</t>
         </is>
@@ -4832,16 +4832,16 @@
         </is>
       </c>
       <c r="H71" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
-          <t>ការចាត់តាំង</t>
+          <t>គុណវុឌ្ឍិ</t>
         </is>
       </c>
       <c r="K71" s="24" t="n"/>
@@ -4871,16 +4871,16 @@
         </is>
       </c>
       <c r="H72" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>Homeroom</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="J72" s="20" t="inlineStr">
         <is>
-          <t>គ្រូប្រចាំថ្នាក់</t>
+          <t>ការចាត់តាំង</t>
         </is>
       </c>
       <c r="K72" s="24" t="n"/>
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H73" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Teaching load</t>
+          <t>Homeroom</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបង្រៀន</t>
+          <t>គ្រូប្រចាំថ្នាក់</t>
         </is>
       </c>
       <c r="K73" s="24" t="n"/>
@@ -4949,16 +4949,16 @@
         </is>
       </c>
       <c r="H74" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Teaching load</t>
         </is>
       </c>
       <c r="J74" s="20" t="inlineStr">
         <is>
-          <t>ពេលទំនេរ</t>
+          <t>ម៉ោងបង្រៀន</t>
         </is>
       </c>
       <c r="K74" s="24" t="n"/>
@@ -4988,16 +4988,16 @@
         </is>
       </c>
       <c r="H75" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>Substitute</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>គ្រូជំនួស</t>
+          <t>ពេលទំនេរ</t>
         </is>
       </c>
       <c r="K75" s="24" t="n"/>
@@ -5027,16 +5027,16 @@
         </is>
       </c>
       <c r="H76" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Substitute</t>
         </is>
       </c>
       <c r="J76" s="20" t="inlineStr">
         <is>
-          <t>ឯកសារ</t>
+          <t>គ្រូជំនួស</t>
         </is>
       </c>
       <c r="K76" s="24" t="n"/>
@@ -5045,29 +5045,39 @@
       <c r="A77" s="19" t="n"/>
       <c r="B77" s="20" t="n"/>
       <c r="C77" s="20" t="n"/>
-      <c r="D77" s="21" t="inlineStr">
-        <is>
-          <t>B6.3</t>
-        </is>
-      </c>
-      <c r="E77" s="22" t="inlineStr">
-        <is>
-          <t>Staff Status History</t>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>B6.2</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>Teachers</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
+          <t>គ្រូ</t>
         </is>
       </c>
       <c r="G77" s="23" t="inlineStr">
         <is>
-          <t>/staff-status-history</t>
-        </is>
-      </c>
-      <c r="H77" s="19" t="n"/>
-      <c r="I77" s="20" t="n"/>
-      <c r="J77" s="20" t="n"/>
+          <t>/teachers</t>
+        </is>
+      </c>
+      <c r="H77" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I77" s="20" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="J77" s="20" t="inlineStr">
+        <is>
+          <t>ឯកសារ</t>
+        </is>
+      </c>
       <c r="K77" s="24" t="n"/>
     </row>
     <row r="78" ht="21.6" customHeight="1">
@@ -5076,49 +5086,39 @@
       <c r="C78" s="20" t="n"/>
       <c r="D78" s="21" t="inlineStr">
         <is>
-          <t>B6.4</t>
+          <t>B6.3</t>
         </is>
       </c>
       <c r="E78" s="22" t="inlineStr">
         <is>
-          <t>Organization Management</t>
+          <t>Staff Status History</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងអង្គភាព</t>
+          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
         <is>
-          <t>/organization</t>
-        </is>
-      </c>
-      <c r="H78" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" s="20" t="inlineStr">
-        <is>
-          <t>School</t>
-        </is>
-      </c>
-      <c r="J78" s="20" t="inlineStr">
-        <is>
-          <t>សាលា</t>
-        </is>
-      </c>
+          <t>/staff-status-history</t>
+        </is>
+      </c>
+      <c r="H78" s="19" t="n"/>
+      <c r="I78" s="20" t="n"/>
+      <c r="J78" s="20" t="n"/>
       <c r="K78" s="24" t="n"/>
     </row>
     <row r="79" ht="21.6" customHeight="1">
       <c r="A79" s="19" t="n"/>
       <c r="B79" s="20" t="n"/>
       <c r="C79" s="20" t="n"/>
-      <c r="D79" s="19" t="inlineStr">
+      <c r="D79" s="21" t="inlineStr">
         <is>
           <t>B6.4</t>
         </is>
       </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="E79" s="22" t="inlineStr">
         <is>
           <t>Organization Management</t>
         </is>
@@ -5134,16 +5134,16 @@
         </is>
       </c>
       <c r="H79" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>School</t>
         </is>
       </c>
       <c r="J79" s="20" t="inlineStr">
         <is>
-          <t>សាខា</t>
+          <t>សាលា</t>
         </is>
       </c>
       <c r="K79" s="24" t="n"/>
@@ -5173,16 +5173,16 @@
         </is>
       </c>
       <c r="H80" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="J80" s="20" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>សាខា</t>
         </is>
       </c>
       <c r="K80" s="24" t="n"/>
@@ -5212,16 +5212,16 @@
         </is>
       </c>
       <c r="H81" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
-          <t>ក្រុម</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="K81" s="24" t="n"/>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="H82" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="J82" s="20" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>ក្រុម</t>
         </is>
       </c>
       <c r="K82" s="24" t="n"/>
@@ -5290,16 +5290,16 @@
         </is>
       </c>
       <c r="H83" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Job grade</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
-          <t>ថ្នាក់ការងារ</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="K83" s="24" t="n"/>
@@ -5329,16 +5329,16 @@
         </is>
       </c>
       <c r="H84" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>Job level</t>
+          <t>Job grade</t>
         </is>
       </c>
       <c r="J84" s="20" t="inlineStr">
         <is>
-          <t>កម្រិតការងារ</t>
+          <t>ថ្នាក់ការងារ</t>
         </is>
       </c>
       <c r="K84" s="24" t="n"/>
@@ -5368,16 +5368,16 @@
         </is>
       </c>
       <c r="H85" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Reporting manager</t>
+          <t>Job level</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
+          <t>កម្រិតការងារ</t>
         </is>
       </c>
       <c r="K85" s="24" t="n"/>
@@ -5407,16 +5407,16 @@
         </is>
       </c>
       <c r="H86" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Organization hierarchy</t>
+          <t>Reporting manager</t>
         </is>
       </c>
       <c r="J86" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
+          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
         </is>
       </c>
       <c r="K86" s="24" t="n"/>
@@ -5425,37 +5425,37 @@
       <c r="A87" s="19" t="n"/>
       <c r="B87" s="20" t="n"/>
       <c r="C87" s="20" t="n"/>
-      <c r="D87" s="21" t="inlineStr">
-        <is>
-          <t>B6.5</t>
-        </is>
-      </c>
-      <c r="E87" s="22" t="inlineStr">
-        <is>
-          <t>Recruitment</t>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>B6.4</t>
+        </is>
+      </c>
+      <c r="E87" s="20" t="inlineStr">
+        <is>
+          <t>Organization Management</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបុគ្គលិក</t>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
         </is>
       </c>
       <c r="G87" s="23" t="inlineStr">
         <is>
-          <t>/recruitment</t>
+          <t>/organization</t>
         </is>
       </c>
       <c r="H87" s="19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Manpower request</t>
+          <t>Organization hierarchy</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>សំណើបុគ្គលិក</t>
+          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
         </is>
       </c>
       <c r="K87" s="24" t="n"/>
@@ -5464,12 +5464,12 @@
       <c r="A88" s="19" t="n"/>
       <c r="B88" s="20" t="n"/>
       <c r="C88" s="20" t="n"/>
-      <c r="D88" s="19" t="inlineStr">
+      <c r="D88" s="21" t="inlineStr">
         <is>
           <t>B6.5</t>
         </is>
       </c>
-      <c r="E88" s="20" t="inlineStr">
+      <c r="E88" s="22" t="inlineStr">
         <is>
           <t>Recruitment</t>
         </is>
@@ -5485,16 +5485,16 @@
         </is>
       </c>
       <c r="H88" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>Job positions</t>
+          <t>Manpower request</t>
         </is>
       </c>
       <c r="J88" s="20" t="inlineStr">
         <is>
-          <t>មុខតំណែងការងារ</t>
+          <t>សំណើបុគ្គលិក</t>
         </is>
       </c>
       <c r="K88" s="24" t="n"/>
@@ -5524,16 +5524,16 @@
         </is>
       </c>
       <c r="H89" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Job postings</t>
+          <t>Job positions</t>
         </is>
       </c>
       <c r="J89" s="20" t="inlineStr">
         <is>
-          <t>ការផ្សព្វផ្សាយការងារ</t>
+          <t>មុខតំណែងការងារ</t>
         </is>
       </c>
       <c r="K89" s="24" t="n"/>
@@ -5563,16 +5563,16 @@
         </is>
       </c>
       <c r="H90" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Applicant management</t>
+          <t>Job postings</t>
         </is>
       </c>
       <c r="J90" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងបេក្ខជន</t>
+          <t>ការផ្សព្វផ្សាយការងារ</t>
         </is>
       </c>
       <c r="K90" s="24" t="n"/>
@@ -5602,16 +5602,16 @@
         </is>
       </c>
       <c r="H91" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>CV/resume</t>
+          <t>Applicant management</t>
         </is>
       </c>
       <c r="J91" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិរូប (CV)</t>
+          <t>គ្រប់គ្រងបេក្ខជន</t>
         </is>
       </c>
       <c r="K91" s="24" t="n"/>
@@ -5641,16 +5641,16 @@
         </is>
       </c>
       <c r="H92" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>CV/resume</t>
         </is>
       </c>
       <c r="J92" s="20" t="inlineStr">
         <is>
-          <t>សម្ភាសន៍</t>
+          <t>ប្រវត្តិរូប (CV)</t>
         </is>
       </c>
       <c r="K92" s="24" t="n"/>
@@ -5680,16 +5680,16 @@
         </is>
       </c>
       <c r="H93" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I93" s="20" t="inlineStr">
         <is>
-          <t>Interview evaluation</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J93" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃសម្ភាសន៍</t>
+          <t>សម្ភាសន៍</t>
         </is>
       </c>
       <c r="K93" s="24" t="n"/>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="H94" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
-          <t>Candidate selection</t>
+          <t>Interview evaluation</t>
         </is>
       </c>
       <c r="J94" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបេក្ខជន</t>
+          <t>ការវាយតម្លៃសម្ភាសន៍</t>
         </is>
       </c>
       <c r="K94" s="24" t="n"/>
@@ -5758,16 +5758,16 @@
         </is>
       </c>
       <c r="H95" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I95" s="20" t="inlineStr">
         <is>
-          <t>Offer letter</t>
+          <t>Candidate selection</t>
         </is>
       </c>
       <c r="J95" s="20" t="inlineStr">
         <is>
-          <t>លិខិតផ្តល់ការងារ</t>
+          <t>ការជ្រើសរើសបេក្ខជន</t>
         </is>
       </c>
       <c r="K95" s="24" t="n"/>
@@ -5797,16 +5797,16 @@
         </is>
       </c>
       <c r="H96" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
-          <t>Recruitment pipeline</t>
+          <t>Offer letter</t>
         </is>
       </c>
       <c r="J96" s="20" t="inlineStr">
         <is>
-          <t>ដំណើរការជ្រើសរើស</t>
+          <t>លិខិតផ្តល់ការងារ</t>
         </is>
       </c>
       <c r="K96" s="24" t="n"/>
@@ -5815,37 +5815,37 @@
       <c r="A97" s="19" t="n"/>
       <c r="B97" s="20" t="n"/>
       <c r="C97" s="20" t="n"/>
-      <c r="D97" s="21" t="inlineStr">
-        <is>
-          <t>B6.6</t>
-        </is>
-      </c>
-      <c r="E97" s="22" t="inlineStr">
-        <is>
-          <t>Attendance &amp; Time</t>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>B6.5</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
         <is>
-          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+          <t>ការជ្រើសរើសបុគ្គលិក</t>
         </is>
       </c>
       <c r="G97" s="23" t="inlineStr">
         <is>
-          <t>/time-attendance</t>
+          <t>/recruitment</t>
         </is>
       </c>
       <c r="H97" s="19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>Employee attendance</t>
+          <t>Recruitment pipeline</t>
         </is>
       </c>
       <c r="J97" s="20" t="inlineStr">
         <is>
-          <t>វត្តមានបុគ្គលិក</t>
+          <t>ដំណើរការជ្រើសរើស</t>
         </is>
       </c>
       <c r="K97" s="24" t="n"/>
@@ -5854,12 +5854,12 @@
       <c r="A98" s="19" t="n"/>
       <c r="B98" s="20" t="n"/>
       <c r="C98" s="20" t="n"/>
-      <c r="D98" s="19" t="inlineStr">
+      <c r="D98" s="21" t="inlineStr">
         <is>
           <t>B6.6</t>
         </is>
       </c>
-      <c r="E98" s="20" t="inlineStr">
+      <c r="E98" s="22" t="inlineStr">
         <is>
           <t>Attendance &amp; Time</t>
         </is>
@@ -5875,16 +5875,16 @@
         </is>
       </c>
       <c r="H98" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
-          <t>Check-in / check-out</t>
+          <t>Employee attendance</t>
         </is>
       </c>
       <c r="J98" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>វត្តមានបុគ្គលិក</t>
         </is>
       </c>
       <c r="K98" s="24" t="n"/>
@@ -5914,16 +5914,16 @@
         </is>
       </c>
       <c r="H99" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I99" s="20" t="inlineStr">
         <is>
-          <t>Late</t>
+          <t>Check-in / check-out</t>
         </is>
       </c>
       <c r="J99" s="20" t="inlineStr">
         <is>
-          <t>មកយឺត</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="K99" s="24" t="n"/>
@@ -5953,16 +5953,16 @@
         </is>
       </c>
       <c r="H100" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
-          <t>Early leave</t>
+          <t>Late</t>
         </is>
       </c>
       <c r="J100" s="20" t="inlineStr">
         <is>
-          <t>ចេញមុន</t>
+          <t>មកយឺត</t>
         </is>
       </c>
       <c r="K100" s="24" t="n"/>
@@ -5992,16 +5992,16 @@
         </is>
       </c>
       <c r="H101" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I101" s="20" t="inlineStr">
         <is>
-          <t>Absence</t>
+          <t>Early leave</t>
         </is>
       </c>
       <c r="J101" s="20" t="inlineStr">
         <is>
-          <t>អវត្តមាន</t>
+          <t>ចេញមុន</t>
         </is>
       </c>
       <c r="K101" s="24" t="n"/>
@@ -6031,16 +6031,16 @@
         </is>
       </c>
       <c r="H102" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Absence</t>
         </is>
       </c>
       <c r="J102" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>អវត្តមាន</t>
         </is>
       </c>
       <c r="K102" s="24" t="n"/>
@@ -6070,16 +6070,16 @@
         </is>
       </c>
       <c r="H103" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
         <is>
-          <t>វេនការងារ</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="K103" s="24" t="n"/>
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="H104" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
-          <t>Staff shift</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="J104" s="20" t="inlineStr">
         <is>
-          <t>វេនបុគ្គលិក</t>
+          <t>វេនការងារ</t>
         </is>
       </c>
       <c r="K104" s="24" t="n"/>
@@ -6148,16 +6148,16 @@
         </is>
       </c>
       <c r="H105" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I105" s="20" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Staff shift</t>
         </is>
       </c>
       <c r="J105" s="20" t="inlineStr">
         <is>
-          <t>ថ្ងៃឈប់សម្រាក</t>
+          <t>វេនបុគ្គលិក</t>
         </is>
       </c>
       <c r="K105" s="24" t="n"/>
@@ -6187,16 +6187,16 @@
         </is>
       </c>
       <c r="H106" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
-          <t>Attendance correction</t>
+          <t>Holidays</t>
         </is>
       </c>
       <c r="J106" s="20" t="inlineStr">
         <is>
-          <t>ការកែវត្តមាន</t>
+          <t>ថ្ងៃឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K106" s="24" t="n"/>
@@ -6226,16 +6226,16 @@
         </is>
       </c>
       <c r="H107" s="19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>Attendance approval</t>
+          <t>Attendance correction</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តវត្តមាន</t>
+          <t>ការកែវត្តមាន</t>
         </is>
       </c>
       <c r="K107" s="24" t="n"/>
@@ -6244,37 +6244,37 @@
       <c r="A108" s="19" t="n"/>
       <c r="B108" s="20" t="n"/>
       <c r="C108" s="20" t="n"/>
-      <c r="D108" s="21" t="inlineStr">
-        <is>
-          <t>B6.7</t>
-        </is>
-      </c>
-      <c r="E108" s="22" t="inlineStr">
-        <is>
-          <t>Leave Management</t>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>B6.6</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Attendance &amp; Time</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
         <is>
-          <t>/leave-management</t>
+          <t>/time-attendance</t>
         </is>
       </c>
       <c r="H108" s="19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
-          <t>Leave types</t>
+          <t>Attendance approval</t>
         </is>
       </c>
       <c r="J108" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
+          <t>ការអនុម័តវត្តមាន</t>
         </is>
       </c>
       <c r="K108" s="24" t="n"/>
@@ -6283,12 +6283,12 @@
       <c r="A109" s="19" t="n"/>
       <c r="B109" s="20" t="n"/>
       <c r="C109" s="20" t="n"/>
-      <c r="D109" s="19" t="inlineStr">
+      <c r="D109" s="21" t="inlineStr">
         <is>
           <t>B6.7</t>
         </is>
       </c>
-      <c r="E109" s="20" t="inlineStr">
+      <c r="E109" s="22" t="inlineStr">
         <is>
           <t>Leave Management</t>
         </is>
@@ -6304,16 +6304,16 @@
         </is>
       </c>
       <c r="H109" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I109" s="20" t="inlineStr">
         <is>
-          <t>Leave policies</t>
+          <t>Leave types</t>
         </is>
       </c>
       <c r="J109" s="20" t="inlineStr">
         <is>
-          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
+          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K109" s="24" t="n"/>
@@ -6343,16 +6343,16 @@
         </is>
       </c>
       <c r="H110" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
-          <t>Leave balance</t>
+          <t>Leave policies</t>
         </is>
       </c>
       <c r="J110" s="20" t="inlineStr">
         <is>
-          <t>សមតុល្យច្បាប់</t>
+          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K110" s="24" t="n"/>
@@ -6382,16 +6382,16 @@
         </is>
       </c>
       <c r="H111" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I111" s="20" t="inlineStr">
         <is>
-          <t>Leave request</t>
+          <t>Leave balance</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
         <is>
-          <t>សំណើច្បាប់ឈប់សម្រាក</t>
+          <t>សមតុល្យច្បាប់</t>
         </is>
       </c>
       <c r="K111" s="24" t="n"/>
@@ -6421,16 +6421,16 @@
         </is>
       </c>
       <c r="H112" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
-          <t>Approval workflow</t>
+          <t>Leave request</t>
         </is>
       </c>
       <c r="J112" s="20" t="inlineStr">
         <is>
-          <t>លំហូរការអនុម័ត</t>
+          <t>សំណើច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K112" s="24" t="n"/>
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="H113" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>Leave calendar</t>
+          <t>Approval workflow</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិទិនច្បាប់</t>
+          <t>លំហូរការអនុម័ត</t>
         </is>
       </c>
       <c r="K113" s="24" t="n"/>
@@ -6499,16 +6499,16 @@
         </is>
       </c>
       <c r="H114" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
-          <t>Carry forward</t>
+          <t>Leave calendar</t>
         </is>
       </c>
       <c r="J114" s="20" t="inlineStr">
         <is>
-          <t>យោងទៅឆ្នាំបន្ទាប់</t>
+          <t>ប្រតិទិនច្បាប់</t>
         </is>
       </c>
       <c r="K114" s="24" t="n"/>
@@ -6538,16 +6538,16 @@
         </is>
       </c>
       <c r="H115" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>Leave reports</t>
+          <t>Carry forward</t>
         </is>
       </c>
       <c r="J115" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ច្បាប់</t>
+          <t>យោងទៅឆ្នាំបន្ទាប់</t>
         </is>
       </c>
       <c r="K115" s="24" t="n"/>
@@ -6556,37 +6556,37 @@
       <c r="A116" s="19" t="n"/>
       <c r="B116" s="20" t="n"/>
       <c r="C116" s="20" t="n"/>
-      <c r="D116" s="21" t="inlineStr">
-        <is>
-          <t>B6.8</t>
-        </is>
-      </c>
-      <c r="E116" s="22" t="inlineStr">
-        <is>
-          <t>Payroll</t>
+      <c r="D116" s="19" t="inlineStr">
+        <is>
+          <t>B6.7</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>Leave Management</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
         <is>
-          <t>បញ្ជីប្រាក់ខែ</t>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
         <is>
-          <t>/payroll</t>
+          <t>/leave-management</t>
         </is>
       </c>
       <c r="H116" s="19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
-          <t>Salary structure</t>
+          <t>Leave reports</t>
         </is>
       </c>
       <c r="J116" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធប្រាក់ខែ</t>
+          <t>របាយការណ៍ច្បាប់</t>
         </is>
       </c>
       <c r="K116" s="24" t="n"/>
@@ -6595,12 +6595,12 @@
       <c r="A117" s="19" t="n"/>
       <c r="B117" s="20" t="n"/>
       <c r="C117" s="20" t="n"/>
-      <c r="D117" s="19" t="inlineStr">
+      <c r="D117" s="21" t="inlineStr">
         <is>
           <t>B6.8</t>
         </is>
       </c>
-      <c r="E117" s="20" t="inlineStr">
+      <c r="E117" s="22" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
@@ -6616,16 +6616,16 @@
         </is>
       </c>
       <c r="H117" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I117" s="20" t="inlineStr">
         <is>
-          <t>Basic salary</t>
+          <t>Salary structure</t>
         </is>
       </c>
       <c r="J117" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ខែគោល</t>
+          <t>រចនាសម្ព័ន្ធប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K117" s="24" t="n"/>
@@ -6655,16 +6655,16 @@
         </is>
       </c>
       <c r="H118" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I118" s="20" t="inlineStr">
         <is>
-          <t>Allowances</t>
+          <t>Basic salary</t>
         </is>
       </c>
       <c r="J118" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ឧបត្ថម្ភ</t>
+          <t>ប្រាក់ខែគោល</t>
         </is>
       </c>
       <c r="K118" s="24" t="n"/>
@@ -6694,16 +6694,16 @@
         </is>
       </c>
       <c r="H119" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
-          <t>Bonuses</t>
+          <t>Allowances</t>
         </is>
       </c>
       <c r="J119" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់រង្វាន់</t>
+          <t>ប្រាក់ឧបត្ថម្ភ</t>
         </is>
       </c>
       <c r="K119" s="24" t="n"/>
@@ -6733,16 +6733,16 @@
         </is>
       </c>
       <c r="H120" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I120" s="20" t="inlineStr">
         <is>
-          <t>Deductions</t>
+          <t>Bonuses</t>
         </is>
       </c>
       <c r="J120" s="20" t="inlineStr">
         <is>
-          <t>ការកាត់ប្រាក់</t>
+          <t>ប្រាក់រង្វាន់</t>
         </is>
       </c>
       <c r="K120" s="24" t="n"/>
@@ -6772,16 +6772,16 @@
         </is>
       </c>
       <c r="H121" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I121" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Deductions</t>
         </is>
       </c>
       <c r="J121" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>ការកាត់ប្រាក់</t>
         </is>
       </c>
       <c r="K121" s="24" t="n"/>
@@ -6811,16 +6811,16 @@
         </is>
       </c>
       <c r="H122" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I122" s="20" t="inlineStr">
         <is>
-          <t>Attendance deduction</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="J122" s="20" t="inlineStr">
         <is>
-          <t>ការកាត់ប្រាក់តាមវត្តមាន</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="K122" s="24" t="n"/>
@@ -6850,16 +6850,16 @@
         </is>
       </c>
       <c r="H123" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I123" s="20" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Attendance deduction</t>
         </is>
       </c>
       <c r="J123" s="20" t="inlineStr">
         <is>
-          <t>ពន្ធ</t>
+          <t>ការកាត់ប្រាក់តាមវត្តមាន</t>
         </is>
       </c>
       <c r="K123" s="24" t="n"/>
@@ -6889,16 +6889,16 @@
         </is>
       </c>
       <c r="H124" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I124" s="20" t="inlineStr">
         <is>
-          <t>Social security</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="J124" s="20" t="inlineStr">
         <is>
-          <t>សន្តិសុខសង្គម</t>
+          <t>ពន្ធ</t>
         </is>
       </c>
       <c r="K124" s="24" t="n"/>
@@ -6928,16 +6928,16 @@
         </is>
       </c>
       <c r="H125" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I125" s="20" t="inlineStr">
         <is>
-          <t>Loan/advance</t>
+          <t>Social security</t>
         </is>
       </c>
       <c r="J125" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់កម្ចី/ប្រាក់បុរេប្រទាន</t>
+          <t>សន្តិសុខសង្គម</t>
         </is>
       </c>
       <c r="K125" s="24" t="n"/>
@@ -6967,16 +6967,16 @@
         </is>
       </c>
       <c r="H126" s="19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
-          <t>Payroll calculation</t>
+          <t>Loan/advance</t>
         </is>
       </c>
       <c r="J126" s="20" t="inlineStr">
         <is>
-          <t>ការគណនាប្រាក់ខែ</t>
+          <t>ប្រាក់កម្ចី/ប្រាក់បុរេប្រទាន</t>
         </is>
       </c>
       <c r="K126" s="24" t="n"/>
@@ -7006,16 +7006,16 @@
         </is>
       </c>
       <c r="H127" s="19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I127" s="20" t="inlineStr">
         <is>
-          <t>Payslip</t>
+          <t>Payroll calculation</t>
         </is>
       </c>
       <c r="J127" s="20" t="inlineStr">
         <is>
-          <t>បង្កាន់ដៃប្រាក់ខែ</t>
+          <t>ការគណនាប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K127" s="24" t="n"/>
@@ -7045,16 +7045,16 @@
         </is>
       </c>
       <c r="H128" s="19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I128" s="20" t="inlineStr">
         <is>
-          <t>Payroll approval</t>
+          <t>Payslip</t>
         </is>
       </c>
       <c r="J128" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តប្រាក់ខែ</t>
+          <t>បង្កាន់ដៃប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K128" s="24" t="n"/>
@@ -7084,16 +7084,16 @@
         </is>
       </c>
       <c r="H129" s="19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I129" s="20" t="inlineStr">
         <is>
-          <t>Payroll history</t>
+          <t>Payroll approval</t>
         </is>
       </c>
       <c r="J129" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិប្រាក់ខែ</t>
+          <t>ការអនុម័តប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K129" s="24" t="n"/>
@@ -7102,47 +7102,51 @@
       <c r="A130" s="19" t="n"/>
       <c r="B130" s="20" t="n"/>
       <c r="C130" s="20" t="n"/>
-      <c r="D130" s="21" t="inlineStr">
-        <is>
-          <t>B6.9</t>
-        </is>
-      </c>
-      <c r="E130" s="22" t="inlineStr">
-        <is>
-          <t>Performance Management</t>
+      <c r="D130" s="19" t="inlineStr">
+        <is>
+          <t>B6.8</t>
+        </is>
+      </c>
+      <c r="E130" s="20" t="inlineStr">
+        <is>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងការងារ</t>
+          <t>បញ្ជីប្រាក់ខែ</t>
         </is>
       </c>
       <c r="G130" s="23" t="inlineStr">
         <is>
-          <t>/performance</t>
+          <t>/payroll</t>
         </is>
       </c>
       <c r="H130" s="19" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I130" s="20" t="inlineStr">
         <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="J130" s="20" t="n"/>
+          <t>Payroll history</t>
+        </is>
+      </c>
+      <c r="J130" s="20" t="inlineStr">
+        <is>
+          <t>ប្រវត្តិប្រាក់ខែ</t>
+        </is>
+      </c>
       <c r="K130" s="24" t="n"/>
     </row>
     <row r="131" ht="21.6" customHeight="1">
       <c r="A131" s="19" t="n"/>
       <c r="B131" s="20" t="n"/>
       <c r="C131" s="20" t="n"/>
-      <c r="D131" s="19" t="inlineStr">
+      <c r="D131" s="21" t="inlineStr">
         <is>
           <t>B6.9</t>
         </is>
       </c>
-      <c r="E131" s="20" t="inlineStr">
+      <c r="E131" s="22" t="inlineStr">
         <is>
           <t>Performance Management</t>
         </is>
@@ -7158,18 +7162,14 @@
         </is>
       </c>
       <c r="H131" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I131" s="20" t="inlineStr">
         <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="J131" s="20" t="inlineStr">
-        <is>
-          <t>គោលដៅ</t>
-        </is>
-      </c>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="J131" s="20" t="n"/>
       <c r="K131" s="24" t="n"/>
     </row>
     <row r="132" ht="21.6" customHeight="1">
@@ -7197,16 +7197,16 @@
         </is>
       </c>
       <c r="H132" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I132" s="20" t="inlineStr">
         <is>
-          <t>Performance review</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="J132" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃការងារ</t>
+          <t>គោលដៅ</t>
         </is>
       </c>
       <c r="K132" s="24" t="n"/>
@@ -7236,16 +7236,16 @@
         </is>
       </c>
       <c r="H133" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I133" s="20" t="inlineStr">
         <is>
-          <t>Evaluation forms</t>
+          <t>Performance review</t>
         </is>
       </c>
       <c r="J133" s="20" t="inlineStr">
         <is>
-          <t>ទម្រង់វាយតម្លៃ</t>
+          <t>ការវាយតម្លៃការងារ</t>
         </is>
       </c>
       <c r="K133" s="24" t="n"/>
@@ -7275,16 +7275,16 @@
         </is>
       </c>
       <c r="H134" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I134" s="20" t="inlineStr">
         <is>
-          <t>Employee self-assessment</t>
+          <t>Evaluation forms</t>
         </is>
       </c>
       <c r="J134" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃខ្លួនឯង</t>
+          <t>ទម្រង់វាយតម្លៃ</t>
         </is>
       </c>
       <c r="K134" s="24" t="n"/>
@@ -7314,16 +7314,16 @@
         </is>
       </c>
       <c r="H135" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I135" s="20" t="inlineStr">
         <is>
-          <t>Manager assessment</t>
+          <t>Employee self-assessment</t>
         </is>
       </c>
       <c r="J135" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃដោយអ្នកគ្រប់គ្រង</t>
+          <t>ការវាយតម្លៃខ្លួនឯង</t>
         </is>
       </c>
       <c r="K135" s="24" t="n"/>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="H136" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I136" s="20" t="inlineStr">
         <is>
-          <t>Performance score</t>
+          <t>Manager assessment</t>
         </is>
       </c>
       <c r="J136" s="20" t="inlineStr">
         <is>
-          <t>ពិន្ទុការងារ</t>
+          <t>ការវាយតម្លៃដោយអ្នកគ្រប់គ្រង</t>
         </is>
       </c>
       <c r="K136" s="24" t="n"/>
@@ -7392,16 +7392,16 @@
         </is>
       </c>
       <c r="H137" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I137" s="20" t="inlineStr">
         <is>
-          <t>Promotion recommendation</t>
+          <t>Performance score</t>
         </is>
       </c>
       <c r="J137" s="20" t="inlineStr">
         <is>
-          <t>ការណែនាំដំឡើងតំណែង</t>
+          <t>ពិន្ទុការងារ</t>
         </is>
       </c>
       <c r="K137" s="24" t="n"/>
@@ -7410,29 +7410,39 @@
       <c r="A138" s="19" t="n"/>
       <c r="B138" s="20" t="n"/>
       <c r="C138" s="20" t="n"/>
-      <c r="D138" s="21" t="inlineStr">
-        <is>
-          <t>B6.10</t>
-        </is>
-      </c>
-      <c r="E138" s="22" t="inlineStr">
-        <is>
-          <t>Check in / Check out</t>
+      <c r="D138" s="19" t="inlineStr">
+        <is>
+          <t>B6.9</t>
+        </is>
+      </c>
+      <c r="E138" s="20" t="inlineStr">
+        <is>
+          <t>Performance Management</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>ការគ្រប់គ្រងការងារ</t>
         </is>
       </c>
       <c r="G138" s="23" t="inlineStr">
         <is>
-          <t>/my-check-in</t>
-        </is>
-      </c>
-      <c r="H138" s="19" t="n"/>
-      <c r="I138" s="20" t="n"/>
-      <c r="J138" s="20" t="n"/>
+          <t>/performance</t>
+        </is>
+      </c>
+      <c r="H138" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I138" s="20" t="inlineStr">
+        <is>
+          <t>Promotion recommendation</t>
+        </is>
+      </c>
+      <c r="J138" s="20" t="inlineStr">
+        <is>
+          <t>ការណែនាំដំឡើងតំណែង</t>
+        </is>
+      </c>
       <c r="K138" s="24" t="n"/>
     </row>
     <row r="139" ht="21.6" customHeight="1">
@@ -7441,49 +7451,39 @@
       <c r="C139" s="20" t="n"/>
       <c r="D139" s="21" t="inlineStr">
         <is>
-          <t>B6.11</t>
+          <t>B6.10</t>
         </is>
       </c>
       <c r="E139" s="22" t="inlineStr">
         <is>
-          <t>Request Leave</t>
+          <t>Check in / Check out</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
-          <t>ស្នើសុំច្បាប់</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H139" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I139" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J139" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
+          <t>/my-check-in</t>
+        </is>
+      </c>
+      <c r="H139" s="19" t="n"/>
+      <c r="I139" s="20" t="n"/>
+      <c r="J139" s="20" t="n"/>
       <c r="K139" s="24" t="n"/>
     </row>
     <row r="140" ht="21.6" customHeight="1">
       <c r="A140" s="19" t="n"/>
       <c r="B140" s="20" t="n"/>
       <c r="C140" s="20" t="n"/>
-      <c r="D140" s="19" t="inlineStr">
+      <c r="D140" s="21" t="inlineStr">
         <is>
           <t>B6.11</t>
         </is>
       </c>
-      <c r="E140" s="20" t="inlineStr">
+      <c r="E140" s="22" t="inlineStr">
         <is>
           <t>Request Leave</t>
         </is>
@@ -7499,16 +7499,16 @@
         </is>
       </c>
       <c r="H140" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I140" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J140" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="K140" s="24" t="n"/>
@@ -7538,16 +7538,16 @@
         </is>
       </c>
       <c r="H141" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I141" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J141" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K141" s="24" t="n"/>
@@ -7577,16 +7577,16 @@
         </is>
       </c>
       <c r="H142" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I142" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J142" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K142" s="24" t="n"/>
@@ -7616,16 +7616,16 @@
         </is>
       </c>
       <c r="H143" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I143" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="J143" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="K143" s="24" t="n"/>
@@ -7634,104 +7634,114 @@
       <c r="A144" s="19" t="n"/>
       <c r="B144" s="20" t="n"/>
       <c r="C144" s="20" t="n"/>
-      <c r="D144" s="21" t="inlineStr">
+      <c r="D144" s="19" t="inlineStr">
+        <is>
+          <t>B6.11</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="F144" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="G144" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="H144" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I144" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="J144" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="K144" s="24" t="n"/>
+    </row>
+    <row r="145" ht="21.6" customHeight="1">
+      <c r="A145" s="19" t="n"/>
+      <c r="B145" s="20" t="n"/>
+      <c r="C145" s="20" t="n"/>
+      <c r="D145" s="21" t="inlineStr">
         <is>
           <t>B6.12</t>
         </is>
       </c>
-      <c r="E144" s="22" t="inlineStr">
+      <c r="E145" s="22" t="inlineStr">
         <is>
           <t>Form</t>
         </is>
       </c>
-      <c r="F144" s="20" t="inlineStr">
+      <c r="F145" s="20" t="inlineStr">
         <is>
           <t>ទម្រង់</t>
         </is>
       </c>
-      <c r="G144" s="23" t="inlineStr">
+      <c r="G145" s="23" t="inlineStr">
         <is>
           <t>/approvals/my-requests?tab=resignation</t>
         </is>
       </c>
-      <c r="H144" s="19" t="n"/>
-      <c r="I144" s="20" t="n"/>
-      <c r="J144" s="20" t="n"/>
-      <c r="K144" s="24" t="inlineStr">
+      <c r="H145" s="19" t="n"/>
+      <c r="I145" s="20" t="n"/>
+      <c r="J145" s="20" t="n"/>
+      <c r="K145" s="24" t="inlineStr">
         <is>
           <t>Resignation form</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="21.6" customHeight="1">
-      <c r="A145" s="1" t="inlineStr">
+    <row r="146" ht="21.6" customHeight="1">
+      <c r="A146" s="1" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>វិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="D145" s="1" t="inlineStr">
+      <c r="D146" s="1" t="inlineStr">
         <is>
           <t>B7.1</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Billing Dashboard</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងវិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="G145" s="4" t="inlineStr">
+      <c r="G146" s="4" t="inlineStr">
         <is>
           <t>/billing</t>
         </is>
       </c>
-      <c r="H145" s="5" t="n"/>
-      <c r="I145" s="3" t="n"/>
-      <c r="J145" s="3" t="n"/>
-      <c r="K145" s="6" t="n"/>
-    </row>
-    <row r="146" ht="21.6" customHeight="1">
-      <c r="A146" s="7" t="n"/>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="8" t="n"/>
-      <c r="D146" s="9" t="inlineStr">
-        <is>
-          <t>B7.2</t>
-        </is>
-      </c>
-      <c r="E146" s="10" t="inlineStr">
-        <is>
-          <t>Products</t>
-        </is>
-      </c>
-      <c r="F146" s="8" t="inlineStr">
-        <is>
-          <t>ផលិតផល</t>
-        </is>
-      </c>
-      <c r="G146" s="11" t="inlineStr">
-        <is>
-          <t>/products</t>
-        </is>
-      </c>
-      <c r="H146" s="7" t="n"/>
-      <c r="I146" s="8" t="n"/>
-      <c r="J146" s="8" t="n"/>
-      <c r="K146" s="12" t="n"/>
+      <c r="H146" s="5" t="n"/>
+      <c r="I146" s="3" t="n"/>
+      <c r="J146" s="3" t="n"/>
+      <c r="K146" s="6" t="n"/>
     </row>
     <row r="147" ht="21.6" customHeight="1">
       <c r="A147" s="7" t="n"/>
@@ -7739,49 +7749,39 @@
       <c r="C147" s="8" t="n"/>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>B7.3</t>
+          <t>B7.2</t>
         </is>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>វិក្កយបត្រ</t>
+          <t>ផលិតផល</t>
         </is>
       </c>
       <c r="G147" s="11" t="inlineStr">
         <is>
-          <t>/invoices</t>
-        </is>
-      </c>
-      <c r="H147" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I147" s="8" t="inlineStr">
-        <is>
-          <t>Invoices</t>
-        </is>
-      </c>
-      <c r="J147" s="8" t="inlineStr">
-        <is>
-          <t>វិក្កយបត្រ</t>
-        </is>
-      </c>
+          <t>/products</t>
+        </is>
+      </c>
+      <c r="H147" s="7" t="n"/>
+      <c r="I147" s="8" t="n"/>
+      <c r="J147" s="8" t="n"/>
       <c r="K147" s="12" t="n"/>
     </row>
     <row r="148" ht="21.6" customHeight="1">
       <c r="A148" s="7" t="n"/>
       <c r="B148" s="8" t="n"/>
       <c r="C148" s="8" t="n"/>
-      <c r="D148" s="7" t="inlineStr">
+      <c r="D148" s="9" t="inlineStr">
         <is>
           <t>B7.3</t>
         </is>
       </c>
-      <c r="E148" s="8" t="inlineStr">
+      <c r="E148" s="10" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
@@ -7797,16 +7797,16 @@
         </is>
       </c>
       <c r="H148" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I148" s="8" t="inlineStr">
         <is>
-          <t>Monthly Invoice</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>វិក្កយបត្រប្រចាំខែ</t>
+          <t>វិក្កយបត្រ</t>
         </is>
       </c>
       <c r="K148" s="12" t="n"/>
@@ -7815,29 +7815,39 @@
       <c r="A149" s="7" t="n"/>
       <c r="B149" s="8" t="n"/>
       <c r="C149" s="8" t="n"/>
-      <c r="D149" s="9" t="inlineStr">
-        <is>
-          <t>B7.4</t>
-        </is>
-      </c>
-      <c r="E149" s="10" t="inlineStr">
-        <is>
-          <t>Payments</t>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>B7.3</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>ការទូទាត់</t>
+          <t>វិក្កយបត្រ</t>
         </is>
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>/payments</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="n"/>
-      <c r="I149" s="8" t="n"/>
-      <c r="J149" s="8" t="n"/>
+          <t>/invoices</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I149" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Invoice</t>
+        </is>
+      </c>
+      <c r="J149" s="8" t="inlineStr">
+        <is>
+          <t>វិក្កយបត្រប្រចាំខែ</t>
+        </is>
+      </c>
       <c r="K149" s="12" t="n"/>
     </row>
     <row r="150" ht="21.6" customHeight="1">
@@ -7846,22 +7856,22 @@
       <c r="C150" s="8" t="n"/>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>B7.5</t>
+          <t>B7.4</t>
         </is>
       </c>
       <c r="E150" s="10" t="inlineStr">
         <is>
-          <t>Currency Rates</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>អត្រាប្តូរប្រាក់</t>
+          <t>ការទូទាត់</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr">
         <is>
-          <t>/currency-rates</t>
+          <t>/payments</t>
         </is>
       </c>
       <c r="H150" s="7" t="n"/>
@@ -7870,74 +7880,74 @@
       <c r="K150" s="12" t="n"/>
     </row>
     <row r="151" ht="21.6" customHeight="1">
-      <c r="A151" s="13" t="inlineStr">
+      <c r="A151" s="7" t="n"/>
+      <c r="B151" s="8" t="n"/>
+      <c r="C151" s="8" t="n"/>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>B7.5</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>Currency Rates</t>
+        </is>
+      </c>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>អត្រាប្តូរប្រាក់</t>
+        </is>
+      </c>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>/currency-rates</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="n"/>
+      <c r="I151" s="8" t="n"/>
+      <c r="J151" s="8" t="n"/>
+      <c r="K151" s="12" t="n"/>
+    </row>
+    <row r="152" ht="21.6" customHeight="1">
+      <c r="A152" s="13" t="inlineStr">
         <is>
           <t>B8</t>
         </is>
       </c>
-      <c r="B151" s="14" t="inlineStr">
+      <c r="B152" s="14" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="C151" s="15" t="inlineStr">
+      <c r="C152" s="15" t="inlineStr">
         <is>
           <t>គណនេយ្យ</t>
         </is>
       </c>
-      <c r="D151" s="13" t="inlineStr">
+      <c r="D152" s="13" t="inlineStr">
         <is>
           <t>B8.1</t>
         </is>
       </c>
-      <c r="E151" s="14" t="inlineStr">
+      <c r="E152" s="14" t="inlineStr">
         <is>
           <t>Accounting Dashboard</t>
         </is>
       </c>
-      <c r="F151" s="15" t="inlineStr">
+      <c r="F152" s="15" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងគណនេយ្យ</t>
         </is>
       </c>
-      <c r="G151" s="16" t="inlineStr">
+      <c r="G152" s="16" t="inlineStr">
         <is>
           <t>/accounting</t>
         </is>
       </c>
-      <c r="H151" s="17" t="n"/>
-      <c r="I151" s="15" t="n"/>
-      <c r="J151" s="15" t="n"/>
-      <c r="K151" s="18" t="n"/>
-    </row>
-    <row r="152" ht="21.6" customHeight="1">
-      <c r="A152" s="19" t="n"/>
-      <c r="B152" s="20" t="n"/>
-      <c r="C152" s="20" t="n"/>
-      <c r="D152" s="21" t="inlineStr">
-        <is>
-          <t>B8.2</t>
-        </is>
-      </c>
-      <c r="E152" s="22" t="inlineStr">
-        <is>
-          <t>Chart of Accounts</t>
-        </is>
-      </c>
-      <c r="F152" s="20" t="inlineStr">
-        <is>
-          <t>តារាងគណនី</t>
-        </is>
-      </c>
-      <c r="G152" s="23" t="inlineStr">
-        <is>
-          <t>/accounts</t>
-        </is>
-      </c>
-      <c r="H152" s="19" t="n"/>
-      <c r="I152" s="20" t="n"/>
-      <c r="J152" s="20" t="n"/>
-      <c r="K152" s="24" t="n"/>
+      <c r="H152" s="17" t="n"/>
+      <c r="I152" s="15" t="n"/>
+      <c r="J152" s="15" t="n"/>
+      <c r="K152" s="18" t="n"/>
     </row>
     <row r="153" ht="21.6" customHeight="1">
       <c r="A153" s="19" t="n"/>
@@ -7945,22 +7955,22 @@
       <c r="C153" s="20" t="n"/>
       <c r="D153" s="21" t="inlineStr">
         <is>
-          <t>B8.3</t>
+          <t>B8.2</t>
         </is>
       </c>
       <c r="E153" s="22" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Chart of Accounts</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>ចំណូល</t>
+          <t>តារាងគណនី</t>
         </is>
       </c>
       <c r="G153" s="23" t="inlineStr">
         <is>
-          <t>/income</t>
+          <t>/accounts</t>
         </is>
       </c>
       <c r="H153" s="19" t="n"/>
@@ -7974,22 +7984,22 @@
       <c r="C154" s="20" t="n"/>
       <c r="D154" s="21" t="inlineStr">
         <is>
-          <t>B8.4</t>
+          <t>B8.3</t>
         </is>
       </c>
       <c r="E154" s="22" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>ចំណាយ</t>
+          <t>ចំណូល</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
         <is>
-          <t>/expenses</t>
+          <t>/income</t>
         </is>
       </c>
       <c r="H154" s="19" t="n"/>
@@ -8003,22 +8013,22 @@
       <c r="C155" s="20" t="n"/>
       <c r="D155" s="21" t="inlineStr">
         <is>
-          <t>B8.5</t>
+          <t>B8.4</t>
         </is>
       </c>
       <c r="E155" s="22" t="inlineStr">
         <is>
-          <t>Transactions</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិបត្តិការ</t>
+          <t>ចំណាយ</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
         <is>
-          <t>/transactions</t>
+          <t>/expenses</t>
         </is>
       </c>
       <c r="H155" s="19" t="n"/>
@@ -8032,49 +8042,39 @@
       <c r="C156" s="20" t="n"/>
       <c r="D156" s="21" t="inlineStr">
         <is>
-          <t>B8.6</t>
+          <t>B8.5</t>
         </is>
       </c>
       <c r="E156" s="22" t="inlineStr">
         <is>
-          <t>Financial Reports</t>
+          <t>Transactions</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+          <t>ប្រតិបត្តិការ</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
         <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H156" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I156" s="20" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="J156" s="20" t="inlineStr">
-        <is>
-          <t>ចំណូល</t>
-        </is>
-      </c>
+          <t>/transactions</t>
+        </is>
+      </c>
+      <c r="H156" s="19" t="n"/>
+      <c r="I156" s="20" t="n"/>
+      <c r="J156" s="20" t="n"/>
       <c r="K156" s="24" t="n"/>
     </row>
     <row r="157" ht="21.6" customHeight="1">
       <c r="A157" s="19" t="n"/>
       <c r="B157" s="20" t="n"/>
       <c r="C157" s="20" t="n"/>
-      <c r="D157" s="19" t="inlineStr">
+      <c r="D157" s="21" t="inlineStr">
         <is>
           <t>B8.6</t>
         </is>
       </c>
-      <c r="E157" s="20" t="inlineStr">
+      <c r="E157" s="22" t="inlineStr">
         <is>
           <t>Financial Reports</t>
         </is>
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="H157" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I157" s="20" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="J157" s="20" t="inlineStr">
         <is>
-          <t>ចំណាយ</t>
+          <t>ចំណូល</t>
         </is>
       </c>
       <c r="K157" s="24" t="n"/>
@@ -8129,16 +8129,16 @@
         </is>
       </c>
       <c r="H158" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I158" s="20" t="inlineStr">
         <is>
-          <t>Profit &amp; Loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="J158" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ចំណេញ និងខាត</t>
+          <t>ចំណាយ</t>
         </is>
       </c>
       <c r="K158" s="24" t="n"/>
@@ -8168,114 +8168,110 @@
         </is>
       </c>
       <c r="H159" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I159" s="20" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss</t>
+        </is>
+      </c>
+      <c r="J159" s="20" t="inlineStr">
+        <is>
+          <t>ប្រាក់ចំណេញ និងខាត</t>
+        </is>
+      </c>
+      <c r="K159" s="24" t="n"/>
+    </row>
+    <row r="160" ht="21.6" customHeight="1">
+      <c r="A160" s="19" t="n"/>
+      <c r="B160" s="20" t="n"/>
+      <c r="C160" s="20" t="n"/>
+      <c r="D160" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E160" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F160" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G160" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H160" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I159" s="20" t="inlineStr">
+      <c r="I160" s="20" t="inlineStr">
         <is>
           <t>Cash Flow</t>
         </is>
       </c>
-      <c r="J159" s="20" t="inlineStr">
+      <c r="J160" s="20" t="inlineStr">
         <is>
           <t>លំហូរសាច់ប្រាក់</t>
         </is>
       </c>
-      <c r="K159" s="24" t="n"/>
-    </row>
-    <row r="160" ht="21.6" customHeight="1">
-      <c r="A160" s="1" t="inlineStr">
+      <c r="K160" s="24" t="n"/>
+    </row>
+    <row r="161" ht="21.6" customHeight="1">
+      <c r="A161" s="1" t="inlineStr">
         <is>
           <t>B9</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>ទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="D160" s="1" t="inlineStr">
+      <c r="D161" s="1" t="inlineStr">
         <is>
           <t>B9.1</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Asset Dashboard</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="G160" s="4" t="inlineStr">
+      <c r="G161" s="4" t="inlineStr">
         <is>
           <t>/assets/dashboard</t>
         </is>
       </c>
-      <c r="H160" s="5" t="n"/>
-      <c r="I160" s="3" t="n"/>
-      <c r="J160" s="3" t="n"/>
-      <c r="K160" s="6" t="n"/>
-    </row>
-    <row r="161" ht="21.6" customHeight="1">
-      <c r="A161" s="7" t="n"/>
-      <c r="B161" s="8" t="n"/>
-      <c r="C161" s="8" t="n"/>
-      <c r="D161" s="9" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E161" s="10" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F161" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G161" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H161" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I161" s="8" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="J161" s="8" t="inlineStr">
-        <is>
-          <t>ទិដ្ឋភាពទូទៅ</t>
-        </is>
-      </c>
-      <c r="K161" s="12" t="inlineStr">
-        <is>
-          <t>Tabs on one asset</t>
-        </is>
-      </c>
+      <c r="H161" s="5" t="n"/>
+      <c r="I161" s="3" t="n"/>
+      <c r="J161" s="3" t="n"/>
+      <c r="K161" s="6" t="n"/>
     </row>
     <row r="162" ht="21.6" customHeight="1">
       <c r="A162" s="7" t="n"/>
       <c r="B162" s="8" t="n"/>
       <c r="C162" s="8" t="n"/>
-      <c r="D162" s="7" t="inlineStr">
+      <c r="D162" s="9" t="inlineStr">
         <is>
           <t>B9.2</t>
         </is>
       </c>
-      <c r="E162" s="8" t="inlineStr">
+      <c r="E162" s="10" t="inlineStr">
         <is>
           <t>All Assets</t>
         </is>
@@ -8291,19 +8287,23 @@
         </is>
       </c>
       <c r="H162" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I162" s="8" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>ការចាត់ចែង</t>
-        </is>
-      </c>
-      <c r="K162" s="12" t="n"/>
+          <t>ទិដ្ឋភាពទូទៅ</t>
+        </is>
+      </c>
+      <c r="K162" s="12" t="inlineStr">
+        <is>
+          <t>Tabs on one asset</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="21.6" customHeight="1">
       <c r="A163" s="7" t="n"/>
@@ -8330,16 +8330,16 @@
         </is>
       </c>
       <c r="H163" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>Transfers</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>ការផ្ទេរ</t>
+          <t>ការចាត់ចែង</t>
         </is>
       </c>
       <c r="K163" s="12" t="n"/>
@@ -8369,16 +8369,16 @@
         </is>
       </c>
       <c r="H164" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>Transfers</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>បញ្ហា</t>
+          <t>ការផ្ទេរ</t>
         </is>
       </c>
       <c r="K164" s="12" t="n"/>
@@ -8408,16 +8408,16 @@
         </is>
       </c>
       <c r="H165" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="J165" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>បញ្ហា</t>
         </is>
       </c>
       <c r="K165" s="12" t="n"/>
@@ -8447,16 +8447,16 @@
         </is>
       </c>
       <c r="H166" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="K166" s="12" t="n"/>
@@ -8465,29 +8465,39 @@
       <c r="A167" s="7" t="n"/>
       <c r="B167" s="8" t="n"/>
       <c r="C167" s="8" t="n"/>
-      <c r="D167" s="9" t="inlineStr">
-        <is>
-          <t>B9.3</t>
-        </is>
-      </c>
-      <c r="E167" s="10" t="inlineStr">
-        <is>
-          <t>My Assets</t>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E167" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr">
         <is>
-          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G167" s="11" t="inlineStr">
         <is>
-          <t>/my-assets</t>
-        </is>
-      </c>
-      <c r="H167" s="7" t="n"/>
-      <c r="I167" s="8" t="n"/>
-      <c r="J167" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I167" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="J167" s="8" t="inlineStr">
+        <is>
+          <t>ការថែទាំ</t>
+        </is>
+      </c>
       <c r="K167" s="12" t="n"/>
     </row>
     <row r="168" ht="21.6" customHeight="1">
@@ -8496,22 +8506,22 @@
       <c r="C168" s="8" t="n"/>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>B9.4</t>
+          <t>B9.3</t>
         </is>
       </c>
       <c r="E168" s="10" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>My Assets</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>បញ្ហា</t>
+          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr">
         <is>
-          <t>/asset-issues</t>
+          <t>/my-assets</t>
         </is>
       </c>
       <c r="H168" s="7" t="n"/>
@@ -8525,22 +8535,22 @@
       <c r="C169" s="8" t="n"/>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>B9.5</t>
+          <t>B9.4</t>
         </is>
       </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>បញ្ហា</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
-          <t>/asset-repairs</t>
+          <t>/asset-issues</t>
         </is>
       </c>
       <c r="H169" s="7" t="n"/>
@@ -8554,22 +8564,22 @@
       <c r="C170" s="8" t="n"/>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>B9.6</t>
+          <t>B9.5</t>
         </is>
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>Repair Shops</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>ហាងជួសជុល</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>/repair-shops</t>
+          <t>/asset-repairs</t>
         </is>
       </c>
       <c r="H170" s="7" t="n"/>
@@ -8583,22 +8593,22 @@
       <c r="C171" s="8" t="n"/>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>B9.7</t>
+          <t>B9.6</t>
         </is>
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Repair Shops</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ហាងជួសជុល</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>/asset-maintenance</t>
+          <t>/repair-shops</t>
         </is>
       </c>
       <c r="H171" s="7" t="n"/>
@@ -8612,22 +8622,22 @@
       <c r="C172" s="8" t="n"/>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>B9.8</t>
+          <t>B9.7</t>
         </is>
       </c>
       <c r="E172" s="10" t="inlineStr">
         <is>
-          <t>Asset Categories</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
+          <t>ការថែទាំ</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
-          <t>/asset-categories</t>
+          <t>/asset-maintenance</t>
         </is>
       </c>
       <c r="H172" s="7" t="n"/>
@@ -8641,22 +8651,22 @@
       <c r="C173" s="8" t="n"/>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>B9.9</t>
+          <t>B9.8</t>
         </is>
       </c>
       <c r="E173" s="10" t="inlineStr">
         <is>
-          <t>Asset Locations</t>
+          <t>Asset Categories</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr">
         <is>
-          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
+          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>/asset-locations</t>
+          <t>/asset-categories</t>
         </is>
       </c>
       <c r="H173" s="7" t="n"/>
@@ -8670,22 +8680,22 @@
       <c r="C174" s="8" t="n"/>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>B9.10</t>
+          <t>B9.9</t>
         </is>
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>Departments</t>
+          <t>Asset Locations</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
-          <t>/departments</t>
+          <t>/asset-locations</t>
         </is>
       </c>
       <c r="H174" s="7" t="n"/>
@@ -8699,22 +8709,22 @@
       <c r="C175" s="8" t="n"/>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>B9.11</t>
+          <t>B9.10</t>
         </is>
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>Suppliers</t>
+          <t>Departments</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr">
         <is>
-          <t>អ្នកផ្គត់ផ្គង់</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>/suppliers</t>
+          <t>/departments</t>
         </is>
       </c>
       <c r="H175" s="7" t="n"/>
@@ -8728,49 +8738,39 @@
       <c r="C176" s="8" t="n"/>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>B9.12</t>
+          <t>B9.11</t>
         </is>
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>Asset Reports</t>
+          <t>Suppliers</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>អ្នកផ្គត់ផ្គង់</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H176" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I176" s="8" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="J176" s="8" t="inlineStr">
-        <is>
-          <t>ស្តុក</t>
-        </is>
-      </c>
+          <t>/suppliers</t>
+        </is>
+      </c>
+      <c r="H176" s="7" t="n"/>
+      <c r="I176" s="8" t="n"/>
+      <c r="J176" s="8" t="n"/>
       <c r="K176" s="12" t="n"/>
     </row>
     <row r="177" ht="21.6" customHeight="1">
       <c r="A177" s="7" t="n"/>
       <c r="B177" s="8" t="n"/>
       <c r="C177" s="8" t="n"/>
-      <c r="D177" s="7" t="inlineStr">
+      <c r="D177" s="9" t="inlineStr">
         <is>
           <t>B9.12</t>
         </is>
       </c>
-      <c r="E177" s="8" t="inlineStr">
+      <c r="E177" s="10" t="inlineStr">
         <is>
           <t>Asset Reports</t>
         </is>
@@ -8786,16 +8786,16 @@
         </is>
       </c>
       <c r="H177" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I177" s="8" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>ស្ថានភាព</t>
+          <t>ស្តុក</t>
         </is>
       </c>
       <c r="K177" s="12" t="n"/>
@@ -8825,16 +8825,16 @@
         </is>
       </c>
       <c r="H178" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>ស្ថានភាព</t>
         </is>
       </c>
       <c r="K178" s="12" t="n"/>
@@ -8864,16 +8864,16 @@
         </is>
       </c>
       <c r="H179" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I179" s="8" t="inlineStr">
         <is>
-          <t>Repair Cost</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="J179" s="8" t="inlineStr">
         <is>
-          <t>ថ្លៃជួសជុល</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="K179" s="12" t="n"/>
@@ -8903,16 +8903,16 @@
         </is>
       </c>
       <c r="H180" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Repair Cost</t>
         </is>
       </c>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ថ្លៃជួសជុល</t>
         </is>
       </c>
       <c r="K180" s="12" t="n"/>
@@ -8942,16 +8942,16 @@
         </is>
       </c>
       <c r="H181" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I181" s="8" t="inlineStr">
         <is>
-          <t>Assignments</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>ការចាត់ចែង</t>
+          <t>ការថែទាំ</t>
         </is>
       </c>
       <c r="K181" s="12" t="n"/>
@@ -8981,89 +8981,99 @@
         </is>
       </c>
       <c r="H182" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I182" s="8" t="inlineStr">
+        <is>
+          <t>Assignments</t>
+        </is>
+      </c>
+      <c r="J182" s="8" t="inlineStr">
+        <is>
+          <t>ការចាត់ចែង</t>
+        </is>
+      </c>
+      <c r="K182" s="12" t="n"/>
+    </row>
+    <row r="183" ht="21.6" customHeight="1">
+      <c r="A183" s="7" t="n"/>
+      <c r="B183" s="8" t="n"/>
+      <c r="C183" s="8" t="n"/>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E183" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G183" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H183" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I182" s="8" t="inlineStr">
+      <c r="I183" s="8" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="J182" s="8" t="inlineStr">
+      <c r="J183" s="8" t="inlineStr">
         <is>
           <t>ប្រវត្តិ</t>
         </is>
       </c>
-      <c r="K182" s="12" t="n"/>
-    </row>
-    <row r="183" ht="21.6" customHeight="1">
-      <c r="A183" s="13" t="inlineStr">
+      <c r="K183" s="12" t="n"/>
+    </row>
+    <row r="184" ht="21.6" customHeight="1">
+      <c r="A184" s="13" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="B183" s="14" t="inlineStr">
+      <c r="B184" s="14" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="C183" s="15" t="inlineStr">
+      <c r="C184" s="15" t="inlineStr">
         <is>
           <t>ការទំនាក់ទំនង</t>
         </is>
       </c>
-      <c r="D183" s="13" t="inlineStr">
+      <c r="D184" s="13" t="inlineStr">
         <is>
           <t>B10.1</t>
         </is>
       </c>
-      <c r="E183" s="14" t="inlineStr">
+      <c r="E184" s="14" t="inlineStr">
         <is>
           <t>Contact Messages</t>
         </is>
       </c>
-      <c r="F183" s="15" t="inlineStr">
+      <c r="F184" s="15" t="inlineStr">
         <is>
           <t>សារទំនាក់ទំនង</t>
         </is>
       </c>
-      <c r="G183" s="16" t="inlineStr">
+      <c r="G184" s="16" t="inlineStr">
         <is>
           <t>/contact-messages</t>
         </is>
       </c>
-      <c r="H183" s="17" t="n"/>
-      <c r="I183" s="15" t="n"/>
-      <c r="J183" s="15" t="n"/>
-      <c r="K183" s="18" t="n"/>
-    </row>
-    <row r="184" ht="21.6" customHeight="1">
-      <c r="A184" s="19" t="n"/>
-      <c r="B184" s="20" t="n"/>
-      <c r="C184" s="20" t="n"/>
-      <c r="D184" s="21" t="inlineStr">
-        <is>
-          <t>B10.2</t>
-        </is>
-      </c>
-      <c r="E184" s="22" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="F184" s="20" t="inlineStr">
-        <is>
-          <t>ការជូនដំណឹង</t>
-        </is>
-      </c>
-      <c r="G184" s="23" t="inlineStr">
-        <is>
-          <t>/notifications</t>
-        </is>
-      </c>
-      <c r="H184" s="19" t="n"/>
-      <c r="I184" s="20" t="n"/>
-      <c r="J184" s="20" t="n"/>
-      <c r="K184" s="24" t="n"/>
+      <c r="H184" s="17" t="n"/>
+      <c r="I184" s="15" t="n"/>
+      <c r="J184" s="15" t="n"/>
+      <c r="K184" s="18" t="n"/>
     </row>
     <row r="185" ht="21.6" customHeight="1">
       <c r="A185" s="19" t="n"/>
@@ -9071,49 +9081,39 @@
       <c r="C185" s="20" t="n"/>
       <c r="D185" s="21" t="inlineStr">
         <is>
-          <t>B10.3</t>
+          <t>B10.2</t>
         </is>
       </c>
       <c r="E185" s="22" t="inlineStr">
         <is>
-          <t>Student Feedback</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
         <is>
-          <t>មតិកែលម្អសិស្ស</t>
+          <t>ការជូនដំណឹង</t>
         </is>
       </c>
       <c r="G185" s="23" t="inlineStr">
         <is>
-          <t>/student-feedback</t>
-        </is>
-      </c>
-      <c r="H185" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I185" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J185" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងបើក</t>
-        </is>
-      </c>
+          <t>/notifications</t>
+        </is>
+      </c>
+      <c r="H185" s="19" t="n"/>
+      <c r="I185" s="20" t="n"/>
+      <c r="J185" s="20" t="n"/>
       <c r="K185" s="24" t="n"/>
     </row>
     <row r="186" ht="21.6" customHeight="1">
       <c r="A186" s="19" t="n"/>
       <c r="B186" s="20" t="n"/>
       <c r="C186" s="20" t="n"/>
-      <c r="D186" s="19" t="inlineStr">
+      <c r="D186" s="21" t="inlineStr">
         <is>
           <t>B10.3</t>
         </is>
       </c>
-      <c r="E186" s="20" t="inlineStr">
+      <c r="E186" s="22" t="inlineStr">
         <is>
           <t>Student Feedback</t>
         </is>
@@ -9129,89 +9129,99 @@
         </is>
       </c>
       <c r="H186" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I186" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J186" s="20" t="inlineStr">
+        <is>
+          <t>កំពុងបើក</t>
+        </is>
+      </c>
+      <c r="K186" s="24" t="n"/>
+    </row>
+    <row r="187" ht="21.6" customHeight="1">
+      <c r="A187" s="19" t="n"/>
+      <c r="B187" s="20" t="n"/>
+      <c r="C187" s="20" t="n"/>
+      <c r="D187" s="19" t="inlineStr">
+        <is>
+          <t>B10.3</t>
+        </is>
+      </c>
+      <c r="E187" s="20" t="inlineStr">
+        <is>
+          <t>Student Feedback</t>
+        </is>
+      </c>
+      <c r="F187" s="20" t="inlineStr">
+        <is>
+          <t>មតិកែលម្អសិស្ស</t>
+        </is>
+      </c>
+      <c r="G187" s="23" t="inlineStr">
+        <is>
+          <t>/student-feedback</t>
+        </is>
+      </c>
+      <c r="H187" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="I186" s="20" t="inlineStr">
+      <c r="I187" s="20" t="inlineStr">
         <is>
           <t>Replied</t>
         </is>
       </c>
-      <c r="J186" s="20" t="inlineStr">
+      <c r="J187" s="20" t="inlineStr">
         <is>
           <t>បានឆ្លើយតប</t>
         </is>
       </c>
-      <c r="K186" s="24" t="n"/>
-    </row>
-    <row r="187" ht="21.6" customHeight="1">
-      <c r="A187" s="1" t="inlineStr">
+      <c r="K187" s="24" t="n"/>
+    </row>
+    <row r="188" ht="21.6" customHeight="1">
+      <c r="A188" s="1" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C187" s="3" t="inlineStr">
+      <c r="C188" s="3" t="inlineStr">
         <is>
           <t>ការកំណត់</t>
         </is>
       </c>
-      <c r="D187" s="1" t="inlineStr">
+      <c r="D188" s="1" t="inlineStr">
         <is>
           <t>B11.1</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="F187" s="3" t="inlineStr">
+      <c r="F188" s="3" t="inlineStr">
         <is>
           <t>ឯកសារ</t>
         </is>
       </c>
-      <c r="G187" s="4" t="inlineStr">
+      <c r="G188" s="4" t="inlineStr">
         <is>
           <t>/school-documents</t>
         </is>
       </c>
-      <c r="H187" s="5" t="n"/>
-      <c r="I187" s="3" t="n"/>
-      <c r="J187" s="3" t="n"/>
-      <c r="K187" s="6" t="n"/>
-    </row>
-    <row r="188" ht="21.6" customHeight="1">
-      <c r="A188" s="7" t="n"/>
-      <c r="B188" s="8" t="n"/>
-      <c r="C188" s="8" t="n"/>
-      <c r="D188" s="9" t="inlineStr">
-        <is>
-          <t>B11.2</t>
-        </is>
-      </c>
-      <c r="E188" s="10" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F188" s="8" t="inlineStr">
-        <is>
-          <t>ទូទៅ</t>
-        </is>
-      </c>
-      <c r="G188" s="11" t="inlineStr">
-        <is>
-          <t>/settings</t>
-        </is>
-      </c>
-      <c r="H188" s="7" t="n"/>
-      <c r="I188" s="8" t="n"/>
-      <c r="J188" s="8" t="n"/>
-      <c r="K188" s="12" t="n"/>
+      <c r="H188" s="5" t="n"/>
+      <c r="I188" s="3" t="n"/>
+      <c r="J188" s="3" t="n"/>
+      <c r="K188" s="6" t="n"/>
     </row>
     <row r="189" ht="21.6" customHeight="1">
       <c r="A189" s="7" t="n"/>
@@ -9219,22 +9229,22 @@
       <c r="C189" s="8" t="n"/>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>B11.3</t>
+          <t>B11.2</t>
         </is>
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>Telegram notifications</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr">
         <is>
-          <t>ការជូនដំណឹង Telegram</t>
+          <t>ទូទៅ</t>
         </is>
       </c>
       <c r="G189" s="11" t="inlineStr">
         <is>
-          <t>/telegram-notifications</t>
+          <t>/settings</t>
         </is>
       </c>
       <c r="H189" s="7" t="n"/>
@@ -9248,22 +9258,22 @@
       <c r="C190" s="8" t="n"/>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>B11.4</t>
+          <t>B11.3</t>
         </is>
       </c>
       <c r="E190" s="10" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Telegram notifications</t>
         </is>
       </c>
       <c r="F190" s="8" t="inlineStr">
         <is>
-          <t>អ្នកប្រើប្រាស់</t>
+          <t>ការជូនដំណឹង Telegram</t>
         </is>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/telegram-notifications</t>
         </is>
       </c>
       <c r="H190" s="7" t="n"/>
@@ -9277,22 +9287,22 @@
       <c r="C191" s="8" t="n"/>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>B11.5</t>
+          <t>B11.4</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>អ្នកប្រើប្រាស់</t>
         </is>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="H191" s="7" t="n"/>
@@ -9306,22 +9316,22 @@
       <c r="C192" s="8" t="n"/>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>B11.6</t>
+          <t>B11.5</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>Audit Logs</t>
+          <t>Roles</t>
         </is>
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>កំណត់ហេតុសវនកម្ម</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
-          <t>/audit-logs</t>
+          <t>/roles</t>
         </is>
       </c>
       <c r="H192" s="7" t="n"/>
@@ -9335,49 +9345,39 @@
       <c r="C193" s="8" t="n"/>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>B11.7</t>
+          <t>B11.6</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Audit Logs</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>កំណត់ហេតុសវនកម្ម</t>
         </is>
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="H193" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I193" s="8" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="J193" s="8" t="inlineStr">
-        <is>
-          <t>ភាសា</t>
-        </is>
-      </c>
+          <t>/audit-logs</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="n"/>
+      <c r="I193" s="8" t="n"/>
+      <c r="J193" s="8" t="n"/>
       <c r="K193" s="12" t="n"/>
     </row>
     <row r="194" ht="21.6" customHeight="1">
       <c r="A194" s="7" t="n"/>
       <c r="B194" s="8" t="n"/>
       <c r="C194" s="8" t="n"/>
-      <c r="D194" s="7" t="inlineStr">
+      <c r="D194" s="9" t="inlineStr">
         <is>
           <t>B11.7</t>
         </is>
       </c>
-      <c r="E194" s="8" t="inlineStr">
+      <c r="E194" s="10" t="inlineStr">
         <is>
           <t>Languages</t>
         </is>
@@ -9393,16 +9393,16 @@
         </is>
       </c>
       <c r="H194" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I194" s="8" t="inlineStr">
         <is>
-          <t>Translation</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>ការបកប្រែ</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="K194" s="12" t="n"/>
@@ -9411,29 +9411,39 @@
       <c r="A195" s="7" t="n"/>
       <c r="B195" s="8" t="n"/>
       <c r="C195" s="8" t="n"/>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>B11.8</t>
-        </is>
-      </c>
-      <c r="E195" s="10" t="inlineStr">
-        <is>
-          <t>Base Data</t>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>B11.7</t>
+        </is>
+      </c>
+      <c r="E195" s="8" t="inlineStr">
+        <is>
+          <t>Languages</t>
         </is>
       </c>
       <c r="F195" s="8" t="inlineStr">
         <is>
-          <t>ទិន្នន័យមូលដ្ឋាន</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="G195" s="11" t="inlineStr">
         <is>
-          <t>/lookup-categories</t>
-        </is>
-      </c>
-      <c r="H195" s="7" t="n"/>
-      <c r="I195" s="8" t="n"/>
-      <c r="J195" s="8" t="n"/>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I195" s="8" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="J195" s="8" t="inlineStr">
+        <is>
+          <t>ការបកប្រែ</t>
+        </is>
+      </c>
       <c r="K195" s="12" t="n"/>
     </row>
     <row r="196" ht="21.6" customHeight="1">
@@ -9442,22 +9452,22 @@
       <c r="C196" s="8" t="n"/>
       <c r="D196" s="9" t="inlineStr">
         <is>
-          <t>B11.9</t>
+          <t>B11.8</t>
         </is>
       </c>
       <c r="E196" s="10" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Base Data</t>
         </is>
       </c>
       <c r="F196" s="8" t="inlineStr">
         <is>
-          <t>បម្រុងទុក</t>
+          <t>ទិន្នន័យមូលដ្ឋាន</t>
         </is>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
-          <t>/database-backups</t>
+          <t>/lookup-categories</t>
         </is>
       </c>
       <c r="H196" s="7" t="n"/>
@@ -9466,91 +9476,81 @@
       <c r="K196" s="12" t="n"/>
     </row>
     <row r="197" ht="21.6" customHeight="1">
-      <c r="A197" s="13" t="inlineStr">
+      <c r="A197" s="7" t="n"/>
+      <c r="B197" s="8" t="n"/>
+      <c r="C197" s="8" t="n"/>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>B11.9</t>
+        </is>
+      </c>
+      <c r="E197" s="10" t="inlineStr">
+        <is>
+          <t>Backup</t>
+        </is>
+      </c>
+      <c r="F197" s="8" t="inlineStr">
+        <is>
+          <t>បម្រុងទុក</t>
+        </is>
+      </c>
+      <c r="G197" s="11" t="inlineStr">
+        <is>
+          <t>/database-backups</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="n"/>
+      <c r="I197" s="8" t="n"/>
+      <c r="J197" s="8" t="n"/>
+      <c r="K197" s="12" t="n"/>
+    </row>
+    <row r="198" ht="21.6" customHeight="1">
+      <c r="A198" s="13" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B197" s="14" t="inlineStr">
+      <c r="B198" s="14" t="inlineStr">
         <is>
           <t>eApprovals</t>
         </is>
       </c>
-      <c r="C197" s="15" t="n"/>
-      <c r="D197" s="13" t="inlineStr">
+      <c r="C198" s="15" t="n"/>
+      <c r="D198" s="13" t="inlineStr">
         <is>
           <t>B12.1</t>
         </is>
       </c>
-      <c r="E197" s="14" t="inlineStr">
+      <c r="E198" s="14" t="inlineStr">
         <is>
           <t>Forms</t>
         </is>
       </c>
-      <c r="F197" s="15" t="inlineStr">
+      <c r="F198" s="15" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="G197" s="16" t="inlineStr">
+      <c r="G198" s="16" t="inlineStr">
         <is>
           <t>/approvals/forms</t>
         </is>
       </c>
-      <c r="H197" s="17" t="n"/>
-      <c r="I197" s="15" t="n"/>
-      <c r="J197" s="15" t="n"/>
-      <c r="K197" s="18" t="n"/>
-    </row>
-    <row r="198" ht="21.6" customHeight="1">
-      <c r="A198" s="19" t="n"/>
-      <c r="B198" s="20" t="n"/>
-      <c r="C198" s="20" t="n"/>
-      <c r="D198" s="21" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E198" s="22" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F198" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G198" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H198" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I198" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J198" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
-      <c r="K198" s="24" t="n"/>
+      <c r="H198" s="17" t="n"/>
+      <c r="I198" s="15" t="n"/>
+      <c r="J198" s="15" t="n"/>
+      <c r="K198" s="18" t="n"/>
     </row>
     <row r="199" ht="21.6" customHeight="1">
       <c r="A199" s="19" t="n"/>
       <c r="B199" s="20" t="n"/>
       <c r="C199" s="20" t="n"/>
-      <c r="D199" s="19" t="inlineStr">
+      <c r="D199" s="21" t="inlineStr">
         <is>
           <t>B12.2</t>
         </is>
       </c>
-      <c r="E199" s="20" t="inlineStr">
+      <c r="E199" s="22" t="inlineStr">
         <is>
           <t>My Request</t>
         </is>
@@ -9566,16 +9566,16 @@
         </is>
       </c>
       <c r="H199" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I199" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J199" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="K199" s="24" t="n"/>
@@ -9605,16 +9605,16 @@
         </is>
       </c>
       <c r="H200" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I200" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J200" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K200" s="24" t="n"/>
@@ -9644,16 +9644,16 @@
         </is>
       </c>
       <c r="H201" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I201" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J201" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K201" s="24" t="n"/>
@@ -9683,16 +9683,16 @@
         </is>
       </c>
       <c r="H202" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I202" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="J202" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="K202" s="24" t="n"/>
@@ -9701,37 +9701,37 @@
       <c r="A203" s="19" t="n"/>
       <c r="B203" s="20" t="n"/>
       <c r="C203" s="20" t="n"/>
-      <c r="D203" s="21" t="inlineStr">
-        <is>
-          <t>B12.3</t>
-        </is>
-      </c>
-      <c r="E203" s="22" t="inlineStr">
-        <is>
-          <t>Approvals</t>
+      <c r="D203" s="19" t="inlineStr">
+        <is>
+          <t>B12.2</t>
+        </is>
+      </c>
+      <c r="E203" s="20" t="inlineStr">
+        <is>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F203" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G203" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H203" s="19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I203" s="20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="J203" s="20" t="inlineStr">
         <is>
-          <t>ថ្មី</t>
+          <t>បានលុបចោល</t>
         </is>
       </c>
       <c r="K203" s="24" t="n"/>
@@ -9740,12 +9740,12 @@
       <c r="A204" s="19" t="n"/>
       <c r="B204" s="20" t="n"/>
       <c r="C204" s="20" t="n"/>
-      <c r="D204" s="19" t="inlineStr">
+      <c r="D204" s="21" t="inlineStr">
         <is>
           <t>B12.3</t>
         </is>
       </c>
-      <c r="E204" s="20" t="inlineStr">
+      <c r="E204" s="22" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
@@ -9761,16 +9761,16 @@
         </is>
       </c>
       <c r="H204" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I204" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>New</t>
         </is>
       </c>
       <c r="J204" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>ថ្មី</t>
         </is>
       </c>
       <c r="K204" s="24" t="n"/>
@@ -9800,16 +9800,16 @@
         </is>
       </c>
       <c r="H205" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I205" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J205" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K205" s="24" t="n"/>
@@ -9839,16 +9839,16 @@
         </is>
       </c>
       <c r="H206" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I206" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J206" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K206" s="24" t="n"/>
@@ -9878,16 +9878,16 @@
         </is>
       </c>
       <c r="H207" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I207" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="J207" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="K207" s="24" t="n"/>
@@ -9896,29 +9896,39 @@
       <c r="A208" s="19" t="n"/>
       <c r="B208" s="20" t="n"/>
       <c r="C208" s="20" t="n"/>
-      <c r="D208" s="21" t="inlineStr">
-        <is>
-          <t>B12.4</t>
-        </is>
-      </c>
-      <c r="E208" s="22" t="inlineStr">
-        <is>
-          <t>Form Categories</t>
+      <c r="D208" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E208" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="F208" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទទម្រង់បែបបទ</t>
+          <t>ការអនុម័ត</t>
         </is>
       </c>
       <c r="G208" s="23" t="inlineStr">
         <is>
-          <t>/form-categories</t>
-        </is>
-      </c>
-      <c r="H208" s="19" t="n"/>
-      <c r="I208" s="20" t="n"/>
-      <c r="J208" s="20" t="n"/>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H208" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I208" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="J208" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
       <c r="K208" s="24" t="n"/>
     </row>
     <row r="209">
@@ -9927,22 +9937,22 @@
       <c r="C209" s="20" t="n"/>
       <c r="D209" s="21" t="inlineStr">
         <is>
-          <t>B12.5</t>
+          <t>B12.4</t>
         </is>
       </c>
       <c r="E209" s="22" t="inlineStr">
         <is>
-          <t>Form Templates</t>
+          <t>Form Categories</t>
         </is>
       </c>
       <c r="F209" s="20" t="inlineStr">
         <is>
-          <t>ទម្រង់បែបបទ</t>
+          <t>ប្រភេទទម្រង់បែបបទ</t>
         </is>
       </c>
       <c r="G209" s="23" t="inlineStr">
         <is>
-          <t>/form-templates</t>
+          <t>/form-categories</t>
         </is>
       </c>
       <c r="H209" s="19" t="n"/>
@@ -9951,86 +9961,115 @@
       <c r="K209" s="24" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="inlineStr">
+      <c r="A210" s="19" t="n"/>
+      <c r="B210" s="20" t="n"/>
+      <c r="C210" s="20" t="n"/>
+      <c r="D210" s="21" t="inlineStr">
+        <is>
+          <t>B12.5</t>
+        </is>
+      </c>
+      <c r="E210" s="22" t="inlineStr">
+        <is>
+          <t>Form Templates</t>
+        </is>
+      </c>
+      <c r="F210" s="20" t="inlineStr">
+        <is>
+          <t>ទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="G210" s="23" t="inlineStr">
+        <is>
+          <t>/form-templates</t>
+        </is>
+      </c>
+      <c r="H210" s="19" t="n"/>
+      <c r="I210" s="20" t="n"/>
+      <c r="J210" s="20" t="n"/>
+      <c r="K210" s="24" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C210" s="3" t="inlineStr">
+      <c r="C211" s="3" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D210" s="1" t="inlineStr">
+      <c r="D211" s="1" t="inlineStr">
         <is>
           <t>B13.1</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>Groups</t>
         </is>
       </c>
-      <c r="F210" s="3" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr">
         <is>
           <t>ក្រុម</t>
         </is>
       </c>
-      <c r="G210" s="4" t="inlineStr">
+      <c r="G211" s="4" t="inlineStr">
         <is>
           <t>/approval-flow/groups</t>
         </is>
       </c>
-      <c r="H210" s="5" t="n"/>
-      <c r="I210" s="3" t="n"/>
-      <c r="J210" s="3" t="n"/>
-      <c r="K210" s="6" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="7" t="inlineStr">
+      <c r="H211" s="5" t="n"/>
+      <c r="I211" s="3" t="n"/>
+      <c r="J211" s="3" t="n"/>
+      <c r="K211" s="6" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B211" s="8" t="inlineStr">
+      <c r="B212" s="8" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C211" s="8" t="inlineStr">
+      <c r="C212" s="8" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D211" s="9" t="inlineStr">
+      <c r="D212" s="9" t="inlineStr">
         <is>
           <t>B13.2</t>
         </is>
       </c>
-      <c r="E211" s="10" t="inlineStr">
+      <c r="E212" s="10" t="inlineStr">
         <is>
           <t>Flow Setting</t>
         </is>
       </c>
-      <c r="F211" s="8" t="inlineStr">
+      <c r="F212" s="8" t="inlineStr">
         <is>
           <t>កំណត់លំហូរ</t>
         </is>
       </c>
-      <c r="G211" s="11" t="inlineStr">
+      <c r="G212" s="11" t="inlineStr">
         <is>
           <t>/approval-flow/settings</t>
         </is>
       </c>
-      <c r="H211" s="7" t="n"/>
-      <c r="I211" s="8" t="n"/>
-      <c r="J211" s="8" t="n"/>
-      <c r="K211" s="12" t="n"/>
+      <c r="H212" s="7" t="n"/>
+      <c r="I212" s="8" t="n"/>
+      <c r="J212" s="8" t="n"/>
+      <c r="K212" s="12" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K208"/>
@@ -11401,7 +11440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12485,12 +12524,12 @@
       </c>
       <c r="H42" s="20" t="inlineStr">
         <is>
-          <t>Result Export</t>
+          <t>Remedial Teaching</t>
         </is>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
-          <t>នាំចេញលទ្ធផល</t>
+          <t>ការបង្រៀនបំប៉ន</t>
         </is>
       </c>
       <c r="J42" s="24" t="n"/>
@@ -12507,12 +12546,12 @@
       </c>
       <c r="H43" s="20" t="inlineStr">
         <is>
-          <t>Exams</t>
+          <t>Result Export</t>
         </is>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>ការប្រឡង</t>
+          <t>នាំចេញលទ្ធផល</t>
         </is>
       </c>
       <c r="J43" s="24" t="n"/>
@@ -12529,12 +12568,12 @@
       </c>
       <c r="H44" s="20" t="inlineStr">
         <is>
-          <t>Grades</t>
+          <t>Exams</t>
         </is>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
-          <t>និទ្ទេស</t>
+          <t>ការប្រឡង</t>
         </is>
       </c>
       <c r="J44" s="24" t="n"/>
@@ -12551,12 +12590,12 @@
       </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
-          <t>Make-up Exam</t>
+          <t>Grades</t>
         </is>
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>ប្រឡងសង</t>
+          <t>និទ្ទេស</t>
         </is>
       </c>
       <c r="J45" s="24" t="n"/>
@@ -12573,75 +12612,73 @@
       </c>
       <c r="H46" s="20" t="inlineStr">
         <is>
+          <t>Make-up Exam</t>
+        </is>
+      </c>
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>ប្រឡងសង</t>
+        </is>
+      </c>
+      <c r="J46" s="24" t="n"/>
+    </row>
+    <row r="47" ht="21.6" customHeight="1">
+      <c r="A47" s="19" t="n"/>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+      <c r="E47" s="20" t="n"/>
+      <c r="F47" s="23" t="n"/>
+      <c r="G47" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
           <t>Certificate</t>
         </is>
       </c>
-      <c r="I46" s="20" t="inlineStr">
+      <c r="I47" s="20" t="inlineStr">
         <is>
           <t>វិញ្ញាបនបត្រ</t>
         </is>
       </c>
-      <c r="J46" s="24" t="n"/>
-    </row>
-    <row r="47" ht="21.6" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="J47" s="24" t="n"/>
+    </row>
+    <row r="48" ht="21.6" customHeight="1">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>សិស្សានុសិស្ស</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>សិស្សានុសិស្ស</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>/students</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="6" t="n"/>
-    </row>
-    <row r="48" ht="21.6" customHeight="1">
-      <c r="A48" s="7" t="n"/>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>Import Students</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>នាំចូលទិន្នន័យសិស្ស</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>/student-imports</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-      <c r="J48" s="12" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="6" t="n"/>
     </row>
     <row r="49" ht="21.6" customHeight="1">
       <c r="A49" s="7" t="n"/>
@@ -12649,17 +12686,17 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Enrollments</t>
+          <t>Import Students</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>ការចុះឈ្មោះចូលរៀន</t>
+          <t>នាំចូលទិន្នន័យសិស្ស</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>/enrollments</t>
+          <t>/student-imports</t>
         </is>
       </c>
       <c r="G49" s="7" t="n"/>
@@ -12668,76 +12705,78 @@
       <c r="J49" s="12" t="n"/>
     </row>
     <row r="50" ht="21.6" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Enrollments</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>ការចុះឈ្មោះចូលរៀន</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>/enrollments</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="12" t="n"/>
+    </row>
+    <row r="51" ht="21.6" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>HRM</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C51" s="15" t="inlineStr">
         <is>
           <t>ធនធានមនុស្ស</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>បុគ្គលិក</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F51" s="16" t="inlineStr">
         <is>
           <t>/staff</t>
         </is>
       </c>
-      <c r="G50" s="17" t="n">
+      <c r="G51" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="H51" s="15" t="inlineStr">
         <is>
           <t>Current Info</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr">
+      <c r="I51" s="15" t="inlineStr">
         <is>
           <t>ព័ត៌មានបច្ចុប្បន្ន</t>
         </is>
       </c>
-      <c r="J50" s="18" t="inlineStr">
+      <c r="J51" s="18" t="inlineStr">
         <is>
           <t>Tabs on the staff form</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="21.6" customHeight="1">
-      <c r="A51" s="19" t="n"/>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="20" t="n"/>
-      <c r="D51" s="20" t="n"/>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="23" t="n"/>
-      <c r="G51" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" s="20" t="inlineStr">
-        <is>
-          <t>Emergency Contacts</t>
-        </is>
-      </c>
-      <c r="I51" s="20" t="inlineStr">
-        <is>
-          <t>ទំនាក់ទំនងបន្ទាន់</t>
-        </is>
-      </c>
-      <c r="J51" s="24" t="n"/>
     </row>
     <row r="52" ht="21.6" customHeight="1">
       <c r="A52" s="19" t="n"/>
@@ -12747,16 +12786,16 @@
       <c r="E52" s="20" t="n"/>
       <c r="F52" s="23" t="n"/>
       <c r="G52" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="38" t="inlineStr">
-        <is>
-          <t>Education</t>
+        <v>2</v>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>Emergency Contacts</t>
         </is>
       </c>
       <c r="I52" s="20" t="inlineStr">
         <is>
-          <t>ការសិក្សា</t>
+          <t>ទំនាក់ទំនងបន្ទាន់</t>
         </is>
       </c>
       <c r="J52" s="24" t="n"/>
@@ -12769,16 +12808,16 @@
       <c r="E53" s="20" t="n"/>
       <c r="F53" s="23" t="n"/>
       <c r="G53" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H53" s="20" t="inlineStr">
-        <is>
-          <t>Family Members</t>
+        <v>3</v>
+      </c>
+      <c r="H53" s="38" t="inlineStr">
+        <is>
+          <t>Education</t>
         </is>
       </c>
       <c r="I53" s="20" t="inlineStr">
         <is>
-          <t>សមាជិកគ្រួសារ</t>
+          <t>ការសិក្សា</t>
         </is>
       </c>
       <c r="J53" s="24" t="n"/>
@@ -12791,16 +12830,16 @@
       <c r="E54" s="20" t="n"/>
       <c r="F54" s="23" t="n"/>
       <c r="G54" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H54" s="20" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Family Members</t>
         </is>
       </c>
       <c r="I54" s="20" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>សមាជិកគ្រួសារ</t>
         </is>
       </c>
       <c r="J54" s="24" t="n"/>
@@ -12813,16 +12852,16 @@
       <c r="E55" s="20" t="n"/>
       <c r="F55" s="23" t="n"/>
       <c r="G55" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H55" s="20" t="inlineStr">
         <is>
-          <t>Previous Work</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>បទពិសោធន៍ការងារពីមុន</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="J55" s="24" t="n"/>
@@ -12831,32 +12870,20 @@
       <c r="A56" s="19" t="n"/>
       <c r="B56" s="20" t="n"/>
       <c r="C56" s="20" t="n"/>
-      <c r="D56" s="22" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="E56" s="20" t="inlineStr">
-        <is>
-          <t>គ្រូ</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>/teachers</t>
-        </is>
-      </c>
+      <c r="D56" s="20" t="n"/>
+      <c r="E56" s="20" t="n"/>
+      <c r="F56" s="23" t="n"/>
       <c r="G56" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" s="38" t="inlineStr">
-        <is>
-          <t>Qualification</t>
+        <v>6</v>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>Previous Work</t>
         </is>
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
-          <t>គុណវុឌ្ឍិ</t>
+          <t>បទពិសោធន៍ការងារពីមុន</t>
         </is>
       </c>
       <c r="J56" s="24" t="n"/>
@@ -12865,20 +12892,32 @@
       <c r="A57" s="19" t="n"/>
       <c r="B57" s="20" t="n"/>
       <c r="C57" s="20" t="n"/>
-      <c r="D57" s="20" t="n"/>
-      <c r="E57" s="20" t="n"/>
-      <c r="F57" s="23" t="n"/>
+      <c r="D57" s="22" t="inlineStr">
+        <is>
+          <t>Teachers</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>គ្រូ</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>/teachers</t>
+        </is>
+      </c>
       <c r="G57" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" s="20" t="inlineStr">
-        <is>
-          <t>Assignment</t>
+        <v>1</v>
+      </c>
+      <c r="H57" s="38" t="inlineStr">
+        <is>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
-          <t>ការចាត់តាំង</t>
+          <t>គុណវុឌ្ឍិ</t>
         </is>
       </c>
       <c r="J57" s="24" t="n"/>
@@ -12891,16 +12930,16 @@
       <c r="E58" s="20" t="n"/>
       <c r="F58" s="23" t="n"/>
       <c r="G58" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" s="20" t="inlineStr">
         <is>
-          <t>Homeroom</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="I58" s="20" t="inlineStr">
         <is>
-          <t>គ្រូប្រចាំថ្នាក់</t>
+          <t>ការចាត់តាំង</t>
         </is>
       </c>
       <c r="J58" s="24" t="n"/>
@@ -12913,16 +12952,16 @@
       <c r="E59" s="20" t="n"/>
       <c r="F59" s="23" t="n"/>
       <c r="G59" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H59" s="20" t="inlineStr">
         <is>
-          <t>Teaching load</t>
+          <t>Homeroom</t>
         </is>
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបង្រៀន</t>
+          <t>គ្រូប្រចាំថ្នាក់</t>
         </is>
       </c>
       <c r="J59" s="24" t="n"/>
@@ -12935,16 +12974,16 @@
       <c r="E60" s="20" t="n"/>
       <c r="F60" s="23" t="n"/>
       <c r="G60" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H60" s="20" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Teaching load</t>
         </is>
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
-          <t>ពេលទំនេរ</t>
+          <t>ម៉ោងបង្រៀន</t>
         </is>
       </c>
       <c r="J60" s="24" t="n"/>
@@ -12957,16 +12996,16 @@
       <c r="E61" s="20" t="n"/>
       <c r="F61" s="23" t="n"/>
       <c r="G61" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H61" s="20" t="inlineStr">
         <is>
-          <t>Substitute</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="I61" s="20" t="inlineStr">
         <is>
-          <t>គ្រូជំនួស</t>
+          <t>ពេលទំនេរ</t>
         </is>
       </c>
       <c r="J61" s="24" t="n"/>
@@ -12979,16 +13018,16 @@
       <c r="E62" s="20" t="n"/>
       <c r="F62" s="23" t="n"/>
       <c r="G62" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H62" s="20" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Substitute</t>
         </is>
       </c>
       <c r="I62" s="20" t="inlineStr">
         <is>
-          <t>ឯកសារ</t>
+          <t>គ្រូជំនួស</t>
         </is>
       </c>
       <c r="J62" s="24" t="n"/>
@@ -12997,24 +13036,22 @@
       <c r="A63" s="19" t="n"/>
       <c r="B63" s="20" t="n"/>
       <c r="C63" s="20" t="n"/>
-      <c r="D63" s="22" t="inlineStr">
-        <is>
-          <t>Staff Status History</t>
-        </is>
-      </c>
-      <c r="E63" s="20" t="inlineStr">
-        <is>
-          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>/staff-status-history</t>
-        </is>
-      </c>
-      <c r="G63" s="19" t="n"/>
-      <c r="H63" s="20" t="n"/>
-      <c r="I63" s="20" t="n"/>
+      <c r="D63" s="20" t="n"/>
+      <c r="E63" s="20" t="n"/>
+      <c r="F63" s="23" t="n"/>
+      <c r="G63" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="I63" s="20" t="inlineStr">
+        <is>
+          <t>ឯកសារ</t>
+        </is>
+      </c>
       <c r="J63" s="24" t="n"/>
     </row>
     <row r="64" ht="21.6" customHeight="1">
@@ -13023,52 +13060,54 @@
       <c r="C64" s="20" t="n"/>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Organization Management</t>
+          <t>Staff Status History</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងអង្គភាព</t>
+          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
         </is>
       </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
-          <t>/organization</t>
-        </is>
-      </c>
-      <c r="G64" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H64" s="36" t="inlineStr">
-        <is>
-          <t>School</t>
-        </is>
-      </c>
-      <c r="I64" s="20" t="inlineStr">
-        <is>
-          <t>សាលា</t>
-        </is>
-      </c>
+          <t>/staff-status-history</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="n"/>
+      <c r="H64" s="20" t="n"/>
+      <c r="I64" s="20" t="n"/>
       <c r="J64" s="24" t="n"/>
     </row>
     <row r="65" ht="21.6" customHeight="1">
       <c r="A65" s="19" t="n"/>
       <c r="B65" s="20" t="n"/>
       <c r="C65" s="20" t="n"/>
-      <c r="D65" s="20" t="n"/>
-      <c r="E65" s="20" t="n"/>
-      <c r="F65" s="23" t="n"/>
+      <c r="D65" s="22" t="inlineStr">
+        <is>
+          <t>Organization Management</t>
+        </is>
+      </c>
+      <c r="E65" s="20" t="inlineStr">
+        <is>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>/organization</t>
+        </is>
+      </c>
       <c r="G65" s="19" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="H65" s="36" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>School</t>
         </is>
       </c>
       <c r="I65" s="20" t="inlineStr">
         <is>
-          <t>សាខា</t>
+          <t>សាលា</t>
         </is>
       </c>
       <c r="J65" s="24" t="n"/>
@@ -13081,16 +13120,16 @@
       <c r="E66" s="20" t="n"/>
       <c r="F66" s="23" t="n"/>
       <c r="G66" s="19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H66" s="36" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="I66" s="20" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>សាខា</t>
         </is>
       </c>
       <c r="J66" s="24" t="n"/>
@@ -13103,16 +13142,16 @@
       <c r="E67" s="20" t="n"/>
       <c r="F67" s="23" t="n"/>
       <c r="G67" s="19" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="H67" s="36" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>ក្រុម</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="J67" s="24" t="n"/>
@@ -13125,16 +13164,16 @@
       <c r="E68" s="20" t="n"/>
       <c r="F68" s="23" t="n"/>
       <c r="G68" s="19" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="H68" s="36" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>ក្រុម</t>
         </is>
       </c>
       <c r="J68" s="24" t="n"/>
@@ -13147,16 +13186,16 @@
       <c r="E69" s="20" t="n"/>
       <c r="F69" s="23" t="n"/>
       <c r="G69" s="19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H69" s="36" t="inlineStr">
         <is>
-          <t>Job grade</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>ថ្នាក់ការងារ</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="J69" s="24" t="n"/>
@@ -13169,16 +13208,16 @@
       <c r="E70" s="20" t="n"/>
       <c r="F70" s="23" t="n"/>
       <c r="G70" s="19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H70" s="36" t="inlineStr">
         <is>
-          <t>Job level</t>
+          <t>Job grade</t>
         </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>កម្រិតការងារ</t>
+          <t>ថ្នាក់ការងារ</t>
         </is>
       </c>
       <c r="J70" s="24" t="n"/>
@@ -13190,19 +13229,17 @@
       <c r="D71" s="20" t="n"/>
       <c r="E71" s="20" t="n"/>
       <c r="F71" s="23" t="n"/>
-      <c r="G71" s="19" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
+      <c r="G71" s="19" t="n">
+        <v>4.6</v>
       </c>
       <c r="H71" s="36" t="inlineStr">
         <is>
-          <t>Reporting manager</t>
+          <t>Job level</t>
         </is>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
+          <t>កម្រិតការងារ</t>
         </is>
       </c>
       <c r="J71" s="24" t="n"/>
@@ -13221,12 +13258,12 @@
       </c>
       <c r="H72" s="36" t="inlineStr">
         <is>
-          <t>Organization hierarchy</t>
+          <t>Reporting manager</t>
         </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
+          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
         </is>
       </c>
       <c r="J72" s="24" t="n"/>
@@ -13235,32 +13272,22 @@
       <c r="A73" s="19" t="n"/>
       <c r="B73" s="20" t="n"/>
       <c r="C73" s="20" t="n"/>
-      <c r="D73" s="22" t="inlineStr">
-        <is>
-          <t>Attendance &amp; Time</t>
-        </is>
-      </c>
-      <c r="E73" s="20" t="inlineStr">
-        <is>
-          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
-        </is>
-      </c>
-      <c r="F73" s="23" t="inlineStr">
-        <is>
-          <t>/time-attendance</t>
-        </is>
-      </c>
-      <c r="G73" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="20" t="inlineStr">
-        <is>
-          <t>Employee attendance</t>
+      <c r="D73" s="20" t="n"/>
+      <c r="E73" s="20" t="n"/>
+      <c r="F73" s="23" t="n"/>
+      <c r="G73" s="19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>Organization hierarchy</t>
         </is>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>វត្តមានបុគ្គលិក</t>
+          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
         </is>
       </c>
       <c r="J73" s="24" t="n"/>
@@ -13269,20 +13296,32 @@
       <c r="A74" s="19" t="n"/>
       <c r="B74" s="20" t="n"/>
       <c r="C74" s="20" t="n"/>
-      <c r="D74" s="20" t="n"/>
-      <c r="E74" s="20" t="n"/>
-      <c r="F74" s="23" t="n"/>
+      <c r="D74" s="22" t="inlineStr">
+        <is>
+          <t>Attendance &amp; Time</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="inlineStr">
+        <is>
+          <t>/time-attendance</t>
+        </is>
+      </c>
       <c r="G74" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" s="20" t="inlineStr">
         <is>
-          <t>Check-in / check-out</t>
+          <t>Employee attendance</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>វត្តមានបុគ្គលិក</t>
         </is>
       </c>
       <c r="J74" s="24" t="n"/>
@@ -13295,16 +13334,16 @@
       <c r="E75" s="20" t="n"/>
       <c r="F75" s="23" t="n"/>
       <c r="G75" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75" s="20" t="inlineStr">
         <is>
-          <t>Late</t>
+          <t>Check-in / check-out</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>មកយឺត</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="J75" s="24" t="n"/>
@@ -13317,16 +13356,16 @@
       <c r="E76" s="20" t="n"/>
       <c r="F76" s="23" t="n"/>
       <c r="G76" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H76" s="20" t="inlineStr">
         <is>
-          <t>Early leave</t>
+          <t>Late</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>ចេញមុន</t>
+          <t>មកយឺត</t>
         </is>
       </c>
       <c r="J76" s="24" t="n"/>
@@ -13339,16 +13378,16 @@
       <c r="E77" s="20" t="n"/>
       <c r="F77" s="23" t="n"/>
       <c r="G77" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>Absence</t>
+          <t>Early leave</t>
         </is>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>អវត្តមាន</t>
+          <t>ចេញមុន</t>
         </is>
       </c>
       <c r="J77" s="24" t="n"/>
@@ -13361,16 +13400,16 @@
       <c r="E78" s="20" t="n"/>
       <c r="F78" s="23" t="n"/>
       <c r="G78" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H78" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Absence</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>អវត្តមាន</t>
         </is>
       </c>
       <c r="J78" s="24" t="n"/>
@@ -13383,16 +13422,16 @@
       <c r="E79" s="20" t="n"/>
       <c r="F79" s="23" t="n"/>
       <c r="G79" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H79" s="20" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>វេនការងារ</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="J79" s="24" t="n"/>
@@ -13405,16 +13444,16 @@
       <c r="E80" s="20" t="n"/>
       <c r="F80" s="23" t="n"/>
       <c r="G80" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H80" s="20" t="inlineStr">
         <is>
-          <t>Staff shift</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>វេនបុគ្គលិក</t>
+          <t>វេនការងារ</t>
         </is>
       </c>
       <c r="J80" s="24" t="n"/>
@@ -13427,16 +13466,16 @@
       <c r="E81" s="20" t="n"/>
       <c r="F81" s="23" t="n"/>
       <c r="G81" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Staff shift</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>ថ្ងៃឈប់សម្រាក</t>
+          <t>វេនបុគ្គលិក</t>
         </is>
       </c>
       <c r="J81" s="24" t="n"/>
@@ -13449,16 +13488,16 @@
       <c r="E82" s="20" t="n"/>
       <c r="F82" s="23" t="n"/>
       <c r="G82" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H82" s="20" t="inlineStr">
         <is>
-          <t>Attendance correction</t>
+          <t>Holidays</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>ការកែវត្តមាន</t>
+          <t>ថ្ងៃឈប់សម្រាក</t>
         </is>
       </c>
       <c r="J82" s="24" t="n"/>
@@ -13471,16 +13510,16 @@
       <c r="E83" s="20" t="n"/>
       <c r="F83" s="23" t="n"/>
       <c r="G83" s="19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>Attendance approval</t>
+          <t>Attendance correction</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តវត្តមាន</t>
+          <t>ការកែវត្តមាន</t>
         </is>
       </c>
       <c r="J83" s="24" t="n"/>
@@ -13489,32 +13528,20 @@
       <c r="A84" s="19" t="n"/>
       <c r="B84" s="20" t="n"/>
       <c r="C84" s="20" t="n"/>
-      <c r="D84" s="22" t="inlineStr">
-        <is>
-          <t>Leave Management</t>
-        </is>
-      </c>
-      <c r="E84" s="20" t="inlineStr">
-        <is>
-          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
-        </is>
-      </c>
-      <c r="F84" s="23" t="inlineStr">
-        <is>
-          <t>/leave-management</t>
-        </is>
-      </c>
+      <c r="D84" s="20" t="n"/>
+      <c r="E84" s="20" t="n"/>
+      <c r="F84" s="23" t="n"/>
       <c r="G84" s="19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H84" s="20" t="inlineStr">
         <is>
-          <t>Leave types</t>
+          <t>Attendance approval</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
+          <t>ការអនុម័តវត្តមាន</t>
         </is>
       </c>
       <c r="J84" s="24" t="n"/>
@@ -13523,20 +13550,32 @@
       <c r="A85" s="19" t="n"/>
       <c r="B85" s="20" t="n"/>
       <c r="C85" s="20" t="n"/>
-      <c r="D85" s="20" t="n"/>
-      <c r="E85" s="20" t="n"/>
-      <c r="F85" s="23" t="n"/>
+      <c r="D85" s="22" t="inlineStr">
+        <is>
+          <t>Leave Management</t>
+        </is>
+      </c>
+      <c r="E85" s="20" t="inlineStr">
+        <is>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>/leave-management</t>
+        </is>
+      </c>
       <c r="G85" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>Leave policies</t>
+          <t>Leave types</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
+          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="J85" s="24" t="n"/>
@@ -13549,16 +13588,16 @@
       <c r="E86" s="20" t="n"/>
       <c r="F86" s="23" t="n"/>
       <c r="G86" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" s="20" t="inlineStr">
         <is>
-          <t>Leave balance</t>
+          <t>Leave policies</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>សមតុល្យច្បាប់</t>
+          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="J86" s="24" t="n"/>
@@ -13571,16 +13610,16 @@
       <c r="E87" s="20" t="n"/>
       <c r="F87" s="23" t="n"/>
       <c r="G87" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>Leave request</t>
+          <t>Leave balance</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>សំណើច្បាប់ឈប់សម្រាក</t>
+          <t>សមតុល្យច្បាប់</t>
         </is>
       </c>
       <c r="J87" s="24" t="n"/>
@@ -13593,16 +13632,16 @@
       <c r="E88" s="20" t="n"/>
       <c r="F88" s="23" t="n"/>
       <c r="G88" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H88" s="20" t="inlineStr">
         <is>
-          <t>Approval workflow</t>
+          <t>Leave request</t>
         </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>លំហូរការអនុម័ត</t>
+          <t>សំណើច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="J88" s="24" t="n"/>
@@ -13615,16 +13654,16 @@
       <c r="E89" s="20" t="n"/>
       <c r="F89" s="23" t="n"/>
       <c r="G89" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H89" s="20" t="inlineStr">
         <is>
-          <t>Leave calendar</t>
+          <t>Approval workflow</t>
         </is>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិទិនច្បាប់</t>
+          <t>លំហូរការអនុម័ត</t>
         </is>
       </c>
       <c r="J89" s="24" t="n"/>
@@ -13637,16 +13676,16 @@
       <c r="E90" s="20" t="n"/>
       <c r="F90" s="23" t="n"/>
       <c r="G90" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H90" s="20" t="inlineStr">
         <is>
-          <t>Carry forward</t>
+          <t>Leave calendar</t>
         </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>យោងទៅឆ្នាំបន្ទាប់</t>
+          <t>ប្រតិទិនច្បាប់</t>
         </is>
       </c>
       <c r="J90" s="24" t="n"/>
@@ -13659,16 +13698,16 @@
       <c r="E91" s="20" t="n"/>
       <c r="F91" s="23" t="n"/>
       <c r="G91" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H91" s="20" t="inlineStr">
         <is>
-          <t>Leave reports</t>
+          <t>Carry forward</t>
         </is>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ច្បាប់</t>
+          <t>យោងទៅឆ្នាំបន្ទាប់</t>
         </is>
       </c>
       <c r="J91" s="24" t="n"/>
@@ -13677,24 +13716,22 @@
       <c r="A92" s="19" t="n"/>
       <c r="B92" s="20" t="n"/>
       <c r="C92" s="20" t="n"/>
-      <c r="D92" s="22" t="inlineStr">
-        <is>
-          <t>Check in / Check out</t>
-        </is>
-      </c>
-      <c r="E92" s="20" t="inlineStr">
-        <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
-        </is>
-      </c>
-      <c r="F92" s="23" t="inlineStr">
-        <is>
-          <t>/my-check-in</t>
-        </is>
-      </c>
-      <c r="G92" s="19" t="n"/>
-      <c r="H92" s="20" t="n"/>
-      <c r="I92" s="20" t="n"/>
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="20" t="n"/>
+      <c r="F92" s="23" t="n"/>
+      <c r="G92" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H92" s="20" t="inlineStr">
+        <is>
+          <t>Leave reports</t>
+        </is>
+      </c>
+      <c r="I92" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ច្បាប់</t>
+        </is>
+      </c>
       <c r="J92" s="24" t="n"/>
     </row>
     <row r="93" ht="21.6" customHeight="1">
@@ -13703,39 +13740,29 @@
       <c r="C93" s="20" t="n"/>
       <c r="D93" s="22" t="inlineStr">
         <is>
-          <t>Request Leave</t>
+          <t>Check in / Check out</t>
         </is>
       </c>
       <c r="E93" s="20" t="inlineStr">
         <is>
-          <t>ស្នើសុំច្បាប់</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="F93" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="G93" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I93" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
+          <t>/my-check-in</t>
+        </is>
+      </c>
+      <c r="G93" s="19" t="n"/>
+      <c r="H93" s="20" t="n"/>
+      <c r="I93" s="20" t="n"/>
       <c r="J93" s="24" t="n"/>
     </row>
     <row r="94" ht="21.6" customHeight="1">
       <c r="A94" s="19" t="n"/>
       <c r="B94" s="20" t="n"/>
       <c r="C94" s="20" t="n"/>
-      <c r="D94" s="20" t="inlineStr">
+      <c r="D94" s="22" t="inlineStr">
         <is>
           <t>Request Leave</t>
         </is>
@@ -13751,16 +13778,16 @@
         </is>
       </c>
       <c r="G94" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="J94" s="24" t="n"/>
@@ -13785,16 +13812,16 @@
         </is>
       </c>
       <c r="G95" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H95" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="I95" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="J95" s="24" t="n"/>
@@ -13819,16 +13846,16 @@
         </is>
       </c>
       <c r="G96" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H96" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="J96" s="24" t="n"/>
@@ -13853,16 +13880,16 @@
         </is>
       </c>
       <c r="G97" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H97" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="J97" s="24" t="n"/>
@@ -13871,101 +13898,111 @@
       <c r="A98" s="19" t="n"/>
       <c r="B98" s="20" t="n"/>
       <c r="C98" s="20" t="n"/>
-      <c r="D98" s="22" t="inlineStr">
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="G98" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H98" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="I98" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="J98" s="24" t="n"/>
+    </row>
+    <row r="99" ht="21.6" customHeight="1">
+      <c r="A99" s="19" t="n"/>
+      <c r="B99" s="20" t="n"/>
+      <c r="C99" s="20" t="n"/>
+      <c r="D99" s="22" t="inlineStr">
         <is>
           <t>Form</t>
         </is>
       </c>
-      <c r="E98" s="20" t="inlineStr">
+      <c r="E99" s="20" t="inlineStr">
         <is>
           <t>ទម្រង់</t>
         </is>
       </c>
-      <c r="F98" s="23" t="inlineStr">
+      <c r="F99" s="23" t="inlineStr">
         <is>
           <t>/approvals/my-requests?tab=resignation</t>
         </is>
       </c>
-      <c r="G98" s="19" t="n"/>
-      <c r="H98" s="20" t="n"/>
-      <c r="I98" s="20" t="n"/>
-      <c r="J98" s="24" t="inlineStr">
+      <c r="G99" s="19" t="n"/>
+      <c r="H99" s="20" t="n"/>
+      <c r="I99" s="20" t="n"/>
+      <c r="J99" s="24" t="inlineStr">
         <is>
           <t>Resignation form</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="21.6" customHeight="1">
-      <c r="A99" s="1" t="inlineStr">
+    <row r="100" ht="21.6" customHeight="1">
+      <c r="A100" s="1" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>ការកំណត់</t>
         </is>
       </c>
-      <c r="D99" s="35" t="n"/>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="4" t="n"/>
-      <c r="G99" s="5" t="n"/>
-      <c r="H99" s="3" t="n"/>
-      <c r="I99" s="3" t="n"/>
-      <c r="J99" s="6" t="n"/>
-    </row>
-    <row r="100" ht="21.6" customHeight="1">
-      <c r="A100" s="29" t="n"/>
-      <c r="B100" s="30" t="n"/>
-      <c r="C100" s="31" t="n"/>
-      <c r="D100" s="30" t="inlineStr">
+      <c r="D100" s="35" t="n"/>
+      <c r="E100" s="3" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="5" t="n"/>
+      <c r="H100" s="3" t="n"/>
+      <c r="I100" s="3" t="n"/>
+      <c r="J100" s="6" t="n"/>
+    </row>
+    <row r="101" ht="21.6" customHeight="1">
+      <c r="A101" s="29" t="n"/>
+      <c r="B101" s="30" t="n"/>
+      <c r="C101" s="31" t="n"/>
+      <c r="D101" s="30" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="E100" s="31" t="inlineStr">
+      <c r="E101" s="31" t="inlineStr">
         <is>
           <t>ឯកសារ</t>
         </is>
       </c>
-      <c r="F100" s="32" t="inlineStr">
+      <c r="F101" s="32" t="inlineStr">
         <is>
           <t>/school-documents</t>
         </is>
       </c>
-      <c r="G100" s="33" t="n"/>
-      <c r="H100" s="31" t="n"/>
-      <c r="I100" s="31" t="n"/>
-      <c r="J100" s="34" t="n"/>
-    </row>
-    <row r="101" ht="21.6" customHeight="1">
-      <c r="A101" s="7" t="n"/>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="8" t="n"/>
-      <c r="D101" s="10" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>ទូទៅ</t>
-        </is>
-      </c>
-      <c r="F101" s="11" t="inlineStr">
-        <is>
-          <t>/settings</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="n"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="8" t="n"/>
-      <c r="J101" s="12" t="n"/>
+      <c r="G101" s="33" t="n"/>
+      <c r="H101" s="31" t="n"/>
+      <c r="I101" s="31" t="n"/>
+      <c r="J101" s="34" t="n"/>
     </row>
     <row r="102" ht="21.6" customHeight="1">
       <c r="A102" s="7" t="n"/>
@@ -13973,17 +14010,17 @@
       <c r="C102" s="8" t="n"/>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Telegram notifications</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>ការជូនដំណឹង Telegram</t>
+          <t>ទូទៅ</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
         <is>
-          <t>/telegram-notifications</t>
+          <t>/settings</t>
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
@@ -13997,17 +14034,17 @@
       <c r="C103" s="8" t="n"/>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Telegram notifications</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>អ្នកប្រើប្រាស់</t>
+          <t>ការជូនដំណឹង Telegram</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/telegram-notifications</t>
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
@@ -14018,22 +14055,20 @@
     <row r="104" ht="21.6" customHeight="1">
       <c r="A104" s="7" t="n"/>
       <c r="B104" s="8" t="n"/>
-      <c r="C104" s="8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="D104" s="37" t="inlineStr">
-        <is>
-          <t>Roles</t>
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>Users</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>អ្នកប្រើប្រាស់</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
@@ -14044,20 +14079,22 @@
     <row r="105" ht="21.6" customHeight="1">
       <c r="A105" s="7" t="n"/>
       <c r="B105" s="8" t="n"/>
-      <c r="C105" s="8" t="n"/>
-      <c r="D105" s="10" t="inlineStr">
-        <is>
-          <t>Audit Logs</t>
+      <c r="C105" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D105" s="37" t="inlineStr">
+        <is>
+          <t>Roles</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>កំណត់ហេតុសវនកម្ម</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>/audit-logs</t>
+          <t>/roles</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
@@ -14071,39 +14108,29 @@
       <c r="C106" s="8" t="n"/>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Audit Logs</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>កំណត់ហេតុសវនកម្ម</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" s="8" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="I106" s="8" t="inlineStr">
-        <is>
-          <t>ភាសា</t>
-        </is>
-      </c>
+          <t>/audit-logs</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="n"/>
+      <c r="H106" s="8" t="n"/>
+      <c r="I106" s="8" t="n"/>
       <c r="J106" s="12" t="n"/>
     </row>
     <row r="107" ht="21.6" customHeight="1">
       <c r="A107" s="7" t="n"/>
       <c r="B107" s="8" t="n"/>
       <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D107" s="10" t="inlineStr">
         <is>
           <t>Languages</t>
         </is>
@@ -14119,16 +14146,16 @@
         </is>
       </c>
       <c r="G107" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>Translation</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>ការបកប្រែ</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="J107" s="12" t="n"/>
@@ -14137,24 +14164,34 @@
       <c r="A108" s="7" t="n"/>
       <c r="B108" s="8" t="n"/>
       <c r="C108" s="8" t="n"/>
-      <c r="D108" s="10" t="inlineStr">
-        <is>
-          <t>Base Data</t>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>Languages</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>ទិន្នន័យមូលដ្ឋាន</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>/lookup-categories</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>ការបកប្រែ</t>
+        </is>
+      </c>
       <c r="J108" s="12" t="n"/>
     </row>
     <row r="109" ht="21.6" customHeight="1">
@@ -14163,17 +14200,17 @@
       <c r="C109" s="8" t="n"/>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Base Data</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>បម្រុងទុក</t>
+          <t>ទិន្នន័យមូលដ្ឋាន</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>/database-backups</t>
+          <t>/lookup-categories</t>
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
@@ -14182,89 +14219,91 @@
       <c r="J109" s="12" t="n"/>
     </row>
     <row r="110" ht="21.6" customHeight="1">
-      <c r="A110" s="13" t="inlineStr">
+      <c r="A110" s="7" t="n"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>Backup</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>បម្រុងទុក</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>/database-backups</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="n"/>
+      <c r="H110" s="8" t="n"/>
+      <c r="I110" s="8" t="n"/>
+      <c r="J110" s="12" t="n"/>
+    </row>
+    <row r="111" ht="21.6" customHeight="1">
+      <c r="A111" s="13" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B110" s="14" t="inlineStr">
+      <c r="B111" s="14" t="inlineStr">
         <is>
           <t>eApprovals</t>
         </is>
       </c>
-      <c r="C110" s="15" t="n"/>
-      <c r="D110" s="14" t="inlineStr">
+      <c r="C111" s="15" t="n"/>
+      <c r="D111" s="14" t="inlineStr">
         <is>
           <t>Forms</t>
         </is>
       </c>
-      <c r="E110" s="15" t="inlineStr">
+      <c r="E111" s="15" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="F110" s="16" t="inlineStr">
+      <c r="F111" s="16" t="inlineStr">
         <is>
           <t>/approvals/forms</t>
         </is>
       </c>
-      <c r="G110" s="17" t="n"/>
-      <c r="H110" s="15" t="n"/>
-      <c r="I110" s="15" t="n"/>
-      <c r="J110" s="18" t="n"/>
-    </row>
-    <row r="111" ht="21.6" customHeight="1">
-      <c r="A111" s="19" t="n"/>
-      <c r="B111" s="20" t="n"/>
-      <c r="C111" s="20" t="n"/>
-      <c r="D111" s="22" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="E111" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="F111" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="G111" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I111" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
-      <c r="J111" s="24" t="n"/>
+      <c r="G111" s="17" t="n"/>
+      <c r="H111" s="15" t="n"/>
+      <c r="I111" s="15" t="n"/>
+      <c r="J111" s="18" t="n"/>
     </row>
     <row r="112" ht="21.6" customHeight="1">
       <c r="A112" s="19" t="n"/>
       <c r="B112" s="20" t="n"/>
       <c r="C112" s="20" t="n"/>
-      <c r="D112" s="20" t="n"/>
-      <c r="E112" s="20" t="n"/>
-      <c r="F112" s="23" t="n"/>
+      <c r="D112" s="22" t="inlineStr">
+        <is>
+          <t>My Request</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>សំណើរបស់ខ្ញុំ</t>
+        </is>
+      </c>
+      <c r="F112" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
       <c r="G112" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H112" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="J112" s="24" t="n"/>
@@ -14277,16 +14316,16 @@
       <c r="E113" s="20" t="n"/>
       <c r="F113" s="23" t="n"/>
       <c r="G113" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H113" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="J113" s="24" t="n"/>
@@ -14299,16 +14338,16 @@
       <c r="E114" s="20" t="n"/>
       <c r="F114" s="23" t="n"/>
       <c r="G114" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H114" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="J114" s="24" t="n"/>
@@ -14321,16 +14360,16 @@
       <c r="E115" s="20" t="n"/>
       <c r="F115" s="23" t="n"/>
       <c r="G115" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H115" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="J115" s="24" t="n"/>
@@ -14339,24 +14378,22 @@
       <c r="A116" s="19" t="n"/>
       <c r="B116" s="20" t="n"/>
       <c r="C116" s="20" t="n"/>
-      <c r="D116" s="22" t="inlineStr">
-        <is>
-          <t>Form Categories</t>
-        </is>
-      </c>
-      <c r="E116" s="20" t="inlineStr">
-        <is>
-          <t>ប្រភេទទម្រង់បែបបទ</t>
-        </is>
-      </c>
-      <c r="F116" s="23" t="inlineStr">
-        <is>
-          <t>/form-categories</t>
-        </is>
-      </c>
-      <c r="G116" s="19" t="n"/>
-      <c r="H116" s="20" t="n"/>
-      <c r="I116" s="20" t="n"/>
+      <c r="D116" s="20" t="n"/>
+      <c r="E116" s="20" t="n"/>
+      <c r="F116" s="23" t="n"/>
+      <c r="G116" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H116" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="I116" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
       <c r="J116" s="24" t="n"/>
     </row>
     <row r="117">
@@ -14365,17 +14402,17 @@
       <c r="C117" s="20" t="n"/>
       <c r="D117" s="22" t="inlineStr">
         <is>
-          <t>Form Templates</t>
+          <t>Form Categories</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
         <is>
-          <t>ទម្រង់បែបបទ</t>
+          <t>ប្រភេទទម្រង់បែបបទ</t>
         </is>
       </c>
       <c r="F117" s="23" t="inlineStr">
         <is>
-          <t>/form-templates</t>
+          <t>/form-categories</t>
         </is>
       </c>
       <c r="G117" s="19" t="n"/>
@@ -14384,76 +14421,100 @@
       <c r="J117" s="24" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="inlineStr">
+      <c r="A118" s="19" t="n"/>
+      <c r="B118" s="20" t="n"/>
+      <c r="C118" s="20" t="n"/>
+      <c r="D118" s="22" t="inlineStr">
+        <is>
+          <t>Form Templates</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>ទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="F118" s="23" t="inlineStr">
+        <is>
+          <t>/form-templates</t>
+        </is>
+      </c>
+      <c r="G118" s="19" t="n"/>
+      <c r="H118" s="20" t="n"/>
+      <c r="I118" s="20" t="n"/>
+      <c r="J118" s="24" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Groups</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>ក្រុម</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="F119" s="4" t="inlineStr">
         <is>
           <t>/approval-flow/groups</t>
         </is>
       </c>
-      <c r="G118" s="5" t="n"/>
-      <c r="H118" s="3" t="n"/>
-      <c r="I118" s="3" t="n"/>
-      <c r="J118" s="6" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="7" t="inlineStr">
+      <c r="G119" s="5" t="n"/>
+      <c r="H119" s="3" t="n"/>
+      <c r="I119" s="3" t="n"/>
+      <c r="J119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
+      <c r="C120" s="8" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D119" s="10" t="inlineStr">
+      <c r="D120" s="10" t="inlineStr">
         <is>
           <t>Flow Setting</t>
         </is>
       </c>
-      <c r="E119" s="8" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>កំណត់លំហូរ</t>
         </is>
       </c>
-      <c r="F119" s="11" t="inlineStr">
+      <c r="F120" s="11" t="inlineStr">
         <is>
           <t>/approval-flow/settings</t>
         </is>
       </c>
-      <c r="G119" s="7" t="n"/>
-      <c r="H119" s="8" t="n"/>
-      <c r="I119" s="8" t="n"/>
-      <c r="J119" s="12" t="n"/>
+      <c r="G120" s="7" t="n"/>
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="8" t="n"/>
+      <c r="J120" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/NTCSWEB-Modules.xlsx
+++ b/docs/NTCSWEB-Modules.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Back office'!$A$1:$K$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Back office'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'System'!$A$1:$K$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'System'!$A$1:$K$209</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'System'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website'!$A$1:$K$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Website'!$1:$1</definedName>
@@ -2098,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K212"/>
+  <dimension ref="A1:K213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2745,100 +2745,114 @@
           <t>/projects</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="6" t="n"/>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Board</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>ផ្ទាំងការងារ</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>Tabs on each project page (/projects/{id})</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="21.6" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>B3.1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>ការគ្រប់គ្រងគម្រោង</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>/projects</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>ដំណាក់កាល</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="21.6" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Academic</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>ការសិក្សា</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>B4.1</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Programs</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>កម្មវិធីសិក្សា</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>/academic-programs</t>
         </is>
       </c>
-      <c r="H18" s="17" t="n">
+      <c r="H19" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>Academic Programs</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J19" s="15" t="inlineStr">
         <is>
           <t>កម្មវិធីសិក្សា</t>
         </is>
       </c>
-      <c r="K18" s="18" t="n"/>
-    </row>
-    <row r="19" ht="21.6" customHeight="1">
-      <c r="A19" s="19" t="n"/>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>B4.1</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>Programs</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>កម្មវិធីសិក្សា</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>/academic-programs</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>Academic Years</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>ឆ្នាំសិក្សា</t>
-        </is>
-      </c>
-      <c r="K19" s="24" t="n"/>
+      <c r="K19" s="18" t="n"/>
     </row>
     <row r="20" ht="21.6" customHeight="1">
       <c r="A20" s="19" t="n"/>
@@ -2865,16 +2879,16 @@
         </is>
       </c>
       <c r="H20" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>Academic Years</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>វគ្គសិក្សា</t>
+          <t>ឆ្នាំសិក្សា</t>
         </is>
       </c>
       <c r="K20" s="24" t="n"/>
@@ -2904,16 +2918,16 @@
         </is>
       </c>
       <c r="H21" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Course</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
         <is>
-          <t>សៀវភៅ</t>
+          <t>វគ្គសិក្សា</t>
         </is>
       </c>
       <c r="K21" s="24" t="n"/>
@@ -2943,16 +2957,16 @@
         </is>
       </c>
       <c r="H22" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
-          <t>Book Categories</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទសៀវភៅ</t>
+          <t>សៀវភៅ</t>
         </is>
       </c>
       <c r="K22" s="24" t="n"/>
@@ -2961,37 +2975,37 @@
       <c r="A23" s="19" t="n"/>
       <c r="B23" s="20" t="n"/>
       <c r="C23" s="20" t="n"/>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>B4.2</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>School Setup</t>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>B4.1</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>Programs</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>ការរៀបចំសាលា</t>
+          <t>កម្មវិធីសិក្សា</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
-          <t>/school-setup</t>
+          <t>/academic-programs</t>
         </is>
       </c>
       <c r="H23" s="19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>Terms / Semesters</t>
+          <t>Book Categories</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>ឆមាស</t>
+          <t>ប្រភេទសៀវភៅ</t>
         </is>
       </c>
       <c r="K23" s="24" t="n"/>
@@ -3000,12 +3014,12 @@
       <c r="A24" s="19" t="n"/>
       <c r="B24" s="20" t="n"/>
       <c r="C24" s="20" t="n"/>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>B4.2</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>School Setup</t>
         </is>
@@ -3021,16 +3035,16 @@
         </is>
       </c>
       <c r="H24" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
-          <t>Grade levels</t>
+          <t>Terms / Semesters</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
         <is>
-          <t>កម្រិតថ្នាក់</t>
+          <t>ឆមាស</t>
         </is>
       </c>
       <c r="K24" s="24" t="n"/>
@@ -3060,16 +3074,16 @@
         </is>
       </c>
       <c r="H25" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" s="20" t="inlineStr">
         <is>
-          <t>Curriculum</t>
+          <t>Grade levels</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>កម្មវិធីសិក្សា</t>
+          <t>កម្រិតថ្នាក់</t>
         </is>
       </c>
       <c r="K25" s="24" t="n"/>
@@ -3099,16 +3113,16 @@
         </is>
       </c>
       <c r="H26" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
-          <t>School calendar</t>
+          <t>Curriculum</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិទិនសាលា</t>
+          <t>កម្មវិធីសិក្សា</t>
         </is>
       </c>
       <c r="K26" s="24" t="n"/>
@@ -3138,16 +3152,16 @@
         </is>
       </c>
       <c r="H27" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I27" s="20" t="inlineStr">
         <is>
-          <t>Promotion rules</t>
+          <t>School calendar</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>លក្ខខណ្ឌឡើងថ្នាក់</t>
+          <t>ប្រតិទិនសាលា</t>
         </is>
       </c>
       <c r="K27" s="24" t="n"/>
@@ -3177,16 +3191,16 @@
         </is>
       </c>
       <c r="H28" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" s="20" t="inlineStr">
         <is>
-          <t>Promote students</t>
+          <t>Promotion rules</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
         <is>
-          <t>ដំឡើងថ្នាក់សិស្ស</t>
+          <t>លក្ខខណ្ឌឡើងថ្នាក់</t>
         </is>
       </c>
       <c r="K28" s="24" t="n"/>
@@ -3195,29 +3209,39 @@
       <c r="A29" s="19" t="n"/>
       <c r="B29" s="20" t="n"/>
       <c r="C29" s="20" t="n"/>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>B4.3</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>Video Lesson</t>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>B4.2</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>School Setup</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>មេរៀនវីដេអូ</t>
+          <t>ការរៀបចំសាលា</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>/videos</t>
-        </is>
-      </c>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="20" t="n"/>
-      <c r="J29" s="20" t="n"/>
+          <t>/school-setup</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>Promote students</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>ដំឡើងថ្នាក់សិស្ស</t>
+        </is>
+      </c>
       <c r="K29" s="24" t="n"/>
     </row>
     <row r="30" ht="21.6" customHeight="1">
@@ -3226,49 +3250,39 @@
       <c r="C30" s="20" t="n"/>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>B4.4</t>
+          <t>B4.3</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>Study Building</t>
+          <t>Video Lesson</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>អគារសិក្សា</t>
+          <t>មេរៀនវីដេអូ</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>/buildings</t>
-        </is>
-      </c>
-      <c r="H30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="20" t="inlineStr">
-        <is>
-          <t>Buildings</t>
-        </is>
-      </c>
-      <c r="J30" s="20" t="inlineStr">
-        <is>
-          <t>អគារ</t>
-        </is>
-      </c>
+          <t>/videos</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="20" t="n"/>
+      <c r="J30" s="20" t="n"/>
       <c r="K30" s="24" t="n"/>
     </row>
     <row r="31" ht="21.6" customHeight="1">
       <c r="A31" s="19" t="n"/>
       <c r="B31" s="20" t="n"/>
       <c r="C31" s="20" t="n"/>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>B4.4</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>Study Building</t>
         </is>
@@ -3284,16 +3298,16 @@
         </is>
       </c>
       <c r="H31" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="20" t="inlineStr">
         <is>
-          <t>Classrooms</t>
+          <t>Buildings</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
         <is>
-          <t>បន្ទប់រៀន</t>
+          <t>អគារ</t>
         </is>
       </c>
       <c r="K31" s="24" t="n"/>
@@ -3302,29 +3316,39 @@
       <c r="A32" s="19" t="n"/>
       <c r="B32" s="20" t="n"/>
       <c r="C32" s="20" t="n"/>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>B4.5</t>
-        </is>
-      </c>
-      <c r="E32" s="22" t="inlineStr">
-        <is>
-          <t>Classes</t>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>B4.4</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>Study Building</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>ថ្នាក់រៀន</t>
+          <t>អគារសិក្សា</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>/classes</t>
-        </is>
-      </c>
-      <c r="H32" s="19" t="n"/>
-      <c r="I32" s="20" t="n"/>
-      <c r="J32" s="20" t="n"/>
+          <t>/buildings</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>Classrooms</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>បន្ទប់រៀន</t>
+        </is>
+      </c>
       <c r="K32" s="24" t="n"/>
     </row>
     <row r="33" ht="21.6" customHeight="1">
@@ -3333,49 +3357,39 @@
       <c r="C33" s="20" t="n"/>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>B4.6</t>
+          <t>B4.5</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>Timetable</t>
+          <t>Classes</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>កាលវិភាគ</t>
+          <t>ថ្នាក់រៀន</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>/timetable</t>
-        </is>
-      </c>
-      <c r="H33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="20" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="J33" s="20" t="inlineStr">
-        <is>
-          <t>ថ្នាក់</t>
-        </is>
-      </c>
+          <t>/classes</t>
+        </is>
+      </c>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="20" t="n"/>
+      <c r="J33" s="20" t="n"/>
       <c r="K33" s="24" t="n"/>
     </row>
     <row r="34" ht="21.6" customHeight="1">
       <c r="A34" s="19" t="n"/>
       <c r="B34" s="20" t="n"/>
       <c r="C34" s="20" t="n"/>
-      <c r="D34" s="19" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>B4.6</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>Timetable</t>
         </is>
@@ -3391,16 +3405,16 @@
         </is>
       </c>
       <c r="H34" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" s="20" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
         <is>
-          <t>គ្រូ</t>
+          <t>ថ្នាក់</t>
         </is>
       </c>
       <c r="K34" s="24" t="n"/>
@@ -3430,16 +3444,16 @@
         </is>
       </c>
       <c r="H35" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" s="20" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
         <is>
-          <t>បន្ទប់</t>
+          <t>គ្រូ</t>
         </is>
       </c>
       <c r="K35" s="24" t="n"/>
@@ -3469,16 +3483,16 @@
         </is>
       </c>
       <c r="H36" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I36" s="20" t="inlineStr">
         <is>
-          <t>Subject hours</t>
+          <t>Room</t>
         </is>
       </c>
       <c r="J36" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងតាមមុខវិជ្ជា</t>
+          <t>បន្ទប់</t>
         </is>
       </c>
       <c r="K36" s="24" t="n"/>
@@ -3508,16 +3522,16 @@
         </is>
       </c>
       <c r="H37" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I37" s="20" t="inlineStr">
         <is>
-          <t>Conflicts</t>
+          <t>Subject hours</t>
         </is>
       </c>
       <c r="J37" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងជាន់គ្នា</t>
+          <t>ម៉ោងតាមមុខវិជ្ជា</t>
         </is>
       </c>
       <c r="K37" s="24" t="n"/>
@@ -3547,16 +3561,16 @@
         </is>
       </c>
       <c r="H38" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I38" s="20" t="inlineStr">
         <is>
-          <t>Schedule changes</t>
+          <t>Conflicts</t>
         </is>
       </c>
       <c r="J38" s="20" t="inlineStr">
         <is>
-          <t>សំណើប្តូរកាលវិភាគ</t>
+          <t>ម៉ោងជាន់គ្នា</t>
         </is>
       </c>
       <c r="K38" s="24" t="n"/>
@@ -3565,37 +3579,37 @@
       <c r="A39" s="19" t="n"/>
       <c r="B39" s="20" t="n"/>
       <c r="C39" s="20" t="n"/>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>B4.7</t>
-        </is>
-      </c>
-      <c r="E39" s="22" t="inlineStr">
-        <is>
-          <t>Lesson Plans</t>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>B4.6</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>Timetable</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>ផែនការបង្រៀន</t>
+          <t>កាលវិភាគ</t>
         </is>
       </c>
       <c r="G39" s="23" t="inlineStr">
         <is>
-          <t>/lessons</t>
+          <t>/timetable</t>
         </is>
       </c>
       <c r="H39" s="19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I39" s="20" t="inlineStr">
         <is>
-          <t>Lesson plans</t>
+          <t>Schedule changes</t>
         </is>
       </c>
       <c r="J39" s="20" t="inlineStr">
         <is>
-          <t>ផែនការមេរៀន</t>
+          <t>សំណើប្តូរកាលវិភាគ</t>
         </is>
       </c>
       <c r="K39" s="24" t="n"/>
@@ -3604,12 +3618,12 @@
       <c r="A40" s="19" t="n"/>
       <c r="B40" s="20" t="n"/>
       <c r="C40" s="20" t="n"/>
-      <c r="D40" s="19" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>B4.7</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E40" s="22" t="inlineStr">
         <is>
           <t>Lesson Plans</t>
         </is>
@@ -3625,16 +3639,16 @@
         </is>
       </c>
       <c r="H40" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" s="20" t="inlineStr">
         <is>
-          <t>Weekly plan</t>
+          <t>Lesson plans</t>
         </is>
       </c>
       <c r="J40" s="20" t="inlineStr">
         <is>
-          <t>ផែនការប្រចាំសប្តាហ៍</t>
+          <t>ផែនការមេរៀន</t>
         </is>
       </c>
       <c r="K40" s="24" t="n"/>
@@ -3664,16 +3678,16 @@
         </is>
       </c>
       <c r="H41" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I41" s="20" t="inlineStr">
         <is>
-          <t>Teaching log</t>
+          <t>Weekly plan</t>
         </is>
       </c>
       <c r="J41" s="20" t="inlineStr">
         <is>
-          <t>កំណត់ត្រាបង្រៀន</t>
+          <t>ផែនការប្រចាំសប្តាហ៍</t>
         </is>
       </c>
       <c r="K41" s="24" t="n"/>
@@ -3703,16 +3717,16 @@
         </is>
       </c>
       <c r="H42" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42" s="20" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Teaching log</t>
         </is>
       </c>
       <c r="J42" s="20" t="inlineStr">
         <is>
-          <t>ពិនិត្យ</t>
+          <t>កំណត់ត្រាបង្រៀន</t>
         </is>
       </c>
       <c r="K42" s="24" t="n"/>
@@ -3742,16 +3756,16 @@
         </is>
       </c>
       <c r="H43" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
-          <t>Curriculum progress</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="J43" s="20" t="inlineStr">
         <is>
-          <t>វឌ្ឍនភាពកម្មវិធីសិក្សា</t>
+          <t>ពិនិត្យ</t>
         </is>
       </c>
       <c r="K43" s="24" t="n"/>
@@ -3781,16 +3795,16 @@
         </is>
       </c>
       <c r="H44" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
-          <t>Delays</t>
+          <t>Curriculum progress</t>
         </is>
       </c>
       <c r="J44" s="20" t="inlineStr">
         <is>
-          <t>យឺតពេល</t>
+          <t>វឌ្ឍនភាពកម្មវិធីសិក្សា</t>
         </is>
       </c>
       <c r="K44" s="24" t="n"/>
@@ -3799,37 +3813,37 @@
       <c r="A45" s="19" t="n"/>
       <c r="B45" s="20" t="n"/>
       <c r="C45" s="20" t="n"/>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>B4.8</t>
-        </is>
-      </c>
-      <c r="E45" s="22" t="inlineStr">
-        <is>
-          <t>Student Attendance</t>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>B4.7</t>
+        </is>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>Lesson Plans</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
-          <t>វត្តមានសិស្ស</t>
+          <t>ផែនការបង្រៀន</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>/attendance</t>
+          <t>/lessons</t>
         </is>
       </c>
       <c r="H45" s="19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
-          <t>Student Attendance</t>
+          <t>Delays</t>
         </is>
       </c>
       <c r="J45" s="20" t="inlineStr">
         <is>
-          <t>វត្តមានសិស្ស</t>
+          <t>យឺតពេល</t>
         </is>
       </c>
       <c r="K45" s="24" t="n"/>
@@ -3838,12 +3852,12 @@
       <c r="A46" s="19" t="n"/>
       <c r="B46" s="20" t="n"/>
       <c r="C46" s="20" t="n"/>
-      <c r="D46" s="19" t="inlineStr">
+      <c r="D46" s="21" t="inlineStr">
         <is>
           <t>B4.8</t>
         </is>
       </c>
-      <c r="E46" s="20" t="inlineStr">
+      <c r="E46" s="22" t="inlineStr">
         <is>
           <t>Student Attendance</t>
         </is>
@@ -3859,16 +3873,16 @@
         </is>
       </c>
       <c r="H46" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
-          <t>Attendance Summary</t>
+          <t>Student Attendance</t>
         </is>
       </c>
       <c r="J46" s="20" t="inlineStr">
         <is>
-          <t>សរុបវត្តមាន</t>
+          <t>វត្តមានសិស្ស</t>
         </is>
       </c>
       <c r="K46" s="24" t="n"/>
@@ -3877,37 +3891,37 @@
       <c r="A47" s="19" t="n"/>
       <c r="B47" s="20" t="n"/>
       <c r="C47" s="20" t="n"/>
-      <c r="D47" s="21" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E47" s="22" t="inlineStr">
-        <is>
-          <t>Examination</t>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>B4.8</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>Student Attendance</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
+          <t>វត្តមានសិស្ស</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>/examination</t>
+          <t>/attendance</t>
         </is>
       </c>
       <c r="H47" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I47" s="20" t="inlineStr">
         <is>
-          <t>Assessment Setup</t>
+          <t>Attendance Summary</t>
         </is>
       </c>
       <c r="J47" s="20" t="inlineStr">
         <is>
-          <t>ការកំណត់ការវាយតម្លៃ</t>
+          <t>សរុបវត្តមាន</t>
         </is>
       </c>
       <c r="K47" s="24" t="n"/>
@@ -3916,12 +3930,12 @@
       <c r="A48" s="19" t="n"/>
       <c r="B48" s="20" t="n"/>
       <c r="C48" s="20" t="n"/>
-      <c r="D48" s="19" t="inlineStr">
+      <c r="D48" s="21" t="inlineStr">
         <is>
           <t>B4.9</t>
         </is>
       </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="E48" s="22" t="inlineStr">
         <is>
           <t>Examination</t>
         </is>
@@ -3937,16 +3951,16 @@
         </is>
       </c>
       <c r="H48" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="20" t="inlineStr">
         <is>
-          <t>Exam Schedule</t>
+          <t>Assessment Setup</t>
         </is>
       </c>
       <c r="J48" s="20" t="inlineStr">
         <is>
-          <t>កាលវិភាគប្រឡង</t>
+          <t>ការកំណត់ការវាយតម្លៃ</t>
         </is>
       </c>
       <c r="K48" s="24" t="n"/>
@@ -3976,16 +3990,16 @@
         </is>
       </c>
       <c r="H49" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" s="20" t="inlineStr">
         <is>
-          <t>Grade Entry</t>
+          <t>Exam Schedule</t>
         </is>
       </c>
       <c r="J49" s="20" t="inlineStr">
         <is>
-          <t>បញ្ចូលពិន្ទុ</t>
+          <t>កាលវិភាគប្រឡង</t>
         </is>
       </c>
       <c r="K49" s="24" t="n"/>
@@ -4015,16 +4029,16 @@
         </is>
       </c>
       <c r="H50" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I50" s="20" t="inlineStr">
         <is>
-          <t>Grade Validation</t>
+          <t>Grade Entry</t>
         </is>
       </c>
       <c r="J50" s="20" t="inlineStr">
         <is>
-          <t>ពិនិត្យពិន្ទុ</t>
+          <t>បញ្ចូលពិន្ទុ</t>
         </is>
       </c>
       <c r="K50" s="24" t="n"/>
@@ -4054,16 +4068,16 @@
         </is>
       </c>
       <c r="H51" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I51" s="20" t="inlineStr">
         <is>
-          <t>Score Calculation</t>
+          <t>Grade Validation</t>
         </is>
       </c>
       <c r="J51" s="20" t="inlineStr">
         <is>
-          <t>គណនាពិន្ទុ</t>
+          <t>ពិនិត្យពិន្ទុ</t>
         </is>
       </c>
       <c r="K51" s="24" t="n"/>
@@ -4093,16 +4107,16 @@
         </is>
       </c>
       <c r="H52" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I52" s="20" t="inlineStr">
         <is>
-          <t>Result Approval</t>
+          <t>Score Calculation</t>
         </is>
       </c>
       <c r="J52" s="20" t="inlineStr">
         <is>
-          <t>អនុម័តលទ្ធផល</t>
+          <t>គណនាពិន្ទុ</t>
         </is>
       </c>
       <c r="K52" s="24" t="n"/>
@@ -4132,16 +4146,16 @@
         </is>
       </c>
       <c r="H53" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I53" s="20" t="inlineStr">
         <is>
-          <t>Grade Correction</t>
+          <t>Result Approval</t>
         </is>
       </c>
       <c r="J53" s="20" t="inlineStr">
         <is>
-          <t>កែពិន្ទុ</t>
+          <t>អនុម័តលទ្ធផល</t>
         </is>
       </c>
       <c r="K53" s="24" t="n"/>
@@ -4171,16 +4185,16 @@
         </is>
       </c>
       <c r="H54" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I54" s="20" t="inlineStr">
         <is>
-          <t>Academic Transcript</t>
+          <t>Grade Correction</t>
         </is>
       </c>
       <c r="J54" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិពិន្ទុ</t>
+          <t>កែពិន្ទុ</t>
         </is>
       </c>
       <c r="K54" s="24" t="n"/>
@@ -4210,16 +4224,16 @@
         </is>
       </c>
       <c r="H55" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I55" s="20" t="inlineStr">
         <is>
-          <t>Student Progress</t>
+          <t>Academic Transcript</t>
         </is>
       </c>
       <c r="J55" s="20" t="inlineStr">
         <is>
-          <t>វឌ្ឍនភាពសិស្ស</t>
+          <t>ប្រវត្តិពិន្ទុ</t>
         </is>
       </c>
       <c r="K55" s="24" t="n"/>
@@ -4249,16 +4263,16 @@
         </is>
       </c>
       <c r="H56" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
-          <t>Remedial Teaching</t>
+          <t>Student Progress</t>
         </is>
       </c>
       <c r="J56" s="20" t="inlineStr">
         <is>
-          <t>ការបង្រៀនបំប៉ន</t>
+          <t>វឌ្ឍនភាពសិស្ស</t>
         </is>
       </c>
       <c r="K56" s="24" t="n"/>
@@ -4288,16 +4302,16 @@
         </is>
       </c>
       <c r="H57" s="19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
-          <t>Result Export</t>
+          <t>Remedial Teaching</t>
         </is>
       </c>
       <c r="J57" s="20" t="inlineStr">
         <is>
-          <t>នាំចេញលទ្ធផល</t>
+          <t>ការបង្រៀនបំប៉ន</t>
         </is>
       </c>
       <c r="K57" s="24" t="n"/>
@@ -4327,16 +4341,16 @@
         </is>
       </c>
       <c r="H58" s="19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I58" s="20" t="inlineStr">
         <is>
-          <t>Exams</t>
+          <t>Result Export</t>
         </is>
       </c>
       <c r="J58" s="20" t="inlineStr">
         <is>
-          <t>ការប្រឡង</t>
+          <t>នាំចេញលទ្ធផល</t>
         </is>
       </c>
       <c r="K58" s="24" t="n"/>
@@ -4366,16 +4380,16 @@
         </is>
       </c>
       <c r="H59" s="19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
-          <t>Grades</t>
+          <t>Exams</t>
         </is>
       </c>
       <c r="J59" s="20" t="inlineStr">
         <is>
-          <t>និទ្ទេស</t>
+          <t>ការប្រឡង</t>
         </is>
       </c>
       <c r="K59" s="24" t="n"/>
@@ -4405,16 +4419,16 @@
         </is>
       </c>
       <c r="H60" s="19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I60" s="20" t="inlineStr">
         <is>
-          <t>Make-up Exam</t>
+          <t>Grades</t>
         </is>
       </c>
       <c r="J60" s="20" t="inlineStr">
         <is>
-          <t>ប្រឡងសង</t>
+          <t>និទ្ទេស</t>
         </is>
       </c>
       <c r="K60" s="24" t="n"/>
@@ -4444,89 +4458,99 @@
         </is>
       </c>
       <c r="H61" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
+          <t>Make-up Exam</t>
+        </is>
+      </c>
+      <c r="J61" s="20" t="inlineStr">
+        <is>
+          <t>ប្រឡងសង</t>
+        </is>
+      </c>
+      <c r="K61" s="24" t="n"/>
+    </row>
+    <row r="62" ht="21.6" customHeight="1">
+      <c r="A62" s="19" t="n"/>
+      <c r="B62" s="20" t="n"/>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>B4.9</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>Examination</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>ការប្រឡងនិងលទ្ធផល</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>/examination</t>
+        </is>
+      </c>
+      <c r="H62" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="I61" s="20" t="inlineStr">
+      <c r="I62" s="20" t="inlineStr">
         <is>
           <t>Certificate</t>
         </is>
       </c>
-      <c r="J61" s="20" t="inlineStr">
+      <c r="J62" s="20" t="inlineStr">
         <is>
           <t>វិញ្ញាបនបត្រ</t>
         </is>
       </c>
-      <c r="K61" s="24" t="n"/>
-    </row>
-    <row r="62" ht="21.6" customHeight="1">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="K62" s="24" t="n"/>
+    </row>
+    <row r="63" ht="21.6" customHeight="1">
+      <c r="A63" s="1" t="inlineStr">
         <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>សិស្សានុសិស្ស</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr">
+      <c r="D63" s="1" t="inlineStr">
         <is>
           <t>B5.1</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>សិស្សានុសិស្ស</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>/students</t>
         </is>
       </c>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="3" t="n"/>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="6" t="n"/>
-    </row>
-    <row r="63" ht="21.6" customHeight="1">
-      <c r="A63" s="7" t="n"/>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>B5.2</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>Import Students</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>នាំចូលទិន្នន័យសិស្ស</t>
-        </is>
-      </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>/student-imports</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="n"/>
-      <c r="I63" s="8" t="n"/>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="12" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="3" t="n"/>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="6" t="n"/>
     </row>
     <row r="64" ht="21.6" customHeight="1">
       <c r="A64" s="7" t="n"/>
@@ -4534,22 +4558,22 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>B5.3</t>
+          <t>B5.2</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>Enrollments</t>
+          <t>Import Students</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>ការចុះឈ្មោះចូលរៀន</t>
+          <t>នាំចូលទិន្នន័យសិស្ស</t>
         </is>
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>/enrollments</t>
+          <t>/student-imports</t>
         </is>
       </c>
       <c r="H64" s="7" t="n"/>
@@ -4558,98 +4582,88 @@
       <c r="K64" s="12" t="n"/>
     </row>
     <row r="65" ht="21.6" customHeight="1">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A65" s="7" t="n"/>
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>B5.3</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>Enrollments</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>ការចុះឈ្មោះចូលរៀន</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>/enrollments</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="8" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="12" t="n"/>
+    </row>
+    <row r="66" ht="21.6" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>HRM</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>ធនធានមនុស្ស</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>B6.1</t>
         </is>
       </c>
-      <c r="E65" s="14" t="inlineStr">
+      <c r="E66" s="14" t="inlineStr">
         <is>
           <t>Staff</t>
         </is>
       </c>
-      <c r="F65" s="15" t="inlineStr">
+      <c r="F66" s="15" t="inlineStr">
         <is>
           <t>បុគ្គលិក</t>
         </is>
       </c>
-      <c r="G65" s="16" t="inlineStr">
+      <c r="G66" s="16" t="inlineStr">
         <is>
           <t>/staff</t>
         </is>
       </c>
-      <c r="H65" s="17" t="n">
+      <c r="H66" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="I65" s="15" t="inlineStr">
+      <c r="I66" s="15" t="inlineStr">
         <is>
           <t>Current Info</t>
         </is>
       </c>
-      <c r="J65" s="15" t="inlineStr">
+      <c r="J66" s="15" t="inlineStr">
         <is>
           <t>ព័ត៌មានបច្ចុប្បន្ន</t>
         </is>
       </c>
-      <c r="K65" s="18" t="inlineStr">
+      <c r="K66" s="18" t="inlineStr">
         <is>
           <t>Tabs on the staff form</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="21.6" customHeight="1">
-      <c r="A66" s="19" t="n"/>
-      <c r="B66" s="20" t="n"/>
-      <c r="C66" s="20" t="n"/>
-      <c r="D66" s="19" t="inlineStr">
-        <is>
-          <t>B6.1</t>
-        </is>
-      </c>
-      <c r="E66" s="20" t="inlineStr">
-        <is>
-          <t>Staff</t>
-        </is>
-      </c>
-      <c r="F66" s="20" t="inlineStr">
-        <is>
-          <t>បុគ្គលិក</t>
-        </is>
-      </c>
-      <c r="G66" s="23" t="inlineStr">
-        <is>
-          <t>/staff</t>
-        </is>
-      </c>
-      <c r="H66" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" s="20" t="inlineStr">
-        <is>
-          <t>Emergency Contacts</t>
-        </is>
-      </c>
-      <c r="J66" s="20" t="inlineStr">
-        <is>
-          <t>ទំនាក់ទំនងបន្ទាន់</t>
-        </is>
-      </c>
-      <c r="K66" s="24" t="n"/>
     </row>
     <row r="67" ht="21.6" customHeight="1">
       <c r="A67" s="19" t="n"/>
@@ -4676,16 +4690,16 @@
         </is>
       </c>
       <c r="H67" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Emergency Contacts</t>
         </is>
       </c>
       <c r="J67" s="20" t="inlineStr">
         <is>
-          <t>ការសិក្សា</t>
+          <t>ទំនាក់ទំនងបន្ទាន់</t>
         </is>
       </c>
       <c r="K67" s="24" t="n"/>
@@ -4715,16 +4729,16 @@
         </is>
       </c>
       <c r="H68" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
-          <t>Family Members</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="J68" s="20" t="inlineStr">
         <is>
-          <t>សមាជិកគ្រួសារ</t>
+          <t>ការសិក្សា</t>
         </is>
       </c>
       <c r="K68" s="24" t="n"/>
@@ -4754,16 +4768,16 @@
         </is>
       </c>
       <c r="H69" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Family Members</t>
         </is>
       </c>
       <c r="J69" s="20" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>សមាជិកគ្រួសារ</t>
         </is>
       </c>
       <c r="K69" s="24" t="n"/>
@@ -4793,16 +4807,16 @@
         </is>
       </c>
       <c r="H70" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>Previous Work</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="J70" s="20" t="inlineStr">
         <is>
-          <t>បទពិសោធន៍ការងារពីមុន</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="K70" s="24" t="n"/>
@@ -4811,37 +4825,37 @@
       <c r="A71" s="19" t="n"/>
       <c r="B71" s="20" t="n"/>
       <c r="C71" s="20" t="n"/>
-      <c r="D71" s="21" t="inlineStr">
-        <is>
-          <t>B6.2</t>
-        </is>
-      </c>
-      <c r="E71" s="22" t="inlineStr">
-        <is>
-          <t>Teachers</t>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>B6.1</t>
+        </is>
+      </c>
+      <c r="E71" s="20" t="inlineStr">
+        <is>
+          <t>Staff</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>គ្រូ</t>
+          <t>បុគ្គលិក</t>
         </is>
       </c>
       <c r="G71" s="23" t="inlineStr">
         <is>
-          <t>/teachers</t>
+          <t>/staff</t>
         </is>
       </c>
       <c r="H71" s="19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Previous Work</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
-          <t>គុណវុឌ្ឍិ</t>
+          <t>បទពិសោធន៍ការងារពីមុន</t>
         </is>
       </c>
       <c r="K71" s="24" t="n"/>
@@ -4850,12 +4864,12 @@
       <c r="A72" s="19" t="n"/>
       <c r="B72" s="20" t="n"/>
       <c r="C72" s="20" t="n"/>
-      <c r="D72" s="19" t="inlineStr">
+      <c r="D72" s="21" t="inlineStr">
         <is>
           <t>B6.2</t>
         </is>
       </c>
-      <c r="E72" s="20" t="inlineStr">
+      <c r="E72" s="22" t="inlineStr">
         <is>
           <t>Teachers</t>
         </is>
@@ -4871,16 +4885,16 @@
         </is>
       </c>
       <c r="H72" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="J72" s="20" t="inlineStr">
         <is>
-          <t>ការចាត់តាំង</t>
+          <t>គុណវុឌ្ឍិ</t>
         </is>
       </c>
       <c r="K72" s="24" t="n"/>
@@ -4910,16 +4924,16 @@
         </is>
       </c>
       <c r="H73" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Homeroom</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
         <is>
-          <t>គ្រូប្រចាំថ្នាក់</t>
+          <t>ការចាត់តាំង</t>
         </is>
       </c>
       <c r="K73" s="24" t="n"/>
@@ -4949,16 +4963,16 @@
         </is>
       </c>
       <c r="H74" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>Teaching load</t>
+          <t>Homeroom</t>
         </is>
       </c>
       <c r="J74" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបង្រៀន</t>
+          <t>គ្រូប្រចាំថ្នាក់</t>
         </is>
       </c>
       <c r="K74" s="24" t="n"/>
@@ -4988,16 +5002,16 @@
         </is>
       </c>
       <c r="H75" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Teaching load</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>ពេលទំនេរ</t>
+          <t>ម៉ោងបង្រៀន</t>
         </is>
       </c>
       <c r="K75" s="24" t="n"/>
@@ -5027,16 +5041,16 @@
         </is>
       </c>
       <c r="H76" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>Substitute</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="J76" s="20" t="inlineStr">
         <is>
-          <t>គ្រូជំនួស</t>
+          <t>ពេលទំនេរ</t>
         </is>
       </c>
       <c r="K76" s="24" t="n"/>
@@ -5066,16 +5080,16 @@
         </is>
       </c>
       <c r="H77" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Substitute</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
         <is>
-          <t>ឯកសារ</t>
+          <t>គ្រូជំនួស</t>
         </is>
       </c>
       <c r="K77" s="24" t="n"/>
@@ -5084,29 +5098,39 @@
       <c r="A78" s="19" t="n"/>
       <c r="B78" s="20" t="n"/>
       <c r="C78" s="20" t="n"/>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>B6.3</t>
-        </is>
-      </c>
-      <c r="E78" s="22" t="inlineStr">
-        <is>
-          <t>Staff Status History</t>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>B6.2</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr">
+        <is>
+          <t>Teachers</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
+          <t>គ្រូ</t>
         </is>
       </c>
       <c r="G78" s="23" t="inlineStr">
         <is>
-          <t>/staff-status-history</t>
-        </is>
-      </c>
-      <c r="H78" s="19" t="n"/>
-      <c r="I78" s="20" t="n"/>
-      <c r="J78" s="20" t="n"/>
+          <t>/teachers</t>
+        </is>
+      </c>
+      <c r="H78" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="J78" s="20" t="inlineStr">
+        <is>
+          <t>ឯកសារ</t>
+        </is>
+      </c>
       <c r="K78" s="24" t="n"/>
     </row>
     <row r="79" ht="21.6" customHeight="1">
@@ -5115,49 +5139,39 @@
       <c r="C79" s="20" t="n"/>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>B6.4</t>
+          <t>B6.3</t>
         </is>
       </c>
       <c r="E79" s="22" t="inlineStr">
         <is>
-          <t>Organization Management</t>
+          <t>Staff Status History</t>
         </is>
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងអង្គភាព</t>
+          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
         <is>
-          <t>/organization</t>
-        </is>
-      </c>
-      <c r="H79" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" s="20" t="inlineStr">
-        <is>
-          <t>School</t>
-        </is>
-      </c>
-      <c r="J79" s="20" t="inlineStr">
-        <is>
-          <t>សាលា</t>
-        </is>
-      </c>
+          <t>/staff-status-history</t>
+        </is>
+      </c>
+      <c r="H79" s="19" t="n"/>
+      <c r="I79" s="20" t="n"/>
+      <c r="J79" s="20" t="n"/>
       <c r="K79" s="24" t="n"/>
     </row>
     <row r="80" ht="21.6" customHeight="1">
       <c r="A80" s="19" t="n"/>
       <c r="B80" s="20" t="n"/>
       <c r="C80" s="20" t="n"/>
-      <c r="D80" s="19" t="inlineStr">
+      <c r="D80" s="21" t="inlineStr">
         <is>
           <t>B6.4</t>
         </is>
       </c>
-      <c r="E80" s="20" t="inlineStr">
+      <c r="E80" s="22" t="inlineStr">
         <is>
           <t>Organization Management</t>
         </is>
@@ -5173,16 +5187,16 @@
         </is>
       </c>
       <c r="H80" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>School</t>
         </is>
       </c>
       <c r="J80" s="20" t="inlineStr">
         <is>
-          <t>សាខា</t>
+          <t>សាលា</t>
         </is>
       </c>
       <c r="K80" s="24" t="n"/>
@@ -5212,16 +5226,16 @@
         </is>
       </c>
       <c r="H81" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>សាខា</t>
         </is>
       </c>
       <c r="K81" s="24" t="n"/>
@@ -5251,16 +5265,16 @@
         </is>
       </c>
       <c r="H82" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="J82" s="20" t="inlineStr">
         <is>
-          <t>ក្រុម</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="K82" s="24" t="n"/>
@@ -5290,16 +5304,16 @@
         </is>
       </c>
       <c r="H83" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>ក្រុម</t>
         </is>
       </c>
       <c r="K83" s="24" t="n"/>
@@ -5329,16 +5343,16 @@
         </is>
       </c>
       <c r="H84" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>Job grade</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="J84" s="20" t="inlineStr">
         <is>
-          <t>ថ្នាក់ការងារ</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="K84" s="24" t="n"/>
@@ -5368,16 +5382,16 @@
         </is>
       </c>
       <c r="H85" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Job level</t>
+          <t>Job grade</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>កម្រិតការងារ</t>
+          <t>ថ្នាក់ការងារ</t>
         </is>
       </c>
       <c r="K85" s="24" t="n"/>
@@ -5407,16 +5421,16 @@
         </is>
       </c>
       <c r="H86" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Reporting manager</t>
+          <t>Job level</t>
         </is>
       </c>
       <c r="J86" s="20" t="inlineStr">
         <is>
-          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
+          <t>កម្រិតការងារ</t>
         </is>
       </c>
       <c r="K86" s="24" t="n"/>
@@ -5446,16 +5460,16 @@
         </is>
       </c>
       <c r="H87" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Organization hierarchy</t>
+          <t>Reporting manager</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
+          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
         </is>
       </c>
       <c r="K87" s="24" t="n"/>
@@ -5464,37 +5478,37 @@
       <c r="A88" s="19" t="n"/>
       <c r="B88" s="20" t="n"/>
       <c r="C88" s="20" t="n"/>
-      <c r="D88" s="21" t="inlineStr">
-        <is>
-          <t>B6.5</t>
-        </is>
-      </c>
-      <c r="E88" s="22" t="inlineStr">
-        <is>
-          <t>Recruitment</t>
+      <c r="D88" s="19" t="inlineStr">
+        <is>
+          <t>B6.4</t>
+        </is>
+      </c>
+      <c r="E88" s="20" t="inlineStr">
+        <is>
+          <t>Organization Management</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបុគ្គលិក</t>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
         </is>
       </c>
       <c r="G88" s="23" t="inlineStr">
         <is>
-          <t>/recruitment</t>
+          <t>/organization</t>
         </is>
       </c>
       <c r="H88" s="19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>Manpower request</t>
+          <t>Organization hierarchy</t>
         </is>
       </c>
       <c r="J88" s="20" t="inlineStr">
         <is>
-          <t>សំណើបុគ្គលិក</t>
+          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
         </is>
       </c>
       <c r="K88" s="24" t="n"/>
@@ -5503,12 +5517,12 @@
       <c r="A89" s="19" t="n"/>
       <c r="B89" s="20" t="n"/>
       <c r="C89" s="20" t="n"/>
-      <c r="D89" s="19" t="inlineStr">
+      <c r="D89" s="21" t="inlineStr">
         <is>
           <t>B6.5</t>
         </is>
       </c>
-      <c r="E89" s="20" t="inlineStr">
+      <c r="E89" s="22" t="inlineStr">
         <is>
           <t>Recruitment</t>
         </is>
@@ -5524,16 +5538,16 @@
         </is>
       </c>
       <c r="H89" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Job positions</t>
+          <t>Manpower request</t>
         </is>
       </c>
       <c r="J89" s="20" t="inlineStr">
         <is>
-          <t>មុខតំណែងការងារ</t>
+          <t>សំណើបុគ្គលិក</t>
         </is>
       </c>
       <c r="K89" s="24" t="n"/>
@@ -5563,16 +5577,16 @@
         </is>
       </c>
       <c r="H90" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Job postings</t>
+          <t>Job positions</t>
         </is>
       </c>
       <c r="J90" s="20" t="inlineStr">
         <is>
-          <t>ការផ្សព្វផ្សាយការងារ</t>
+          <t>មុខតំណែងការងារ</t>
         </is>
       </c>
       <c r="K90" s="24" t="n"/>
@@ -5602,16 +5616,16 @@
         </is>
       </c>
       <c r="H91" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>Applicant management</t>
+          <t>Job postings</t>
         </is>
       </c>
       <c r="J91" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងបេក្ខជន</t>
+          <t>ការផ្សព្វផ្សាយការងារ</t>
         </is>
       </c>
       <c r="K91" s="24" t="n"/>
@@ -5641,16 +5655,16 @@
         </is>
       </c>
       <c r="H92" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
-          <t>CV/resume</t>
+          <t>Applicant management</t>
         </is>
       </c>
       <c r="J92" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិរូប (CV)</t>
+          <t>គ្រប់គ្រងបេក្ខជន</t>
         </is>
       </c>
       <c r="K92" s="24" t="n"/>
@@ -5680,16 +5694,16 @@
         </is>
       </c>
       <c r="H93" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I93" s="20" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>CV/resume</t>
         </is>
       </c>
       <c r="J93" s="20" t="inlineStr">
         <is>
-          <t>សម្ភាសន៍</t>
+          <t>ប្រវត្តិរូប (CV)</t>
         </is>
       </c>
       <c r="K93" s="24" t="n"/>
@@ -5719,16 +5733,16 @@
         </is>
       </c>
       <c r="H94" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
-          <t>Interview evaluation</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J94" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃសម្ភាសន៍</t>
+          <t>សម្ភាសន៍</t>
         </is>
       </c>
       <c r="K94" s="24" t="n"/>
@@ -5758,16 +5772,16 @@
         </is>
       </c>
       <c r="H95" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I95" s="20" t="inlineStr">
         <is>
-          <t>Candidate selection</t>
+          <t>Interview evaluation</t>
         </is>
       </c>
       <c r="J95" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបេក្ខជន</t>
+          <t>ការវាយតម្លៃសម្ភាសន៍</t>
         </is>
       </c>
       <c r="K95" s="24" t="n"/>
@@ -5797,16 +5811,16 @@
         </is>
       </c>
       <c r="H96" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
-          <t>Offer letter</t>
+          <t>Candidate selection</t>
         </is>
       </c>
       <c r="J96" s="20" t="inlineStr">
         <is>
-          <t>លិខិតផ្តល់ការងារ</t>
+          <t>ការជ្រើសរើសបេក្ខជន</t>
         </is>
       </c>
       <c r="K96" s="24" t="n"/>
@@ -5836,16 +5850,16 @@
         </is>
       </c>
       <c r="H97" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>Recruitment pipeline</t>
+          <t>Offer letter</t>
         </is>
       </c>
       <c r="J97" s="20" t="inlineStr">
         <is>
-          <t>ដំណើរការជ្រើសរើស</t>
+          <t>លិខិតផ្តល់ការងារ</t>
         </is>
       </c>
       <c r="K97" s="24" t="n"/>
@@ -5854,37 +5868,37 @@
       <c r="A98" s="19" t="n"/>
       <c r="B98" s="20" t="n"/>
       <c r="C98" s="20" t="n"/>
-      <c r="D98" s="21" t="inlineStr">
-        <is>
-          <t>B6.6</t>
-        </is>
-      </c>
-      <c r="E98" s="22" t="inlineStr">
-        <is>
-          <t>Attendance &amp; Time</t>
+      <c r="D98" s="19" t="inlineStr">
+        <is>
+          <t>B6.5</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
         <is>
-          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+          <t>ការជ្រើសរើសបុគ្គលិក</t>
         </is>
       </c>
       <c r="G98" s="23" t="inlineStr">
         <is>
-          <t>/time-attendance</t>
+          <t>/recruitment</t>
         </is>
       </c>
       <c r="H98" s="19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
-          <t>Employee attendance</t>
+          <t>Recruitment pipeline</t>
         </is>
       </c>
       <c r="J98" s="20" t="inlineStr">
         <is>
-          <t>វត្តមានបុគ្គលិក</t>
+          <t>ដំណើរការជ្រើសរើស</t>
         </is>
       </c>
       <c r="K98" s="24" t="n"/>
@@ -5893,12 +5907,12 @@
       <c r="A99" s="19" t="n"/>
       <c r="B99" s="20" t="n"/>
       <c r="C99" s="20" t="n"/>
-      <c r="D99" s="19" t="inlineStr">
+      <c r="D99" s="21" t="inlineStr">
         <is>
           <t>B6.6</t>
         </is>
       </c>
-      <c r="E99" s="20" t="inlineStr">
+      <c r="E99" s="22" t="inlineStr">
         <is>
           <t>Attendance &amp; Time</t>
         </is>
@@ -5914,16 +5928,16 @@
         </is>
       </c>
       <c r="H99" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" s="20" t="inlineStr">
         <is>
-          <t>Check-in / check-out</t>
+          <t>Employee attendance</t>
         </is>
       </c>
       <c r="J99" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>វត្តមានបុគ្គលិក</t>
         </is>
       </c>
       <c r="K99" s="24" t="n"/>
@@ -5953,16 +5967,16 @@
         </is>
       </c>
       <c r="H100" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
-          <t>Late</t>
+          <t>Check-in / check-out</t>
         </is>
       </c>
       <c r="J100" s="20" t="inlineStr">
         <is>
-          <t>មកយឺត</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="K100" s="24" t="n"/>
@@ -5992,16 +6006,16 @@
         </is>
       </c>
       <c r="H101" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I101" s="20" t="inlineStr">
         <is>
-          <t>Early leave</t>
+          <t>Late</t>
         </is>
       </c>
       <c r="J101" s="20" t="inlineStr">
         <is>
-          <t>ចេញមុន</t>
+          <t>មកយឺត</t>
         </is>
       </c>
       <c r="K101" s="24" t="n"/>
@@ -6031,16 +6045,16 @@
         </is>
       </c>
       <c r="H102" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
-          <t>Absence</t>
+          <t>Early leave</t>
         </is>
       </c>
       <c r="J102" s="20" t="inlineStr">
         <is>
-          <t>អវត្តមាន</t>
+          <t>ចេញមុន</t>
         </is>
       </c>
       <c r="K102" s="24" t="n"/>
@@ -6070,16 +6084,16 @@
         </is>
       </c>
       <c r="H103" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Absence</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>អវត្តមាន</t>
         </is>
       </c>
       <c r="K103" s="24" t="n"/>
@@ -6109,16 +6123,16 @@
         </is>
       </c>
       <c r="H104" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="J104" s="20" t="inlineStr">
         <is>
-          <t>វេនការងារ</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="K104" s="24" t="n"/>
@@ -6148,16 +6162,16 @@
         </is>
       </c>
       <c r="H105" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I105" s="20" t="inlineStr">
         <is>
-          <t>Staff shift</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="J105" s="20" t="inlineStr">
         <is>
-          <t>វេនបុគ្គលិក</t>
+          <t>វេនការងារ</t>
         </is>
       </c>
       <c r="K105" s="24" t="n"/>
@@ -6187,16 +6201,16 @@
         </is>
       </c>
       <c r="H106" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Staff shift</t>
         </is>
       </c>
       <c r="J106" s="20" t="inlineStr">
         <is>
-          <t>ថ្ងៃឈប់សម្រាក</t>
+          <t>វេនបុគ្គលិក</t>
         </is>
       </c>
       <c r="K106" s="24" t="n"/>
@@ -6226,16 +6240,16 @@
         </is>
       </c>
       <c r="H107" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>Attendance correction</t>
+          <t>Holidays</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
         <is>
-          <t>ការកែវត្តមាន</t>
+          <t>ថ្ងៃឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K107" s="24" t="n"/>
@@ -6265,16 +6279,16 @@
         </is>
       </c>
       <c r="H108" s="19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
-          <t>Attendance approval</t>
+          <t>Attendance correction</t>
         </is>
       </c>
       <c r="J108" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តវត្តមាន</t>
+          <t>ការកែវត្តមាន</t>
         </is>
       </c>
       <c r="K108" s="24" t="n"/>
@@ -6283,37 +6297,37 @@
       <c r="A109" s="19" t="n"/>
       <c r="B109" s="20" t="n"/>
       <c r="C109" s="20" t="n"/>
-      <c r="D109" s="21" t="inlineStr">
-        <is>
-          <t>B6.7</t>
-        </is>
-      </c>
-      <c r="E109" s="22" t="inlineStr">
-        <is>
-          <t>Leave Management</t>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>B6.6</t>
+        </is>
+      </c>
+      <c r="E109" s="20" t="inlineStr">
+        <is>
+          <t>Attendance &amp; Time</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
         </is>
       </c>
       <c r="G109" s="23" t="inlineStr">
         <is>
-          <t>/leave-management</t>
+          <t>/time-attendance</t>
         </is>
       </c>
       <c r="H109" s="19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I109" s="20" t="inlineStr">
         <is>
-          <t>Leave types</t>
+          <t>Attendance approval</t>
         </is>
       </c>
       <c r="J109" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
+          <t>ការអនុម័តវត្តមាន</t>
         </is>
       </c>
       <c r="K109" s="24" t="n"/>
@@ -6322,12 +6336,12 @@
       <c r="A110" s="19" t="n"/>
       <c r="B110" s="20" t="n"/>
       <c r="C110" s="20" t="n"/>
-      <c r="D110" s="19" t="inlineStr">
+      <c r="D110" s="21" t="inlineStr">
         <is>
           <t>B6.7</t>
         </is>
       </c>
-      <c r="E110" s="20" t="inlineStr">
+      <c r="E110" s="22" t="inlineStr">
         <is>
           <t>Leave Management</t>
         </is>
@@ -6343,16 +6357,16 @@
         </is>
       </c>
       <c r="H110" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
-          <t>Leave policies</t>
+          <t>Leave types</t>
         </is>
       </c>
       <c r="J110" s="20" t="inlineStr">
         <is>
-          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
+          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K110" s="24" t="n"/>
@@ -6382,16 +6396,16 @@
         </is>
       </c>
       <c r="H111" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I111" s="20" t="inlineStr">
         <is>
-          <t>Leave balance</t>
+          <t>Leave policies</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
         <is>
-          <t>សមតុល្យច្បាប់</t>
+          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K111" s="24" t="n"/>
@@ -6421,16 +6435,16 @@
         </is>
       </c>
       <c r="H112" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
-          <t>Leave request</t>
+          <t>Leave balance</t>
         </is>
       </c>
       <c r="J112" s="20" t="inlineStr">
         <is>
-          <t>សំណើច្បាប់ឈប់សម្រាក</t>
+          <t>សមតុល្យច្បាប់</t>
         </is>
       </c>
       <c r="K112" s="24" t="n"/>
@@ -6460,16 +6474,16 @@
         </is>
       </c>
       <c r="H113" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>Approval workflow</t>
+          <t>Leave request</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
         <is>
-          <t>លំហូរការអនុម័ត</t>
+          <t>សំណើច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K113" s="24" t="n"/>
@@ -6499,16 +6513,16 @@
         </is>
       </c>
       <c r="H114" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
-          <t>Leave calendar</t>
+          <t>Approval workflow</t>
         </is>
       </c>
       <c r="J114" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិទិនច្បាប់</t>
+          <t>លំហូរការអនុម័ត</t>
         </is>
       </c>
       <c r="K114" s="24" t="n"/>
@@ -6538,16 +6552,16 @@
         </is>
       </c>
       <c r="H115" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>Carry forward</t>
+          <t>Leave calendar</t>
         </is>
       </c>
       <c r="J115" s="20" t="inlineStr">
         <is>
-          <t>យោងទៅឆ្នាំបន្ទាប់</t>
+          <t>ប្រតិទិនច្បាប់</t>
         </is>
       </c>
       <c r="K115" s="24" t="n"/>
@@ -6577,16 +6591,16 @@
         </is>
       </c>
       <c r="H116" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
-          <t>Leave reports</t>
+          <t>Carry forward</t>
         </is>
       </c>
       <c r="J116" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ច្បាប់</t>
+          <t>យោងទៅឆ្នាំបន្ទាប់</t>
         </is>
       </c>
       <c r="K116" s="24" t="n"/>
@@ -6595,37 +6609,37 @@
       <c r="A117" s="19" t="n"/>
       <c r="B117" s="20" t="n"/>
       <c r="C117" s="20" t="n"/>
-      <c r="D117" s="21" t="inlineStr">
-        <is>
-          <t>B6.8</t>
-        </is>
-      </c>
-      <c r="E117" s="22" t="inlineStr">
-        <is>
-          <t>Payroll</t>
+      <c r="D117" s="19" t="inlineStr">
+        <is>
+          <t>B6.7</t>
+        </is>
+      </c>
+      <c r="E117" s="20" t="inlineStr">
+        <is>
+          <t>Leave Management</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
         <is>
-          <t>បញ្ជីប្រាក់ខែ</t>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
         <is>
-          <t>/payroll</t>
+          <t>/leave-management</t>
         </is>
       </c>
       <c r="H117" s="19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I117" s="20" t="inlineStr">
         <is>
-          <t>Salary structure</t>
+          <t>Leave reports</t>
         </is>
       </c>
       <c r="J117" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធប្រាក់ខែ</t>
+          <t>របាយការណ៍ច្បាប់</t>
         </is>
       </c>
       <c r="K117" s="24" t="n"/>
@@ -6634,12 +6648,12 @@
       <c r="A118" s="19" t="n"/>
       <c r="B118" s="20" t="n"/>
       <c r="C118" s="20" t="n"/>
-      <c r="D118" s="19" t="inlineStr">
+      <c r="D118" s="21" t="inlineStr">
         <is>
           <t>B6.8</t>
         </is>
       </c>
-      <c r="E118" s="20" t="inlineStr">
+      <c r="E118" s="22" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
@@ -6655,16 +6669,16 @@
         </is>
       </c>
       <c r="H118" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I118" s="20" t="inlineStr">
         <is>
-          <t>Basic salary</t>
+          <t>Salary structure</t>
         </is>
       </c>
       <c r="J118" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ខែគោល</t>
+          <t>រចនាសម្ព័ន្ធប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K118" s="24" t="n"/>
@@ -6694,16 +6708,16 @@
         </is>
       </c>
       <c r="H119" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
-          <t>Allowances</t>
+          <t>Basic salary</t>
         </is>
       </c>
       <c r="J119" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ឧបត្ថម្ភ</t>
+          <t>ប្រាក់ខែគោល</t>
         </is>
       </c>
       <c r="K119" s="24" t="n"/>
@@ -6733,16 +6747,16 @@
         </is>
       </c>
       <c r="H120" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I120" s="20" t="inlineStr">
         <is>
-          <t>Bonuses</t>
+          <t>Allowances</t>
         </is>
       </c>
       <c r="J120" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់រង្វាន់</t>
+          <t>ប្រាក់ឧបត្ថម្ភ</t>
         </is>
       </c>
       <c r="K120" s="24" t="n"/>
@@ -6772,16 +6786,16 @@
         </is>
       </c>
       <c r="H121" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I121" s="20" t="inlineStr">
         <is>
-          <t>Deductions</t>
+          <t>Bonuses</t>
         </is>
       </c>
       <c r="J121" s="20" t="inlineStr">
         <is>
-          <t>ការកាត់ប្រាក់</t>
+          <t>ប្រាក់រង្វាន់</t>
         </is>
       </c>
       <c r="K121" s="24" t="n"/>
@@ -6811,16 +6825,16 @@
         </is>
       </c>
       <c r="H122" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I122" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Deductions</t>
         </is>
       </c>
       <c r="J122" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>ការកាត់ប្រាក់</t>
         </is>
       </c>
       <c r="K122" s="24" t="n"/>
@@ -6850,16 +6864,16 @@
         </is>
       </c>
       <c r="H123" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I123" s="20" t="inlineStr">
         <is>
-          <t>Attendance deduction</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="J123" s="20" t="inlineStr">
         <is>
-          <t>ការកាត់ប្រាក់តាមវត្តមាន</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="K123" s="24" t="n"/>
@@ -6889,16 +6903,16 @@
         </is>
       </c>
       <c r="H124" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I124" s="20" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Attendance deduction</t>
         </is>
       </c>
       <c r="J124" s="20" t="inlineStr">
         <is>
-          <t>ពន្ធ</t>
+          <t>ការកាត់ប្រាក់តាមវត្តមាន</t>
         </is>
       </c>
       <c r="K124" s="24" t="n"/>
@@ -6928,16 +6942,16 @@
         </is>
       </c>
       <c r="H125" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I125" s="20" t="inlineStr">
         <is>
-          <t>Social security</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="J125" s="20" t="inlineStr">
         <is>
-          <t>សន្តិសុខសង្គម</t>
+          <t>ពន្ធ</t>
         </is>
       </c>
       <c r="K125" s="24" t="n"/>
@@ -6967,16 +6981,16 @@
         </is>
       </c>
       <c r="H126" s="19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
-          <t>Loan/advance</t>
+          <t>Social security</t>
         </is>
       </c>
       <c r="J126" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់កម្ចី/ប្រាក់បុរេប្រទាន</t>
+          <t>សន្តិសុខសង្គម</t>
         </is>
       </c>
       <c r="K126" s="24" t="n"/>
@@ -7006,16 +7020,16 @@
         </is>
       </c>
       <c r="H127" s="19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I127" s="20" t="inlineStr">
         <is>
-          <t>Payroll calculation</t>
+          <t>Loan/advance</t>
         </is>
       </c>
       <c r="J127" s="20" t="inlineStr">
         <is>
-          <t>ការគណនាប្រាក់ខែ</t>
+          <t>ប្រាក់កម្ចី/ប្រាក់បុរេប្រទាន</t>
         </is>
       </c>
       <c r="K127" s="24" t="n"/>
@@ -7045,16 +7059,16 @@
         </is>
       </c>
       <c r="H128" s="19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I128" s="20" t="inlineStr">
         <is>
-          <t>Payslip</t>
+          <t>Payroll calculation</t>
         </is>
       </c>
       <c r="J128" s="20" t="inlineStr">
         <is>
-          <t>បង្កាន់ដៃប្រាក់ខែ</t>
+          <t>ការគណនាប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K128" s="24" t="n"/>
@@ -7084,16 +7098,16 @@
         </is>
       </c>
       <c r="H129" s="19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I129" s="20" t="inlineStr">
         <is>
-          <t>Payroll approval</t>
+          <t>Payslip</t>
         </is>
       </c>
       <c r="J129" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តប្រាក់ខែ</t>
+          <t>បង្កាន់ដៃប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K129" s="24" t="n"/>
@@ -7123,16 +7137,16 @@
         </is>
       </c>
       <c r="H130" s="19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I130" s="20" t="inlineStr">
         <is>
-          <t>Payroll history</t>
+          <t>Payroll approval</t>
         </is>
       </c>
       <c r="J130" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិប្រាក់ខែ</t>
+          <t>ការអនុម័តប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K130" s="24" t="n"/>
@@ -7141,47 +7155,51 @@
       <c r="A131" s="19" t="n"/>
       <c r="B131" s="20" t="n"/>
       <c r="C131" s="20" t="n"/>
-      <c r="D131" s="21" t="inlineStr">
-        <is>
-          <t>B6.9</t>
-        </is>
-      </c>
-      <c r="E131" s="22" t="inlineStr">
-        <is>
-          <t>Performance Management</t>
+      <c r="D131" s="19" t="inlineStr">
+        <is>
+          <t>B6.8</t>
+        </is>
+      </c>
+      <c r="E131" s="20" t="inlineStr">
+        <is>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងការងារ</t>
+          <t>បញ្ជីប្រាក់ខែ</t>
         </is>
       </c>
       <c r="G131" s="23" t="inlineStr">
         <is>
-          <t>/performance</t>
+          <t>/payroll</t>
         </is>
       </c>
       <c r="H131" s="19" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I131" s="20" t="inlineStr">
         <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="J131" s="20" t="n"/>
+          <t>Payroll history</t>
+        </is>
+      </c>
+      <c r="J131" s="20" t="inlineStr">
+        <is>
+          <t>ប្រវត្តិប្រាក់ខែ</t>
+        </is>
+      </c>
       <c r="K131" s="24" t="n"/>
     </row>
     <row r="132" ht="21.6" customHeight="1">
       <c r="A132" s="19" t="n"/>
       <c r="B132" s="20" t="n"/>
       <c r="C132" s="20" t="n"/>
-      <c r="D132" s="19" t="inlineStr">
+      <c r="D132" s="21" t="inlineStr">
         <is>
           <t>B6.9</t>
         </is>
       </c>
-      <c r="E132" s="20" t="inlineStr">
+      <c r="E132" s="22" t="inlineStr">
         <is>
           <t>Performance Management</t>
         </is>
@@ -7197,18 +7215,14 @@
         </is>
       </c>
       <c r="H132" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I132" s="20" t="inlineStr">
         <is>
-          <t>Goals</t>
-        </is>
-      </c>
-      <c r="J132" s="20" t="inlineStr">
-        <is>
-          <t>គោលដៅ</t>
-        </is>
-      </c>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="J132" s="20" t="n"/>
       <c r="K132" s="24" t="n"/>
     </row>
     <row r="133" ht="21.6" customHeight="1">
@@ -7236,21 +7250,21 @@
         </is>
       </c>
       <c r="H133" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I133" s="20" t="inlineStr">
         <is>
-          <t>Performance review</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="J133" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃការងារ</t>
+          <t>គោលដៅ</t>
         </is>
       </c>
       <c r="K133" s="24" t="n"/>
     </row>
-    <row r="134" ht="37.2" customHeight="1">
+    <row r="134" ht="21.6" customHeight="1">
       <c r="A134" s="19" t="n"/>
       <c r="B134" s="20" t="n"/>
       <c r="C134" s="20" t="n"/>
@@ -7275,21 +7289,21 @@
         </is>
       </c>
       <c r="H134" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I134" s="20" t="inlineStr">
         <is>
-          <t>Evaluation forms</t>
+          <t>Performance review</t>
         </is>
       </c>
       <c r="J134" s="20" t="inlineStr">
         <is>
-          <t>ទម្រង់វាយតម្លៃ</t>
+          <t>ការវាយតម្លៃការងារ</t>
         </is>
       </c>
       <c r="K134" s="24" t="n"/>
     </row>
-    <row r="135" ht="21.6" customHeight="1">
+    <row r="135" ht="37.2" customHeight="1">
       <c r="A135" s="19" t="n"/>
       <c r="B135" s="20" t="n"/>
       <c r="C135" s="20" t="n"/>
@@ -7314,16 +7328,16 @@
         </is>
       </c>
       <c r="H135" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I135" s="20" t="inlineStr">
         <is>
-          <t>Employee self-assessment</t>
+          <t>Evaluation forms</t>
         </is>
       </c>
       <c r="J135" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃខ្លួនឯង</t>
+          <t>ទម្រង់វាយតម្លៃ</t>
         </is>
       </c>
       <c r="K135" s="24" t="n"/>
@@ -7353,16 +7367,16 @@
         </is>
       </c>
       <c r="H136" s="19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I136" s="20" t="inlineStr">
         <is>
-          <t>Manager assessment</t>
+          <t>Employee self-assessment</t>
         </is>
       </c>
       <c r="J136" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃដោយអ្នកគ្រប់គ្រង</t>
+          <t>ការវាយតម្លៃខ្លួនឯង</t>
         </is>
       </c>
       <c r="K136" s="24" t="n"/>
@@ -7392,16 +7406,16 @@
         </is>
       </c>
       <c r="H137" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I137" s="20" t="inlineStr">
         <is>
-          <t>Performance score</t>
+          <t>Manager assessment</t>
         </is>
       </c>
       <c r="J137" s="20" t="inlineStr">
         <is>
-          <t>ពិន្ទុការងារ</t>
+          <t>ការវាយតម្លៃដោយអ្នកគ្រប់គ្រង</t>
         </is>
       </c>
       <c r="K137" s="24" t="n"/>
@@ -7431,16 +7445,16 @@
         </is>
       </c>
       <c r="H138" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I138" s="20" t="inlineStr">
         <is>
-          <t>Promotion recommendation</t>
+          <t>Performance score</t>
         </is>
       </c>
       <c r="J138" s="20" t="inlineStr">
         <is>
-          <t>ការណែនាំដំឡើងតំណែង</t>
+          <t>ពិន្ទុការងារ</t>
         </is>
       </c>
       <c r="K138" s="24" t="n"/>
@@ -7449,29 +7463,39 @@
       <c r="A139" s="19" t="n"/>
       <c r="B139" s="20" t="n"/>
       <c r="C139" s="20" t="n"/>
-      <c r="D139" s="21" t="inlineStr">
-        <is>
-          <t>B6.10</t>
-        </is>
-      </c>
-      <c r="E139" s="22" t="inlineStr">
-        <is>
-          <t>Check in / Check out</t>
+      <c r="D139" s="19" t="inlineStr">
+        <is>
+          <t>B6.9</t>
+        </is>
+      </c>
+      <c r="E139" s="20" t="inlineStr">
+        <is>
+          <t>Performance Management</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>ការគ្រប់គ្រងការងារ</t>
         </is>
       </c>
       <c r="G139" s="23" t="inlineStr">
         <is>
-          <t>/my-check-in</t>
-        </is>
-      </c>
-      <c r="H139" s="19" t="n"/>
-      <c r="I139" s="20" t="n"/>
-      <c r="J139" s="20" t="n"/>
+          <t>/performance</t>
+        </is>
+      </c>
+      <c r="H139" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I139" s="20" t="inlineStr">
+        <is>
+          <t>Promotion recommendation</t>
+        </is>
+      </c>
+      <c r="J139" s="20" t="inlineStr">
+        <is>
+          <t>ការណែនាំដំឡើងតំណែង</t>
+        </is>
+      </c>
       <c r="K139" s="24" t="n"/>
     </row>
     <row r="140" ht="21.6" customHeight="1">
@@ -7480,49 +7504,39 @@
       <c r="C140" s="20" t="n"/>
       <c r="D140" s="21" t="inlineStr">
         <is>
-          <t>B6.11</t>
+          <t>B6.10</t>
         </is>
       </c>
       <c r="E140" s="22" t="inlineStr">
         <is>
-          <t>Request Leave</t>
+          <t>Check in / Check out</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
-          <t>ស្នើសុំច្បាប់</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H140" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I140" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J140" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
+          <t>/my-check-in</t>
+        </is>
+      </c>
+      <c r="H140" s="19" t="n"/>
+      <c r="I140" s="20" t="n"/>
+      <c r="J140" s="20" t="n"/>
       <c r="K140" s="24" t="n"/>
     </row>
     <row r="141" ht="21.6" customHeight="1">
       <c r="A141" s="19" t="n"/>
       <c r="B141" s="20" t="n"/>
       <c r="C141" s="20" t="n"/>
-      <c r="D141" s="19" t="inlineStr">
+      <c r="D141" s="21" t="inlineStr">
         <is>
           <t>B6.11</t>
         </is>
       </c>
-      <c r="E141" s="20" t="inlineStr">
+      <c r="E141" s="22" t="inlineStr">
         <is>
           <t>Request Leave</t>
         </is>
@@ -7538,16 +7552,16 @@
         </is>
       </c>
       <c r="H141" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I141" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J141" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="K141" s="24" t="n"/>
@@ -7577,16 +7591,16 @@
         </is>
       </c>
       <c r="H142" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I142" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J142" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K142" s="24" t="n"/>
@@ -7616,16 +7630,16 @@
         </is>
       </c>
       <c r="H143" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I143" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J143" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K143" s="24" t="n"/>
@@ -7655,16 +7669,16 @@
         </is>
       </c>
       <c r="H144" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I144" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="J144" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="K144" s="24" t="n"/>
@@ -7673,104 +7687,114 @@
       <c r="A145" s="19" t="n"/>
       <c r="B145" s="20" t="n"/>
       <c r="C145" s="20" t="n"/>
-      <c r="D145" s="21" t="inlineStr">
+      <c r="D145" s="19" t="inlineStr">
+        <is>
+          <t>B6.11</t>
+        </is>
+      </c>
+      <c r="E145" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="F145" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="H145" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I145" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="J145" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="K145" s="24" t="n"/>
+    </row>
+    <row r="146" ht="21.6" customHeight="1">
+      <c r="A146" s="19" t="n"/>
+      <c r="B146" s="20" t="n"/>
+      <c r="C146" s="20" t="n"/>
+      <c r="D146" s="21" t="inlineStr">
         <is>
           <t>B6.12</t>
         </is>
       </c>
-      <c r="E145" s="22" t="inlineStr">
+      <c r="E146" s="22" t="inlineStr">
         <is>
           <t>Form</t>
         </is>
       </c>
-      <c r="F145" s="20" t="inlineStr">
+      <c r="F146" s="20" t="inlineStr">
         <is>
           <t>ទម្រង់</t>
         </is>
       </c>
-      <c r="G145" s="23" t="inlineStr">
+      <c r="G146" s="23" t="inlineStr">
         <is>
           <t>/approvals/my-requests?tab=resignation</t>
         </is>
       </c>
-      <c r="H145" s="19" t="n"/>
-      <c r="I145" s="20" t="n"/>
-      <c r="J145" s="20" t="n"/>
-      <c r="K145" s="24" t="inlineStr">
+      <c r="H146" s="19" t="n"/>
+      <c r="I146" s="20" t="n"/>
+      <c r="J146" s="20" t="n"/>
+      <c r="K146" s="24" t="inlineStr">
         <is>
           <t>Resignation form</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="21.6" customHeight="1">
-      <c r="A146" s="1" t="inlineStr">
+    <row r="147" ht="21.6" customHeight="1">
+      <c r="A147" s="1" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>វិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="D146" s="1" t="inlineStr">
+      <c r="D147" s="1" t="inlineStr">
         <is>
           <t>B7.1</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Billing Dashboard</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងវិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="G146" s="4" t="inlineStr">
+      <c r="G147" s="4" t="inlineStr">
         <is>
           <t>/billing</t>
         </is>
       </c>
-      <c r="H146" s="5" t="n"/>
-      <c r="I146" s="3" t="n"/>
-      <c r="J146" s="3" t="n"/>
-      <c r="K146" s="6" t="n"/>
-    </row>
-    <row r="147" ht="21.6" customHeight="1">
-      <c r="A147" s="7" t="n"/>
-      <c r="B147" s="8" t="n"/>
-      <c r="C147" s="8" t="n"/>
-      <c r="D147" s="9" t="inlineStr">
-        <is>
-          <t>B7.2</t>
-        </is>
-      </c>
-      <c r="E147" s="10" t="inlineStr">
-        <is>
-          <t>Products</t>
-        </is>
-      </c>
-      <c r="F147" s="8" t="inlineStr">
-        <is>
-          <t>ផលិតផល</t>
-        </is>
-      </c>
-      <c r="G147" s="11" t="inlineStr">
-        <is>
-          <t>/products</t>
-        </is>
-      </c>
-      <c r="H147" s="7" t="n"/>
-      <c r="I147" s="8" t="n"/>
-      <c r="J147" s="8" t="n"/>
-      <c r="K147" s="12" t="n"/>
+      <c r="H147" s="5" t="n"/>
+      <c r="I147" s="3" t="n"/>
+      <c r="J147" s="3" t="n"/>
+      <c r="K147" s="6" t="n"/>
     </row>
     <row r="148" ht="21.6" customHeight="1">
       <c r="A148" s="7" t="n"/>
@@ -7778,49 +7802,39 @@
       <c r="C148" s="8" t="n"/>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>B7.3</t>
+          <t>B7.2</t>
         </is>
       </c>
       <c r="E148" s="10" t="inlineStr">
         <is>
-          <t>Invoices</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
         <is>
-          <t>វិក្កយបត្រ</t>
+          <t>ផលិតផល</t>
         </is>
       </c>
       <c r="G148" s="11" t="inlineStr">
         <is>
-          <t>/invoices</t>
-        </is>
-      </c>
-      <c r="H148" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I148" s="8" t="inlineStr">
-        <is>
-          <t>Invoices</t>
-        </is>
-      </c>
-      <c r="J148" s="8" t="inlineStr">
-        <is>
-          <t>វិក្កយបត្រ</t>
-        </is>
-      </c>
+          <t>/products</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="n"/>
+      <c r="I148" s="8" t="n"/>
+      <c r="J148" s="8" t="n"/>
       <c r="K148" s="12" t="n"/>
     </row>
     <row r="149" ht="21.6" customHeight="1">
       <c r="A149" s="7" t="n"/>
       <c r="B149" s="8" t="n"/>
       <c r="C149" s="8" t="n"/>
-      <c r="D149" s="7" t="inlineStr">
+      <c r="D149" s="9" t="inlineStr">
         <is>
           <t>B7.3</t>
         </is>
       </c>
-      <c r="E149" s="8" t="inlineStr">
+      <c r="E149" s="10" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
@@ -7836,16 +7850,16 @@
         </is>
       </c>
       <c r="H149" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I149" s="8" t="inlineStr">
         <is>
-          <t>Monthly Invoice</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>វិក្កយបត្រប្រចាំខែ</t>
+          <t>វិក្កយបត្រ</t>
         </is>
       </c>
       <c r="K149" s="12" t="n"/>
@@ -7854,29 +7868,39 @@
       <c r="A150" s="7" t="n"/>
       <c r="B150" s="8" t="n"/>
       <c r="C150" s="8" t="n"/>
-      <c r="D150" s="9" t="inlineStr">
-        <is>
-          <t>B7.4</t>
-        </is>
-      </c>
-      <c r="E150" s="10" t="inlineStr">
-        <is>
-          <t>Payments</t>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>B7.3</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
         <is>
-          <t>ការទូទាត់</t>
+          <t>វិក្កយបត្រ</t>
         </is>
       </c>
       <c r="G150" s="11" t="inlineStr">
         <is>
-          <t>/payments</t>
-        </is>
-      </c>
-      <c r="H150" s="7" t="n"/>
-      <c r="I150" s="8" t="n"/>
-      <c r="J150" s="8" t="n"/>
+          <t>/invoices</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Invoice</t>
+        </is>
+      </c>
+      <c r="J150" s="8" t="inlineStr">
+        <is>
+          <t>វិក្កយបត្រប្រចាំខែ</t>
+        </is>
+      </c>
       <c r="K150" s="12" t="n"/>
     </row>
     <row r="151" ht="21.6" customHeight="1">
@@ -7885,22 +7909,22 @@
       <c r="C151" s="8" t="n"/>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>B7.5</t>
+          <t>B7.4</t>
         </is>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>Currency Rates</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t>អត្រាប្តូរប្រាក់</t>
+          <t>ការទូទាត់</t>
         </is>
       </c>
       <c r="G151" s="11" t="inlineStr">
         <is>
-          <t>/currency-rates</t>
+          <t>/payments</t>
         </is>
       </c>
       <c r="H151" s="7" t="n"/>
@@ -7909,74 +7933,74 @@
       <c r="K151" s="12" t="n"/>
     </row>
     <row r="152" ht="21.6" customHeight="1">
-      <c r="A152" s="13" t="inlineStr">
+      <c r="A152" s="7" t="n"/>
+      <c r="B152" s="8" t="n"/>
+      <c r="C152" s="8" t="n"/>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>B7.5</t>
+        </is>
+      </c>
+      <c r="E152" s="10" t="inlineStr">
+        <is>
+          <t>Currency Rates</t>
+        </is>
+      </c>
+      <c r="F152" s="8" t="inlineStr">
+        <is>
+          <t>អត្រាប្តូរប្រាក់</t>
+        </is>
+      </c>
+      <c r="G152" s="11" t="inlineStr">
+        <is>
+          <t>/currency-rates</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="n"/>
+      <c r="I152" s="8" t="n"/>
+      <c r="J152" s="8" t="n"/>
+      <c r="K152" s="12" t="n"/>
+    </row>
+    <row r="153" ht="21.6" customHeight="1">
+      <c r="A153" s="13" t="inlineStr">
         <is>
           <t>B8</t>
         </is>
       </c>
-      <c r="B152" s="14" t="inlineStr">
+      <c r="B153" s="14" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="C152" s="15" t="inlineStr">
+      <c r="C153" s="15" t="inlineStr">
         <is>
           <t>គណនេយ្យ</t>
         </is>
       </c>
-      <c r="D152" s="13" t="inlineStr">
+      <c r="D153" s="13" t="inlineStr">
         <is>
           <t>B8.1</t>
         </is>
       </c>
-      <c r="E152" s="14" t="inlineStr">
+      <c r="E153" s="14" t="inlineStr">
         <is>
           <t>Accounting Dashboard</t>
         </is>
       </c>
-      <c r="F152" s="15" t="inlineStr">
+      <c r="F153" s="15" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងគណនេយ្យ</t>
         </is>
       </c>
-      <c r="G152" s="16" t="inlineStr">
+      <c r="G153" s="16" t="inlineStr">
         <is>
           <t>/accounting</t>
         </is>
       </c>
-      <c r="H152" s="17" t="n"/>
-      <c r="I152" s="15" t="n"/>
-      <c r="J152" s="15" t="n"/>
-      <c r="K152" s="18" t="n"/>
-    </row>
-    <row r="153" ht="21.6" customHeight="1">
-      <c r="A153" s="19" t="n"/>
-      <c r="B153" s="20" t="n"/>
-      <c r="C153" s="20" t="n"/>
-      <c r="D153" s="21" t="inlineStr">
-        <is>
-          <t>B8.2</t>
-        </is>
-      </c>
-      <c r="E153" s="22" t="inlineStr">
-        <is>
-          <t>Chart of Accounts</t>
-        </is>
-      </c>
-      <c r="F153" s="20" t="inlineStr">
-        <is>
-          <t>តារាងគណនី</t>
-        </is>
-      </c>
-      <c r="G153" s="23" t="inlineStr">
-        <is>
-          <t>/accounts</t>
-        </is>
-      </c>
-      <c r="H153" s="19" t="n"/>
-      <c r="I153" s="20" t="n"/>
-      <c r="J153" s="20" t="n"/>
-      <c r="K153" s="24" t="n"/>
+      <c r="H153" s="17" t="n"/>
+      <c r="I153" s="15" t="n"/>
+      <c r="J153" s="15" t="n"/>
+      <c r="K153" s="18" t="n"/>
     </row>
     <row r="154" ht="21.6" customHeight="1">
       <c r="A154" s="19" t="n"/>
@@ -7984,22 +8008,22 @@
       <c r="C154" s="20" t="n"/>
       <c r="D154" s="21" t="inlineStr">
         <is>
-          <t>B8.3</t>
+          <t>B8.2</t>
         </is>
       </c>
       <c r="E154" s="22" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Chart of Accounts</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>ចំណូល</t>
+          <t>តារាងគណនី</t>
         </is>
       </c>
       <c r="G154" s="23" t="inlineStr">
         <is>
-          <t>/income</t>
+          <t>/accounts</t>
         </is>
       </c>
       <c r="H154" s="19" t="n"/>
@@ -8013,22 +8037,22 @@
       <c r="C155" s="20" t="n"/>
       <c r="D155" s="21" t="inlineStr">
         <is>
-          <t>B8.4</t>
+          <t>B8.3</t>
         </is>
       </c>
       <c r="E155" s="22" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>ចំណាយ</t>
+          <t>ចំណូល</t>
         </is>
       </c>
       <c r="G155" s="23" t="inlineStr">
         <is>
-          <t>/expenses</t>
+          <t>/income</t>
         </is>
       </c>
       <c r="H155" s="19" t="n"/>
@@ -8042,22 +8066,22 @@
       <c r="C156" s="20" t="n"/>
       <c r="D156" s="21" t="inlineStr">
         <is>
-          <t>B8.5</t>
+          <t>B8.4</t>
         </is>
       </c>
       <c r="E156" s="22" t="inlineStr">
         <is>
-          <t>Transactions</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិបត្តិការ</t>
+          <t>ចំណាយ</t>
         </is>
       </c>
       <c r="G156" s="23" t="inlineStr">
         <is>
-          <t>/transactions</t>
+          <t>/expenses</t>
         </is>
       </c>
       <c r="H156" s="19" t="n"/>
@@ -8071,49 +8095,39 @@
       <c r="C157" s="20" t="n"/>
       <c r="D157" s="21" t="inlineStr">
         <is>
-          <t>B8.6</t>
+          <t>B8.5</t>
         </is>
       </c>
       <c r="E157" s="22" t="inlineStr">
         <is>
-          <t>Financial Reports</t>
+          <t>Transactions</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+          <t>ប្រតិបត្តិការ</t>
         </is>
       </c>
       <c r="G157" s="23" t="inlineStr">
         <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H157" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I157" s="20" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="J157" s="20" t="inlineStr">
-        <is>
-          <t>ចំណូល</t>
-        </is>
-      </c>
+          <t>/transactions</t>
+        </is>
+      </c>
+      <c r="H157" s="19" t="n"/>
+      <c r="I157" s="20" t="n"/>
+      <c r="J157" s="20" t="n"/>
       <c r="K157" s="24" t="n"/>
     </row>
     <row r="158" ht="21.6" customHeight="1">
       <c r="A158" s="19" t="n"/>
       <c r="B158" s="20" t="n"/>
       <c r="C158" s="20" t="n"/>
-      <c r="D158" s="19" t="inlineStr">
+      <c r="D158" s="21" t="inlineStr">
         <is>
           <t>B8.6</t>
         </is>
       </c>
-      <c r="E158" s="20" t="inlineStr">
+      <c r="E158" s="22" t="inlineStr">
         <is>
           <t>Financial Reports</t>
         </is>
@@ -8129,16 +8143,16 @@
         </is>
       </c>
       <c r="H158" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I158" s="20" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="J158" s="20" t="inlineStr">
         <is>
-          <t>ចំណាយ</t>
+          <t>ចំណូល</t>
         </is>
       </c>
       <c r="K158" s="24" t="n"/>
@@ -8168,16 +8182,16 @@
         </is>
       </c>
       <c r="H159" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I159" s="20" t="inlineStr">
         <is>
-          <t>Profit &amp; Loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="J159" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ចំណេញ និងខាត</t>
+          <t>ចំណាយ</t>
         </is>
       </c>
       <c r="K159" s="24" t="n"/>
@@ -8207,114 +8221,110 @@
         </is>
       </c>
       <c r="H160" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I160" s="20" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss</t>
+        </is>
+      </c>
+      <c r="J160" s="20" t="inlineStr">
+        <is>
+          <t>ប្រាក់ចំណេញ និងខាត</t>
+        </is>
+      </c>
+      <c r="K160" s="24" t="n"/>
+    </row>
+    <row r="161" ht="21.6" customHeight="1">
+      <c r="A161" s="19" t="n"/>
+      <c r="B161" s="20" t="n"/>
+      <c r="C161" s="20" t="n"/>
+      <c r="D161" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E161" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F161" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H161" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I160" s="20" t="inlineStr">
+      <c r="I161" s="20" t="inlineStr">
         <is>
           <t>Cash Flow</t>
         </is>
       </c>
-      <c r="J160" s="20" t="inlineStr">
+      <c r="J161" s="20" t="inlineStr">
         <is>
           <t>លំហូរសាច់ប្រាក់</t>
         </is>
       </c>
-      <c r="K160" s="24" t="n"/>
-    </row>
-    <row r="161" ht="21.6" customHeight="1">
-      <c r="A161" s="1" t="inlineStr">
+      <c r="K161" s="24" t="n"/>
+    </row>
+    <row r="162" ht="21.6" customHeight="1">
+      <c r="A162" s="1" t="inlineStr">
         <is>
           <t>B9</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr">
+      <c r="C162" s="3" t="inlineStr">
         <is>
           <t>ទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="D161" s="1" t="inlineStr">
+      <c r="D162" s="1" t="inlineStr">
         <is>
           <t>B9.1</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Asset Dashboard</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="G161" s="4" t="inlineStr">
+      <c r="G162" s="4" t="inlineStr">
         <is>
           <t>/assets/dashboard</t>
         </is>
       </c>
-      <c r="H161" s="5" t="n"/>
-      <c r="I161" s="3" t="n"/>
-      <c r="J161" s="3" t="n"/>
-      <c r="K161" s="6" t="n"/>
-    </row>
-    <row r="162" ht="21.6" customHeight="1">
-      <c r="A162" s="7" t="n"/>
-      <c r="B162" s="8" t="n"/>
-      <c r="C162" s="8" t="n"/>
-      <c r="D162" s="9" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E162" s="10" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F162" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G162" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H162" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I162" s="8" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="J162" s="8" t="inlineStr">
-        <is>
-          <t>ទិដ្ឋភាពទូទៅ</t>
-        </is>
-      </c>
-      <c r="K162" s="12" t="inlineStr">
-        <is>
-          <t>Tabs on one asset</t>
-        </is>
-      </c>
+      <c r="H162" s="5" t="n"/>
+      <c r="I162" s="3" t="n"/>
+      <c r="J162" s="3" t="n"/>
+      <c r="K162" s="6" t="n"/>
     </row>
     <row r="163" ht="21.6" customHeight="1">
       <c r="A163" s="7" t="n"/>
       <c r="B163" s="8" t="n"/>
       <c r="C163" s="8" t="n"/>
-      <c r="D163" s="7" t="inlineStr">
+      <c r="D163" s="9" t="inlineStr">
         <is>
           <t>B9.2</t>
         </is>
       </c>
-      <c r="E163" s="8" t="inlineStr">
+      <c r="E163" s="10" t="inlineStr">
         <is>
           <t>All Assets</t>
         </is>
@@ -8330,19 +8340,23 @@
         </is>
       </c>
       <c r="H163" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I163" s="8" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>ការចាត់ចែង</t>
-        </is>
-      </c>
-      <c r="K163" s="12" t="n"/>
+          <t>ទិដ្ឋភាពទូទៅ</t>
+        </is>
+      </c>
+      <c r="K163" s="12" t="inlineStr">
+        <is>
+          <t>Tabs on one asset</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="21.6" customHeight="1">
       <c r="A164" s="7" t="n"/>
@@ -8369,16 +8383,16 @@
         </is>
       </c>
       <c r="H164" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I164" s="8" t="inlineStr">
         <is>
-          <t>Transfers</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>ការផ្ទេរ</t>
+          <t>ការចាត់ចែង</t>
         </is>
       </c>
       <c r="K164" s="12" t="n"/>
@@ -8408,16 +8422,16 @@
         </is>
       </c>
       <c r="H165" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I165" s="8" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>Transfers</t>
         </is>
       </c>
       <c r="J165" s="8" t="inlineStr">
         <is>
-          <t>បញ្ហា</t>
+          <t>ការផ្ទេរ</t>
         </is>
       </c>
       <c r="K165" s="12" t="n"/>
@@ -8447,16 +8461,16 @@
         </is>
       </c>
       <c r="H166" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I166" s="8" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>បញ្ហា</t>
         </is>
       </c>
       <c r="K166" s="12" t="n"/>
@@ -8486,16 +8500,16 @@
         </is>
       </c>
       <c r="H167" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I167" s="8" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="J167" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="K167" s="12" t="n"/>
@@ -8504,29 +8518,39 @@
       <c r="A168" s="7" t="n"/>
       <c r="B168" s="8" t="n"/>
       <c r="C168" s="8" t="n"/>
-      <c r="D168" s="9" t="inlineStr">
-        <is>
-          <t>B9.3</t>
-        </is>
-      </c>
-      <c r="E168" s="10" t="inlineStr">
-        <is>
-          <t>My Assets</t>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G168" s="11" t="inlineStr">
         <is>
-          <t>/my-assets</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="n"/>
-      <c r="I168" s="8" t="n"/>
-      <c r="J168" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I168" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="J168" s="8" t="inlineStr">
+        <is>
+          <t>ការថែទាំ</t>
+        </is>
+      </c>
       <c r="K168" s="12" t="n"/>
     </row>
     <row r="169" ht="21.6" customHeight="1">
@@ -8535,22 +8559,22 @@
       <c r="C169" s="8" t="n"/>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>B9.4</t>
+          <t>B9.3</t>
         </is>
       </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>My Assets</t>
         </is>
       </c>
       <c r="F169" s="8" t="inlineStr">
         <is>
-          <t>បញ្ហា</t>
+          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G169" s="11" t="inlineStr">
         <is>
-          <t>/asset-issues</t>
+          <t>/my-assets</t>
         </is>
       </c>
       <c r="H169" s="7" t="n"/>
@@ -8564,22 +8588,22 @@
       <c r="C170" s="8" t="n"/>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>B9.5</t>
+          <t>B9.4</t>
         </is>
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>បញ្ហា</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>/asset-repairs</t>
+          <t>/asset-issues</t>
         </is>
       </c>
       <c r="H170" s="7" t="n"/>
@@ -8593,22 +8617,22 @@
       <c r="C171" s="8" t="n"/>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>B9.6</t>
+          <t>B9.5</t>
         </is>
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>Repair Shops</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr">
         <is>
-          <t>ហាងជួសជុល</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>/repair-shops</t>
+          <t>/asset-repairs</t>
         </is>
       </c>
       <c r="H171" s="7" t="n"/>
@@ -8622,22 +8646,22 @@
       <c r="C172" s="8" t="n"/>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>B9.7</t>
+          <t>B9.6</t>
         </is>
       </c>
       <c r="E172" s="10" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Repair Shops</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ហាងជួសជុល</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
-          <t>/asset-maintenance</t>
+          <t>/repair-shops</t>
         </is>
       </c>
       <c r="H172" s="7" t="n"/>
@@ -8651,22 +8675,22 @@
       <c r="C173" s="8" t="n"/>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>B9.8</t>
+          <t>B9.7</t>
         </is>
       </c>
       <c r="E173" s="10" t="inlineStr">
         <is>
-          <t>Asset Categories</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr">
         <is>
-          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
+          <t>ការថែទាំ</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>/asset-categories</t>
+          <t>/asset-maintenance</t>
         </is>
       </c>
       <c r="H173" s="7" t="n"/>
@@ -8680,22 +8704,22 @@
       <c r="C174" s="8" t="n"/>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>B9.9</t>
+          <t>B9.8</t>
         </is>
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>Asset Locations</t>
+          <t>Asset Categories</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
+          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
-          <t>/asset-locations</t>
+          <t>/asset-categories</t>
         </is>
       </c>
       <c r="H174" s="7" t="n"/>
@@ -8709,22 +8733,22 @@
       <c r="C175" s="8" t="n"/>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>B9.10</t>
+          <t>B9.9</t>
         </is>
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>Departments</t>
+          <t>Asset Locations</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>/departments</t>
+          <t>/asset-locations</t>
         </is>
       </c>
       <c r="H175" s="7" t="n"/>
@@ -8738,22 +8762,22 @@
       <c r="C176" s="8" t="n"/>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>B9.11</t>
+          <t>B9.10</t>
         </is>
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>Suppliers</t>
+          <t>Departments</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>អ្នកផ្គត់ផ្គង់</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
-          <t>/suppliers</t>
+          <t>/departments</t>
         </is>
       </c>
       <c r="H176" s="7" t="n"/>
@@ -8767,49 +8791,39 @@
       <c r="C177" s="8" t="n"/>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>B9.12</t>
+          <t>B9.11</t>
         </is>
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
-          <t>Asset Reports</t>
+          <t>Suppliers</t>
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>អ្នកផ្គត់ផ្គង់</t>
         </is>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I177" s="8" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="J177" s="8" t="inlineStr">
-        <is>
-          <t>ស្តុក</t>
-        </is>
-      </c>
+          <t>/suppliers</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="n"/>
+      <c r="I177" s="8" t="n"/>
+      <c r="J177" s="8" t="n"/>
       <c r="K177" s="12" t="n"/>
     </row>
     <row r="178" ht="21.6" customHeight="1">
       <c r="A178" s="7" t="n"/>
       <c r="B178" s="8" t="n"/>
       <c r="C178" s="8" t="n"/>
-      <c r="D178" s="7" t="inlineStr">
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>B9.12</t>
         </is>
       </c>
-      <c r="E178" s="8" t="inlineStr">
+      <c r="E178" s="10" t="inlineStr">
         <is>
           <t>Asset Reports</t>
         </is>
@@ -8825,16 +8839,16 @@
         </is>
       </c>
       <c r="H178" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I178" s="8" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
-          <t>ស្ថានភាព</t>
+          <t>ស្តុក</t>
         </is>
       </c>
       <c r="K178" s="12" t="n"/>
@@ -8864,16 +8878,16 @@
         </is>
       </c>
       <c r="H179" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I179" s="8" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="J179" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>ស្ថានភាព</t>
         </is>
       </c>
       <c r="K179" s="12" t="n"/>
@@ -8903,16 +8917,16 @@
         </is>
       </c>
       <c r="H180" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I180" s="8" t="inlineStr">
         <is>
-          <t>Repair Cost</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>ថ្លៃជួសជុល</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="K180" s="12" t="n"/>
@@ -8942,16 +8956,16 @@
         </is>
       </c>
       <c r="H181" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I181" s="8" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Repair Cost</t>
         </is>
       </c>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ថ្លៃជួសជុល</t>
         </is>
       </c>
       <c r="K181" s="12" t="n"/>
@@ -8981,16 +8995,16 @@
         </is>
       </c>
       <c r="H182" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I182" s="8" t="inlineStr">
         <is>
-          <t>Assignments</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>ការចាត់ចែង</t>
+          <t>ការថែទាំ</t>
         </is>
       </c>
       <c r="K182" s="12" t="n"/>
@@ -9020,89 +9034,99 @@
         </is>
       </c>
       <c r="H183" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I183" s="8" t="inlineStr">
+        <is>
+          <t>Assignments</t>
+        </is>
+      </c>
+      <c r="J183" s="8" t="inlineStr">
+        <is>
+          <t>ការចាត់ចែង</t>
+        </is>
+      </c>
+      <c r="K183" s="12" t="n"/>
+    </row>
+    <row r="184" ht="21.6" customHeight="1">
+      <c r="A184" s="7" t="n"/>
+      <c r="B184" s="8" t="n"/>
+      <c r="C184" s="8" t="n"/>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E184" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F184" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G184" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I183" s="8" t="inlineStr">
+      <c r="I184" s="8" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="J183" s="8" t="inlineStr">
+      <c r="J184" s="8" t="inlineStr">
         <is>
           <t>ប្រវត្តិ</t>
         </is>
       </c>
-      <c r="K183" s="12" t="n"/>
-    </row>
-    <row r="184" ht="21.6" customHeight="1">
-      <c r="A184" s="13" t="inlineStr">
+      <c r="K184" s="12" t="n"/>
+    </row>
+    <row r="185" ht="21.6" customHeight="1">
+      <c r="A185" s="13" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="B184" s="14" t="inlineStr">
+      <c r="B185" s="14" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="C184" s="15" t="inlineStr">
+      <c r="C185" s="15" t="inlineStr">
         <is>
           <t>ការទំនាក់ទំនង</t>
         </is>
       </c>
-      <c r="D184" s="13" t="inlineStr">
+      <c r="D185" s="13" t="inlineStr">
         <is>
           <t>B10.1</t>
         </is>
       </c>
-      <c r="E184" s="14" t="inlineStr">
+      <c r="E185" s="14" t="inlineStr">
         <is>
           <t>Contact Messages</t>
         </is>
       </c>
-      <c r="F184" s="15" t="inlineStr">
+      <c r="F185" s="15" t="inlineStr">
         <is>
           <t>សារទំនាក់ទំនង</t>
         </is>
       </c>
-      <c r="G184" s="16" t="inlineStr">
+      <c r="G185" s="16" t="inlineStr">
         <is>
           <t>/contact-messages</t>
         </is>
       </c>
-      <c r="H184" s="17" t="n"/>
-      <c r="I184" s="15" t="n"/>
-      <c r="J184" s="15" t="n"/>
-      <c r="K184" s="18" t="n"/>
-    </row>
-    <row r="185" ht="21.6" customHeight="1">
-      <c r="A185" s="19" t="n"/>
-      <c r="B185" s="20" t="n"/>
-      <c r="C185" s="20" t="n"/>
-      <c r="D185" s="21" t="inlineStr">
-        <is>
-          <t>B10.2</t>
-        </is>
-      </c>
-      <c r="E185" s="22" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="F185" s="20" t="inlineStr">
-        <is>
-          <t>ការជូនដំណឹង</t>
-        </is>
-      </c>
-      <c r="G185" s="23" t="inlineStr">
-        <is>
-          <t>/notifications</t>
-        </is>
-      </c>
-      <c r="H185" s="19" t="n"/>
-      <c r="I185" s="20" t="n"/>
-      <c r="J185" s="20" t="n"/>
-      <c r="K185" s="24" t="n"/>
+      <c r="H185" s="17" t="n"/>
+      <c r="I185" s="15" t="n"/>
+      <c r="J185" s="15" t="n"/>
+      <c r="K185" s="18" t="n"/>
     </row>
     <row r="186" ht="21.6" customHeight="1">
       <c r="A186" s="19" t="n"/>
@@ -9110,49 +9134,39 @@
       <c r="C186" s="20" t="n"/>
       <c r="D186" s="21" t="inlineStr">
         <is>
-          <t>B10.3</t>
+          <t>B10.2</t>
         </is>
       </c>
       <c r="E186" s="22" t="inlineStr">
         <is>
-          <t>Student Feedback</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>មតិកែលម្អសិស្ស</t>
+          <t>ការជូនដំណឹង</t>
         </is>
       </c>
       <c r="G186" s="23" t="inlineStr">
         <is>
-          <t>/student-feedback</t>
-        </is>
-      </c>
-      <c r="H186" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I186" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J186" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងបើក</t>
-        </is>
-      </c>
+          <t>/notifications</t>
+        </is>
+      </c>
+      <c r="H186" s="19" t="n"/>
+      <c r="I186" s="20" t="n"/>
+      <c r="J186" s="20" t="n"/>
       <c r="K186" s="24" t="n"/>
     </row>
     <row r="187" ht="21.6" customHeight="1">
       <c r="A187" s="19" t="n"/>
       <c r="B187" s="20" t="n"/>
       <c r="C187" s="20" t="n"/>
-      <c r="D187" s="19" t="inlineStr">
+      <c r="D187" s="21" t="inlineStr">
         <is>
           <t>B10.3</t>
         </is>
       </c>
-      <c r="E187" s="20" t="inlineStr">
+      <c r="E187" s="22" t="inlineStr">
         <is>
           <t>Student Feedback</t>
         </is>
@@ -9168,89 +9182,99 @@
         </is>
       </c>
       <c r="H187" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I187" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J187" s="20" t="inlineStr">
+        <is>
+          <t>កំពុងបើក</t>
+        </is>
+      </c>
+      <c r="K187" s="24" t="n"/>
+    </row>
+    <row r="188" ht="21.6" customHeight="1">
+      <c r="A188" s="19" t="n"/>
+      <c r="B188" s="20" t="n"/>
+      <c r="C188" s="20" t="n"/>
+      <c r="D188" s="19" t="inlineStr">
+        <is>
+          <t>B10.3</t>
+        </is>
+      </c>
+      <c r="E188" s="20" t="inlineStr">
+        <is>
+          <t>Student Feedback</t>
+        </is>
+      </c>
+      <c r="F188" s="20" t="inlineStr">
+        <is>
+          <t>មតិកែលម្អសិស្ស</t>
+        </is>
+      </c>
+      <c r="G188" s="23" t="inlineStr">
+        <is>
+          <t>/student-feedback</t>
+        </is>
+      </c>
+      <c r="H188" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="I187" s="20" t="inlineStr">
+      <c r="I188" s="20" t="inlineStr">
         <is>
           <t>Replied</t>
         </is>
       </c>
-      <c r="J187" s="20" t="inlineStr">
+      <c r="J188" s="20" t="inlineStr">
         <is>
           <t>បានឆ្លើយតប</t>
         </is>
       </c>
-      <c r="K187" s="24" t="n"/>
-    </row>
-    <row r="188" ht="21.6" customHeight="1">
-      <c r="A188" s="1" t="inlineStr">
+      <c r="K188" s="24" t="n"/>
+    </row>
+    <row r="189" ht="21.6" customHeight="1">
+      <c r="A189" s="1" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C188" s="3" t="inlineStr">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t>ការកំណត់</t>
         </is>
       </c>
-      <c r="D188" s="1" t="inlineStr">
+      <c r="D189" s="1" t="inlineStr">
         <is>
           <t>B11.1</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="F188" s="3" t="inlineStr">
+      <c r="F189" s="3" t="inlineStr">
         <is>
           <t>ឯកសារ</t>
         </is>
       </c>
-      <c r="G188" s="4" t="inlineStr">
+      <c r="G189" s="4" t="inlineStr">
         <is>
           <t>/school-documents</t>
         </is>
       </c>
-      <c r="H188" s="5" t="n"/>
-      <c r="I188" s="3" t="n"/>
-      <c r="J188" s="3" t="n"/>
-      <c r="K188" s="6" t="n"/>
-    </row>
-    <row r="189" ht="21.6" customHeight="1">
-      <c r="A189" s="7" t="n"/>
-      <c r="B189" s="8" t="n"/>
-      <c r="C189" s="8" t="n"/>
-      <c r="D189" s="9" t="inlineStr">
-        <is>
-          <t>B11.2</t>
-        </is>
-      </c>
-      <c r="E189" s="10" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F189" s="8" t="inlineStr">
-        <is>
-          <t>ទូទៅ</t>
-        </is>
-      </c>
-      <c r="G189" s="11" t="inlineStr">
-        <is>
-          <t>/settings</t>
-        </is>
-      </c>
-      <c r="H189" s="7" t="n"/>
-      <c r="I189" s="8" t="n"/>
-      <c r="J189" s="8" t="n"/>
-      <c r="K189" s="12" t="n"/>
+      <c r="H189" s="5" t="n"/>
+      <c r="I189" s="3" t="n"/>
+      <c r="J189" s="3" t="n"/>
+      <c r="K189" s="6" t="n"/>
     </row>
     <row r="190" ht="21.6" customHeight="1">
       <c r="A190" s="7" t="n"/>
@@ -9258,22 +9282,22 @@
       <c r="C190" s="8" t="n"/>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>B11.3</t>
+          <t>B11.2</t>
         </is>
       </c>
       <c r="E190" s="10" t="inlineStr">
         <is>
-          <t>Telegram notifications</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F190" s="8" t="inlineStr">
         <is>
-          <t>ការជូនដំណឹង Telegram</t>
+          <t>ទូទៅ</t>
         </is>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>/telegram-notifications</t>
+          <t>/settings</t>
         </is>
       </c>
       <c r="H190" s="7" t="n"/>
@@ -9287,22 +9311,22 @@
       <c r="C191" s="8" t="n"/>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>B11.4</t>
+          <t>B11.3</t>
         </is>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>Telegram notifications</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>អ្នកប្រើប្រាស់</t>
+          <t>ការជូនដំណឹង Telegram</t>
         </is>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/telegram-notifications</t>
         </is>
       </c>
       <c r="H191" s="7" t="n"/>
@@ -9316,22 +9340,22 @@
       <c r="C192" s="8" t="n"/>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>B11.5</t>
+          <t>B11.4</t>
         </is>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>អ្នកប្រើប្រាស់</t>
         </is>
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="H192" s="7" t="n"/>
@@ -9345,22 +9369,22 @@
       <c r="C193" s="8" t="n"/>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>B11.6</t>
+          <t>B11.5</t>
         </is>
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>Audit Logs</t>
+          <t>Roles</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr">
         <is>
-          <t>កំណត់ហេតុសវនកម្ម</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
-          <t>/audit-logs</t>
+          <t>/roles</t>
         </is>
       </c>
       <c r="H193" s="7" t="n"/>
@@ -9374,49 +9398,39 @@
       <c r="C194" s="8" t="n"/>
       <c r="D194" s="9" t="inlineStr">
         <is>
-          <t>B11.7</t>
+          <t>B11.6</t>
         </is>
       </c>
       <c r="E194" s="10" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Audit Logs</t>
         </is>
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>កំណត់ហេតុសវនកម្ម</t>
         </is>
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="H194" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I194" s="8" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="J194" s="8" t="inlineStr">
-        <is>
-          <t>ភាសា</t>
-        </is>
-      </c>
+          <t>/audit-logs</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="n"/>
+      <c r="I194" s="8" t="n"/>
+      <c r="J194" s="8" t="n"/>
       <c r="K194" s="12" t="n"/>
     </row>
     <row r="195" ht="21.6" customHeight="1">
       <c r="A195" s="7" t="n"/>
       <c r="B195" s="8" t="n"/>
       <c r="C195" s="8" t="n"/>
-      <c r="D195" s="7" t="inlineStr">
+      <c r="D195" s="9" t="inlineStr">
         <is>
           <t>B11.7</t>
         </is>
       </c>
-      <c r="E195" s="8" t="inlineStr">
+      <c r="E195" s="10" t="inlineStr">
         <is>
           <t>Languages</t>
         </is>
@@ -9432,16 +9446,16 @@
         </is>
       </c>
       <c r="H195" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I195" s="8" t="inlineStr">
         <is>
-          <t>Translation</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>ការបកប្រែ</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="K195" s="12" t="n"/>
@@ -9450,29 +9464,39 @@
       <c r="A196" s="7" t="n"/>
       <c r="B196" s="8" t="n"/>
       <c r="C196" s="8" t="n"/>
-      <c r="D196" s="9" t="inlineStr">
-        <is>
-          <t>B11.8</t>
-        </is>
-      </c>
-      <c r="E196" s="10" t="inlineStr">
-        <is>
-          <t>Base Data</t>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>B11.7</t>
+        </is>
+      </c>
+      <c r="E196" s="8" t="inlineStr">
+        <is>
+          <t>Languages</t>
         </is>
       </c>
       <c r="F196" s="8" t="inlineStr">
         <is>
-          <t>ទិន្នន័យមូលដ្ឋាន</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
-          <t>/lookup-categories</t>
-        </is>
-      </c>
-      <c r="H196" s="7" t="n"/>
-      <c r="I196" s="8" t="n"/>
-      <c r="J196" s="8" t="n"/>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="H196" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I196" s="8" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="J196" s="8" t="inlineStr">
+        <is>
+          <t>ការបកប្រែ</t>
+        </is>
+      </c>
       <c r="K196" s="12" t="n"/>
     </row>
     <row r="197" ht="21.6" customHeight="1">
@@ -9481,22 +9505,22 @@
       <c r="C197" s="8" t="n"/>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>B11.9</t>
+          <t>B11.8</t>
         </is>
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Base Data</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr">
         <is>
-          <t>បម្រុងទុក</t>
+          <t>ទិន្នន័យមូលដ្ឋាន</t>
         </is>
       </c>
       <c r="G197" s="11" t="inlineStr">
         <is>
-          <t>/database-backups</t>
+          <t>/lookup-categories</t>
         </is>
       </c>
       <c r="H197" s="7" t="n"/>
@@ -9505,91 +9529,81 @@
       <c r="K197" s="12" t="n"/>
     </row>
     <row r="198" ht="21.6" customHeight="1">
-      <c r="A198" s="13" t="inlineStr">
+      <c r="A198" s="7" t="n"/>
+      <c r="B198" s="8" t="n"/>
+      <c r="C198" s="8" t="n"/>
+      <c r="D198" s="9" t="inlineStr">
+        <is>
+          <t>B11.9</t>
+        </is>
+      </c>
+      <c r="E198" s="10" t="inlineStr">
+        <is>
+          <t>Backup</t>
+        </is>
+      </c>
+      <c r="F198" s="8" t="inlineStr">
+        <is>
+          <t>បម្រុងទុក</t>
+        </is>
+      </c>
+      <c r="G198" s="11" t="inlineStr">
+        <is>
+          <t>/database-backups</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="n"/>
+      <c r="I198" s="8" t="n"/>
+      <c r="J198" s="8" t="n"/>
+      <c r="K198" s="12" t="n"/>
+    </row>
+    <row r="199" ht="21.6" customHeight="1">
+      <c r="A199" s="13" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B198" s="14" t="inlineStr">
+      <c r="B199" s="14" t="inlineStr">
         <is>
           <t>eApprovals</t>
         </is>
       </c>
-      <c r="C198" s="15" t="n"/>
-      <c r="D198" s="13" t="inlineStr">
+      <c r="C199" s="15" t="n"/>
+      <c r="D199" s="13" t="inlineStr">
         <is>
           <t>B12.1</t>
         </is>
       </c>
-      <c r="E198" s="14" t="inlineStr">
+      <c r="E199" s="14" t="inlineStr">
         <is>
           <t>Forms</t>
         </is>
       </c>
-      <c r="F198" s="15" t="inlineStr">
+      <c r="F199" s="15" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="G198" s="16" t="inlineStr">
+      <c r="G199" s="16" t="inlineStr">
         <is>
           <t>/approvals/forms</t>
         </is>
       </c>
-      <c r="H198" s="17" t="n"/>
-      <c r="I198" s="15" t="n"/>
-      <c r="J198" s="15" t="n"/>
-      <c r="K198" s="18" t="n"/>
-    </row>
-    <row r="199" ht="21.6" customHeight="1">
-      <c r="A199" s="19" t="n"/>
-      <c r="B199" s="20" t="n"/>
-      <c r="C199" s="20" t="n"/>
-      <c r="D199" s="21" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E199" s="22" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F199" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G199" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H199" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I199" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J199" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
-      <c r="K199" s="24" t="n"/>
+      <c r="H199" s="17" t="n"/>
+      <c r="I199" s="15" t="n"/>
+      <c r="J199" s="15" t="n"/>
+      <c r="K199" s="18" t="n"/>
     </row>
     <row r="200" ht="21.6" customHeight="1">
       <c r="A200" s="19" t="n"/>
       <c r="B200" s="20" t="n"/>
       <c r="C200" s="20" t="n"/>
-      <c r="D200" s="19" t="inlineStr">
+      <c r="D200" s="21" t="inlineStr">
         <is>
           <t>B12.2</t>
         </is>
       </c>
-      <c r="E200" s="20" t="inlineStr">
+      <c r="E200" s="22" t="inlineStr">
         <is>
           <t>My Request</t>
         </is>
@@ -9605,16 +9619,16 @@
         </is>
       </c>
       <c r="H200" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I200" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J200" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="K200" s="24" t="n"/>
@@ -9644,16 +9658,16 @@
         </is>
       </c>
       <c r="H201" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I201" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J201" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K201" s="24" t="n"/>
@@ -9683,16 +9697,16 @@
         </is>
       </c>
       <c r="H202" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I202" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J202" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K202" s="24" t="n"/>
@@ -9722,16 +9736,16 @@
         </is>
       </c>
       <c r="H203" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I203" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="J203" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="K203" s="24" t="n"/>
@@ -9740,37 +9754,37 @@
       <c r="A204" s="19" t="n"/>
       <c r="B204" s="20" t="n"/>
       <c r="C204" s="20" t="n"/>
-      <c r="D204" s="21" t="inlineStr">
-        <is>
-          <t>B12.3</t>
-        </is>
-      </c>
-      <c r="E204" s="22" t="inlineStr">
-        <is>
-          <t>Approvals</t>
+      <c r="D204" s="19" t="inlineStr">
+        <is>
+          <t>B12.2</t>
+        </is>
+      </c>
+      <c r="E204" s="20" t="inlineStr">
+        <is>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F204" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G204" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H204" s="19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I204" s="20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="J204" s="20" t="inlineStr">
         <is>
-          <t>ថ្មី</t>
+          <t>បានលុបចោល</t>
         </is>
       </c>
       <c r="K204" s="24" t="n"/>
@@ -9779,12 +9793,12 @@
       <c r="A205" s="19" t="n"/>
       <c r="B205" s="20" t="n"/>
       <c r="C205" s="20" t="n"/>
-      <c r="D205" s="19" t="inlineStr">
+      <c r="D205" s="21" t="inlineStr">
         <is>
           <t>B12.3</t>
         </is>
       </c>
-      <c r="E205" s="20" t="inlineStr">
+      <c r="E205" s="22" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
@@ -9800,16 +9814,16 @@
         </is>
       </c>
       <c r="H205" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I205" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>New</t>
         </is>
       </c>
       <c r="J205" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>ថ្មី</t>
         </is>
       </c>
       <c r="K205" s="24" t="n"/>
@@ -9839,16 +9853,16 @@
         </is>
       </c>
       <c r="H206" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I206" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J206" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K206" s="24" t="n"/>
@@ -9878,16 +9892,16 @@
         </is>
       </c>
       <c r="H207" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I207" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J207" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K207" s="24" t="n"/>
@@ -9917,47 +9931,57 @@
         </is>
       </c>
       <c r="H208" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I208" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="J208" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="K208" s="24" t="n"/>
     </row>
-    <row r="209">
+    <row r="209" ht="21.6" customHeight="1">
       <c r="A209" s="19" t="n"/>
       <c r="B209" s="20" t="n"/>
       <c r="C209" s="20" t="n"/>
-      <c r="D209" s="21" t="inlineStr">
-        <is>
-          <t>B12.4</t>
-        </is>
-      </c>
-      <c r="E209" s="22" t="inlineStr">
-        <is>
-          <t>Form Categories</t>
+      <c r="D209" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E209" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="F209" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទទម្រង់បែបបទ</t>
+          <t>ការអនុម័ត</t>
         </is>
       </c>
       <c r="G209" s="23" t="inlineStr">
         <is>
-          <t>/form-categories</t>
-        </is>
-      </c>
-      <c r="H209" s="19" t="n"/>
-      <c r="I209" s="20" t="n"/>
-      <c r="J209" s="20" t="n"/>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H209" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I209" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="J209" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
       <c r="K209" s="24" t="n"/>
     </row>
     <row r="210">
@@ -9966,22 +9990,22 @@
       <c r="C210" s="20" t="n"/>
       <c r="D210" s="21" t="inlineStr">
         <is>
-          <t>B12.5</t>
+          <t>B12.4</t>
         </is>
       </c>
       <c r="E210" s="22" t="inlineStr">
         <is>
-          <t>Form Templates</t>
+          <t>Form Categories</t>
         </is>
       </c>
       <c r="F210" s="20" t="inlineStr">
         <is>
-          <t>ទម្រង់បែបបទ</t>
+          <t>ប្រភេទទម្រង់បែបបទ</t>
         </is>
       </c>
       <c r="G210" s="23" t="inlineStr">
         <is>
-          <t>/form-templates</t>
+          <t>/form-categories</t>
         </is>
       </c>
       <c r="H210" s="19" t="n"/>
@@ -9990,89 +10014,118 @@
       <c r="K210" s="24" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="inlineStr">
+      <c r="A211" s="19" t="n"/>
+      <c r="B211" s="20" t="n"/>
+      <c r="C211" s="20" t="n"/>
+      <c r="D211" s="21" t="inlineStr">
+        <is>
+          <t>B12.5</t>
+        </is>
+      </c>
+      <c r="E211" s="22" t="inlineStr">
+        <is>
+          <t>Form Templates</t>
+        </is>
+      </c>
+      <c r="F211" s="20" t="inlineStr">
+        <is>
+          <t>ទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="G211" s="23" t="inlineStr">
+        <is>
+          <t>/form-templates</t>
+        </is>
+      </c>
+      <c r="H211" s="19" t="n"/>
+      <c r="I211" s="20" t="n"/>
+      <c r="J211" s="20" t="n"/>
+      <c r="K211" s="24" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C211" s="3" t="inlineStr">
+      <c r="C212" s="3" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D211" s="1" t="inlineStr">
+      <c r="D212" s="1" t="inlineStr">
         <is>
           <t>B13.1</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>Groups</t>
         </is>
       </c>
-      <c r="F211" s="3" t="inlineStr">
+      <c r="F212" s="3" t="inlineStr">
         <is>
           <t>ក្រុម</t>
         </is>
       </c>
-      <c r="G211" s="4" t="inlineStr">
+      <c r="G212" s="4" t="inlineStr">
         <is>
           <t>/approval-flow/groups</t>
         </is>
       </c>
-      <c r="H211" s="5" t="n"/>
-      <c r="I211" s="3" t="n"/>
-      <c r="J211" s="3" t="n"/>
-      <c r="K211" s="6" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="7" t="inlineStr">
+      <c r="H212" s="5" t="n"/>
+      <c r="I212" s="3" t="n"/>
+      <c r="J212" s="3" t="n"/>
+      <c r="K212" s="6" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="7" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B212" s="8" t="inlineStr">
+      <c r="B213" s="8" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C212" s="8" t="inlineStr">
+      <c r="C213" s="8" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D212" s="9" t="inlineStr">
+      <c r="D213" s="9" t="inlineStr">
         <is>
           <t>B13.2</t>
         </is>
       </c>
-      <c r="E212" s="10" t="inlineStr">
+      <c r="E213" s="10" t="inlineStr">
         <is>
           <t>Flow Setting</t>
         </is>
       </c>
-      <c r="F212" s="8" t="inlineStr">
+      <c r="F213" s="8" t="inlineStr">
         <is>
           <t>កំណត់លំហូរ</t>
         </is>
       </c>
-      <c r="G212" s="11" t="inlineStr">
+      <c r="G213" s="11" t="inlineStr">
         <is>
           <t>/approval-flow/settings</t>
         </is>
       </c>
-      <c r="H212" s="7" t="n"/>
-      <c r="I212" s="8" t="n"/>
-      <c r="J212" s="8" t="n"/>
-      <c r="K212" s="12" t="n"/>
+      <c r="H213" s="7" t="n"/>
+      <c r="I213" s="8" t="n"/>
+      <c r="J213" s="8" t="n"/>
+      <c r="K213" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K208"/>
+  <autoFilter ref="A1:K209"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>

--- a/docs/NTCSWEB-Modules.xlsx
+++ b/docs/NTCSWEB-Modules.xlsx
@@ -754,7 +754,7 @@
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>List of every customer (school / organization), its plan, status and health.</t>
+          <t>List of every customer (school / organization), its plan, status and health. New customer can copy setup from another customer (programs, courses, classes, lists, accounts, HRM setup; never users, students or records).</t>
         </is>
       </c>
     </row>

--- a/docs/NTCSWEB-Modules.xlsx
+++ b/docs/NTCSWEB-Modules.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2082,6 +2082,51 @@
       <c r="K39" s="18" t="inlineStr">
         <is>
           <t>Own password and two-factor sign-in (profile row at the bottom of the menu).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="21.6" customHeight="1">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Organization types</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>ប្រភេទស្ថាប័ន</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>A11.1</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Organization types</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>ប្រភេទស្ថាប័ន</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>/organization-types</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>In the menu right under Customers. School, Company, Organization, Ministry… with their word for "school" in each language; a customer's screens use its word. Picked on New customer, the customer profile and website sign-up.</t>
         </is>
       </c>
     </row>

--- a/docs/NTCSWEB-Modules.xlsx
+++ b/docs/NTCSWEB-Modules.xlsx
@@ -2143,7 +2143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K213"/>
+  <dimension ref="A1:K217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -10168,6 +10168,226 @@
       <c r="I213" s="8" t="n"/>
       <c r="J213" s="8" t="n"/>
       <c r="K213" s="12" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>ការិយាល័យទទួលភ្ញៀវ</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="inlineStr">
+        <is>
+          <t>B14.1</t>
+        </is>
+      </c>
+      <c r="E214" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="F214" s="8" t="inlineStr">
+        <is>
+          <t>ការិយាល័យទទួលភ្ញៀវ</t>
+        </is>
+      </c>
+      <c r="G214" s="11" t="inlineStr">
+        <is>
+          <t>/front-office</t>
+        </is>
+      </c>
+      <c r="H214" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" s="8" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="J214" s="8" t="inlineStr">
+        <is>
+          <t>ការសាកសួរ</t>
+        </is>
+      </c>
+      <c r="K214" s="12" t="inlineStr">
+        <is>
+          <t>In the menu after Project Management. People who ask about the school: source, interest, follow-up history, next follow-up date; Register student fills the student form and links it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>ការិយាល័យទទួលភ្ញៀវ</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
+        <is>
+          <t>B14.1</t>
+        </is>
+      </c>
+      <c r="E215" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="F215" s="8" t="inlineStr">
+        <is>
+          <t>ការិយាល័យទទួលភ្ញៀវ</t>
+        </is>
+      </c>
+      <c r="G215" s="11" t="inlineStr">
+        <is>
+          <t>/front-office</t>
+        </is>
+      </c>
+      <c r="H215" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I215" s="8" t="inlineStr">
+        <is>
+          <t>Meeting arrangement</t>
+        </is>
+      </c>
+      <c r="J215" s="8" t="inlineStr">
+        <is>
+          <t>រៀបចំកិច្ចប្រជុំ</t>
+        </is>
+      </c>
+      <c r="K215" s="12" t="inlineStr">
+        <is>
+          <t>Date, start/end time, place, organizer, agenda; participants are staff (notified when invited, moved or cancelled) plus outside guests; meeting note; Scheduled / Completed / Cancelled. Upcoming, Past, All and Only mine. Teachers can view by default. Also shown on School setup &gt; School calendar (not cancelled ones; only to people who can view meetings); a click opens the meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B216" s="8" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C216" s="8" t="inlineStr">
+        <is>
+          <t>ការិយាល័យទទួលភ្ញៀវ</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="inlineStr">
+        <is>
+          <t>B14.1</t>
+        </is>
+      </c>
+      <c r="E216" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="F216" s="8" t="inlineStr">
+        <is>
+          <t>ការិយាល័យទទួលភ្ញៀវ</t>
+        </is>
+      </c>
+      <c r="G216" s="11" t="inlineStr">
+        <is>
+          <t>/front-office</t>
+        </is>
+      </c>
+      <c r="H216" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I216" s="8" t="inlineStr">
+        <is>
+          <t>Appointment</t>
+        </is>
+      </c>
+      <c r="J216" s="8" t="inlineStr">
+        <is>
+          <t>ការណាត់ជួប</t>
+        </is>
+      </c>
+      <c r="K216" s="12" t="inlineStr">
+        <is>
+          <t>Book a visit: visitor, phone, organization, purpose, date and time, Meeting with (staff, notified). Today / Upcoming / Past / All. Check in adds them to the Visitor log and tells the host; No-show, Cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>ការិយាល័យទទួលភ្ញៀវ</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>B14.1</t>
+        </is>
+      </c>
+      <c r="E217" s="10" t="inlineStr">
+        <is>
+          <t>Front Office</t>
+        </is>
+      </c>
+      <c r="F217" s="8" t="inlineStr">
+        <is>
+          <t>ការិយាល័យទទួលភ្ញៀវ</t>
+        </is>
+      </c>
+      <c r="G217" s="11" t="inlineStr">
+        <is>
+          <t>/front-office</t>
+        </is>
+      </c>
+      <c r="H217" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I217" s="8" t="inlineStr">
+        <is>
+          <t>Visitor</t>
+        </is>
+      </c>
+      <c r="J217" s="8" t="inlineStr">
+        <is>
+          <t>ភ្ញៀវ</t>
+        </is>
+      </c>
+      <c r="K217" s="12" t="inlineStr">
+        <is>
+          <t>Visitor log by day: walk-ins checked in here, appointments via Check in; people count, ID no., badge; check-in and check-out times; On site now. Check out completes the appointment.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K209"/>

--- a/docs/NTCSWEB-Modules.xlsx
+++ b/docs/NTCSWEB-Modules.xlsx
@@ -10220,7 +10220,7 @@
       </c>
       <c r="K214" s="12" t="inlineStr">
         <is>
-          <t>In the menu after Project Management. People who ask about the school: source, interest, follow-up history, next follow-up date; Register student fills the student form and links it.</t>
+          <t>In the menu after Project Management. People who ask about the school: source, interest, follow-up history, next follow-up date; Register student fills the student form and links it. The website Register form (C4.4) also lands here as source Website, and staff who can update inquiries are notified.</t>
         </is>
       </c>
     </row>

--- a/docs/NTCSWEB-Modules.xlsx
+++ b/docs/NTCSWEB-Modules.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Back office" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Back office'!$A$1:$K$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Back office'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'System'!$A$1:$K$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'System'!$A$1:$K$216</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'System'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website'!$A$1:$K$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Website'!$1:$1</definedName>
@@ -2143,7 +2143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K217"/>
+  <dimension ref="A1:K224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4014,26 +4014,10 @@
       <c r="A49" s="19" t="n"/>
       <c r="B49" s="20" t="n"/>
       <c r="C49" s="20" t="n"/>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D49" s="19" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="23" t="n"/>
       <c r="H49" s="19" t="n">
         <v>2</v>
       </c>
@@ -4053,26 +4037,10 @@
       <c r="A50" s="19" t="n"/>
       <c r="B50" s="20" t="n"/>
       <c r="C50" s="20" t="n"/>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E50" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F50" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D50" s="19" t="n"/>
+      <c r="E50" s="20" t="n"/>
+      <c r="F50" s="20" t="n"/>
+      <c r="G50" s="23" t="n"/>
       <c r="H50" s="19" t="n">
         <v>3</v>
       </c>
@@ -4092,26 +4060,10 @@
       <c r="A51" s="19" t="n"/>
       <c r="B51" s="20" t="n"/>
       <c r="C51" s="20" t="n"/>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E51" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F51" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="20" t="n"/>
+      <c r="G51" s="23" t="n"/>
       <c r="H51" s="19" t="n">
         <v>4</v>
       </c>
@@ -4131,26 +4083,10 @@
       <c r="A52" s="19" t="n"/>
       <c r="B52" s="20" t="n"/>
       <c r="C52" s="20" t="n"/>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E52" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F52" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="20" t="n"/>
+      <c r="G52" s="23" t="n"/>
       <c r="H52" s="19" t="n">
         <v>5</v>
       </c>
@@ -4170,26 +4106,10 @@
       <c r="A53" s="19" t="n"/>
       <c r="B53" s="20" t="n"/>
       <c r="C53" s="20" t="n"/>
-      <c r="D53" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E53" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F53" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G53" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="20" t="n"/>
+      <c r="G53" s="23" t="n"/>
       <c r="H53" s="19" t="n">
         <v>6</v>
       </c>
@@ -4209,26 +4129,10 @@
       <c r="A54" s="19" t="n"/>
       <c r="B54" s="20" t="n"/>
       <c r="C54" s="20" t="n"/>
-      <c r="D54" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E54" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F54" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G54" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="20" t="n"/>
+      <c r="F54" s="20" t="n"/>
+      <c r="G54" s="23" t="n"/>
       <c r="H54" s="19" t="n">
         <v>7</v>
       </c>
@@ -4248,26 +4152,10 @@
       <c r="A55" s="19" t="n"/>
       <c r="B55" s="20" t="n"/>
       <c r="C55" s="20" t="n"/>
-      <c r="D55" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G55" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="23" t="n"/>
       <c r="H55" s="19" t="n">
         <v>8</v>
       </c>
@@ -4287,26 +4175,10 @@
       <c r="A56" s="19" t="n"/>
       <c r="B56" s="20" t="n"/>
       <c r="C56" s="20" t="n"/>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E56" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F56" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="20" t="n"/>
+      <c r="F56" s="20" t="n"/>
+      <c r="G56" s="23" t="n"/>
       <c r="H56" s="19" t="n">
         <v>9</v>
       </c>
@@ -4326,26 +4198,10 @@
       <c r="A57" s="19" t="n"/>
       <c r="B57" s="20" t="n"/>
       <c r="C57" s="20" t="n"/>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E57" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F57" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G57" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="20" t="n"/>
+      <c r="G57" s="23" t="n"/>
       <c r="H57" s="19" t="n">
         <v>10</v>
       </c>
@@ -4365,26 +4221,10 @@
       <c r="A58" s="19" t="n"/>
       <c r="B58" s="20" t="n"/>
       <c r="C58" s="20" t="n"/>
-      <c r="D58" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E58" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F58" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="20" t="n"/>
+      <c r="F58" s="20" t="n"/>
+      <c r="G58" s="23" t="n"/>
       <c r="H58" s="19" t="n">
         <v>11</v>
       </c>
@@ -4404,26 +4244,10 @@
       <c r="A59" s="19" t="n"/>
       <c r="B59" s="20" t="n"/>
       <c r="C59" s="20" t="n"/>
-      <c r="D59" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E59" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G59" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D59" s="19" t="n"/>
+      <c r="E59" s="20" t="n"/>
+      <c r="F59" s="20" t="n"/>
+      <c r="G59" s="23" t="n"/>
       <c r="H59" s="19" t="n">
         <v>12</v>
       </c>
@@ -4443,26 +4267,10 @@
       <c r="A60" s="19" t="n"/>
       <c r="B60" s="20" t="n"/>
       <c r="C60" s="20" t="n"/>
-      <c r="D60" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E60" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F60" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="20" t="n"/>
+      <c r="F60" s="20" t="n"/>
+      <c r="G60" s="23" t="n"/>
       <c r="H60" s="19" t="n">
         <v>13</v>
       </c>
@@ -4482,26 +4290,10 @@
       <c r="A61" s="19" t="n"/>
       <c r="B61" s="20" t="n"/>
       <c r="C61" s="20" t="n"/>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E61" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F61" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G61" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="20" t="n"/>
+      <c r="F61" s="20" t="n"/>
+      <c r="G61" s="23" t="n"/>
       <c r="H61" s="19" t="n">
         <v>14</v>
       </c>
@@ -4521,26 +4313,10 @@
       <c r="A62" s="19" t="n"/>
       <c r="B62" s="20" t="n"/>
       <c r="C62" s="20" t="n"/>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>B4.9</t>
-        </is>
-      </c>
-      <c r="E62" s="20" t="inlineStr">
-        <is>
-          <t>Examination</t>
-        </is>
-      </c>
-      <c r="F62" s="20" t="inlineStr">
-        <is>
-          <t>ការប្រឡងនិងលទ្ធផល</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr">
-        <is>
-          <t>/examination</t>
-        </is>
-      </c>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="20" t="n"/>
+      <c r="F62" s="20" t="n"/>
+      <c r="G62" s="23" t="n"/>
       <c r="H62" s="19" t="n">
         <v>15</v>
       </c>
@@ -7801,831 +7577,837 @@
       </c>
     </row>
     <row r="147" ht="21.6" customHeight="1">
-      <c r="A147" s="1" t="inlineStr">
+      <c r="A147" s="19" t="n"/>
+      <c r="B147" s="20" t="n"/>
+      <c r="C147" s="20" t="n"/>
+      <c r="D147" s="21" t="inlineStr">
+        <is>
+          <t>B6.13</t>
+        </is>
+      </c>
+      <c r="E147" s="22" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="F147" s="20" t="inlineStr">
+        <is>
+          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="inlineStr">
+        <is>
+          <t>/professional-development</t>
+        </is>
+      </c>
+      <c r="H147" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="20" t="inlineStr">
+        <is>
+          <t>Training records</t>
+        </is>
+      </c>
+      <c r="J147" s="20" t="inlineStr">
+        <is>
+          <t>ប្រវត្តិវគ្គបណ្តុះបណ្តាល</t>
+        </is>
+      </c>
+      <c r="K147" s="24" t="n"/>
+    </row>
+    <row r="148" ht="21.6" customHeight="1">
+      <c r="A148" s="19" t="n"/>
+      <c r="B148" s="20" t="n"/>
+      <c r="C148" s="20" t="n"/>
+      <c r="D148" s="21" t="inlineStr">
+        <is>
+          <t>B6.13</t>
+        </is>
+      </c>
+      <c r="E148" s="22" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="F148" s="20" t="inlineStr">
+        <is>
+          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+        </is>
+      </c>
+      <c r="G148" s="23" t="inlineStr">
+        <is>
+          <t>/professional-development</t>
+        </is>
+      </c>
+      <c r="H148" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I148" s="20" t="inlineStr">
+        <is>
+          <t>Training calendar</t>
+        </is>
+      </c>
+      <c r="J148" s="20" t="inlineStr">
+        <is>
+          <t>ប្រតិទិនវគ្គបណ្តុះបណ្តាល</t>
+        </is>
+      </c>
+      <c r="K148" s="24" t="n"/>
+    </row>
+    <row r="149" ht="21.6" customHeight="1">
+      <c r="A149" s="19" t="n"/>
+      <c r="B149" s="20" t="n"/>
+      <c r="C149" s="20" t="n"/>
+      <c r="D149" s="21" t="inlineStr">
+        <is>
+          <t>B6.13</t>
+        </is>
+      </c>
+      <c r="E149" s="22" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="F149" s="20" t="inlineStr">
+        <is>
+          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+        </is>
+      </c>
+      <c r="G149" s="23" t="inlineStr">
+        <is>
+          <t>/professional-development</t>
+        </is>
+      </c>
+      <c r="H149" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I149" s="20" t="inlineStr">
+        <is>
+          <t>Certificates</t>
+        </is>
+      </c>
+      <c r="J149" s="20" t="inlineStr">
+        <is>
+          <t>វិញ្ញាបនបត្រ</t>
+        </is>
+      </c>
+      <c r="K149" s="24" t="n"/>
+    </row>
+    <row r="150" ht="21.6" customHeight="1">
+      <c r="A150" s="19" t="n"/>
+      <c r="B150" s="20" t="n"/>
+      <c r="C150" s="20" t="n"/>
+      <c r="D150" s="21" t="inlineStr">
+        <is>
+          <t>B6.13</t>
+        </is>
+      </c>
+      <c r="E150" s="22" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="F150" s="20" t="inlineStr">
+        <is>
+          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+        </is>
+      </c>
+      <c r="G150" s="23" t="inlineStr">
+        <is>
+          <t>/professional-development</t>
+        </is>
+      </c>
+      <c r="H150" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I150" s="20" t="inlineStr">
+        <is>
+          <t>Classroom observation</t>
+        </is>
+      </c>
+      <c r="J150" s="20" t="inlineStr">
+        <is>
+          <t>ការសង្កេតការបង្រៀនក្នុងថ្នាក់</t>
+        </is>
+      </c>
+      <c r="K150" s="24" t="n"/>
+    </row>
+    <row r="151" ht="21.6" customHeight="1">
+      <c r="A151" s="19" t="n"/>
+      <c r="B151" s="20" t="n"/>
+      <c r="C151" s="20" t="n"/>
+      <c r="D151" s="21" t="inlineStr">
+        <is>
+          <t>B6.13</t>
+        </is>
+      </c>
+      <c r="E151" s="22" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="F151" s="20" t="inlineStr">
+        <is>
+          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+        </is>
+      </c>
+      <c r="G151" s="23" t="inlineStr">
+        <is>
+          <t>/professional-development</t>
+        </is>
+      </c>
+      <c r="H151" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I151" s="20" t="inlineStr">
+        <is>
+          <t>Coaching &amp; mentoring</t>
+        </is>
+      </c>
+      <c r="J151" s="20" t="inlineStr">
+        <is>
+          <t>ការណែនាំ និងការជួយគាំទ្រ</t>
+        </is>
+      </c>
+      <c r="K151" s="24" t="n"/>
+    </row>
+    <row r="152" ht="21.6" customHeight="1">
+      <c r="A152" s="19" t="n"/>
+      <c r="B152" s="20" t="n"/>
+      <c r="C152" s="20" t="n"/>
+      <c r="D152" s="21" t="inlineStr">
+        <is>
+          <t>B6.13</t>
+        </is>
+      </c>
+      <c r="E152" s="22" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="F152" s="20" t="inlineStr">
+        <is>
+          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="inlineStr">
+        <is>
+          <t>/professional-development</t>
+        </is>
+      </c>
+      <c r="H152" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I152" s="20" t="inlineStr">
+        <is>
+          <t>Development plan</t>
+        </is>
+      </c>
+      <c r="J152" s="20" t="inlineStr">
+        <is>
+          <t>ផែនការអភិវឌ្ឍន៍</t>
+        </is>
+      </c>
+      <c r="K152" s="24" t="n"/>
+    </row>
+    <row r="153" ht="21.6" customHeight="1">
+      <c r="A153" s="19" t="n"/>
+      <c r="B153" s="20" t="n"/>
+      <c r="C153" s="20" t="n"/>
+      <c r="D153" s="21" t="inlineStr">
+        <is>
+          <t>B6.13</t>
+        </is>
+      </c>
+      <c r="E153" s="22" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="F153" s="20" t="inlineStr">
+        <is>
+          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="inlineStr">
+        <is>
+          <t>/professional-development</t>
+        </is>
+      </c>
+      <c r="H153" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I153" s="20" t="inlineStr">
+        <is>
+          <t>Training reports</t>
+        </is>
+      </c>
+      <c r="J153" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍វគ្គបណ្តុះបណ្តាល</t>
+        </is>
+      </c>
+      <c r="K153" s="24" t="n"/>
+    </row>
+    <row r="154" ht="21.6" customHeight="1">
+      <c r="A154" s="1" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t>វិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="D147" s="1" t="inlineStr">
+      <c r="D154" s="1" t="inlineStr">
         <is>
           <t>B7.1</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Billing Dashboard</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងវិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="G147" s="4" t="inlineStr">
+      <c r="G154" s="4" t="inlineStr">
         <is>
           <t>/billing</t>
         </is>
       </c>
-      <c r="H147" s="5" t="n"/>
-      <c r="I147" s="3" t="n"/>
-      <c r="J147" s="3" t="n"/>
-      <c r="K147" s="6" t="n"/>
-    </row>
-    <row r="148" ht="21.6" customHeight="1">
-      <c r="A148" s="7" t="n"/>
-      <c r="B148" s="8" t="n"/>
-      <c r="C148" s="8" t="n"/>
-      <c r="D148" s="9" t="inlineStr">
+      <c r="H154" s="5" t="n"/>
+      <c r="I154" s="3" t="n"/>
+      <c r="J154" s="3" t="n"/>
+      <c r="K154" s="6" t="n"/>
+    </row>
+    <row r="155" ht="21.6" customHeight="1">
+      <c r="A155" s="7" t="n"/>
+      <c r="B155" s="8" t="n"/>
+      <c r="C155" s="8" t="n"/>
+      <c r="D155" s="9" t="inlineStr">
         <is>
           <t>B7.2</t>
         </is>
       </c>
-      <c r="E148" s="10" t="inlineStr">
+      <c r="E155" s="10" t="inlineStr">
         <is>
           <t>Products</t>
         </is>
       </c>
-      <c r="F148" s="8" t="inlineStr">
+      <c r="F155" s="8" t="inlineStr">
         <is>
           <t>ផលិតផល</t>
         </is>
       </c>
-      <c r="G148" s="11" t="inlineStr">
+      <c r="G155" s="11" t="inlineStr">
         <is>
           <t>/products</t>
         </is>
       </c>
-      <c r="H148" s="7" t="n"/>
-      <c r="I148" s="8" t="n"/>
-      <c r="J148" s="8" t="n"/>
-      <c r="K148" s="12" t="n"/>
-    </row>
-    <row r="149" ht="21.6" customHeight="1">
-      <c r="A149" s="7" t="n"/>
-      <c r="B149" s="8" t="n"/>
-      <c r="C149" s="8" t="n"/>
-      <c r="D149" s="9" t="inlineStr">
+      <c r="H155" s="7" t="n"/>
+      <c r="I155" s="8" t="n"/>
+      <c r="J155" s="8" t="n"/>
+      <c r="K155" s="12" t="n"/>
+    </row>
+    <row r="156" ht="21.6" customHeight="1">
+      <c r="A156" s="7" t="n"/>
+      <c r="B156" s="8" t="n"/>
+      <c r="C156" s="8" t="n"/>
+      <c r="D156" s="9" t="inlineStr">
         <is>
           <t>B7.3</t>
         </is>
       </c>
-      <c r="E149" s="10" t="inlineStr">
+      <c r="E156" s="10" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
       </c>
-      <c r="F149" s="8" t="inlineStr">
+      <c r="F156" s="8" t="inlineStr">
         <is>
           <t>វិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="G149" s="11" t="inlineStr">
+      <c r="G156" s="11" t="inlineStr">
         <is>
           <t>/invoices</t>
         </is>
       </c>
-      <c r="H149" s="7" t="n">
+      <c r="H156" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I149" s="8" t="inlineStr">
+      <c r="I156" s="8" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
       </c>
-      <c r="J149" s="8" t="inlineStr">
+      <c r="J156" s="8" t="inlineStr">
         <is>
           <t>វិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="K149" s="12" t="n"/>
-    </row>
-    <row r="150" ht="21.6" customHeight="1">
-      <c r="A150" s="7" t="n"/>
-      <c r="B150" s="8" t="n"/>
-      <c r="C150" s="8" t="n"/>
-      <c r="D150" s="7" t="inlineStr">
+      <c r="K156" s="12" t="n"/>
+    </row>
+    <row r="157" ht="21.6" customHeight="1">
+      <c r="A157" s="7" t="n"/>
+      <c r="B157" s="8" t="n"/>
+      <c r="C157" s="8" t="n"/>
+      <c r="D157" s="7" t="inlineStr">
         <is>
           <t>B7.3</t>
         </is>
       </c>
-      <c r="E150" s="8" t="inlineStr">
+      <c r="E157" s="8" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
       </c>
-      <c r="F150" s="8" t="inlineStr">
+      <c r="F157" s="8" t="inlineStr">
         <is>
           <t>វិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="G150" s="11" t="inlineStr">
+      <c r="G157" s="11" t="inlineStr">
         <is>
           <t>/invoices</t>
         </is>
       </c>
-      <c r="H150" s="7" t="n">
+      <c r="H157" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I150" s="8" t="inlineStr">
+      <c r="I157" s="8" t="inlineStr">
         <is>
           <t>Monthly Invoice</t>
         </is>
       </c>
-      <c r="J150" s="8" t="inlineStr">
+      <c r="J157" s="8" t="inlineStr">
         <is>
           <t>វិក្កយបត្រប្រចាំខែ</t>
         </is>
       </c>
-      <c r="K150" s="12" t="n"/>
-    </row>
-    <row r="151" ht="21.6" customHeight="1">
-      <c r="A151" s="7" t="n"/>
-      <c r="B151" s="8" t="n"/>
-      <c r="C151" s="8" t="n"/>
-      <c r="D151" s="9" t="inlineStr">
+      <c r="K157" s="12" t="n"/>
+    </row>
+    <row r="158" ht="21.6" customHeight="1">
+      <c r="A158" s="7" t="n"/>
+      <c r="B158" s="8" t="n"/>
+      <c r="C158" s="8" t="n"/>
+      <c r="D158" s="9" t="inlineStr">
         <is>
           <t>B7.4</t>
         </is>
       </c>
-      <c r="E151" s="10" t="inlineStr">
+      <c r="E158" s="10" t="inlineStr">
         <is>
           <t>Payments</t>
         </is>
       </c>
-      <c r="F151" s="8" t="inlineStr">
+      <c r="F158" s="8" t="inlineStr">
         <is>
           <t>ការទូទាត់</t>
         </is>
       </c>
-      <c r="G151" s="11" t="inlineStr">
+      <c r="G158" s="11" t="inlineStr">
         <is>
           <t>/payments</t>
         </is>
       </c>
-      <c r="H151" s="7" t="n"/>
-      <c r="I151" s="8" t="n"/>
-      <c r="J151" s="8" t="n"/>
-      <c r="K151" s="12" t="n"/>
-    </row>
-    <row r="152" ht="21.6" customHeight="1">
-      <c r="A152" s="7" t="n"/>
-      <c r="B152" s="8" t="n"/>
-      <c r="C152" s="8" t="n"/>
-      <c r="D152" s="9" t="inlineStr">
+      <c r="H158" s="7" t="n"/>
+      <c r="I158" s="8" t="n"/>
+      <c r="J158" s="8" t="n"/>
+      <c r="K158" s="12" t="n"/>
+    </row>
+    <row r="159" ht="21.6" customHeight="1">
+      <c r="A159" s="7" t="n"/>
+      <c r="B159" s="8" t="n"/>
+      <c r="C159" s="8" t="n"/>
+      <c r="D159" s="9" t="inlineStr">
         <is>
           <t>B7.5</t>
         </is>
       </c>
-      <c r="E152" s="10" t="inlineStr">
+      <c r="E159" s="10" t="inlineStr">
         <is>
           <t>Currency Rates</t>
         </is>
       </c>
-      <c r="F152" s="8" t="inlineStr">
+      <c r="F159" s="8" t="inlineStr">
         <is>
           <t>អត្រាប្តូរប្រាក់</t>
         </is>
       </c>
-      <c r="G152" s="11" t="inlineStr">
+      <c r="G159" s="11" t="inlineStr">
         <is>
           <t>/currency-rates</t>
         </is>
       </c>
-      <c r="H152" s="7" t="n"/>
-      <c r="I152" s="8" t="n"/>
-      <c r="J152" s="8" t="n"/>
-      <c r="K152" s="12" t="n"/>
-    </row>
-    <row r="153" ht="21.6" customHeight="1">
-      <c r="A153" s="13" t="inlineStr">
+      <c r="H159" s="7" t="n"/>
+      <c r="I159" s="8" t="n"/>
+      <c r="J159" s="8" t="n"/>
+      <c r="K159" s="12" t="n"/>
+    </row>
+    <row r="160" ht="21.6" customHeight="1">
+      <c r="A160" s="13" t="inlineStr">
         <is>
           <t>B8</t>
         </is>
       </c>
-      <c r="B153" s="14" t="inlineStr">
+      <c r="B160" s="14" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="C153" s="15" t="inlineStr">
+      <c r="C160" s="15" t="inlineStr">
         <is>
           <t>គណនេយ្យ</t>
         </is>
       </c>
-      <c r="D153" s="13" t="inlineStr">
+      <c r="D160" s="13" t="inlineStr">
         <is>
           <t>B8.1</t>
         </is>
       </c>
-      <c r="E153" s="14" t="inlineStr">
+      <c r="E160" s="14" t="inlineStr">
         <is>
           <t>Accounting Dashboard</t>
         </is>
       </c>
-      <c r="F153" s="15" t="inlineStr">
+      <c r="F160" s="15" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងគណនេយ្យ</t>
         </is>
       </c>
-      <c r="G153" s="16" t="inlineStr">
+      <c r="G160" s="16" t="inlineStr">
         <is>
           <t>/accounting</t>
         </is>
       </c>
-      <c r="H153" s="17" t="n"/>
-      <c r="I153" s="15" t="n"/>
-      <c r="J153" s="15" t="n"/>
-      <c r="K153" s="18" t="n"/>
-    </row>
-    <row r="154" ht="21.6" customHeight="1">
-      <c r="A154" s="19" t="n"/>
-      <c r="B154" s="20" t="n"/>
-      <c r="C154" s="20" t="n"/>
-      <c r="D154" s="21" t="inlineStr">
-        <is>
-          <t>B8.2</t>
-        </is>
-      </c>
-      <c r="E154" s="22" t="inlineStr">
-        <is>
-          <t>Chart of Accounts</t>
-        </is>
-      </c>
-      <c r="F154" s="20" t="inlineStr">
-        <is>
-          <t>តារាងគណនី</t>
-        </is>
-      </c>
-      <c r="G154" s="23" t="inlineStr">
-        <is>
-          <t>/accounts</t>
-        </is>
-      </c>
-      <c r="H154" s="19" t="n"/>
-      <c r="I154" s="20" t="n"/>
-      <c r="J154" s="20" t="n"/>
-      <c r="K154" s="24" t="n"/>
-    </row>
-    <row r="155" ht="21.6" customHeight="1">
-      <c r="A155" s="19" t="n"/>
-      <c r="B155" s="20" t="n"/>
-      <c r="C155" s="20" t="n"/>
-      <c r="D155" s="21" t="inlineStr">
-        <is>
-          <t>B8.3</t>
-        </is>
-      </c>
-      <c r="E155" s="22" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="F155" s="20" t="inlineStr">
-        <is>
-          <t>ចំណូល</t>
-        </is>
-      </c>
-      <c r="G155" s="23" t="inlineStr">
-        <is>
-          <t>/income</t>
-        </is>
-      </c>
-      <c r="H155" s="19" t="n"/>
-      <c r="I155" s="20" t="n"/>
-      <c r="J155" s="20" t="n"/>
-      <c r="K155" s="24" t="n"/>
-    </row>
-    <row r="156" ht="21.6" customHeight="1">
-      <c r="A156" s="19" t="n"/>
-      <c r="B156" s="20" t="n"/>
-      <c r="C156" s="20" t="n"/>
-      <c r="D156" s="21" t="inlineStr">
-        <is>
-          <t>B8.4</t>
-        </is>
-      </c>
-      <c r="E156" s="22" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="F156" s="20" t="inlineStr">
-        <is>
-          <t>ចំណាយ</t>
-        </is>
-      </c>
-      <c r="G156" s="23" t="inlineStr">
-        <is>
-          <t>/expenses</t>
-        </is>
-      </c>
-      <c r="H156" s="19" t="n"/>
-      <c r="I156" s="20" t="n"/>
-      <c r="J156" s="20" t="n"/>
-      <c r="K156" s="24" t="n"/>
-    </row>
-    <row r="157" ht="21.6" customHeight="1">
-      <c r="A157" s="19" t="n"/>
-      <c r="B157" s="20" t="n"/>
-      <c r="C157" s="20" t="n"/>
-      <c r="D157" s="21" t="inlineStr">
-        <is>
-          <t>B8.5</t>
-        </is>
-      </c>
-      <c r="E157" s="22" t="inlineStr">
-        <is>
-          <t>Transactions</t>
-        </is>
-      </c>
-      <c r="F157" s="20" t="inlineStr">
-        <is>
-          <t>ប្រតិបត្តិការ</t>
-        </is>
-      </c>
-      <c r="G157" s="23" t="inlineStr">
-        <is>
-          <t>/transactions</t>
-        </is>
-      </c>
-      <c r="H157" s="19" t="n"/>
-      <c r="I157" s="20" t="n"/>
-      <c r="J157" s="20" t="n"/>
-      <c r="K157" s="24" t="n"/>
-    </row>
-    <row r="158" ht="21.6" customHeight="1">
-      <c r="A158" s="19" t="n"/>
-      <c r="B158" s="20" t="n"/>
-      <c r="C158" s="20" t="n"/>
-      <c r="D158" s="21" t="inlineStr">
-        <is>
-          <t>B8.6</t>
-        </is>
-      </c>
-      <c r="E158" s="22" t="inlineStr">
-        <is>
-          <t>Financial Reports</t>
-        </is>
-      </c>
-      <c r="F158" s="20" t="inlineStr">
-        <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
-        </is>
-      </c>
-      <c r="G158" s="23" t="inlineStr">
-        <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H158" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I158" s="20" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="J158" s="20" t="inlineStr">
-        <is>
-          <t>ចំណូល</t>
-        </is>
-      </c>
-      <c r="K158" s="24" t="n"/>
-    </row>
-    <row r="159" ht="21.6" customHeight="1">
-      <c r="A159" s="19" t="n"/>
-      <c r="B159" s="20" t="n"/>
-      <c r="C159" s="20" t="n"/>
-      <c r="D159" s="19" t="inlineStr">
-        <is>
-          <t>B8.6</t>
-        </is>
-      </c>
-      <c r="E159" s="20" t="inlineStr">
-        <is>
-          <t>Financial Reports</t>
-        </is>
-      </c>
-      <c r="F159" s="20" t="inlineStr">
-        <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
-        </is>
-      </c>
-      <c r="G159" s="23" t="inlineStr">
-        <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H159" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I159" s="20" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="J159" s="20" t="inlineStr">
-        <is>
-          <t>ចំណាយ</t>
-        </is>
-      </c>
-      <c r="K159" s="24" t="n"/>
-    </row>
-    <row r="160" ht="21.6" customHeight="1">
-      <c r="A160" s="19" t="n"/>
-      <c r="B160" s="20" t="n"/>
-      <c r="C160" s="20" t="n"/>
-      <c r="D160" s="19" t="inlineStr">
-        <is>
-          <t>B8.6</t>
-        </is>
-      </c>
-      <c r="E160" s="20" t="inlineStr">
-        <is>
-          <t>Financial Reports</t>
-        </is>
-      </c>
-      <c r="F160" s="20" t="inlineStr">
-        <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
-        </is>
-      </c>
-      <c r="G160" s="23" t="inlineStr">
-        <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H160" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I160" s="20" t="inlineStr">
-        <is>
-          <t>Profit &amp; Loss</t>
-        </is>
-      </c>
-      <c r="J160" s="20" t="inlineStr">
-        <is>
-          <t>ប្រាក់ចំណេញ និងខាត</t>
-        </is>
-      </c>
-      <c r="K160" s="24" t="n"/>
+      <c r="H160" s="17" t="n"/>
+      <c r="I160" s="15" t="n"/>
+      <c r="J160" s="15" t="n"/>
+      <c r="K160" s="18" t="n"/>
     </row>
     <row r="161" ht="21.6" customHeight="1">
       <c r="A161" s="19" t="n"/>
       <c r="B161" s="20" t="n"/>
       <c r="C161" s="20" t="n"/>
-      <c r="D161" s="19" t="inlineStr">
+      <c r="D161" s="21" t="inlineStr">
+        <is>
+          <t>B8.2</t>
+        </is>
+      </c>
+      <c r="E161" s="22" t="inlineStr">
+        <is>
+          <t>Chart of Accounts</t>
+        </is>
+      </c>
+      <c r="F161" s="20" t="inlineStr">
+        <is>
+          <t>តារាងគណនី</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="inlineStr">
+        <is>
+          <t>/accounts</t>
+        </is>
+      </c>
+      <c r="H161" s="19" t="n"/>
+      <c r="I161" s="20" t="n"/>
+      <c r="J161" s="20" t="n"/>
+      <c r="K161" s="24" t="n"/>
+    </row>
+    <row r="162" ht="21.6" customHeight="1">
+      <c r="A162" s="19" t="n"/>
+      <c r="B162" s="20" t="n"/>
+      <c r="C162" s="20" t="n"/>
+      <c r="D162" s="21" t="inlineStr">
+        <is>
+          <t>B8.3</t>
+        </is>
+      </c>
+      <c r="E162" s="22" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="F162" s="20" t="inlineStr">
+        <is>
+          <t>ចំណូល</t>
+        </is>
+      </c>
+      <c r="G162" s="23" t="inlineStr">
+        <is>
+          <t>/income</t>
+        </is>
+      </c>
+      <c r="H162" s="19" t="n"/>
+      <c r="I162" s="20" t="n"/>
+      <c r="J162" s="20" t="n"/>
+      <c r="K162" s="24" t="n"/>
+    </row>
+    <row r="163" ht="21.6" customHeight="1">
+      <c r="A163" s="19" t="n"/>
+      <c r="B163" s="20" t="n"/>
+      <c r="C163" s="20" t="n"/>
+      <c r="D163" s="21" t="inlineStr">
+        <is>
+          <t>B8.4</t>
+        </is>
+      </c>
+      <c r="E163" s="22" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="F163" s="20" t="inlineStr">
+        <is>
+          <t>ចំណាយ</t>
+        </is>
+      </c>
+      <c r="G163" s="23" t="inlineStr">
+        <is>
+          <t>/expenses</t>
+        </is>
+      </c>
+      <c r="H163" s="19" t="n"/>
+      <c r="I163" s="20" t="n"/>
+      <c r="J163" s="20" t="n"/>
+      <c r="K163" s="24" t="n"/>
+    </row>
+    <row r="164" ht="21.6" customHeight="1">
+      <c r="A164" s="19" t="n"/>
+      <c r="B164" s="20" t="n"/>
+      <c r="C164" s="20" t="n"/>
+      <c r="D164" s="21" t="inlineStr">
+        <is>
+          <t>B8.5</t>
+        </is>
+      </c>
+      <c r="E164" s="22" t="inlineStr">
+        <is>
+          <t>Transactions</t>
+        </is>
+      </c>
+      <c r="F164" s="20" t="inlineStr">
+        <is>
+          <t>ប្រតិបត្តិការ</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="inlineStr">
+        <is>
+          <t>/transactions</t>
+        </is>
+      </c>
+      <c r="H164" s="19" t="n"/>
+      <c r="I164" s="20" t="n"/>
+      <c r="J164" s="20" t="n"/>
+      <c r="K164" s="24" t="n"/>
+    </row>
+    <row r="165" ht="21.6" customHeight="1">
+      <c r="A165" s="19" t="n"/>
+      <c r="B165" s="20" t="n"/>
+      <c r="C165" s="20" t="n"/>
+      <c r="D165" s="21" t="inlineStr">
         <is>
           <t>B8.6</t>
         </is>
       </c>
-      <c r="E161" s="20" t="inlineStr">
+      <c r="E165" s="22" t="inlineStr">
         <is>
           <t>Financial Reports</t>
         </is>
       </c>
-      <c r="F161" s="20" t="inlineStr">
+      <c r="F165" s="20" t="inlineStr">
         <is>
           <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
         </is>
       </c>
-      <c r="G161" s="23" t="inlineStr">
+      <c r="G165" s="23" t="inlineStr">
         <is>
           <t>/accounting-reports</t>
         </is>
       </c>
-      <c r="H161" s="19" t="n">
+      <c r="H165" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="20" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="J165" s="20" t="inlineStr">
+        <is>
+          <t>ចំណូល</t>
+        </is>
+      </c>
+      <c r="K165" s="24" t="n"/>
+    </row>
+    <row r="166" ht="21.6" customHeight="1">
+      <c r="A166" s="19" t="n"/>
+      <c r="B166" s="20" t="n"/>
+      <c r="C166" s="20" t="n"/>
+      <c r="D166" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E166" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F166" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G166" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H166" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I166" s="20" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="J166" s="20" t="inlineStr">
+        <is>
+          <t>ចំណាយ</t>
+        </is>
+      </c>
+      <c r="K166" s="24" t="n"/>
+    </row>
+    <row r="167" ht="21.6" customHeight="1">
+      <c r="A167" s="19" t="n"/>
+      <c r="B167" s="20" t="n"/>
+      <c r="C167" s="20" t="n"/>
+      <c r="D167" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E167" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F167" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G167" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H167" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I167" s="20" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss</t>
+        </is>
+      </c>
+      <c r="J167" s="20" t="inlineStr">
+        <is>
+          <t>ប្រាក់ចំណេញ និងខាត</t>
+        </is>
+      </c>
+      <c r="K167" s="24" t="n"/>
+    </row>
+    <row r="168" ht="21.6" customHeight="1">
+      <c r="A168" s="19" t="n"/>
+      <c r="B168" s="20" t="n"/>
+      <c r="C168" s="20" t="n"/>
+      <c r="D168" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E168" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F168" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H168" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I161" s="20" t="inlineStr">
+      <c r="I168" s="20" t="inlineStr">
         <is>
           <t>Cash Flow</t>
         </is>
       </c>
-      <c r="J161" s="20" t="inlineStr">
+      <c r="J168" s="20" t="inlineStr">
         <is>
           <t>លំហូរសាច់ប្រាក់</t>
         </is>
       </c>
-      <c r="K161" s="24" t="n"/>
-    </row>
-    <row r="162" ht="21.6" customHeight="1">
-      <c r="A162" s="1" t="inlineStr">
+      <c r="K168" s="24" t="n"/>
+    </row>
+    <row r="169" ht="21.6" customHeight="1">
+      <c r="A169" s="1" t="inlineStr">
         <is>
           <t>B9</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t>ទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="D162" s="1" t="inlineStr">
+      <c r="D169" s="1" t="inlineStr">
         <is>
           <t>B9.1</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Asset Dashboard</t>
         </is>
       </c>
-      <c r="F162" s="3" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="G162" s="4" t="inlineStr">
+      <c r="G169" s="4" t="inlineStr">
         <is>
           <t>/assets/dashboard</t>
         </is>
       </c>
-      <c r="H162" s="5" t="n"/>
-      <c r="I162" s="3" t="n"/>
-      <c r="J162" s="3" t="n"/>
-      <c r="K162" s="6" t="n"/>
-    </row>
-    <row r="163" ht="21.6" customHeight="1">
-      <c r="A163" s="7" t="n"/>
-      <c r="B163" s="8" t="n"/>
-      <c r="C163" s="8" t="n"/>
-      <c r="D163" s="9" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E163" s="10" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F163" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G163" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H163" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I163" s="8" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="J163" s="8" t="inlineStr">
-        <is>
-          <t>ទិដ្ឋភាពទូទៅ</t>
-        </is>
-      </c>
-      <c r="K163" s="12" t="inlineStr">
-        <is>
-          <t>Tabs on one asset</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="21.6" customHeight="1">
-      <c r="A164" s="7" t="n"/>
-      <c r="B164" s="8" t="n"/>
-      <c r="C164" s="8" t="n"/>
-      <c r="D164" s="7" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E164" s="8" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F164" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G164" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H164" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I164" s="8" t="inlineStr">
-        <is>
-          <t>Assignment</t>
-        </is>
-      </c>
-      <c r="J164" s="8" t="inlineStr">
-        <is>
-          <t>ការចាត់ចែង</t>
-        </is>
-      </c>
-      <c r="K164" s="12" t="n"/>
-    </row>
-    <row r="165" ht="21.6" customHeight="1">
-      <c r="A165" s="7" t="n"/>
-      <c r="B165" s="8" t="n"/>
-      <c r="C165" s="8" t="n"/>
-      <c r="D165" s="7" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E165" s="8" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F165" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G165" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H165" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I165" s="8" t="inlineStr">
-        <is>
-          <t>Transfers</t>
-        </is>
-      </c>
-      <c r="J165" s="8" t="inlineStr">
-        <is>
-          <t>ការផ្ទេរ</t>
-        </is>
-      </c>
-      <c r="K165" s="12" t="n"/>
-    </row>
-    <row r="166" ht="21.6" customHeight="1">
-      <c r="A166" s="7" t="n"/>
-      <c r="B166" s="8" t="n"/>
-      <c r="C166" s="8" t="n"/>
-      <c r="D166" s="7" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E166" s="8" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F166" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G166" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H166" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I166" s="8" t="inlineStr">
-        <is>
-          <t>Issues</t>
-        </is>
-      </c>
-      <c r="J166" s="8" t="inlineStr">
-        <is>
-          <t>បញ្ហា</t>
-        </is>
-      </c>
-      <c r="K166" s="12" t="n"/>
-    </row>
-    <row r="167" ht="21.6" customHeight="1">
-      <c r="A167" s="7" t="n"/>
-      <c r="B167" s="8" t="n"/>
-      <c r="C167" s="8" t="n"/>
-      <c r="D167" s="7" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E167" s="8" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F167" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G167" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H167" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I167" s="8" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="J167" s="8" t="inlineStr">
-        <is>
-          <t>ការជួសជុល</t>
-        </is>
-      </c>
-      <c r="K167" s="12" t="n"/>
-    </row>
-    <row r="168" ht="21.6" customHeight="1">
-      <c r="A168" s="7" t="n"/>
-      <c r="B168" s="8" t="n"/>
-      <c r="C168" s="8" t="n"/>
-      <c r="D168" s="7" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E168" s="8" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F168" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G168" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I168" s="8" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="J168" s="8" t="inlineStr">
-        <is>
-          <t>ការថែទាំ</t>
-        </is>
-      </c>
-      <c r="K168" s="12" t="n"/>
-    </row>
-    <row r="169" ht="21.6" customHeight="1">
-      <c r="A169" s="7" t="n"/>
-      <c r="B169" s="8" t="n"/>
-      <c r="C169" s="8" t="n"/>
-      <c r="D169" s="9" t="inlineStr">
-        <is>
-          <t>B9.3</t>
-        </is>
-      </c>
-      <c r="E169" s="10" t="inlineStr">
-        <is>
-          <t>My Assets</t>
-        </is>
-      </c>
-      <c r="F169" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G169" s="11" t="inlineStr">
-        <is>
-          <t>/my-assets</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="n"/>
-      <c r="I169" s="8" t="n"/>
-      <c r="J169" s="8" t="n"/>
-      <c r="K169" s="12" t="n"/>
+      <c r="H169" s="5" t="n"/>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="3" t="n"/>
+      <c r="K169" s="6" t="n"/>
     </row>
     <row r="170" ht="21.6" customHeight="1">
       <c r="A170" s="7" t="n"/>
@@ -8633,172 +8415,236 @@
       <c r="C170" s="8" t="n"/>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>B9.4</t>
+          <t>B9.2</t>
         </is>
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>បញ្ហា</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G170" s="11" t="inlineStr">
         <is>
-          <t>/asset-issues</t>
-        </is>
-      </c>
-      <c r="H170" s="7" t="n"/>
-      <c r="I170" s="8" t="n"/>
-      <c r="J170" s="8" t="n"/>
-      <c r="K170" s="12" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="8" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="J170" s="8" t="inlineStr">
+        <is>
+          <t>ទិដ្ឋភាពទូទៅ</t>
+        </is>
+      </c>
+      <c r="K170" s="12" t="inlineStr">
+        <is>
+          <t>Tabs on one asset</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="21.6" customHeight="1">
       <c r="A171" s="7" t="n"/>
       <c r="B171" s="8" t="n"/>
       <c r="C171" s="8" t="n"/>
-      <c r="D171" s="9" t="inlineStr">
-        <is>
-          <t>B9.5</t>
-        </is>
-      </c>
-      <c r="E171" s="10" t="inlineStr">
-        <is>
-          <t>Repairs</t>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G171" s="11" t="inlineStr">
         <is>
-          <t>/asset-repairs</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="n"/>
-      <c r="I171" s="8" t="n"/>
-      <c r="J171" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I171" s="8" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="J171" s="8" t="inlineStr">
+        <is>
+          <t>ការចាត់ចែង</t>
+        </is>
+      </c>
       <c r="K171" s="12" t="n"/>
     </row>
     <row r="172" ht="21.6" customHeight="1">
       <c r="A172" s="7" t="n"/>
       <c r="B172" s="8" t="n"/>
       <c r="C172" s="8" t="n"/>
-      <c r="D172" s="9" t="inlineStr">
-        <is>
-          <t>B9.6</t>
-        </is>
-      </c>
-      <c r="E172" s="10" t="inlineStr">
-        <is>
-          <t>Repair Shops</t>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>ហាងជួសជុល</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G172" s="11" t="inlineStr">
         <is>
-          <t>/repair-shops</t>
-        </is>
-      </c>
-      <c r="H172" s="7" t="n"/>
-      <c r="I172" s="8" t="n"/>
-      <c r="J172" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I172" s="8" t="inlineStr">
+        <is>
+          <t>Transfers</t>
+        </is>
+      </c>
+      <c r="J172" s="8" t="inlineStr">
+        <is>
+          <t>ការផ្ទេរ</t>
+        </is>
+      </c>
       <c r="K172" s="12" t="n"/>
     </row>
     <row r="173" ht="21.6" customHeight="1">
       <c r="A173" s="7" t="n"/>
       <c r="B173" s="8" t="n"/>
       <c r="C173" s="8" t="n"/>
-      <c r="D173" s="9" t="inlineStr">
-        <is>
-          <t>B9.7</t>
-        </is>
-      </c>
-      <c r="E173" s="10" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G173" s="11" t="inlineStr">
         <is>
-          <t>/asset-maintenance</t>
-        </is>
-      </c>
-      <c r="H173" s="7" t="n"/>
-      <c r="I173" s="8" t="n"/>
-      <c r="J173" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I173" s="8" t="inlineStr">
+        <is>
+          <t>Issues</t>
+        </is>
+      </c>
+      <c r="J173" s="8" t="inlineStr">
+        <is>
+          <t>បញ្ហា</t>
+        </is>
+      </c>
       <c r="K173" s="12" t="n"/>
     </row>
     <row r="174" ht="21.6" customHeight="1">
       <c r="A174" s="7" t="n"/>
       <c r="B174" s="8" t="n"/>
       <c r="C174" s="8" t="n"/>
-      <c r="D174" s="9" t="inlineStr">
-        <is>
-          <t>B9.8</t>
-        </is>
-      </c>
-      <c r="E174" s="10" t="inlineStr">
-        <is>
-          <t>Asset Categories</t>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G174" s="11" t="inlineStr">
         <is>
-          <t>/asset-categories</t>
-        </is>
-      </c>
-      <c r="H174" s="7" t="n"/>
-      <c r="I174" s="8" t="n"/>
-      <c r="J174" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I174" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="J174" s="8" t="inlineStr">
+        <is>
+          <t>ការជួសជុល</t>
+        </is>
+      </c>
       <c r="K174" s="12" t="n"/>
     </row>
     <row r="175" ht="21.6" customHeight="1">
       <c r="A175" s="7" t="n"/>
       <c r="B175" s="8" t="n"/>
       <c r="C175" s="8" t="n"/>
-      <c r="D175" s="9" t="inlineStr">
-        <is>
-          <t>B9.9</t>
-        </is>
-      </c>
-      <c r="E175" s="10" t="inlineStr">
-        <is>
-          <t>Asset Locations</t>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F175" s="8" t="inlineStr">
         <is>
-          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G175" s="11" t="inlineStr">
         <is>
-          <t>/asset-locations</t>
-        </is>
-      </c>
-      <c r="H175" s="7" t="n"/>
-      <c r="I175" s="8" t="n"/>
-      <c r="J175" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I175" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="J175" s="8" t="inlineStr">
+        <is>
+          <t>ការថែទាំ</t>
+        </is>
+      </c>
       <c r="K175" s="12" t="n"/>
     </row>
     <row r="176" ht="21.6" customHeight="1">
@@ -8807,22 +8653,22 @@
       <c r="C176" s="8" t="n"/>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>B9.10</t>
+          <t>B9.3</t>
         </is>
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>Departments</t>
+          <t>My Assets</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
-          <t>/departments</t>
+          <t>/my-assets</t>
         </is>
       </c>
       <c r="H176" s="7" t="n"/>
@@ -8836,22 +8682,22 @@
       <c r="C177" s="8" t="n"/>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>B9.11</t>
+          <t>B9.4</t>
         </is>
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
-          <t>Suppliers</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr">
         <is>
-          <t>អ្នកផ្គត់ផ្គង់</t>
+          <t>បញ្ហា</t>
         </is>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
-          <t>/suppliers</t>
+          <t>/asset-issues</t>
         </is>
       </c>
       <c r="H177" s="7" t="n"/>
@@ -8865,684 +8711,664 @@
       <c r="C178" s="8" t="n"/>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>B9.12</t>
+          <t>B9.5</t>
         </is>
       </c>
       <c r="E178" s="10" t="inlineStr">
         <is>
-          <t>Asset Reports</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H178" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I178" s="8" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="J178" s="8" t="inlineStr">
-        <is>
-          <t>ស្តុក</t>
-        </is>
-      </c>
+          <t>/asset-repairs</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="n"/>
+      <c r="I178" s="8" t="n"/>
+      <c r="J178" s="8" t="n"/>
       <c r="K178" s="12" t="n"/>
     </row>
     <row r="179" ht="21.6" customHeight="1">
       <c r="A179" s="7" t="n"/>
       <c r="B179" s="8" t="n"/>
       <c r="C179" s="8" t="n"/>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>B9.12</t>
-        </is>
-      </c>
-      <c r="E179" s="8" t="inlineStr">
-        <is>
-          <t>Asset Reports</t>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>B9.6</t>
+        </is>
+      </c>
+      <c r="E179" s="10" t="inlineStr">
+        <is>
+          <t>Repair Shops</t>
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>ហាងជួសជុល</t>
         </is>
       </c>
       <c r="G179" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H179" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I179" s="8" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="J179" s="8" t="inlineStr">
-        <is>
-          <t>ស្ថានភាព</t>
-        </is>
-      </c>
+          <t>/repair-shops</t>
+        </is>
+      </c>
+      <c r="H179" s="7" t="n"/>
+      <c r="I179" s="8" t="n"/>
+      <c r="J179" s="8" t="n"/>
       <c r="K179" s="12" t="n"/>
     </row>
     <row r="180" ht="21.6" customHeight="1">
       <c r="A180" s="7" t="n"/>
       <c r="B180" s="8" t="n"/>
       <c r="C180" s="8" t="n"/>
-      <c r="D180" s="7" t="inlineStr">
-        <is>
-          <t>B9.12</t>
-        </is>
-      </c>
-      <c r="E180" s="8" t="inlineStr">
-        <is>
-          <t>Asset Reports</t>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>B9.7</t>
+        </is>
+      </c>
+      <c r="E180" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>ការថែទាំ</t>
         </is>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H180" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I180" s="8" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="J180" s="8" t="inlineStr">
-        <is>
-          <t>ការជួសជុល</t>
-        </is>
-      </c>
+          <t>/asset-maintenance</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="n"/>
+      <c r="I180" s="8" t="n"/>
+      <c r="J180" s="8" t="n"/>
       <c r="K180" s="12" t="n"/>
     </row>
     <row r="181" ht="21.6" customHeight="1">
       <c r="A181" s="7" t="n"/>
       <c r="B181" s="8" t="n"/>
       <c r="C181" s="8" t="n"/>
-      <c r="D181" s="7" t="inlineStr">
-        <is>
-          <t>B9.12</t>
-        </is>
-      </c>
-      <c r="E181" s="8" t="inlineStr">
-        <is>
-          <t>Asset Reports</t>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>B9.8</t>
+        </is>
+      </c>
+      <c r="E181" s="10" t="inlineStr">
+        <is>
+          <t>Asset Categories</t>
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H181" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I181" s="8" t="inlineStr">
-        <is>
-          <t>Repair Cost</t>
-        </is>
-      </c>
-      <c r="J181" s="8" t="inlineStr">
-        <is>
-          <t>ថ្លៃជួសជុល</t>
-        </is>
-      </c>
+          <t>/asset-categories</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="n"/>
+      <c r="I181" s="8" t="n"/>
+      <c r="J181" s="8" t="n"/>
       <c r="K181" s="12" t="n"/>
     </row>
     <row r="182" ht="21.6" customHeight="1">
       <c r="A182" s="7" t="n"/>
       <c r="B182" s="8" t="n"/>
       <c r="C182" s="8" t="n"/>
-      <c r="D182" s="7" t="inlineStr">
-        <is>
-          <t>B9.12</t>
-        </is>
-      </c>
-      <c r="E182" s="8" t="inlineStr">
-        <is>
-          <t>Asset Reports</t>
+      <c r="D182" s="9" t="inlineStr">
+        <is>
+          <t>B9.9</t>
+        </is>
+      </c>
+      <c r="E182" s="10" t="inlineStr">
+        <is>
+          <t>Asset Locations</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H182" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I182" s="8" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="J182" s="8" t="inlineStr">
-        <is>
-          <t>ការថែទាំ</t>
-        </is>
-      </c>
+          <t>/asset-locations</t>
+        </is>
+      </c>
+      <c r="H182" s="7" t="n"/>
+      <c r="I182" s="8" t="n"/>
+      <c r="J182" s="8" t="n"/>
       <c r="K182" s="12" t="n"/>
     </row>
     <row r="183" ht="21.6" customHeight="1">
       <c r="A183" s="7" t="n"/>
       <c r="B183" s="8" t="n"/>
       <c r="C183" s="8" t="n"/>
-      <c r="D183" s="7" t="inlineStr">
-        <is>
-          <t>B9.12</t>
-        </is>
-      </c>
-      <c r="E183" s="8" t="inlineStr">
-        <is>
-          <t>Asset Reports</t>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>B9.10</t>
+        </is>
+      </c>
+      <c r="E183" s="10" t="inlineStr">
+        <is>
+          <t>Departments</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H183" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I183" s="8" t="inlineStr">
-        <is>
-          <t>Assignments</t>
-        </is>
-      </c>
-      <c r="J183" s="8" t="inlineStr">
-        <is>
-          <t>ការចាត់ចែង</t>
-        </is>
-      </c>
+          <t>/departments</t>
+        </is>
+      </c>
+      <c r="H183" s="7" t="n"/>
+      <c r="I183" s="8" t="n"/>
+      <c r="J183" s="8" t="n"/>
       <c r="K183" s="12" t="n"/>
     </row>
     <row r="184" ht="21.6" customHeight="1">
       <c r="A184" s="7" t="n"/>
       <c r="B184" s="8" t="n"/>
       <c r="C184" s="8" t="n"/>
-      <c r="D184" s="7" t="inlineStr">
+      <c r="D184" s="9" t="inlineStr">
+        <is>
+          <t>B9.11</t>
+        </is>
+      </c>
+      <c r="E184" s="10" t="inlineStr">
+        <is>
+          <t>Suppliers</t>
+        </is>
+      </c>
+      <c r="F184" s="8" t="inlineStr">
+        <is>
+          <t>អ្នកផ្គត់ផ្គង់</t>
+        </is>
+      </c>
+      <c r="G184" s="11" t="inlineStr">
+        <is>
+          <t>/suppliers</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="n"/>
+      <c r="I184" s="8" t="n"/>
+      <c r="J184" s="8" t="n"/>
+      <c r="K184" s="12" t="n"/>
+    </row>
+    <row r="185" ht="21.6" customHeight="1">
+      <c r="A185" s="7" t="n"/>
+      <c r="B185" s="8" t="n"/>
+      <c r="C185" s="8" t="n"/>
+      <c r="D185" s="9" t="inlineStr">
         <is>
           <t>B9.12</t>
         </is>
       </c>
-      <c r="E184" s="8" t="inlineStr">
+      <c r="E185" s="10" t="inlineStr">
         <is>
           <t>Asset Reports</t>
         </is>
       </c>
-      <c r="F184" s="8" t="inlineStr">
+      <c r="F185" s="8" t="inlineStr">
         <is>
           <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="G184" s="11" t="inlineStr">
+      <c r="G185" s="11" t="inlineStr">
         <is>
           <t>/asset-reports</t>
         </is>
       </c>
-      <c r="H184" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I184" s="8" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="J184" s="8" t="inlineStr">
-        <is>
-          <t>ប្រវត្តិ</t>
-        </is>
-      </c>
-      <c r="K184" s="12" t="n"/>
-    </row>
-    <row r="185" ht="21.6" customHeight="1">
-      <c r="A185" s="13" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="B185" s="14" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="C185" s="15" t="inlineStr">
-        <is>
-          <t>ការទំនាក់ទំនង</t>
-        </is>
-      </c>
-      <c r="D185" s="13" t="inlineStr">
-        <is>
-          <t>B10.1</t>
-        </is>
-      </c>
-      <c r="E185" s="14" t="inlineStr">
-        <is>
-          <t>Contact Messages</t>
-        </is>
-      </c>
-      <c r="F185" s="15" t="inlineStr">
-        <is>
-          <t>សារទំនាក់ទំនង</t>
-        </is>
-      </c>
-      <c r="G185" s="16" t="inlineStr">
-        <is>
-          <t>/contact-messages</t>
-        </is>
-      </c>
-      <c r="H185" s="17" t="n"/>
-      <c r="I185" s="15" t="n"/>
-      <c r="J185" s="15" t="n"/>
-      <c r="K185" s="18" t="n"/>
+      <c r="H185" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" s="8" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="J185" s="8" t="inlineStr">
+        <is>
+          <t>ស្តុក</t>
+        </is>
+      </c>
+      <c r="K185" s="12" t="n"/>
     </row>
     <row r="186" ht="21.6" customHeight="1">
-      <c r="A186" s="19" t="n"/>
-      <c r="B186" s="20" t="n"/>
-      <c r="C186" s="20" t="n"/>
-      <c r="D186" s="21" t="inlineStr">
-        <is>
-          <t>B10.2</t>
-        </is>
-      </c>
-      <c r="E186" s="22" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="F186" s="20" t="inlineStr">
-        <is>
-          <t>ការជូនដំណឹង</t>
-        </is>
-      </c>
-      <c r="G186" s="23" t="inlineStr">
-        <is>
-          <t>/notifications</t>
-        </is>
-      </c>
-      <c r="H186" s="19" t="n"/>
-      <c r="I186" s="20" t="n"/>
-      <c r="J186" s="20" t="n"/>
-      <c r="K186" s="24" t="n"/>
+      <c r="A186" s="7" t="n"/>
+      <c r="B186" s="8" t="n"/>
+      <c r="C186" s="8" t="n"/>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E186" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G186" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I186" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J186" s="8" t="inlineStr">
+        <is>
+          <t>ស្ថានភាព</t>
+        </is>
+      </c>
+      <c r="K186" s="12" t="n"/>
     </row>
     <row r="187" ht="21.6" customHeight="1">
-      <c r="A187" s="19" t="n"/>
-      <c r="B187" s="20" t="n"/>
-      <c r="C187" s="20" t="n"/>
-      <c r="D187" s="21" t="inlineStr">
-        <is>
-          <t>B10.3</t>
-        </is>
-      </c>
-      <c r="E187" s="22" t="inlineStr">
-        <is>
-          <t>Student Feedback</t>
-        </is>
-      </c>
-      <c r="F187" s="20" t="inlineStr">
-        <is>
-          <t>មតិកែលម្អសិស្ស</t>
-        </is>
-      </c>
-      <c r="G187" s="23" t="inlineStr">
-        <is>
-          <t>/student-feedback</t>
-        </is>
-      </c>
-      <c r="H187" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I187" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J187" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងបើក</t>
-        </is>
-      </c>
-      <c r="K187" s="24" t="n"/>
+      <c r="A187" s="7" t="n"/>
+      <c r="B187" s="8" t="n"/>
+      <c r="C187" s="8" t="n"/>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E187" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G187" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I187" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="J187" s="8" t="inlineStr">
+        <is>
+          <t>ការជួសជុល</t>
+        </is>
+      </c>
+      <c r="K187" s="12" t="n"/>
     </row>
     <row r="188" ht="21.6" customHeight="1">
-      <c r="A188" s="19" t="n"/>
-      <c r="B188" s="20" t="n"/>
-      <c r="C188" s="20" t="n"/>
-      <c r="D188" s="19" t="inlineStr">
-        <is>
-          <t>B10.3</t>
-        </is>
-      </c>
-      <c r="E188" s="20" t="inlineStr">
-        <is>
-          <t>Student Feedback</t>
-        </is>
-      </c>
-      <c r="F188" s="20" t="inlineStr">
-        <is>
-          <t>មតិកែលម្អសិស្ស</t>
-        </is>
-      </c>
-      <c r="G188" s="23" t="inlineStr">
-        <is>
-          <t>/student-feedback</t>
-        </is>
-      </c>
-      <c r="H188" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I188" s="20" t="inlineStr">
-        <is>
-          <t>Replied</t>
-        </is>
-      </c>
-      <c r="J188" s="20" t="inlineStr">
-        <is>
-          <t>បានឆ្លើយតប</t>
-        </is>
-      </c>
-      <c r="K188" s="24" t="n"/>
+      <c r="A188" s="7" t="n"/>
+      <c r="B188" s="8" t="n"/>
+      <c r="C188" s="8" t="n"/>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E188" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F188" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G188" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H188" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I188" s="8" t="inlineStr">
+        <is>
+          <t>Repair Cost</t>
+        </is>
+      </c>
+      <c r="J188" s="8" t="inlineStr">
+        <is>
+          <t>ថ្លៃជួសជុល</t>
+        </is>
+      </c>
+      <c r="K188" s="12" t="n"/>
     </row>
     <row r="189" ht="21.6" customHeight="1">
-      <c r="A189" s="1" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>ការកំណត់</t>
-        </is>
-      </c>
-      <c r="D189" s="1" t="inlineStr">
-        <is>
-          <t>B11.1</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="inlineStr">
-        <is>
-          <t>ឯកសារ</t>
-        </is>
-      </c>
-      <c r="G189" s="4" t="inlineStr">
-        <is>
-          <t>/school-documents</t>
-        </is>
-      </c>
-      <c r="H189" s="5" t="n"/>
-      <c r="I189" s="3" t="n"/>
-      <c r="J189" s="3" t="n"/>
-      <c r="K189" s="6" t="n"/>
+      <c r="A189" s="7" t="n"/>
+      <c r="B189" s="8" t="n"/>
+      <c r="C189" s="8" t="n"/>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G189" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I189" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="J189" s="8" t="inlineStr">
+        <is>
+          <t>ការថែទាំ</t>
+        </is>
+      </c>
+      <c r="K189" s="12" t="n"/>
     </row>
     <row r="190" ht="21.6" customHeight="1">
       <c r="A190" s="7" t="n"/>
       <c r="B190" s="8" t="n"/>
       <c r="C190" s="8" t="n"/>
-      <c r="D190" s="9" t="inlineStr">
-        <is>
-          <t>B11.2</t>
-        </is>
-      </c>
-      <c r="E190" s="10" t="inlineStr">
-        <is>
-          <t>General</t>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E190" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
         </is>
       </c>
       <c r="F190" s="8" t="inlineStr">
         <is>
-          <t>ទូទៅ</t>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
-          <t>/settings</t>
-        </is>
-      </c>
-      <c r="H190" s="7" t="n"/>
-      <c r="I190" s="8" t="n"/>
-      <c r="J190" s="8" t="n"/>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H190" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I190" s="8" t="inlineStr">
+        <is>
+          <t>Assignments</t>
+        </is>
+      </c>
+      <c r="J190" s="8" t="inlineStr">
+        <is>
+          <t>ការចាត់ចែង</t>
+        </is>
+      </c>
       <c r="K190" s="12" t="n"/>
     </row>
     <row r="191" ht="21.6" customHeight="1">
       <c r="A191" s="7" t="n"/>
       <c r="B191" s="8" t="n"/>
       <c r="C191" s="8" t="n"/>
-      <c r="D191" s="9" t="inlineStr">
-        <is>
-          <t>B11.3</t>
-        </is>
-      </c>
-      <c r="E191" s="10" t="inlineStr">
-        <is>
-          <t>Telegram notifications</t>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E191" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr">
         <is>
-          <t>ការជូនដំណឹង Telegram</t>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
-          <t>/telegram-notifications</t>
-        </is>
-      </c>
-      <c r="H191" s="7" t="n"/>
-      <c r="I191" s="8" t="n"/>
-      <c r="J191" s="8" t="n"/>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I191" s="8" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="J191" s="8" t="inlineStr">
+        <is>
+          <t>ប្រវត្តិ</t>
+        </is>
+      </c>
       <c r="K191" s="12" t="n"/>
     </row>
     <row r="192" ht="21.6" customHeight="1">
-      <c r="A192" s="7" t="n"/>
-      <c r="B192" s="8" t="n"/>
-      <c r="C192" s="8" t="n"/>
-      <c r="D192" s="9" t="inlineStr">
-        <is>
-          <t>B11.4</t>
-        </is>
-      </c>
-      <c r="E192" s="10" t="inlineStr">
-        <is>
-          <t>Users</t>
-        </is>
-      </c>
-      <c r="F192" s="8" t="inlineStr">
-        <is>
-          <t>អ្នកប្រើប្រាស់</t>
-        </is>
-      </c>
-      <c r="G192" s="11" t="inlineStr">
-        <is>
-          <t>/users</t>
-        </is>
-      </c>
-      <c r="H192" s="7" t="n"/>
-      <c r="I192" s="8" t="n"/>
-      <c r="J192" s="8" t="n"/>
-      <c r="K192" s="12" t="n"/>
+      <c r="A192" s="13" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="B192" s="14" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr">
+        <is>
+          <t>ការទំនាក់ទំនង</t>
+        </is>
+      </c>
+      <c r="D192" s="13" t="inlineStr">
+        <is>
+          <t>B10.1</t>
+        </is>
+      </c>
+      <c r="E192" s="14" t="inlineStr">
+        <is>
+          <t>Contact Messages</t>
+        </is>
+      </c>
+      <c r="F192" s="15" t="inlineStr">
+        <is>
+          <t>សារទំនាក់ទំនង</t>
+        </is>
+      </c>
+      <c r="G192" s="16" t="inlineStr">
+        <is>
+          <t>/contact-messages</t>
+        </is>
+      </c>
+      <c r="H192" s="17" t="n"/>
+      <c r="I192" s="15" t="n"/>
+      <c r="J192" s="15" t="n"/>
+      <c r="K192" s="18" t="n"/>
     </row>
     <row r="193" ht="21.6" customHeight="1">
-      <c r="A193" s="7" t="n"/>
-      <c r="B193" s="8" t="n"/>
-      <c r="C193" s="8" t="n"/>
-      <c r="D193" s="9" t="inlineStr">
-        <is>
-          <t>B11.5</t>
-        </is>
-      </c>
-      <c r="E193" s="10" t="inlineStr">
-        <is>
-          <t>Roles</t>
-        </is>
-      </c>
-      <c r="F193" s="8" t="inlineStr">
-        <is>
-          <t>តួនាទី</t>
-        </is>
-      </c>
-      <c r="G193" s="11" t="inlineStr">
-        <is>
-          <t>/roles</t>
-        </is>
-      </c>
-      <c r="H193" s="7" t="n"/>
-      <c r="I193" s="8" t="n"/>
-      <c r="J193" s="8" t="n"/>
-      <c r="K193" s="12" t="n"/>
+      <c r="A193" s="19" t="n"/>
+      <c r="B193" s="20" t="n"/>
+      <c r="C193" s="20" t="n"/>
+      <c r="D193" s="21" t="inlineStr">
+        <is>
+          <t>B10.2</t>
+        </is>
+      </c>
+      <c r="E193" s="22" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="F193" s="20" t="inlineStr">
+        <is>
+          <t>ការជូនដំណឹង</t>
+        </is>
+      </c>
+      <c r="G193" s="23" t="inlineStr">
+        <is>
+          <t>/notifications</t>
+        </is>
+      </c>
+      <c r="H193" s="19" t="n"/>
+      <c r="I193" s="20" t="n"/>
+      <c r="J193" s="20" t="n"/>
+      <c r="K193" s="24" t="n"/>
     </row>
     <row r="194" ht="21.6" customHeight="1">
-      <c r="A194" s="7" t="n"/>
-      <c r="B194" s="8" t="n"/>
-      <c r="C194" s="8" t="n"/>
-      <c r="D194" s="9" t="inlineStr">
-        <is>
-          <t>B11.6</t>
-        </is>
-      </c>
-      <c r="E194" s="10" t="inlineStr">
-        <is>
-          <t>Audit Logs</t>
-        </is>
-      </c>
-      <c r="F194" s="8" t="inlineStr">
-        <is>
-          <t>កំណត់ហេតុសវនកម្ម</t>
-        </is>
-      </c>
-      <c r="G194" s="11" t="inlineStr">
-        <is>
-          <t>/audit-logs</t>
-        </is>
-      </c>
-      <c r="H194" s="7" t="n"/>
-      <c r="I194" s="8" t="n"/>
-      <c r="J194" s="8" t="n"/>
-      <c r="K194" s="12" t="n"/>
+      <c r="A194" s="19" t="n"/>
+      <c r="B194" s="20" t="n"/>
+      <c r="C194" s="20" t="n"/>
+      <c r="D194" s="21" t="inlineStr">
+        <is>
+          <t>B10.3</t>
+        </is>
+      </c>
+      <c r="E194" s="22" t="inlineStr">
+        <is>
+          <t>Student Feedback</t>
+        </is>
+      </c>
+      <c r="F194" s="20" t="inlineStr">
+        <is>
+          <t>មតិកែលម្អសិស្ស</t>
+        </is>
+      </c>
+      <c r="G194" s="23" t="inlineStr">
+        <is>
+          <t>/student-feedback</t>
+        </is>
+      </c>
+      <c r="H194" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J194" s="20" t="inlineStr">
+        <is>
+          <t>កំពុងបើក</t>
+        </is>
+      </c>
+      <c r="K194" s="24" t="n"/>
     </row>
     <row r="195" ht="21.6" customHeight="1">
-      <c r="A195" s="7" t="n"/>
-      <c r="B195" s="8" t="n"/>
-      <c r="C195" s="8" t="n"/>
-      <c r="D195" s="9" t="inlineStr">
-        <is>
-          <t>B11.7</t>
-        </is>
-      </c>
-      <c r="E195" s="10" t="inlineStr">
-        <is>
-          <t>Languages</t>
-        </is>
-      </c>
-      <c r="F195" s="8" t="inlineStr">
-        <is>
-          <t>ភាសា</t>
-        </is>
-      </c>
-      <c r="G195" s="11" t="inlineStr">
-        <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="H195" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I195" s="8" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="J195" s="8" t="inlineStr">
-        <is>
-          <t>ភាសា</t>
-        </is>
-      </c>
-      <c r="K195" s="12" t="n"/>
+      <c r="A195" s="19" t="n"/>
+      <c r="B195" s="20" t="n"/>
+      <c r="C195" s="20" t="n"/>
+      <c r="D195" s="19" t="inlineStr">
+        <is>
+          <t>B10.3</t>
+        </is>
+      </c>
+      <c r="E195" s="20" t="inlineStr">
+        <is>
+          <t>Student Feedback</t>
+        </is>
+      </c>
+      <c r="F195" s="20" t="inlineStr">
+        <is>
+          <t>មតិកែលម្អសិស្ស</t>
+        </is>
+      </c>
+      <c r="G195" s="23" t="inlineStr">
+        <is>
+          <t>/student-feedback</t>
+        </is>
+      </c>
+      <c r="H195" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I195" s="20" t="inlineStr">
+        <is>
+          <t>Replied</t>
+        </is>
+      </c>
+      <c r="J195" s="20" t="inlineStr">
+        <is>
+          <t>បានឆ្លើយតប</t>
+        </is>
+      </c>
+      <c r="K195" s="24" t="n"/>
     </row>
     <row r="196" ht="21.6" customHeight="1">
-      <c r="A196" s="7" t="n"/>
-      <c r="B196" s="8" t="n"/>
-      <c r="C196" s="8" t="n"/>
-      <c r="D196" s="7" t="inlineStr">
-        <is>
-          <t>B11.7</t>
-        </is>
-      </c>
-      <c r="E196" s="8" t="inlineStr">
-        <is>
-          <t>Languages</t>
-        </is>
-      </c>
-      <c r="F196" s="8" t="inlineStr">
-        <is>
-          <t>ភាសា</t>
-        </is>
-      </c>
-      <c r="G196" s="11" t="inlineStr">
-        <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="H196" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I196" s="8" t="inlineStr">
-        <is>
-          <t>Translation</t>
-        </is>
-      </c>
-      <c r="J196" s="8" t="inlineStr">
-        <is>
-          <t>ការបកប្រែ</t>
-        </is>
-      </c>
-      <c r="K196" s="12" t="n"/>
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>ការកំណត់</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t>B11.1</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>ឯកសារ</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>/school-documents</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="n"/>
+      <c r="I196" s="3" t="n"/>
+      <c r="J196" s="3" t="n"/>
+      <c r="K196" s="6" t="n"/>
     </row>
     <row r="197" ht="21.6" customHeight="1">
       <c r="A197" s="7" t="n"/>
@@ -9550,22 +9376,22 @@
       <c r="C197" s="8" t="n"/>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>B11.8</t>
+          <t>B11.2</t>
         </is>
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>Base Data</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr">
         <is>
-          <t>ទិន្នន័យមូលដ្ឋាន</t>
+          <t>ទូទៅ</t>
         </is>
       </c>
       <c r="G197" s="11" t="inlineStr">
         <is>
-          <t>/lookup-categories</t>
+          <t>/settings</t>
         </is>
       </c>
       <c r="H197" s="7" t="n"/>
@@ -9579,22 +9405,22 @@
       <c r="C198" s="8" t="n"/>
       <c r="D198" s="9" t="inlineStr">
         <is>
-          <t>B11.9</t>
+          <t>B11.3</t>
         </is>
       </c>
       <c r="E198" s="10" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Telegram notifications</t>
         </is>
       </c>
       <c r="F198" s="8" t="inlineStr">
         <is>
-          <t>បម្រុងទុក</t>
+          <t>ការជូនដំណឹង Telegram</t>
         </is>
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
-          <t>/database-backups</t>
+          <t>/telegram-notifications</t>
         </is>
       </c>
       <c r="H198" s="7" t="n"/>
@@ -9603,350 +9429,300 @@
       <c r="K198" s="12" t="n"/>
     </row>
     <row r="199" ht="21.6" customHeight="1">
-      <c r="A199" s="13" t="inlineStr">
+      <c r="A199" s="7" t="n"/>
+      <c r="B199" s="8" t="n"/>
+      <c r="C199" s="8" t="n"/>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>B11.4</t>
+        </is>
+      </c>
+      <c r="E199" s="10" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="F199" s="8" t="inlineStr">
+        <is>
+          <t>អ្នកប្រើប្រាស់</t>
+        </is>
+      </c>
+      <c r="G199" s="11" t="inlineStr">
+        <is>
+          <t>/users</t>
+        </is>
+      </c>
+      <c r="H199" s="7" t="n"/>
+      <c r="I199" s="8" t="n"/>
+      <c r="J199" s="8" t="n"/>
+      <c r="K199" s="12" t="n"/>
+    </row>
+    <row r="200" ht="21.6" customHeight="1">
+      <c r="A200" s="7" t="n"/>
+      <c r="B200" s="8" t="n"/>
+      <c r="C200" s="8" t="n"/>
+      <c r="D200" s="9" t="inlineStr">
+        <is>
+          <t>B11.5</t>
+        </is>
+      </c>
+      <c r="E200" s="10" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="F200" s="8" t="inlineStr">
+        <is>
+          <t>តួនាទី</t>
+        </is>
+      </c>
+      <c r="G200" s="11" t="inlineStr">
+        <is>
+          <t>/roles</t>
+        </is>
+      </c>
+      <c r="H200" s="7" t="n"/>
+      <c r="I200" s="8" t="n"/>
+      <c r="J200" s="8" t="n"/>
+      <c r="K200" s="12" t="n"/>
+    </row>
+    <row r="201" ht="21.6" customHeight="1">
+      <c r="A201" s="7" t="n"/>
+      <c r="B201" s="8" t="n"/>
+      <c r="C201" s="8" t="n"/>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>B11.6</t>
+        </is>
+      </c>
+      <c r="E201" s="10" t="inlineStr">
+        <is>
+          <t>Audit Logs</t>
+        </is>
+      </c>
+      <c r="F201" s="8" t="inlineStr">
+        <is>
+          <t>កំណត់ហេតុសវនកម្ម</t>
+        </is>
+      </c>
+      <c r="G201" s="11" t="inlineStr">
+        <is>
+          <t>/audit-logs</t>
+        </is>
+      </c>
+      <c r="H201" s="7" t="n"/>
+      <c r="I201" s="8" t="n"/>
+      <c r="J201" s="8" t="n"/>
+      <c r="K201" s="12" t="n"/>
+    </row>
+    <row r="202" ht="21.6" customHeight="1">
+      <c r="A202" s="7" t="n"/>
+      <c r="B202" s="8" t="n"/>
+      <c r="C202" s="8" t="n"/>
+      <c r="D202" s="9" t="inlineStr">
+        <is>
+          <t>B11.7</t>
+        </is>
+      </c>
+      <c r="E202" s="10" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="F202" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="G202" s="11" t="inlineStr">
+        <is>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" s="8" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="J202" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="K202" s="12" t="n"/>
+    </row>
+    <row r="203" ht="21.6" customHeight="1">
+      <c r="A203" s="7" t="n"/>
+      <c r="B203" s="8" t="n"/>
+      <c r="C203" s="8" t="n"/>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>B11.7</t>
+        </is>
+      </c>
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="F203" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="G203" s="11" t="inlineStr">
+        <is>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I203" s="8" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="J203" s="8" t="inlineStr">
+        <is>
+          <t>ការបកប្រែ</t>
+        </is>
+      </c>
+      <c r="K203" s="12" t="n"/>
+    </row>
+    <row r="204" ht="21.6" customHeight="1">
+      <c r="A204" s="7" t="n"/>
+      <c r="B204" s="8" t="n"/>
+      <c r="C204" s="8" t="n"/>
+      <c r="D204" s="9" t="inlineStr">
+        <is>
+          <t>B11.8</t>
+        </is>
+      </c>
+      <c r="E204" s="10" t="inlineStr">
+        <is>
+          <t>Base Data</t>
+        </is>
+      </c>
+      <c r="F204" s="8" t="inlineStr">
+        <is>
+          <t>ទិន្នន័យមូលដ្ឋាន</t>
+        </is>
+      </c>
+      <c r="G204" s="11" t="inlineStr">
+        <is>
+          <t>/lookup-categories</t>
+        </is>
+      </c>
+      <c r="H204" s="7" t="n"/>
+      <c r="I204" s="8" t="n"/>
+      <c r="J204" s="8" t="n"/>
+      <c r="K204" s="12" t="n"/>
+    </row>
+    <row r="205" ht="21.6" customHeight="1">
+      <c r="A205" s="7" t="n"/>
+      <c r="B205" s="8" t="n"/>
+      <c r="C205" s="8" t="n"/>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>B11.9</t>
+        </is>
+      </c>
+      <c r="E205" s="10" t="inlineStr">
+        <is>
+          <t>Backup</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>បម្រុងទុក</t>
+        </is>
+      </c>
+      <c r="G205" s="11" t="inlineStr">
+        <is>
+          <t>/database-backups</t>
+        </is>
+      </c>
+      <c r="H205" s="7" t="n"/>
+      <c r="I205" s="8" t="n"/>
+      <c r="J205" s="8" t="n"/>
+      <c r="K205" s="12" t="n"/>
+    </row>
+    <row r="206" ht="21.6" customHeight="1">
+      <c r="A206" s="13" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B199" s="14" t="inlineStr">
+      <c r="B206" s="14" t="inlineStr">
         <is>
           <t>eApprovals</t>
         </is>
       </c>
-      <c r="C199" s="15" t="n"/>
-      <c r="D199" s="13" t="inlineStr">
+      <c r="C206" s="15" t="n"/>
+      <c r="D206" s="13" t="inlineStr">
         <is>
           <t>B12.1</t>
         </is>
       </c>
-      <c r="E199" s="14" t="inlineStr">
+      <c r="E206" s="14" t="inlineStr">
         <is>
           <t>Forms</t>
         </is>
       </c>
-      <c r="F199" s="15" t="inlineStr">
+      <c r="F206" s="15" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="G199" s="16" t="inlineStr">
+      <c r="G206" s="16" t="inlineStr">
         <is>
           <t>/approvals/forms</t>
         </is>
       </c>
-      <c r="H199" s="17" t="n"/>
-      <c r="I199" s="15" t="n"/>
-      <c r="J199" s="15" t="n"/>
-      <c r="K199" s="18" t="n"/>
-    </row>
-    <row r="200" ht="21.6" customHeight="1">
-      <c r="A200" s="19" t="n"/>
-      <c r="B200" s="20" t="n"/>
-      <c r="C200" s="20" t="n"/>
-      <c r="D200" s="21" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E200" s="22" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F200" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G200" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H200" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I200" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J200" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
-      <c r="K200" s="24" t="n"/>
-    </row>
-    <row r="201" ht="21.6" customHeight="1">
-      <c r="A201" s="19" t="n"/>
-      <c r="B201" s="20" t="n"/>
-      <c r="C201" s="20" t="n"/>
-      <c r="D201" s="19" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E201" s="20" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F201" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G201" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H201" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I201" s="20" t="inlineStr">
-        <is>
-          <t>Approved to study</t>
-        </is>
-      </c>
-      <c r="J201" s="20" t="inlineStr">
-        <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
-        </is>
-      </c>
-      <c r="K201" s="24" t="n"/>
-    </row>
-    <row r="202" ht="21.6" customHeight="1">
-      <c r="A202" s="19" t="n"/>
-      <c r="B202" s="20" t="n"/>
-      <c r="C202" s="20" t="n"/>
-      <c r="D202" s="19" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E202" s="20" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F202" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G202" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H202" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I202" s="20" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J202" s="20" t="inlineStr">
-        <is>
-          <t>បានអនុម័ត</t>
-        </is>
-      </c>
-      <c r="K202" s="24" t="n"/>
-    </row>
-    <row r="203" ht="21.6" customHeight="1">
-      <c r="A203" s="19" t="n"/>
-      <c r="B203" s="20" t="n"/>
-      <c r="C203" s="20" t="n"/>
-      <c r="D203" s="19" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E203" s="20" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F203" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G203" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H203" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I203" s="20" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="J203" s="20" t="inlineStr">
-        <is>
-          <t>បានបដិសេធ</t>
-        </is>
-      </c>
-      <c r="K203" s="24" t="n"/>
-    </row>
-    <row r="204" ht="21.6" customHeight="1">
-      <c r="A204" s="19" t="n"/>
-      <c r="B204" s="20" t="n"/>
-      <c r="C204" s="20" t="n"/>
-      <c r="D204" s="19" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E204" s="20" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F204" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G204" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H204" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="I204" s="20" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-      <c r="J204" s="20" t="inlineStr">
-        <is>
-          <t>បានលុបចោល</t>
-        </is>
-      </c>
-      <c r="K204" s="24" t="n"/>
-    </row>
-    <row r="205" ht="21.6" customHeight="1">
-      <c r="A205" s="19" t="n"/>
-      <c r="B205" s="20" t="n"/>
-      <c r="C205" s="20" t="n"/>
-      <c r="D205" s="21" t="inlineStr">
-        <is>
-          <t>B12.3</t>
-        </is>
-      </c>
-      <c r="E205" s="22" t="inlineStr">
-        <is>
-          <t>Approvals</t>
-        </is>
-      </c>
-      <c r="F205" s="20" t="inlineStr">
-        <is>
-          <t>ការអនុម័ត</t>
-        </is>
-      </c>
-      <c r="G205" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/queue</t>
-        </is>
-      </c>
-      <c r="H205" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I205" s="20" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J205" s="20" t="inlineStr">
-        <is>
-          <t>ថ្មី</t>
-        </is>
-      </c>
-      <c r="K205" s="24" t="n"/>
-    </row>
-    <row r="206" ht="21.6" customHeight="1">
-      <c r="A206" s="19" t="n"/>
-      <c r="B206" s="20" t="n"/>
-      <c r="C206" s="20" t="n"/>
-      <c r="D206" s="19" t="inlineStr">
-        <is>
-          <t>B12.3</t>
-        </is>
-      </c>
-      <c r="E206" s="20" t="inlineStr">
-        <is>
-          <t>Approvals</t>
-        </is>
-      </c>
-      <c r="F206" s="20" t="inlineStr">
-        <is>
-          <t>ការអនុម័ត</t>
-        </is>
-      </c>
-      <c r="G206" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/queue</t>
-        </is>
-      </c>
-      <c r="H206" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I206" s="20" t="inlineStr">
-        <is>
-          <t>Approved to study</t>
-        </is>
-      </c>
-      <c r="J206" s="20" t="inlineStr">
-        <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
-        </is>
-      </c>
-      <c r="K206" s="24" t="n"/>
+      <c r="H206" s="17" t="n"/>
+      <c r="I206" s="15" t="n"/>
+      <c r="J206" s="15" t="n"/>
+      <c r="K206" s="18" t="n"/>
     </row>
     <row r="207" ht="21.6" customHeight="1">
       <c r="A207" s="19" t="n"/>
       <c r="B207" s="20" t="n"/>
       <c r="C207" s="20" t="n"/>
-      <c r="D207" s="19" t="inlineStr">
-        <is>
-          <t>B12.3</t>
-        </is>
-      </c>
-      <c r="E207" s="20" t="inlineStr">
-        <is>
-          <t>Approvals</t>
+      <c r="D207" s="21" t="inlineStr">
+        <is>
+          <t>B12.2</t>
+        </is>
+      </c>
+      <c r="E207" s="22" t="inlineStr">
+        <is>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F207" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G207" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H207" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I207" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J207" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="K207" s="24" t="n"/>
@@ -9957,35 +9733,35 @@
       <c r="C208" s="20" t="n"/>
       <c r="D208" s="19" t="inlineStr">
         <is>
-          <t>B12.3</t>
+          <t>B12.2</t>
         </is>
       </c>
       <c r="E208" s="20" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F208" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G208" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H208" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I208" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J208" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K208" s="24" t="n"/>
@@ -9996,401 +9772,674 @@
       <c r="C209" s="20" t="n"/>
       <c r="D209" s="19" t="inlineStr">
         <is>
-          <t>B12.3</t>
+          <t>B12.2</t>
         </is>
       </c>
       <c r="E209" s="20" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F209" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G209" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H209" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I209" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J209" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K209" s="24" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" ht="21.6" customHeight="1">
       <c r="A210" s="19" t="n"/>
       <c r="B210" s="20" t="n"/>
       <c r="C210" s="20" t="n"/>
-      <c r="D210" s="21" t="inlineStr">
-        <is>
-          <t>B12.4</t>
-        </is>
-      </c>
-      <c r="E210" s="22" t="inlineStr">
-        <is>
-          <t>Form Categories</t>
+      <c r="D210" s="19" t="inlineStr">
+        <is>
+          <t>B12.2</t>
+        </is>
+      </c>
+      <c r="E210" s="20" t="inlineStr">
+        <is>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F210" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទទម្រង់បែបបទ</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G210" s="23" t="inlineStr">
         <is>
-          <t>/form-categories</t>
-        </is>
-      </c>
-      <c r="H210" s="19" t="n"/>
-      <c r="I210" s="20" t="n"/>
-      <c r="J210" s="20" t="n"/>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="H210" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I210" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="J210" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
       <c r="K210" s="24" t="n"/>
     </row>
-    <row r="211">
+    <row r="211" ht="21.6" customHeight="1">
       <c r="A211" s="19" t="n"/>
       <c r="B211" s="20" t="n"/>
       <c r="C211" s="20" t="n"/>
-      <c r="D211" s="21" t="inlineStr">
+      <c r="D211" s="19" t="inlineStr">
+        <is>
+          <t>B12.2</t>
+        </is>
+      </c>
+      <c r="E211" s="20" t="inlineStr">
+        <is>
+          <t>My Request</t>
+        </is>
+      </c>
+      <c r="F211" s="20" t="inlineStr">
+        <is>
+          <t>សំណើរបស់ខ្ញុំ</t>
+        </is>
+      </c>
+      <c r="G211" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="H211" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I211" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="J211" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="K211" s="24" t="n"/>
+    </row>
+    <row r="212" ht="21.6" customHeight="1">
+      <c r="A212" s="19" t="n"/>
+      <c r="B212" s="20" t="n"/>
+      <c r="C212" s="20" t="n"/>
+      <c r="D212" s="21" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E212" s="22" t="inlineStr">
+        <is>
+          <t>Approvals</t>
+        </is>
+      </c>
+      <c r="F212" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័ត</t>
+        </is>
+      </c>
+      <c r="G212" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H212" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I212" s="20" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="J212" s="20" t="inlineStr">
+        <is>
+          <t>ថ្មី</t>
+        </is>
+      </c>
+      <c r="K212" s="24" t="n"/>
+    </row>
+    <row r="213" ht="21.6" customHeight="1">
+      <c r="A213" s="19" t="n"/>
+      <c r="B213" s="20" t="n"/>
+      <c r="C213" s="20" t="n"/>
+      <c r="D213" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E213" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
+        </is>
+      </c>
+      <c r="F213" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័ត</t>
+        </is>
+      </c>
+      <c r="G213" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H213" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I213" s="20" t="inlineStr">
+        <is>
+          <t>Approved to study</t>
+        </is>
+      </c>
+      <c r="J213" s="20" t="inlineStr">
+        <is>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
+        </is>
+      </c>
+      <c r="K213" s="24" t="n"/>
+    </row>
+    <row r="214" ht="151.2" customHeight="1">
+      <c r="A214" s="19" t="n"/>
+      <c r="B214" s="20" t="n"/>
+      <c r="C214" s="20" t="n"/>
+      <c r="D214" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E214" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
+        </is>
+      </c>
+      <c r="F214" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័ត</t>
+        </is>
+      </c>
+      <c r="G214" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H214" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I214" s="20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J214" s="20" t="inlineStr">
+        <is>
+          <t>បានអនុម័ត</t>
+        </is>
+      </c>
+      <c r="K214" s="24" t="n"/>
+    </row>
+    <row r="215" ht="194.4" customHeight="1">
+      <c r="A215" s="19" t="n"/>
+      <c r="B215" s="20" t="n"/>
+      <c r="C215" s="20" t="n"/>
+      <c r="D215" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E215" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
+        </is>
+      </c>
+      <c r="F215" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័ត</t>
+        </is>
+      </c>
+      <c r="G215" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H215" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I215" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="J215" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
+      <c r="K215" s="24" t="n"/>
+    </row>
+    <row r="216" ht="108" customHeight="1">
+      <c r="A216" s="19" t="n"/>
+      <c r="B216" s="20" t="n"/>
+      <c r="C216" s="20" t="n"/>
+      <c r="D216" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E216" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
+        </is>
+      </c>
+      <c r="F216" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័ត</t>
+        </is>
+      </c>
+      <c r="G216" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H216" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I216" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="J216" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="K216" s="24" t="n"/>
+    </row>
+    <row r="217" ht="86.40000000000001" customHeight="1">
+      <c r="A217" s="19" t="n"/>
+      <c r="B217" s="20" t="n"/>
+      <c r="C217" s="20" t="n"/>
+      <c r="D217" s="21" t="inlineStr">
+        <is>
+          <t>B12.4</t>
+        </is>
+      </c>
+      <c r="E217" s="22" t="inlineStr">
+        <is>
+          <t>Form Categories</t>
+        </is>
+      </c>
+      <c r="F217" s="20" t="inlineStr">
+        <is>
+          <t>ប្រភេទទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="G217" s="23" t="inlineStr">
+        <is>
+          <t>/form-categories</t>
+        </is>
+      </c>
+      <c r="H217" s="19" t="n"/>
+      <c r="I217" s="20" t="n"/>
+      <c r="J217" s="20" t="n"/>
+      <c r="K217" s="24" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="19" t="n"/>
+      <c r="B218" s="20" t="n"/>
+      <c r="C218" s="20" t="n"/>
+      <c r="D218" s="21" t="inlineStr">
         <is>
           <t>B12.5</t>
         </is>
       </c>
-      <c r="E211" s="22" t="inlineStr">
+      <c r="E218" s="22" t="inlineStr">
         <is>
           <t>Form Templates</t>
         </is>
       </c>
-      <c r="F211" s="20" t="inlineStr">
+      <c r="F218" s="20" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="G211" s="23" t="inlineStr">
+      <c r="G218" s="23" t="inlineStr">
         <is>
           <t>/form-templates</t>
         </is>
       </c>
-      <c r="H211" s="19" t="n"/>
-      <c r="I211" s="20" t="n"/>
-      <c r="J211" s="20" t="n"/>
-      <c r="K211" s="24" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="1" t="inlineStr">
+      <c r="H218" s="19" t="n"/>
+      <c r="I218" s="20" t="n"/>
+      <c r="J218" s="20" t="n"/>
+      <c r="K218" s="24" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C212" s="3" t="inlineStr">
+      <c r="C219" s="3" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D212" s="1" t="inlineStr">
+      <c r="D219" s="1" t="inlineStr">
         <is>
           <t>B13.1</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>Groups</t>
         </is>
       </c>
-      <c r="F212" s="3" t="inlineStr">
+      <c r="F219" s="3" t="inlineStr">
         <is>
           <t>ក្រុម</t>
         </is>
       </c>
-      <c r="G212" s="4" t="inlineStr">
+      <c r="G219" s="4" t="inlineStr">
         <is>
           <t>/approval-flow/groups</t>
         </is>
       </c>
-      <c r="H212" s="5" t="n"/>
-      <c r="I212" s="3" t="n"/>
-      <c r="J212" s="3" t="n"/>
-      <c r="K212" s="6" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="7" t="inlineStr">
+      <c r="H219" s="5" t="n"/>
+      <c r="I219" s="3" t="n"/>
+      <c r="J219" s="3" t="n"/>
+      <c r="K219" s="6" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B213" s="8" t="inlineStr">
+      <c r="B220" s="8" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C213" s="8" t="inlineStr">
+      <c r="C220" s="8" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D213" s="9" t="inlineStr">
+      <c r="D220" s="9" t="inlineStr">
         <is>
           <t>B13.2</t>
         </is>
       </c>
-      <c r="E213" s="10" t="inlineStr">
+      <c r="E220" s="10" t="inlineStr">
         <is>
           <t>Flow Setting</t>
         </is>
       </c>
-      <c r="F213" s="8" t="inlineStr">
+      <c r="F220" s="8" t="inlineStr">
         <is>
           <t>កំណត់លំហូរ</t>
         </is>
       </c>
-      <c r="G213" s="11" t="inlineStr">
+      <c r="G220" s="11" t="inlineStr">
         <is>
           <t>/approval-flow/settings</t>
         </is>
       </c>
-      <c r="H213" s="7" t="n"/>
-      <c r="I213" s="8" t="n"/>
-      <c r="J213" s="8" t="n"/>
-      <c r="K213" s="12" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="7" t="inlineStr">
+      <c r="H220" s="7" t="n"/>
+      <c r="I220" s="8" t="n"/>
+      <c r="J220" s="8" t="n"/>
+      <c r="K220" s="12" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="B214" s="8" t="inlineStr">
+      <c r="B221" s="8" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="C214" s="8" t="inlineStr">
+      <c r="C221" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="D214" s="9" t="inlineStr">
+      <c r="D221" s="9" t="inlineStr">
         <is>
           <t>B14.1</t>
         </is>
       </c>
-      <c r="E214" s="10" t="inlineStr">
+      <c r="E221" s="10" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="F214" s="8" t="inlineStr">
+      <c r="F221" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="G214" s="11" t="inlineStr">
+      <c r="G221" s="11" t="inlineStr">
         <is>
           <t>/front-office</t>
         </is>
       </c>
-      <c r="H214" s="7" t="n">
+      <c r="H221" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I214" s="8" t="inlineStr">
+      <c r="I221" s="8" t="inlineStr">
         <is>
           <t>Inquiry</t>
         </is>
       </c>
-      <c r="J214" s="8" t="inlineStr">
+      <c r="J221" s="8" t="inlineStr">
         <is>
           <t>ការសាកសួរ</t>
         </is>
       </c>
-      <c r="K214" s="12" t="inlineStr">
+      <c r="K221" s="12" t="inlineStr">
         <is>
           <t>In the menu after Project Management. People who ask about the school: source, interest, follow-up history, next follow-up date; Register student fills the student form and links it. The website Register form (C4.4) also lands here as source Website, and staff who can update inquiries are notified.</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="7" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="B215" s="8" t="inlineStr">
+      <c r="B222" s="8" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="C215" s="8" t="inlineStr">
+      <c r="C222" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="D215" s="9" t="inlineStr">
+      <c r="D222" s="9" t="inlineStr">
         <is>
           <t>B14.1</t>
         </is>
       </c>
-      <c r="E215" s="10" t="inlineStr">
+      <c r="E222" s="10" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="F215" s="8" t="inlineStr">
+      <c r="F222" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="G215" s="11" t="inlineStr">
+      <c r="G222" s="11" t="inlineStr">
         <is>
           <t>/front-office</t>
         </is>
       </c>
-      <c r="H215" s="7" t="n">
+      <c r="H222" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I215" s="8" t="inlineStr">
+      <c r="I222" s="8" t="inlineStr">
         <is>
           <t>Meeting arrangement</t>
         </is>
       </c>
-      <c r="J215" s="8" t="inlineStr">
+      <c r="J222" s="8" t="inlineStr">
         <is>
           <t>រៀបចំកិច្ចប្រជុំ</t>
         </is>
       </c>
-      <c r="K215" s="12" t="inlineStr">
+      <c r="K222" s="12" t="inlineStr">
         <is>
           <t>Date, start/end time, place, organizer, agenda; participants are staff (notified when invited, moved or cancelled) plus outside guests; meeting note; Scheduled / Completed / Cancelled. Upcoming, Past, All and Only mine. Teachers can view by default. Also shown on School setup &gt; School calendar (not cancelled ones; only to people who can view meetings); a click opens the meeting.</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="7" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="7" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="B216" s="8" t="inlineStr">
+      <c r="B223" s="8" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="C216" s="8" t="inlineStr">
+      <c r="C223" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="D216" s="9" t="inlineStr">
+      <c r="D223" s="9" t="inlineStr">
         <is>
           <t>B14.1</t>
         </is>
       </c>
-      <c r="E216" s="10" t="inlineStr">
+      <c r="E223" s="10" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="F216" s="8" t="inlineStr">
+      <c r="F223" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="G216" s="11" t="inlineStr">
+      <c r="G223" s="11" t="inlineStr">
         <is>
           <t>/front-office</t>
         </is>
       </c>
-      <c r="H216" s="7" t="n">
+      <c r="H223" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I216" s="8" t="inlineStr">
+      <c r="I223" s="8" t="inlineStr">
         <is>
           <t>Appointment</t>
         </is>
       </c>
-      <c r="J216" s="8" t="inlineStr">
+      <c r="J223" s="8" t="inlineStr">
         <is>
           <t>ការណាត់ជួប</t>
         </is>
       </c>
-      <c r="K216" s="12" t="inlineStr">
+      <c r="K223" s="12" t="inlineStr">
         <is>
           <t>Book a visit: visitor, phone, organization, purpose, date and time, Meeting with (staff, notified). Today / Upcoming / Past / All. Check in adds them to the Visitor log and tells the host; No-show, Cancel.</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="7" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="7" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="B217" s="8" t="inlineStr">
+      <c r="B224" s="8" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="C217" s="8" t="inlineStr">
+      <c r="C224" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="D217" s="9" t="inlineStr">
+      <c r="D224" s="9" t="inlineStr">
         <is>
           <t>B14.1</t>
         </is>
       </c>
-      <c r="E217" s="10" t="inlineStr">
+      <c r="E224" s="10" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="F217" s="8" t="inlineStr">
+      <c r="F224" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="G217" s="11" t="inlineStr">
+      <c r="G224" s="11" t="inlineStr">
         <is>
           <t>/front-office</t>
         </is>
       </c>
-      <c r="H217" s="7" t="n">
+      <c r="H224" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I217" s="8" t="inlineStr">
+      <c r="I224" s="8" t="inlineStr">
         <is>
           <t>Visitor</t>
         </is>
       </c>
-      <c r="J217" s="8" t="inlineStr">
+      <c r="J224" s="8" t="inlineStr">
         <is>
           <t>ភ្ញៀវ</t>
         </is>
       </c>
-      <c r="K217" s="12" t="inlineStr">
+      <c r="K224" s="12" t="inlineStr">
         <is>
           <t>Visitor log by day: walk-ins checked in here, appointments via Check in; people count, ID no., badge; check-in and check-out times; On site now. Check out completes the appointment.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K209"/>
+  <autoFilter ref="A1:K216"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -10413,8 +10462,8 @@
     <col width="10.5546875" bestFit="1" customWidth="1" style="27" min="8" max="8"/>
     <col width="28" customWidth="1" style="27" min="9" max="10"/>
     <col width="44" customWidth="1" style="27" min="11" max="11"/>
-    <col width="8.88671875" customWidth="1" style="27" min="12" max="12"/>
-    <col width="8.88671875" customWidth="1" style="27" min="13" max="16384"/>
+    <col width="8.88671875" customWidth="1" style="27" min="12" max="13"/>
+    <col width="8.88671875" customWidth="1" style="27" min="14" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customFormat="1" customHeight="1" s="28">
@@ -14714,7 +14763,7 @@
       </c>
       <c r="J116" s="24" t="n"/>
     </row>
-    <row r="117">
+    <row r="117" ht="21.6" customHeight="1">
       <c r="A117" s="19" t="n"/>
       <c r="B117" s="20" t="n"/>
       <c r="C117" s="20" t="n"/>
@@ -14738,7 +14787,7 @@
       <c r="I117" s="20" t="n"/>
       <c r="J117" s="24" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" ht="21.6" customHeight="1">
       <c r="A118" s="19" t="n"/>
       <c r="B118" s="20" t="n"/>
       <c r="C118" s="20" t="n"/>
@@ -14762,7 +14811,7 @@
       <c r="I118" s="20" t="n"/>
       <c r="J118" s="24" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" ht="21.6" customHeight="1">
       <c r="A119" s="1" t="inlineStr">
         <is>
           <t>B13</t>
@@ -14798,7 +14847,7 @@
       <c r="I119" s="3" t="n"/>
       <c r="J119" s="6" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" ht="21.6" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
           <t>B13</t>

--- a/docs/NTCSWEB-Modules.xlsx
+++ b/docs/NTCSWEB-Modules.xlsx
@@ -14,12 +14,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Back office'!$A$1:$K$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Back office'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'System'!$A$1:$K$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'System'!$A$1:$K$218</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'System'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Website'!$A$1:$K$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Website'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2143,7 +2143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K224"/>
+  <dimension ref="A1:K226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="J70" s="20" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>Previous Work</t>
+          <t>Job experience</t>
         </is>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
-          <t>បទពិសោធន៍ការងារពីមុន</t>
+          <t>បទពិសោធន៍ការងារ</t>
         </is>
       </c>
       <c r="K71" s="24" t="n"/>
@@ -4685,37 +4685,37 @@
       <c r="A72" s="19" t="n"/>
       <c r="B72" s="20" t="n"/>
       <c r="C72" s="20" t="n"/>
-      <c r="D72" s="21" t="inlineStr">
-        <is>
-          <t>B6.2</t>
-        </is>
-      </c>
-      <c r="E72" s="22" t="inlineStr">
-        <is>
-          <t>Teachers</t>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>B6.1</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr">
+        <is>
+          <t>Staff</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>គ្រូ</t>
+          <t>បុគ្គលិក</t>
         </is>
       </c>
       <c r="G72" s="23" t="inlineStr">
         <is>
-          <t>/teachers</t>
+          <t>/staff</t>
         </is>
       </c>
       <c r="H72" s="19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Other Skills</t>
         </is>
       </c>
       <c r="J72" s="20" t="inlineStr">
         <is>
-          <t>គុណវុឌ្ឍិ</t>
+          <t>ជំនាញផ្សេងៗ</t>
         </is>
       </c>
       <c r="K72" s="24" t="n"/>
@@ -4726,35 +4726,35 @@
       <c r="C73" s="20" t="n"/>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t>B6.2</t>
+          <t>B6.1</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>Teachers</t>
+          <t>Staff</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>គ្រូ</t>
+          <t>បុគ្គលិក</t>
         </is>
       </c>
       <c r="G73" s="23" t="inlineStr">
         <is>
-          <t>/teachers</t>
+          <t>/staff</t>
         </is>
       </c>
       <c r="H73" s="19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="J73" s="20" t="inlineStr">
         <is>
-          <t>ការចាត់តាំង</t>
+          <t>ឯកសារ</t>
         </is>
       </c>
       <c r="K73" s="24" t="n"/>
@@ -4763,12 +4763,12 @@
       <c r="A74" s="19" t="n"/>
       <c r="B74" s="20" t="n"/>
       <c r="C74" s="20" t="n"/>
-      <c r="D74" s="19" t="inlineStr">
+      <c r="D74" s="21" t="inlineStr">
         <is>
           <t>B6.2</t>
         </is>
       </c>
-      <c r="E74" s="20" t="inlineStr">
+      <c r="E74" s="22" t="inlineStr">
         <is>
           <t>Teachers</t>
         </is>
@@ -4784,16 +4784,16 @@
         </is>
       </c>
       <c r="H74" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>Homeroom</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="J74" s="20" t="inlineStr">
         <is>
-          <t>គ្រូប្រចាំថ្នាក់</t>
+          <t>គុណវុឌ្ឍិ</t>
         </is>
       </c>
       <c r="K74" s="24" t="n"/>
@@ -4823,16 +4823,16 @@
         </is>
       </c>
       <c r="H75" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>Teaching load</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបង្រៀន</t>
+          <t>ការចាត់តាំង</t>
         </is>
       </c>
       <c r="K75" s="24" t="n"/>
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="H76" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Homeroom</t>
         </is>
       </c>
       <c r="J76" s="20" t="inlineStr">
         <is>
-          <t>ពេលទំនេរ</t>
+          <t>គ្រូប្រចាំថ្នាក់</t>
         </is>
       </c>
       <c r="K76" s="24" t="n"/>
@@ -4901,16 +4901,16 @@
         </is>
       </c>
       <c r="H77" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>Substitute</t>
+          <t>Teaching load</t>
         </is>
       </c>
       <c r="J77" s="20" t="inlineStr">
         <is>
-          <t>គ្រូជំនួស</t>
+          <t>ម៉ោងបង្រៀន</t>
         </is>
       </c>
       <c r="K77" s="24" t="n"/>
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="H78" s="19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="J78" s="20" t="inlineStr">
         <is>
-          <t>ឯកសារ</t>
+          <t>ពេលទំនេរ</t>
         </is>
       </c>
       <c r="K78" s="24" t="n"/>
@@ -4958,66 +4958,76 @@
       <c r="A79" s="19" t="n"/>
       <c r="B79" s="20" t="n"/>
       <c r="C79" s="20" t="n"/>
-      <c r="D79" s="21" t="inlineStr">
-        <is>
-          <t>B6.3</t>
-        </is>
-      </c>
-      <c r="E79" s="22" t="inlineStr">
-        <is>
-          <t>Staff Status History</t>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>B6.2</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>Teachers</t>
         </is>
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
+          <t>គ្រូ</t>
         </is>
       </c>
       <c r="G79" s="23" t="inlineStr">
         <is>
-          <t>/staff-status-history</t>
-        </is>
-      </c>
-      <c r="H79" s="19" t="n"/>
-      <c r="I79" s="20" t="n"/>
-      <c r="J79" s="20" t="n"/>
+          <t>/teachers</t>
+        </is>
+      </c>
+      <c r="H79" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I79" s="20" t="inlineStr">
+        <is>
+          <t>Substitute</t>
+        </is>
+      </c>
+      <c r="J79" s="20" t="inlineStr">
+        <is>
+          <t>គ្រូជំនួស</t>
+        </is>
+      </c>
       <c r="K79" s="24" t="n"/>
     </row>
     <row r="80" ht="21.6" customHeight="1">
       <c r="A80" s="19" t="n"/>
       <c r="B80" s="20" t="n"/>
       <c r="C80" s="20" t="n"/>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>B6.4</t>
-        </is>
-      </c>
-      <c r="E80" s="22" t="inlineStr">
-        <is>
-          <t>Organization Management</t>
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>B6.2</t>
+        </is>
+      </c>
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>Teachers</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងអង្គភាព</t>
+          <t>គ្រូ</t>
         </is>
       </c>
       <c r="G80" s="23" t="inlineStr">
         <is>
-          <t>/organization</t>
+          <t>/teachers</t>
         </is>
       </c>
       <c r="H80" s="19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="J80" s="20" t="inlineStr">
         <is>
-          <t>សាលា</t>
+          <t>ឯកសារ</t>
         </is>
       </c>
       <c r="K80" s="24" t="n"/>
@@ -5026,51 +5036,41 @@
       <c r="A81" s="19" t="n"/>
       <c r="B81" s="20" t="n"/>
       <c r="C81" s="20" t="n"/>
-      <c r="D81" s="19" t="inlineStr">
-        <is>
-          <t>B6.4</t>
-        </is>
-      </c>
-      <c r="E81" s="20" t="inlineStr">
-        <is>
-          <t>Organization Management</t>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>B6.3</t>
+        </is>
+      </c>
+      <c r="E81" s="22" t="inlineStr">
+        <is>
+          <t>Staff Status History</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងអង្គភាព</t>
+          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
         </is>
       </c>
       <c r="G81" s="23" t="inlineStr">
         <is>
-          <t>/organization</t>
-        </is>
-      </c>
-      <c r="H81" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I81" s="20" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="J81" s="20" t="inlineStr">
-        <is>
-          <t>សាខា</t>
-        </is>
-      </c>
+          <t>/staff-status-history</t>
+        </is>
+      </c>
+      <c r="H81" s="19" t="n"/>
+      <c r="I81" s="20" t="n"/>
+      <c r="J81" s="20" t="n"/>
       <c r="K81" s="24" t="n"/>
     </row>
     <row r="82" ht="21.6" customHeight="1">
       <c r="A82" s="19" t="n"/>
       <c r="B82" s="20" t="n"/>
       <c r="C82" s="20" t="n"/>
-      <c r="D82" s="19" t="inlineStr">
+      <c r="D82" s="21" t="inlineStr">
         <is>
           <t>B6.4</t>
         </is>
       </c>
-      <c r="E82" s="20" t="inlineStr">
+      <c r="E82" s="22" t="inlineStr">
         <is>
           <t>Organization Management</t>
         </is>
@@ -5086,16 +5086,16 @@
         </is>
       </c>
       <c r="H82" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>School</t>
         </is>
       </c>
       <c r="J82" s="20" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>សាលា</t>
         </is>
       </c>
       <c r="K82" s="24" t="n"/>
@@ -5125,16 +5125,16 @@
         </is>
       </c>
       <c r="H83" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
-          <t>ក្រុម</t>
+          <t>សាខា</t>
         </is>
       </c>
       <c r="K83" s="24" t="n"/>
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="H84" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="J84" s="20" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="K84" s="24" t="n"/>
@@ -5203,16 +5203,16 @@
         </is>
       </c>
       <c r="H85" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Job grade</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
-          <t>ថ្នាក់ការងារ</t>
+          <t>ក្រុម</t>
         </is>
       </c>
       <c r="K85" s="24" t="n"/>
@@ -5242,16 +5242,16 @@
         </is>
       </c>
       <c r="H86" s="19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Job level</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="J86" s="20" t="inlineStr">
         <is>
-          <t>កម្រិតការងារ</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="K86" s="24" t="n"/>
@@ -5281,16 +5281,16 @@
         </is>
       </c>
       <c r="H87" s="19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Reporting manager</t>
+          <t>Job grade</t>
         </is>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
-          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
+          <t>ថ្នាក់ការងារ</t>
         </is>
       </c>
       <c r="K87" s="24" t="n"/>
@@ -5320,16 +5320,16 @@
         </is>
       </c>
       <c r="H88" s="19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>Organization hierarchy</t>
+          <t>Job level</t>
         </is>
       </c>
       <c r="J88" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
+          <t>កម្រិតការងារ</t>
         </is>
       </c>
       <c r="K88" s="24" t="n"/>
@@ -5338,37 +5338,37 @@
       <c r="A89" s="19" t="n"/>
       <c r="B89" s="20" t="n"/>
       <c r="C89" s="20" t="n"/>
-      <c r="D89" s="21" t="inlineStr">
-        <is>
-          <t>B6.5</t>
-        </is>
-      </c>
-      <c r="E89" s="22" t="inlineStr">
-        <is>
-          <t>Recruitment</t>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>B6.4</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>Organization Management</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបុគ្គលិក</t>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
         </is>
       </c>
       <c r="G89" s="23" t="inlineStr">
         <is>
-          <t>/recruitment</t>
+          <t>/organization</t>
         </is>
       </c>
       <c r="H89" s="19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Manpower request</t>
+          <t>Reporting manager</t>
         </is>
       </c>
       <c r="J89" s="20" t="inlineStr">
         <is>
-          <t>សំណើបុគ្គលិក</t>
+          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
         </is>
       </c>
       <c r="K89" s="24" t="n"/>
@@ -5379,35 +5379,35 @@
       <c r="C90" s="20" t="n"/>
       <c r="D90" s="19" t="inlineStr">
         <is>
-          <t>B6.5</t>
+          <t>B6.4</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Organization Management</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបុគ្គលិក</t>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
         <is>
-          <t>/recruitment</t>
+          <t>/organization</t>
         </is>
       </c>
       <c r="H90" s="19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Job positions</t>
+          <t>Organization hierarchy</t>
         </is>
       </c>
       <c r="J90" s="20" t="inlineStr">
         <is>
-          <t>មុខតំណែងការងារ</t>
+          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
         </is>
       </c>
       <c r="K90" s="24" t="n"/>
@@ -5416,12 +5416,12 @@
       <c r="A91" s="19" t="n"/>
       <c r="B91" s="20" t="n"/>
       <c r="C91" s="20" t="n"/>
-      <c r="D91" s="19" t="inlineStr">
+      <c r="D91" s="21" t="inlineStr">
         <is>
           <t>B6.5</t>
         </is>
       </c>
-      <c r="E91" s="20" t="inlineStr">
+      <c r="E91" s="22" t="inlineStr">
         <is>
           <t>Recruitment</t>
         </is>
@@ -5437,16 +5437,16 @@
         </is>
       </c>
       <c r="H91" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>Job postings</t>
+          <t>Manpower request</t>
         </is>
       </c>
       <c r="J91" s="20" t="inlineStr">
         <is>
-          <t>ការផ្សព្វផ្សាយការងារ</t>
+          <t>សំណើបុគ្គលិក</t>
         </is>
       </c>
       <c r="K91" s="24" t="n"/>
@@ -5476,16 +5476,16 @@
         </is>
       </c>
       <c r="H92" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
-          <t>Applicant management</t>
+          <t>Job positions</t>
         </is>
       </c>
       <c r="J92" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងបេក្ខជន</t>
+          <t>មុខតំណែងការងារ</t>
         </is>
       </c>
       <c r="K92" s="24" t="n"/>
@@ -5515,16 +5515,16 @@
         </is>
       </c>
       <c r="H93" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I93" s="20" t="inlineStr">
         <is>
-          <t>CV/resume</t>
+          <t>Job postings</t>
         </is>
       </c>
       <c r="J93" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិរូប (CV)</t>
+          <t>ការផ្សព្វផ្សាយការងារ</t>
         </is>
       </c>
       <c r="K93" s="24" t="n"/>
@@ -5554,16 +5554,16 @@
         </is>
       </c>
       <c r="H94" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Applicant management</t>
         </is>
       </c>
       <c r="J94" s="20" t="inlineStr">
         <is>
-          <t>សម្ភាសន៍</t>
+          <t>គ្រប់គ្រងបេក្ខជន</t>
         </is>
       </c>
       <c r="K94" s="24" t="n"/>
@@ -5593,16 +5593,16 @@
         </is>
       </c>
       <c r="H95" s="19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I95" s="20" t="inlineStr">
         <is>
-          <t>Interview evaluation</t>
+          <t>CV/resume</t>
         </is>
       </c>
       <c r="J95" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃសម្ភាសន៍</t>
+          <t>ប្រវត្តិរូប (CV)</t>
         </is>
       </c>
       <c r="K95" s="24" t="n"/>
@@ -5632,16 +5632,16 @@
         </is>
       </c>
       <c r="H96" s="19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
-          <t>Candidate selection</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="J96" s="20" t="inlineStr">
         <is>
-          <t>ការជ្រើសរើសបេក្ខជន</t>
+          <t>សម្ភាសន៍</t>
         </is>
       </c>
       <c r="K96" s="24" t="n"/>
@@ -5671,16 +5671,16 @@
         </is>
       </c>
       <c r="H97" s="19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>Offer letter</t>
+          <t>Interview evaluation</t>
         </is>
       </c>
       <c r="J97" s="20" t="inlineStr">
         <is>
-          <t>លិខិតផ្តល់ការងារ</t>
+          <t>ការវាយតម្លៃសម្ភាសន៍</t>
         </is>
       </c>
       <c r="K97" s="24" t="n"/>
@@ -5710,16 +5710,16 @@
         </is>
       </c>
       <c r="H98" s="19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
-          <t>Recruitment pipeline</t>
+          <t>Candidate selection</t>
         </is>
       </c>
       <c r="J98" s="20" t="inlineStr">
         <is>
-          <t>ដំណើរការជ្រើសរើស</t>
+          <t>ការជ្រើសរើសបេក្ខជន</t>
         </is>
       </c>
       <c r="K98" s="24" t="n"/>
@@ -5728,37 +5728,37 @@
       <c r="A99" s="19" t="n"/>
       <c r="B99" s="20" t="n"/>
       <c r="C99" s="20" t="n"/>
-      <c r="D99" s="21" t="inlineStr">
-        <is>
-          <t>B6.6</t>
-        </is>
-      </c>
-      <c r="E99" s="22" t="inlineStr">
-        <is>
-          <t>Attendance &amp; Time</t>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>B6.5</t>
+        </is>
+      </c>
+      <c r="E99" s="20" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
         <is>
-          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+          <t>ការជ្រើសរើសបុគ្គលិក</t>
         </is>
       </c>
       <c r="G99" s="23" t="inlineStr">
         <is>
-          <t>/time-attendance</t>
+          <t>/recruitment</t>
         </is>
       </c>
       <c r="H99" s="19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I99" s="20" t="inlineStr">
         <is>
-          <t>Employee attendance</t>
+          <t>Offer letter</t>
         </is>
       </c>
       <c r="J99" s="20" t="inlineStr">
         <is>
-          <t>វត្តមានបុគ្គលិក</t>
+          <t>លិខិតផ្តល់ការងារ</t>
         </is>
       </c>
       <c r="K99" s="24" t="n"/>
@@ -5769,35 +5769,35 @@
       <c r="C100" s="20" t="n"/>
       <c r="D100" s="19" t="inlineStr">
         <is>
-          <t>B6.6</t>
+          <t>B6.5</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Attendance &amp; Time</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
         <is>
-          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+          <t>ការជ្រើសរើសបុគ្គលិក</t>
         </is>
       </c>
       <c r="G100" s="23" t="inlineStr">
         <is>
-          <t>/time-attendance</t>
+          <t>/recruitment</t>
         </is>
       </c>
       <c r="H100" s="19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I100" s="20" t="inlineStr">
         <is>
-          <t>Check-in / check-out</t>
+          <t>Recruitment pipeline</t>
         </is>
       </c>
       <c r="J100" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>ដំណើរការជ្រើសរើស</t>
         </is>
       </c>
       <c r="K100" s="24" t="n"/>
@@ -5806,12 +5806,12 @@
       <c r="A101" s="19" t="n"/>
       <c r="B101" s="20" t="n"/>
       <c r="C101" s="20" t="n"/>
-      <c r="D101" s="19" t="inlineStr">
+      <c r="D101" s="21" t="inlineStr">
         <is>
           <t>B6.6</t>
         </is>
       </c>
-      <c r="E101" s="20" t="inlineStr">
+      <c r="E101" s="22" t="inlineStr">
         <is>
           <t>Attendance &amp; Time</t>
         </is>
@@ -5827,16 +5827,16 @@
         </is>
       </c>
       <c r="H101" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I101" s="20" t="inlineStr">
         <is>
-          <t>Late</t>
+          <t>Employee attendance</t>
         </is>
       </c>
       <c r="J101" s="20" t="inlineStr">
         <is>
-          <t>មកយឺត</t>
+          <t>វត្តមានបុគ្គលិក</t>
         </is>
       </c>
       <c r="K101" s="24" t="n"/>
@@ -5866,16 +5866,16 @@
         </is>
       </c>
       <c r="H102" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I102" s="20" t="inlineStr">
         <is>
-          <t>Early leave</t>
+          <t>Check-in / check-out</t>
         </is>
       </c>
       <c r="J102" s="20" t="inlineStr">
         <is>
-          <t>ចេញមុន</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="K102" s="24" t="n"/>
@@ -5905,16 +5905,16 @@
         </is>
       </c>
       <c r="H103" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I103" s="20" t="inlineStr">
         <is>
-          <t>Absence</t>
+          <t>Late</t>
         </is>
       </c>
       <c r="J103" s="20" t="inlineStr">
         <is>
-          <t>អវត្តមាន</t>
+          <t>មកយឺត</t>
         </is>
       </c>
       <c r="K103" s="24" t="n"/>
@@ -5944,16 +5944,16 @@
         </is>
       </c>
       <c r="H104" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I104" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Early leave</t>
         </is>
       </c>
       <c r="J104" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>ចេញមុន</t>
         </is>
       </c>
       <c r="K104" s="24" t="n"/>
@@ -5983,16 +5983,16 @@
         </is>
       </c>
       <c r="H105" s="19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I105" s="20" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Absence</t>
         </is>
       </c>
       <c r="J105" s="20" t="inlineStr">
         <is>
-          <t>វេនការងារ</t>
+          <t>អវត្តមាន</t>
         </is>
       </c>
       <c r="K105" s="24" t="n"/>
@@ -6022,16 +6022,16 @@
         </is>
       </c>
       <c r="H106" s="19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I106" s="20" t="inlineStr">
         <is>
-          <t>Staff shift</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="J106" s="20" t="inlineStr">
         <is>
-          <t>វេនបុគ្គលិក</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="K106" s="24" t="n"/>
@@ -6061,16 +6061,16 @@
         </is>
       </c>
       <c r="H107" s="19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I107" s="20" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="J107" s="20" t="inlineStr">
         <is>
-          <t>ថ្ងៃឈប់សម្រាក</t>
+          <t>វេនការងារ</t>
         </is>
       </c>
       <c r="K107" s="24" t="n"/>
@@ -6100,16 +6100,16 @@
         </is>
       </c>
       <c r="H108" s="19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I108" s="20" t="inlineStr">
         <is>
-          <t>Attendance correction</t>
+          <t>Staff shift</t>
         </is>
       </c>
       <c r="J108" s="20" t="inlineStr">
         <is>
-          <t>ការកែវត្តមាន</t>
+          <t>វេនបុគ្គលិក</t>
         </is>
       </c>
       <c r="K108" s="24" t="n"/>
@@ -6139,16 +6139,16 @@
         </is>
       </c>
       <c r="H109" s="19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I109" s="20" t="inlineStr">
         <is>
-          <t>Attendance approval</t>
+          <t>Holidays</t>
         </is>
       </c>
       <c r="J109" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តវត្តមាន</t>
+          <t>ថ្ងៃឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K109" s="24" t="n"/>
@@ -6157,37 +6157,37 @@
       <c r="A110" s="19" t="n"/>
       <c r="B110" s="20" t="n"/>
       <c r="C110" s="20" t="n"/>
-      <c r="D110" s="21" t="inlineStr">
-        <is>
-          <t>B6.7</t>
-        </is>
-      </c>
-      <c r="E110" s="22" t="inlineStr">
-        <is>
-          <t>Leave Management</t>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>B6.6</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>Attendance &amp; Time</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
         <is>
-          <t>/leave-management</t>
+          <t>/time-attendance</t>
         </is>
       </c>
       <c r="H110" s="19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I110" s="20" t="inlineStr">
         <is>
-          <t>Leave types</t>
+          <t>Attendance correction</t>
         </is>
       </c>
       <c r="J110" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
+          <t>ការកែវត្តមាន</t>
         </is>
       </c>
       <c r="K110" s="24" t="n"/>
@@ -6198,35 +6198,35 @@
       <c r="C111" s="20" t="n"/>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t>B6.7</t>
+          <t>B6.6</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
         <is>
-          <t>Leave Management</t>
+          <t>Attendance &amp; Time</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
         <is>
-          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
         <is>
-          <t>/leave-management</t>
+          <t>/time-attendance</t>
         </is>
       </c>
       <c r="H111" s="19" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I111" s="20" t="inlineStr">
         <is>
-          <t>Leave policies</t>
+          <t>Attendance approval</t>
         </is>
       </c>
       <c r="J111" s="20" t="inlineStr">
         <is>
-          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
+          <t>ការអនុម័តវត្តមាន</t>
         </is>
       </c>
       <c r="K111" s="24" t="n"/>
@@ -6235,12 +6235,12 @@
       <c r="A112" s="19" t="n"/>
       <c r="B112" s="20" t="n"/>
       <c r="C112" s="20" t="n"/>
-      <c r="D112" s="19" t="inlineStr">
+      <c r="D112" s="21" t="inlineStr">
         <is>
           <t>B6.7</t>
         </is>
       </c>
-      <c r="E112" s="20" t="inlineStr">
+      <c r="E112" s="22" t="inlineStr">
         <is>
           <t>Leave Management</t>
         </is>
@@ -6256,16 +6256,16 @@
         </is>
       </c>
       <c r="H112" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I112" s="20" t="inlineStr">
         <is>
-          <t>Leave balance</t>
+          <t>Leave types</t>
         </is>
       </c>
       <c r="J112" s="20" t="inlineStr">
         <is>
-          <t>សមតុល្យច្បាប់</t>
+          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K112" s="24" t="n"/>
@@ -6295,16 +6295,16 @@
         </is>
       </c>
       <c r="H113" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I113" s="20" t="inlineStr">
         <is>
-          <t>Leave request</t>
+          <t>Leave policies</t>
         </is>
       </c>
       <c r="J113" s="20" t="inlineStr">
         <is>
-          <t>សំណើច្បាប់ឈប់សម្រាក</t>
+          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K113" s="24" t="n"/>
@@ -6334,16 +6334,16 @@
         </is>
       </c>
       <c r="H114" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
-          <t>Approval workflow</t>
+          <t>Leave balance</t>
         </is>
       </c>
       <c r="J114" s="20" t="inlineStr">
         <is>
-          <t>លំហូរការអនុម័ត</t>
+          <t>សមតុល្យច្បាប់</t>
         </is>
       </c>
       <c r="K114" s="24" t="n"/>
@@ -6373,16 +6373,16 @@
         </is>
       </c>
       <c r="H115" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>Leave calendar</t>
+          <t>Leave request</t>
         </is>
       </c>
       <c r="J115" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិទិនច្បាប់</t>
+          <t>សំណើច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="K115" s="24" t="n"/>
@@ -6412,16 +6412,16 @@
         </is>
       </c>
       <c r="H116" s="19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
-          <t>Carry forward</t>
+          <t>Approval workflow</t>
         </is>
       </c>
       <c r="J116" s="20" t="inlineStr">
         <is>
-          <t>យោងទៅឆ្នាំបន្ទាប់</t>
+          <t>លំហូរការអនុម័ត</t>
         </is>
       </c>
       <c r="K116" s="24" t="n"/>
@@ -6451,16 +6451,16 @@
         </is>
       </c>
       <c r="H117" s="19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I117" s="20" t="inlineStr">
         <is>
-          <t>Leave reports</t>
+          <t>Leave calendar</t>
         </is>
       </c>
       <c r="J117" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ច្បាប់</t>
+          <t>ប្រតិទិនច្បាប់</t>
         </is>
       </c>
       <c r="K117" s="24" t="n"/>
@@ -6469,37 +6469,37 @@
       <c r="A118" s="19" t="n"/>
       <c r="B118" s="20" t="n"/>
       <c r="C118" s="20" t="n"/>
-      <c r="D118" s="21" t="inlineStr">
-        <is>
-          <t>B6.8</t>
-        </is>
-      </c>
-      <c r="E118" s="22" t="inlineStr">
-        <is>
-          <t>Payroll</t>
+      <c r="D118" s="19" t="inlineStr">
+        <is>
+          <t>B6.7</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>Leave Management</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
         <is>
-          <t>បញ្ជីប្រាក់ខែ</t>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
         <is>
-          <t>/payroll</t>
+          <t>/leave-management</t>
         </is>
       </c>
       <c r="H118" s="19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I118" s="20" t="inlineStr">
         <is>
-          <t>Salary structure</t>
+          <t>Carry forward</t>
         </is>
       </c>
       <c r="J118" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធប្រាក់ខែ</t>
+          <t>យោងទៅឆ្នាំបន្ទាប់</t>
         </is>
       </c>
       <c r="K118" s="24" t="n"/>
@@ -6510,35 +6510,35 @@
       <c r="C119" s="20" t="n"/>
       <c r="D119" s="19" t="inlineStr">
         <is>
-          <t>B6.8</t>
+          <t>B6.7</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>Payroll</t>
+          <t>Leave Management</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
         <is>
-          <t>បញ្ជីប្រាក់ខែ</t>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
         <is>
-          <t>/payroll</t>
+          <t>/leave-management</t>
         </is>
       </c>
       <c r="H119" s="19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I119" s="20" t="inlineStr">
         <is>
-          <t>Basic salary</t>
+          <t>Leave reports</t>
         </is>
       </c>
       <c r="J119" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ខែគោល</t>
+          <t>របាយការណ៍ច្បាប់</t>
         </is>
       </c>
       <c r="K119" s="24" t="n"/>
@@ -6547,12 +6547,12 @@
       <c r="A120" s="19" t="n"/>
       <c r="B120" s="20" t="n"/>
       <c r="C120" s="20" t="n"/>
-      <c r="D120" s="19" t="inlineStr">
+      <c r="D120" s="21" t="inlineStr">
         <is>
           <t>B6.8</t>
         </is>
       </c>
-      <c r="E120" s="20" t="inlineStr">
+      <c r="E120" s="22" t="inlineStr">
         <is>
           <t>Payroll</t>
         </is>
@@ -6568,16 +6568,16 @@
         </is>
       </c>
       <c r="H120" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I120" s="20" t="inlineStr">
         <is>
-          <t>Allowances</t>
+          <t>Salary structure</t>
         </is>
       </c>
       <c r="J120" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ឧបត្ថម្ភ</t>
+          <t>រចនាសម្ព័ន្ធប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K120" s="24" t="n"/>
@@ -6607,16 +6607,16 @@
         </is>
       </c>
       <c r="H121" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I121" s="20" t="inlineStr">
         <is>
-          <t>Bonuses</t>
+          <t>Basic salary</t>
         </is>
       </c>
       <c r="J121" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់រង្វាន់</t>
+          <t>ប្រាក់ខែគោល</t>
         </is>
       </c>
       <c r="K121" s="24" t="n"/>
@@ -6646,16 +6646,16 @@
         </is>
       </c>
       <c r="H122" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I122" s="20" t="inlineStr">
         <is>
-          <t>Deductions</t>
+          <t>Allowances</t>
         </is>
       </c>
       <c r="J122" s="20" t="inlineStr">
         <is>
-          <t>ការកាត់ប្រាក់</t>
+          <t>ប្រាក់ឧបត្ថម្ភ</t>
         </is>
       </c>
       <c r="K122" s="24" t="n"/>
@@ -6685,16 +6685,16 @@
         </is>
       </c>
       <c r="H123" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I123" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Bonuses</t>
         </is>
       </c>
       <c r="J123" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>ប្រាក់រង្វាន់</t>
         </is>
       </c>
       <c r="K123" s="24" t="n"/>
@@ -6724,16 +6724,16 @@
         </is>
       </c>
       <c r="H124" s="19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I124" s="20" t="inlineStr">
         <is>
-          <t>Attendance deduction</t>
+          <t>Deductions</t>
         </is>
       </c>
       <c r="J124" s="20" t="inlineStr">
         <is>
-          <t>ការកាត់ប្រាក់តាមវត្តមាន</t>
+          <t>ការកាត់ប្រាក់</t>
         </is>
       </c>
       <c r="K124" s="24" t="n"/>
@@ -6763,16 +6763,16 @@
         </is>
       </c>
       <c r="H125" s="19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I125" s="20" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="J125" s="20" t="inlineStr">
         <is>
-          <t>ពន្ធ</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="K125" s="24" t="n"/>
@@ -6802,16 +6802,16 @@
         </is>
       </c>
       <c r="H126" s="19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I126" s="20" t="inlineStr">
         <is>
-          <t>Social security</t>
+          <t>Attendance deduction</t>
         </is>
       </c>
       <c r="J126" s="20" t="inlineStr">
         <is>
-          <t>សន្តិសុខសង្គម</t>
+          <t>ការកាត់ប្រាក់តាមវត្តមាន</t>
         </is>
       </c>
       <c r="K126" s="24" t="n"/>
@@ -6841,16 +6841,16 @@
         </is>
       </c>
       <c r="H127" s="19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I127" s="20" t="inlineStr">
         <is>
-          <t>Loan/advance</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="J127" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់កម្ចី/ប្រាក់បុរេប្រទាន</t>
+          <t>ពន្ធ</t>
         </is>
       </c>
       <c r="K127" s="24" t="n"/>
@@ -6880,16 +6880,16 @@
         </is>
       </c>
       <c r="H128" s="19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I128" s="20" t="inlineStr">
         <is>
-          <t>Payroll calculation</t>
+          <t>Social security</t>
         </is>
       </c>
       <c r="J128" s="20" t="inlineStr">
         <is>
-          <t>ការគណនាប្រាក់ខែ</t>
+          <t>សន្តិសុខសង្គម</t>
         </is>
       </c>
       <c r="K128" s="24" t="n"/>
@@ -6919,16 +6919,16 @@
         </is>
       </c>
       <c r="H129" s="19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I129" s="20" t="inlineStr">
         <is>
-          <t>Payslip</t>
+          <t>Loan/advance</t>
         </is>
       </c>
       <c r="J129" s="20" t="inlineStr">
         <is>
-          <t>បង្កាន់ដៃប្រាក់ខែ</t>
+          <t>ប្រាក់កម្ចី/ប្រាក់បុរេប្រទាន</t>
         </is>
       </c>
       <c r="K129" s="24" t="n"/>
@@ -6958,16 +6958,16 @@
         </is>
       </c>
       <c r="H130" s="19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I130" s="20" t="inlineStr">
         <is>
-          <t>Payroll approval</t>
+          <t>Payroll calculation</t>
         </is>
       </c>
       <c r="J130" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តប្រាក់ខែ</t>
+          <t>ការគណនាប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K130" s="24" t="n"/>
@@ -6997,16 +6997,16 @@
         </is>
       </c>
       <c r="H131" s="19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I131" s="20" t="inlineStr">
         <is>
-          <t>Payroll history</t>
+          <t>Payslip</t>
         </is>
       </c>
       <c r="J131" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិប្រាក់ខែ</t>
+          <t>បង្កាន់ដៃប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K131" s="24" t="n"/>
@@ -7015,35 +7015,39 @@
       <c r="A132" s="19" t="n"/>
       <c r="B132" s="20" t="n"/>
       <c r="C132" s="20" t="n"/>
-      <c r="D132" s="21" t="inlineStr">
-        <is>
-          <t>B6.9</t>
-        </is>
-      </c>
-      <c r="E132" s="22" t="inlineStr">
-        <is>
-          <t>Performance Management</t>
+      <c r="D132" s="19" t="inlineStr">
+        <is>
+          <t>B6.8</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងការងារ</t>
+          <t>បញ្ជីប្រាក់ខែ</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
         <is>
-          <t>/performance</t>
+          <t>/payroll</t>
         </is>
       </c>
       <c r="H132" s="19" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I132" s="20" t="inlineStr">
         <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="J132" s="20" t="n"/>
+          <t>Payroll approval</t>
+        </is>
+      </c>
+      <c r="J132" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័តប្រាក់ខែ</t>
+        </is>
+      </c>
       <c r="K132" s="24" t="n"/>
     </row>
     <row r="133" ht="21.6" customHeight="1">
@@ -7052,35 +7056,35 @@
       <c r="C133" s="20" t="n"/>
       <c r="D133" s="19" t="inlineStr">
         <is>
-          <t>B6.9</t>
+          <t>B6.8</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
         <is>
-          <t>Performance Management</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
         <is>
-          <t>ការគ្រប់គ្រងការងារ</t>
+          <t>បញ្ជីប្រាក់ខែ</t>
         </is>
       </c>
       <c r="G133" s="23" t="inlineStr">
         <is>
-          <t>/performance</t>
+          <t>/payroll</t>
         </is>
       </c>
       <c r="H133" s="19" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I133" s="20" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Payroll history</t>
         </is>
       </c>
       <c r="J133" s="20" t="inlineStr">
         <is>
-          <t>គោលដៅ</t>
+          <t>ប្រវត្តិប្រាក់ខែ</t>
         </is>
       </c>
       <c r="K133" s="24" t="n"/>
@@ -7089,12 +7093,12 @@
       <c r="A134" s="19" t="n"/>
       <c r="B134" s="20" t="n"/>
       <c r="C134" s="20" t="n"/>
-      <c r="D134" s="19" t="inlineStr">
+      <c r="D134" s="21" t="inlineStr">
         <is>
           <t>B6.9</t>
         </is>
       </c>
-      <c r="E134" s="20" t="inlineStr">
+      <c r="E134" s="22" t="inlineStr">
         <is>
           <t>Performance Management</t>
         </is>
@@ -7110,21 +7114,17 @@
         </is>
       </c>
       <c r="H134" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I134" s="20" t="inlineStr">
         <is>
-          <t>Performance review</t>
-        </is>
-      </c>
-      <c r="J134" s="20" t="inlineStr">
-        <is>
-          <t>ការវាយតម្លៃការងារ</t>
-        </is>
-      </c>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="J134" s="20" t="n"/>
       <c r="K134" s="24" t="n"/>
     </row>
-    <row r="135" ht="37.2" customHeight="1">
+    <row r="135" ht="21.6" customHeight="1">
       <c r="A135" s="19" t="n"/>
       <c r="B135" s="20" t="n"/>
       <c r="C135" s="20" t="n"/>
@@ -7149,16 +7149,16 @@
         </is>
       </c>
       <c r="H135" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I135" s="20" t="inlineStr">
         <is>
-          <t>Evaluation forms</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="J135" s="20" t="inlineStr">
         <is>
-          <t>ទម្រង់វាយតម្លៃ</t>
+          <t>គោលដៅ</t>
         </is>
       </c>
       <c r="K135" s="24" t="n"/>
@@ -7188,21 +7188,21 @@
         </is>
       </c>
       <c r="H136" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I136" s="20" t="inlineStr">
         <is>
-          <t>Employee self-assessment</t>
+          <t>Performance review</t>
         </is>
       </c>
       <c r="J136" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃខ្លួនឯង</t>
+          <t>ការវាយតម្លៃការងារ</t>
         </is>
       </c>
       <c r="K136" s="24" t="n"/>
     </row>
-    <row r="137" ht="21.6" customHeight="1">
+    <row r="137" ht="37.2" customHeight="1">
       <c r="A137" s="19" t="n"/>
       <c r="B137" s="20" t="n"/>
       <c r="C137" s="20" t="n"/>
@@ -7227,16 +7227,16 @@
         </is>
       </c>
       <c r="H137" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I137" s="20" t="inlineStr">
         <is>
-          <t>Manager assessment</t>
+          <t>Evaluation forms</t>
         </is>
       </c>
       <c r="J137" s="20" t="inlineStr">
         <is>
-          <t>ការវាយតម្លៃដោយអ្នកគ្រប់គ្រង</t>
+          <t>ទម្រង់វាយតម្លៃ</t>
         </is>
       </c>
       <c r="K137" s="24" t="n"/>
@@ -7266,16 +7266,16 @@
         </is>
       </c>
       <c r="H138" s="19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I138" s="20" t="inlineStr">
         <is>
-          <t>Performance score</t>
+          <t>Employee self-assessment</t>
         </is>
       </c>
       <c r="J138" s="20" t="inlineStr">
         <is>
-          <t>ពិន្ទុការងារ</t>
+          <t>ការវាយតម្លៃខ្លួនឯង</t>
         </is>
       </c>
       <c r="K138" s="24" t="n"/>
@@ -7305,16 +7305,16 @@
         </is>
       </c>
       <c r="H139" s="19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I139" s="20" t="inlineStr">
         <is>
-          <t>Promotion recommendation</t>
+          <t>Manager assessment</t>
         </is>
       </c>
       <c r="J139" s="20" t="inlineStr">
         <is>
-          <t>ការណែនាំដំឡើងតំណែង</t>
+          <t>ការវាយតម្លៃដោយអ្នកគ្រប់គ្រង</t>
         </is>
       </c>
       <c r="K139" s="24" t="n"/>
@@ -7323,66 +7323,76 @@
       <c r="A140" s="19" t="n"/>
       <c r="B140" s="20" t="n"/>
       <c r="C140" s="20" t="n"/>
-      <c r="D140" s="21" t="inlineStr">
-        <is>
-          <t>B6.10</t>
-        </is>
-      </c>
-      <c r="E140" s="22" t="inlineStr">
-        <is>
-          <t>Check in / Check out</t>
+      <c r="D140" s="19" t="inlineStr">
+        <is>
+          <t>B6.9</t>
+        </is>
+      </c>
+      <c r="E140" s="20" t="inlineStr">
+        <is>
+          <t>Performance Management</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>ការគ្រប់គ្រងការងារ</t>
         </is>
       </c>
       <c r="G140" s="23" t="inlineStr">
         <is>
-          <t>/my-check-in</t>
-        </is>
-      </c>
-      <c r="H140" s="19" t="n"/>
-      <c r="I140" s="20" t="n"/>
-      <c r="J140" s="20" t="n"/>
+          <t>/performance</t>
+        </is>
+      </c>
+      <c r="H140" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I140" s="20" t="inlineStr">
+        <is>
+          <t>Performance score</t>
+        </is>
+      </c>
+      <c r="J140" s="20" t="inlineStr">
+        <is>
+          <t>ពិន្ទុការងារ</t>
+        </is>
+      </c>
       <c r="K140" s="24" t="n"/>
     </row>
     <row r="141" ht="21.6" customHeight="1">
       <c r="A141" s="19" t="n"/>
       <c r="B141" s="20" t="n"/>
       <c r="C141" s="20" t="n"/>
-      <c r="D141" s="21" t="inlineStr">
-        <is>
-          <t>B6.11</t>
-        </is>
-      </c>
-      <c r="E141" s="22" t="inlineStr">
-        <is>
-          <t>Request Leave</t>
+      <c r="D141" s="19" t="inlineStr">
+        <is>
+          <t>B6.9</t>
+        </is>
+      </c>
+      <c r="E141" s="20" t="inlineStr">
+        <is>
+          <t>Performance Management</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
         <is>
-          <t>ស្នើសុំច្បាប់</t>
+          <t>ការគ្រប់គ្រងការងារ</t>
         </is>
       </c>
       <c r="G141" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests</t>
+          <t>/performance</t>
         </is>
       </c>
       <c r="H141" s="19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I141" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Promotion recommendation</t>
         </is>
       </c>
       <c r="J141" s="20" t="inlineStr">
         <is>
-          <t>កំពុងរង់ចាំ</t>
+          <t>ការណែនាំដំឡើងតំណែង</t>
         </is>
       </c>
       <c r="K141" s="24" t="n"/>
@@ -7391,51 +7401,41 @@
       <c r="A142" s="19" t="n"/>
       <c r="B142" s="20" t="n"/>
       <c r="C142" s="20" t="n"/>
-      <c r="D142" s="19" t="inlineStr">
-        <is>
-          <t>B6.11</t>
-        </is>
-      </c>
-      <c r="E142" s="20" t="inlineStr">
-        <is>
-          <t>Request Leave</t>
+      <c r="D142" s="21" t="inlineStr">
+        <is>
+          <t>B6.10</t>
+        </is>
+      </c>
+      <c r="E142" s="22" t="inlineStr">
+        <is>
+          <t>Check in / Check out</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>ស្នើសុំច្បាប់</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="G142" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H142" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I142" s="20" t="inlineStr">
-        <is>
-          <t>Approved to study</t>
-        </is>
-      </c>
-      <c r="J142" s="20" t="inlineStr">
-        <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
-        </is>
-      </c>
+          <t>/my-check-in</t>
+        </is>
+      </c>
+      <c r="H142" s="19" t="n"/>
+      <c r="I142" s="20" t="n"/>
+      <c r="J142" s="20" t="n"/>
       <c r="K142" s="24" t="n"/>
     </row>
     <row r="143" ht="21.6" customHeight="1">
       <c r="A143" s="19" t="n"/>
       <c r="B143" s="20" t="n"/>
       <c r="C143" s="20" t="n"/>
-      <c r="D143" s="19" t="inlineStr">
+      <c r="D143" s="21" t="inlineStr">
         <is>
           <t>B6.11</t>
         </is>
       </c>
-      <c r="E143" s="20" t="inlineStr">
+      <c r="E143" s="22" t="inlineStr">
         <is>
           <t>Request Leave</t>
         </is>
@@ -7451,16 +7451,16 @@
         </is>
       </c>
       <c r="H143" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I143" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J143" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="K143" s="24" t="n"/>
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H144" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I144" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J144" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K144" s="24" t="n"/>
@@ -7529,16 +7529,16 @@
         </is>
       </c>
       <c r="H145" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I145" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J145" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K145" s="24" t="n"/>
@@ -7547,70 +7547,76 @@
       <c r="A146" s="19" t="n"/>
       <c r="B146" s="20" t="n"/>
       <c r="C146" s="20" t="n"/>
-      <c r="D146" s="21" t="inlineStr">
-        <is>
-          <t>B6.12</t>
-        </is>
-      </c>
-      <c r="E146" s="22" t="inlineStr">
-        <is>
-          <t>Form</t>
+      <c r="D146" s="19" t="inlineStr">
+        <is>
+          <t>B6.11</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
         <is>
-          <t>ទម្រង់</t>
+          <t>ស្នើសុំច្បាប់</t>
         </is>
       </c>
       <c r="G146" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests?tab=resignation</t>
-        </is>
-      </c>
-      <c r="H146" s="19" t="n"/>
-      <c r="I146" s="20" t="n"/>
-      <c r="J146" s="20" t="n"/>
-      <c r="K146" s="24" t="inlineStr">
-        <is>
-          <t>Resignation form</t>
-        </is>
-      </c>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="H146" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I146" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="J146" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
+      <c r="K146" s="24" t="n"/>
     </row>
     <row r="147" ht="21.6" customHeight="1">
       <c r="A147" s="19" t="n"/>
       <c r="B147" s="20" t="n"/>
       <c r="C147" s="20" t="n"/>
-      <c r="D147" s="21" t="inlineStr">
-        <is>
-          <t>B6.13</t>
-        </is>
-      </c>
-      <c r="E147" s="22" t="inlineStr">
-        <is>
-          <t>Professional Development</t>
+      <c r="D147" s="19" t="inlineStr">
+        <is>
+          <t>B6.11</t>
+        </is>
+      </c>
+      <c r="E147" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
         <is>
-          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+          <t>ស្នើសុំច្បាប់</t>
         </is>
       </c>
       <c r="G147" s="23" t="inlineStr">
         <is>
-          <t>/professional-development</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H147" s="19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I147" s="20" t="inlineStr">
         <is>
-          <t>Training records</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="J147" s="20" t="inlineStr">
         <is>
-          <t>ប្រវត្តិវគ្គបណ្តុះបណ្តាល</t>
+          <t>បានលុបចោល</t>
         </is>
       </c>
       <c r="K147" s="24" t="n"/>
@@ -7621,38 +7627,32 @@
       <c r="C148" s="20" t="n"/>
       <c r="D148" s="21" t="inlineStr">
         <is>
-          <t>B6.13</t>
+          <t>B6.12</t>
         </is>
       </c>
       <c r="E148" s="22" t="inlineStr">
         <is>
-          <t>Professional Development</t>
+          <t>Form</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+          <t>ទម្រង់</t>
         </is>
       </c>
       <c r="G148" s="23" t="inlineStr">
         <is>
-          <t>/professional-development</t>
-        </is>
-      </c>
-      <c r="H148" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I148" s="20" t="inlineStr">
-        <is>
-          <t>Training calendar</t>
-        </is>
-      </c>
-      <c r="J148" s="20" t="inlineStr">
-        <is>
-          <t>ប្រតិទិនវគ្គបណ្តុះបណ្តាល</t>
-        </is>
-      </c>
-      <c r="K148" s="24" t="n"/>
+          <t>/approvals/my-requests?tab=resignation</t>
+        </is>
+      </c>
+      <c r="H148" s="19" t="n"/>
+      <c r="I148" s="20" t="n"/>
+      <c r="J148" s="20" t="n"/>
+      <c r="K148" s="24" t="inlineStr">
+        <is>
+          <t>Resignation form</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="21.6" customHeight="1">
       <c r="A149" s="19" t="n"/>
@@ -7679,16 +7679,16 @@
         </is>
       </c>
       <c r="H149" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I149" s="20" t="inlineStr">
         <is>
-          <t>Certificates</t>
+          <t>Training records</t>
         </is>
       </c>
       <c r="J149" s="20" t="inlineStr">
         <is>
-          <t>វិញ្ញាបនបត្រ</t>
+          <t>ប្រវត្តិវគ្គបណ្តុះបណ្តាល</t>
         </is>
       </c>
       <c r="K149" s="24" t="n"/>
@@ -7718,16 +7718,16 @@
         </is>
       </c>
       <c r="H150" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I150" s="20" t="inlineStr">
         <is>
-          <t>Classroom observation</t>
+          <t>Training calendar</t>
         </is>
       </c>
       <c r="J150" s="20" t="inlineStr">
         <is>
-          <t>ការសង្កេតការបង្រៀនក្នុងថ្នាក់</t>
+          <t>ប្រតិទិនវគ្គបណ្តុះបណ្តាល</t>
         </is>
       </c>
       <c r="K150" s="24" t="n"/>
@@ -7757,16 +7757,16 @@
         </is>
       </c>
       <c r="H151" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I151" s="20" t="inlineStr">
         <is>
-          <t>Coaching &amp; mentoring</t>
+          <t>Certificates</t>
         </is>
       </c>
       <c r="J151" s="20" t="inlineStr">
         <is>
-          <t>ការណែនាំ និងការជួយគាំទ្រ</t>
+          <t>វិញ្ញាបនបត្រ</t>
         </is>
       </c>
       <c r="K151" s="24" t="n"/>
@@ -7796,16 +7796,16 @@
         </is>
       </c>
       <c r="H152" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I152" s="20" t="inlineStr">
         <is>
-          <t>Development plan</t>
+          <t>Classroom observation</t>
         </is>
       </c>
       <c r="J152" s="20" t="inlineStr">
         <is>
-          <t>ផែនការអភិវឌ្ឍន៍</t>
+          <t>ការសង្កេតការបង្រៀនក្នុងថ្នាក់</t>
         </is>
       </c>
       <c r="K152" s="24" t="n"/>
@@ -7835,166 +7835,166 @@
         </is>
       </c>
       <c r="H153" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I153" s="20" t="inlineStr">
+        <is>
+          <t>Coaching &amp; mentoring</t>
+        </is>
+      </c>
+      <c r="J153" s="20" t="inlineStr">
+        <is>
+          <t>ការណែនាំ និងការជួយគាំទ្រ</t>
+        </is>
+      </c>
+      <c r="K153" s="24" t="n"/>
+    </row>
+    <row r="154" ht="21.6" customHeight="1">
+      <c r="A154" s="19" t="n"/>
+      <c r="B154" s="20" t="n"/>
+      <c r="C154" s="20" t="n"/>
+      <c r="D154" s="21" t="inlineStr">
+        <is>
+          <t>B6.13</t>
+        </is>
+      </c>
+      <c r="E154" s="22" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="F154" s="20" t="inlineStr">
+        <is>
+          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+        </is>
+      </c>
+      <c r="G154" s="23" t="inlineStr">
+        <is>
+          <t>/professional-development</t>
+        </is>
+      </c>
+      <c r="H154" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I154" s="20" t="inlineStr">
+        <is>
+          <t>Development plan</t>
+        </is>
+      </c>
+      <c r="J154" s="20" t="inlineStr">
+        <is>
+          <t>ផែនការអភិវឌ្ឍន៍</t>
+        </is>
+      </c>
+      <c r="K154" s="24" t="n"/>
+    </row>
+    <row r="155" ht="21.6" customHeight="1">
+      <c r="A155" s="19" t="n"/>
+      <c r="B155" s="20" t="n"/>
+      <c r="C155" s="20" t="n"/>
+      <c r="D155" s="21" t="inlineStr">
+        <is>
+          <t>B6.13</t>
+        </is>
+      </c>
+      <c r="E155" s="22" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+      <c r="F155" s="20" t="inlineStr">
+        <is>
+          <t>ការអភិវឌ្ឍវិជ្ជាជីវៈ</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="inlineStr">
+        <is>
+          <t>/professional-development</t>
+        </is>
+      </c>
+      <c r="H155" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="I153" s="20" t="inlineStr">
+      <c r="I155" s="20" t="inlineStr">
         <is>
           <t>Training reports</t>
         </is>
       </c>
-      <c r="J153" s="20" t="inlineStr">
+      <c r="J155" s="20" t="inlineStr">
         <is>
           <t>របាយការណ៍វគ្គបណ្តុះបណ្តាល</t>
         </is>
       </c>
-      <c r="K153" s="24" t="n"/>
-    </row>
-    <row r="154" ht="21.6" customHeight="1">
-      <c r="A154" s="1" t="inlineStr">
+      <c r="K155" s="24" t="n"/>
+    </row>
+    <row r="156" ht="21.6" customHeight="1">
+      <c r="A156" s="1" t="inlineStr">
         <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C156" s="3" t="inlineStr">
         <is>
           <t>វិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="D154" s="1" t="inlineStr">
+      <c r="D156" s="1" t="inlineStr">
         <is>
           <t>B7.1</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Billing Dashboard</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងវិក្កយបត្រ</t>
         </is>
       </c>
-      <c r="G154" s="4" t="inlineStr">
+      <c r="G156" s="4" t="inlineStr">
         <is>
           <t>/billing</t>
         </is>
       </c>
-      <c r="H154" s="5" t="n"/>
-      <c r="I154" s="3" t="n"/>
-      <c r="J154" s="3" t="n"/>
-      <c r="K154" s="6" t="n"/>
-    </row>
-    <row r="155" ht="21.6" customHeight="1">
-      <c r="A155" s="7" t="n"/>
-      <c r="B155" s="8" t="n"/>
-      <c r="C155" s="8" t="n"/>
-      <c r="D155" s="9" t="inlineStr">
-        <is>
-          <t>B7.2</t>
-        </is>
-      </c>
-      <c r="E155" s="10" t="inlineStr">
-        <is>
-          <t>Products</t>
-        </is>
-      </c>
-      <c r="F155" s="8" t="inlineStr">
-        <is>
-          <t>ផលិតផល</t>
-        </is>
-      </c>
-      <c r="G155" s="11" t="inlineStr">
-        <is>
-          <t>/products</t>
-        </is>
-      </c>
-      <c r="H155" s="7" t="n"/>
-      <c r="I155" s="8" t="n"/>
-      <c r="J155" s="8" t="n"/>
-      <c r="K155" s="12" t="n"/>
-    </row>
-    <row r="156" ht="21.6" customHeight="1">
-      <c r="A156" s="7" t="n"/>
-      <c r="B156" s="8" t="n"/>
-      <c r="C156" s="8" t="n"/>
-      <c r="D156" s="9" t="inlineStr">
-        <is>
-          <t>B7.3</t>
-        </is>
-      </c>
-      <c r="E156" s="10" t="inlineStr">
-        <is>
-          <t>Invoices</t>
-        </is>
-      </c>
-      <c r="F156" s="8" t="inlineStr">
-        <is>
-          <t>វិក្កយបត្រ</t>
-        </is>
-      </c>
-      <c r="G156" s="11" t="inlineStr">
-        <is>
-          <t>/invoices</t>
-        </is>
-      </c>
-      <c r="H156" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I156" s="8" t="inlineStr">
-        <is>
-          <t>Invoices</t>
-        </is>
-      </c>
-      <c r="J156" s="8" t="inlineStr">
-        <is>
-          <t>វិក្កយបត្រ</t>
-        </is>
-      </c>
-      <c r="K156" s="12" t="n"/>
+      <c r="H156" s="5" t="n"/>
+      <c r="I156" s="3" t="n"/>
+      <c r="J156" s="3" t="n"/>
+      <c r="K156" s="6" t="n"/>
     </row>
     <row r="157" ht="21.6" customHeight="1">
       <c r="A157" s="7" t="n"/>
       <c r="B157" s="8" t="n"/>
       <c r="C157" s="8" t="n"/>
-      <c r="D157" s="7" t="inlineStr">
-        <is>
-          <t>B7.3</t>
-        </is>
-      </c>
-      <c r="E157" s="8" t="inlineStr">
-        <is>
-          <t>Invoices</t>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>B7.2</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="inlineStr">
+        <is>
+          <t>Products</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
         <is>
-          <t>វិក្កយបត្រ</t>
+          <t>ផលិតផល</t>
         </is>
       </c>
       <c r="G157" s="11" t="inlineStr">
         <is>
-          <t>/invoices</t>
-        </is>
-      </c>
-      <c r="H157" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I157" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Invoice</t>
-        </is>
-      </c>
-      <c r="J157" s="8" t="inlineStr">
-        <is>
-          <t>វិក្កយបត្រប្រចាំខែ</t>
-        </is>
-      </c>
+          <t>/products</t>
+        </is>
+      </c>
+      <c r="H157" s="7" t="n"/>
+      <c r="I157" s="8" t="n"/>
+      <c r="J157" s="8" t="n"/>
       <c r="K157" s="12" t="n"/>
     </row>
     <row r="158" ht="21.6" customHeight="1">
@@ -8003,156 +8003,176 @@
       <c r="C158" s="8" t="n"/>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>B7.4</t>
+          <t>B7.3</t>
         </is>
       </c>
       <c r="E158" s="10" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Invoices</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
         <is>
-          <t>ការទូទាត់</t>
+          <t>វិក្កយបត្រ</t>
         </is>
       </c>
       <c r="G158" s="11" t="inlineStr">
         <is>
-          <t>/payments</t>
-        </is>
-      </c>
-      <c r="H158" s="7" t="n"/>
-      <c r="I158" s="8" t="n"/>
-      <c r="J158" s="8" t="n"/>
+          <t>/invoices</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" s="8" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="J158" s="8" t="inlineStr">
+        <is>
+          <t>វិក្កយបត្រ</t>
+        </is>
+      </c>
       <c r="K158" s="12" t="n"/>
     </row>
     <row r="159" ht="21.6" customHeight="1">
       <c r="A159" s="7" t="n"/>
       <c r="B159" s="8" t="n"/>
       <c r="C159" s="8" t="n"/>
-      <c r="D159" s="9" t="inlineStr">
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>B7.3</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="F159" s="8" t="inlineStr">
+        <is>
+          <t>វិក្កយបត្រ</t>
+        </is>
+      </c>
+      <c r="G159" s="11" t="inlineStr">
+        <is>
+          <t>/invoices</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I159" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Invoice</t>
+        </is>
+      </c>
+      <c r="J159" s="8" t="inlineStr">
+        <is>
+          <t>វិក្កយបត្រប្រចាំខែ</t>
+        </is>
+      </c>
+      <c r="K159" s="12" t="n"/>
+    </row>
+    <row r="160" ht="21.6" customHeight="1">
+      <c r="A160" s="7" t="n"/>
+      <c r="B160" s="8" t="n"/>
+      <c r="C160" s="8" t="n"/>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>B7.4</t>
+        </is>
+      </c>
+      <c r="E160" s="10" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>ការទូទាត់</t>
+        </is>
+      </c>
+      <c r="G160" s="11" t="inlineStr">
+        <is>
+          <t>/payments</t>
+        </is>
+      </c>
+      <c r="H160" s="7" t="n"/>
+      <c r="I160" s="8" t="n"/>
+      <c r="J160" s="8" t="n"/>
+      <c r="K160" s="12" t="n"/>
+    </row>
+    <row r="161" ht="21.6" customHeight="1">
+      <c r="A161" s="7" t="n"/>
+      <c r="B161" s="8" t="n"/>
+      <c r="C161" s="8" t="n"/>
+      <c r="D161" s="9" t="inlineStr">
         <is>
           <t>B7.5</t>
         </is>
       </c>
-      <c r="E159" s="10" t="inlineStr">
+      <c r="E161" s="10" t="inlineStr">
         <is>
           <t>Currency Rates</t>
         </is>
       </c>
-      <c r="F159" s="8" t="inlineStr">
+      <c r="F161" s="8" t="inlineStr">
         <is>
           <t>អត្រាប្តូរប្រាក់</t>
         </is>
       </c>
-      <c r="G159" s="11" t="inlineStr">
+      <c r="G161" s="11" t="inlineStr">
         <is>
           <t>/currency-rates</t>
         </is>
       </c>
-      <c r="H159" s="7" t="n"/>
-      <c r="I159" s="8" t="n"/>
-      <c r="J159" s="8" t="n"/>
-      <c r="K159" s="12" t="n"/>
-    </row>
-    <row r="160" ht="21.6" customHeight="1">
-      <c r="A160" s="13" t="inlineStr">
+      <c r="H161" s="7" t="n"/>
+      <c r="I161" s="8" t="n"/>
+      <c r="J161" s="8" t="n"/>
+      <c r="K161" s="12" t="n"/>
+    </row>
+    <row r="162" ht="21.6" customHeight="1">
+      <c r="A162" s="13" t="inlineStr">
         <is>
           <t>B8</t>
         </is>
       </c>
-      <c r="B160" s="14" t="inlineStr">
+      <c r="B162" s="14" t="inlineStr">
         <is>
           <t>Accounting</t>
         </is>
       </c>
-      <c r="C160" s="15" t="inlineStr">
+      <c r="C162" s="15" t="inlineStr">
         <is>
           <t>គណនេយ្យ</t>
         </is>
       </c>
-      <c r="D160" s="13" t="inlineStr">
+      <c r="D162" s="13" t="inlineStr">
         <is>
           <t>B8.1</t>
         </is>
       </c>
-      <c r="E160" s="14" t="inlineStr">
+      <c r="E162" s="14" t="inlineStr">
         <is>
           <t>Accounting Dashboard</t>
         </is>
       </c>
-      <c r="F160" s="15" t="inlineStr">
+      <c r="F162" s="15" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងគណនេយ្យ</t>
         </is>
       </c>
-      <c r="G160" s="16" t="inlineStr">
+      <c r="G162" s="16" t="inlineStr">
         <is>
           <t>/accounting</t>
         </is>
       </c>
-      <c r="H160" s="17" t="n"/>
-      <c r="I160" s="15" t="n"/>
-      <c r="J160" s="15" t="n"/>
-      <c r="K160" s="18" t="n"/>
-    </row>
-    <row r="161" ht="21.6" customHeight="1">
-      <c r="A161" s="19" t="n"/>
-      <c r="B161" s="20" t="n"/>
-      <c r="C161" s="20" t="n"/>
-      <c r="D161" s="21" t="inlineStr">
-        <is>
-          <t>B8.2</t>
-        </is>
-      </c>
-      <c r="E161" s="22" t="inlineStr">
-        <is>
-          <t>Chart of Accounts</t>
-        </is>
-      </c>
-      <c r="F161" s="20" t="inlineStr">
-        <is>
-          <t>តារាងគណនី</t>
-        </is>
-      </c>
-      <c r="G161" s="23" t="inlineStr">
-        <is>
-          <t>/accounts</t>
-        </is>
-      </c>
-      <c r="H161" s="19" t="n"/>
-      <c r="I161" s="20" t="n"/>
-      <c r="J161" s="20" t="n"/>
-      <c r="K161" s="24" t="n"/>
-    </row>
-    <row r="162" ht="21.6" customHeight="1">
-      <c r="A162" s="19" t="n"/>
-      <c r="B162" s="20" t="n"/>
-      <c r="C162" s="20" t="n"/>
-      <c r="D162" s="21" t="inlineStr">
-        <is>
-          <t>B8.3</t>
-        </is>
-      </c>
-      <c r="E162" s="22" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="F162" s="20" t="inlineStr">
-        <is>
-          <t>ចំណូល</t>
-        </is>
-      </c>
-      <c r="G162" s="23" t="inlineStr">
-        <is>
-          <t>/income</t>
-        </is>
-      </c>
-      <c r="H162" s="19" t="n"/>
-      <c r="I162" s="20" t="n"/>
-      <c r="J162" s="20" t="n"/>
-      <c r="K162" s="24" t="n"/>
+      <c r="H162" s="17" t="n"/>
+      <c r="I162" s="15" t="n"/>
+      <c r="J162" s="15" t="n"/>
+      <c r="K162" s="18" t="n"/>
     </row>
     <row r="163" ht="21.6" customHeight="1">
       <c r="A163" s="19" t="n"/>
@@ -8160,22 +8180,22 @@
       <c r="C163" s="20" t="n"/>
       <c r="D163" s="21" t="inlineStr">
         <is>
-          <t>B8.4</t>
+          <t>B8.2</t>
         </is>
       </c>
       <c r="E163" s="22" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Chart of Accounts</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
         <is>
-          <t>ចំណាយ</t>
+          <t>តារាងគណនី</t>
         </is>
       </c>
       <c r="G163" s="23" t="inlineStr">
         <is>
-          <t>/expenses</t>
+          <t>/accounts</t>
         </is>
       </c>
       <c r="H163" s="19" t="n"/>
@@ -8189,22 +8209,22 @@
       <c r="C164" s="20" t="n"/>
       <c r="D164" s="21" t="inlineStr">
         <is>
-          <t>B8.5</t>
+          <t>B8.3</t>
         </is>
       </c>
       <c r="E164" s="22" t="inlineStr">
         <is>
-          <t>Transactions</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិបត្តិការ</t>
+          <t>ចំណូល</t>
         </is>
       </c>
       <c r="G164" s="23" t="inlineStr">
         <is>
-          <t>/transactions</t>
+          <t>/income</t>
         </is>
       </c>
       <c r="H164" s="19" t="n"/>
@@ -8218,88 +8238,68 @@
       <c r="C165" s="20" t="n"/>
       <c r="D165" s="21" t="inlineStr">
         <is>
-          <t>B8.6</t>
+          <t>B8.4</t>
         </is>
       </c>
       <c r="E165" s="22" t="inlineStr">
         <is>
-          <t>Financial Reports</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+          <t>ចំណាយ</t>
         </is>
       </c>
       <c r="G165" s="23" t="inlineStr">
         <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H165" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I165" s="20" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="J165" s="20" t="inlineStr">
-        <is>
-          <t>ចំណូល</t>
-        </is>
-      </c>
+          <t>/expenses</t>
+        </is>
+      </c>
+      <c r="H165" s="19" t="n"/>
+      <c r="I165" s="20" t="n"/>
+      <c r="J165" s="20" t="n"/>
       <c r="K165" s="24" t="n"/>
     </row>
     <row r="166" ht="21.6" customHeight="1">
       <c r="A166" s="19" t="n"/>
       <c r="B166" s="20" t="n"/>
       <c r="C166" s="20" t="n"/>
-      <c r="D166" s="19" t="inlineStr">
-        <is>
-          <t>B8.6</t>
-        </is>
-      </c>
-      <c r="E166" s="20" t="inlineStr">
-        <is>
-          <t>Financial Reports</t>
+      <c r="D166" s="21" t="inlineStr">
+        <is>
+          <t>B8.5</t>
+        </is>
+      </c>
+      <c r="E166" s="22" t="inlineStr">
+        <is>
+          <t>Transactions</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+          <t>ប្រតិបត្តិការ</t>
         </is>
       </c>
       <c r="G166" s="23" t="inlineStr">
         <is>
-          <t>/accounting-reports</t>
-        </is>
-      </c>
-      <c r="H166" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I166" s="20" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="J166" s="20" t="inlineStr">
-        <is>
-          <t>ចំណាយ</t>
-        </is>
-      </c>
+          <t>/transactions</t>
+        </is>
+      </c>
+      <c r="H166" s="19" t="n"/>
+      <c r="I166" s="20" t="n"/>
+      <c r="J166" s="20" t="n"/>
       <c r="K166" s="24" t="n"/>
     </row>
     <row r="167" ht="21.6" customHeight="1">
       <c r="A167" s="19" t="n"/>
       <c r="B167" s="20" t="n"/>
       <c r="C167" s="20" t="n"/>
-      <c r="D167" s="19" t="inlineStr">
+      <c r="D167" s="21" t="inlineStr">
         <is>
           <t>B8.6</t>
         </is>
       </c>
-      <c r="E167" s="20" t="inlineStr">
+      <c r="E167" s="22" t="inlineStr">
         <is>
           <t>Financial Reports</t>
         </is>
@@ -8315,16 +8315,16 @@
         </is>
       </c>
       <c r="H167" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I167" s="20" t="inlineStr">
         <is>
-          <t>Profit &amp; Loss</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="J167" s="20" t="inlineStr">
         <is>
-          <t>ប្រាក់ចំណេញ និងខាត</t>
+          <t>ចំណូល</t>
         </is>
       </c>
       <c r="K167" s="24" t="n"/>
@@ -8354,153 +8354,149 @@
         </is>
       </c>
       <c r="H168" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I168" s="20" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="J168" s="20" t="inlineStr">
+        <is>
+          <t>ចំណាយ</t>
+        </is>
+      </c>
+      <c r="K168" s="24" t="n"/>
+    </row>
+    <row r="169" ht="21.6" customHeight="1">
+      <c r="A169" s="19" t="n"/>
+      <c r="B169" s="20" t="n"/>
+      <c r="C169" s="20" t="n"/>
+      <c r="D169" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E169" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F169" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H169" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I169" s="20" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss</t>
+        </is>
+      </c>
+      <c r="J169" s="20" t="inlineStr">
+        <is>
+          <t>ប្រាក់ចំណេញ និងខាត</t>
+        </is>
+      </c>
+      <c r="K169" s="24" t="n"/>
+    </row>
+    <row r="170" ht="21.6" customHeight="1">
+      <c r="A170" s="19" t="n"/>
+      <c r="B170" s="20" t="n"/>
+      <c r="C170" s="20" t="n"/>
+      <c r="D170" s="19" t="inlineStr">
+        <is>
+          <t>B8.6</t>
+        </is>
+      </c>
+      <c r="E170" s="20" t="inlineStr">
+        <is>
+          <t>Financial Reports</t>
+        </is>
+      </c>
+      <c r="F170" s="20" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ហិរញ្ញវត្ថុ</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="inlineStr">
+        <is>
+          <t>/accounting-reports</t>
+        </is>
+      </c>
+      <c r="H170" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="I168" s="20" t="inlineStr">
+      <c r="I170" s="20" t="inlineStr">
         <is>
           <t>Cash Flow</t>
         </is>
       </c>
-      <c r="J168" s="20" t="inlineStr">
+      <c r="J170" s="20" t="inlineStr">
         <is>
           <t>លំហូរសាច់ប្រាក់</t>
         </is>
       </c>
-      <c r="K168" s="24" t="n"/>
-    </row>
-    <row r="169" ht="21.6" customHeight="1">
-      <c r="A169" s="1" t="inlineStr">
+      <c r="K170" s="24" t="n"/>
+    </row>
+    <row r="171" ht="21.6" customHeight="1">
+      <c r="A171" s="1" t="inlineStr">
         <is>
           <t>B9</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
-      <c r="C169" s="3" t="inlineStr">
+      <c r="C171" s="3" t="inlineStr">
         <is>
           <t>ទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="D169" s="1" t="inlineStr">
+      <c r="D171" s="1" t="inlineStr">
         <is>
           <t>B9.1</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Asset Dashboard</t>
         </is>
       </c>
-      <c r="F169" s="3" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr">
         <is>
           <t>ផ្ទាំងគ្រប់គ្រងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
-      <c r="G169" s="4" t="inlineStr">
+      <c r="G171" s="4" t="inlineStr">
         <is>
           <t>/assets/dashboard</t>
         </is>
       </c>
-      <c r="H169" s="5" t="n"/>
-      <c r="I169" s="3" t="n"/>
-      <c r="J169" s="3" t="n"/>
-      <c r="K169" s="6" t="n"/>
-    </row>
-    <row r="170" ht="21.6" customHeight="1">
-      <c r="A170" s="7" t="n"/>
-      <c r="B170" s="8" t="n"/>
-      <c r="C170" s="8" t="n"/>
-      <c r="D170" s="9" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E170" s="10" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F170" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G170" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H170" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I170" s="8" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="J170" s="8" t="inlineStr">
-        <is>
-          <t>ទិដ្ឋភាពទូទៅ</t>
-        </is>
-      </c>
-      <c r="K170" s="12" t="inlineStr">
-        <is>
-          <t>Tabs on one asset</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="21.6" customHeight="1">
-      <c r="A171" s="7" t="n"/>
-      <c r="B171" s="8" t="n"/>
-      <c r="C171" s="8" t="n"/>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>B9.2</t>
-        </is>
-      </c>
-      <c r="E171" s="8" t="inlineStr">
-        <is>
-          <t>All Assets</t>
-        </is>
-      </c>
-      <c r="F171" s="8" t="inlineStr">
-        <is>
-          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
-        </is>
-      </c>
-      <c r="G171" s="11" t="inlineStr">
-        <is>
-          <t>/assets</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I171" s="8" t="inlineStr">
-        <is>
-          <t>Assignment</t>
-        </is>
-      </c>
-      <c r="J171" s="8" t="inlineStr">
-        <is>
-          <t>ការចាត់ចែង</t>
-        </is>
-      </c>
-      <c r="K171" s="12" t="n"/>
+      <c r="H171" s="5" t="n"/>
+      <c r="I171" s="3" t="n"/>
+      <c r="J171" s="3" t="n"/>
+      <c r="K171" s="6" t="n"/>
     </row>
     <row r="172" ht="21.6" customHeight="1">
       <c r="A172" s="7" t="n"/>
       <c r="B172" s="8" t="n"/>
       <c r="C172" s="8" t="n"/>
-      <c r="D172" s="7" t="inlineStr">
+      <c r="D172" s="9" t="inlineStr">
         <is>
           <t>B9.2</t>
         </is>
       </c>
-      <c r="E172" s="8" t="inlineStr">
+      <c r="E172" s="10" t="inlineStr">
         <is>
           <t>All Assets</t>
         </is>
@@ -8516,19 +8512,23 @@
         </is>
       </c>
       <c r="H172" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>Transfers</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="J172" s="8" t="inlineStr">
         <is>
-          <t>ការផ្ទេរ</t>
-        </is>
-      </c>
-      <c r="K172" s="12" t="n"/>
+          <t>ទិដ្ឋភាពទូទៅ</t>
+        </is>
+      </c>
+      <c r="K172" s="12" t="inlineStr">
+        <is>
+          <t>Tabs on one asset</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="21.6" customHeight="1">
       <c r="A173" s="7" t="n"/>
@@ -8555,16 +8555,16 @@
         </is>
       </c>
       <c r="H173" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I173" s="8" t="inlineStr">
         <is>
-          <t>Issues</t>
+          <t>Assignment</t>
         </is>
       </c>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>បញ្ហា</t>
+          <t>ការចាត់ចែង</t>
         </is>
       </c>
       <c r="K173" s="12" t="n"/>
@@ -8594,16 +8594,16 @@
         </is>
       </c>
       <c r="H174" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I174" s="8" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Transfers</t>
         </is>
       </c>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>ការផ្ទេរ</t>
         </is>
       </c>
       <c r="K174" s="12" t="n"/>
@@ -8633,16 +8633,16 @@
         </is>
       </c>
       <c r="H175" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I175" s="8" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>បញ្ហា</t>
         </is>
       </c>
       <c r="K175" s="12" t="n"/>
@@ -8651,58 +8651,78 @@
       <c r="A176" s="7" t="n"/>
       <c r="B176" s="8" t="n"/>
       <c r="C176" s="8" t="n"/>
-      <c r="D176" s="9" t="inlineStr">
-        <is>
-          <t>B9.3</t>
-        </is>
-      </c>
-      <c r="E176" s="10" t="inlineStr">
-        <is>
-          <t>My Assets</t>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E176" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G176" s="11" t="inlineStr">
         <is>
-          <t>/my-assets</t>
-        </is>
-      </c>
-      <c r="H176" s="7" t="n"/>
-      <c r="I176" s="8" t="n"/>
-      <c r="J176" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H176" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I176" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="J176" s="8" t="inlineStr">
+        <is>
+          <t>ការជួសជុល</t>
+        </is>
+      </c>
       <c r="K176" s="12" t="n"/>
     </row>
     <row r="177" ht="21.6" customHeight="1">
       <c r="A177" s="7" t="n"/>
       <c r="B177" s="8" t="n"/>
       <c r="C177" s="8" t="n"/>
-      <c r="D177" s="9" t="inlineStr">
-        <is>
-          <t>B9.4</t>
-        </is>
-      </c>
-      <c r="E177" s="10" t="inlineStr">
-        <is>
-          <t>Issues</t>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>B9.2</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>All Assets</t>
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr">
         <is>
-          <t>បញ្ហា</t>
+          <t>ទ្រព្យសម្បត្តិទាំងអស់</t>
         </is>
       </c>
       <c r="G177" s="11" t="inlineStr">
         <is>
-          <t>/asset-issues</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="n"/>
-      <c r="I177" s="8" t="n"/>
-      <c r="J177" s="8" t="n"/>
+          <t>/assets</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I177" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="J177" s="8" t="inlineStr">
+        <is>
+          <t>ការថែទាំ</t>
+        </is>
+      </c>
       <c r="K177" s="12" t="n"/>
     </row>
     <row r="178" ht="21.6" customHeight="1">
@@ -8711,22 +8731,22 @@
       <c r="C178" s="8" t="n"/>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>B9.5</t>
+          <t>B9.3</t>
         </is>
       </c>
       <c r="E178" s="10" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>My Assets</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>ទ្រព្យសម្បត្តិរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G178" s="11" t="inlineStr">
         <is>
-          <t>/asset-repairs</t>
+          <t>/my-assets</t>
         </is>
       </c>
       <c r="H178" s="7" t="n"/>
@@ -8740,22 +8760,22 @@
       <c r="C179" s="8" t="n"/>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>B9.6</t>
+          <t>B9.4</t>
         </is>
       </c>
       <c r="E179" s="10" t="inlineStr">
         <is>
-          <t>Repair Shops</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr">
         <is>
-          <t>ហាងជួសជុល</t>
+          <t>បញ្ហា</t>
         </is>
       </c>
       <c r="G179" s="11" t="inlineStr">
         <is>
-          <t>/repair-shops</t>
+          <t>/asset-issues</t>
         </is>
       </c>
       <c r="H179" s="7" t="n"/>
@@ -8769,22 +8789,22 @@
       <c r="C180" s="8" t="n"/>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>B9.7</t>
+          <t>B9.5</t>
         </is>
       </c>
       <c r="E180" s="10" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="G180" s="11" t="inlineStr">
         <is>
-          <t>/asset-maintenance</t>
+          <t>/asset-repairs</t>
         </is>
       </c>
       <c r="H180" s="7" t="n"/>
@@ -8798,22 +8818,22 @@
       <c r="C181" s="8" t="n"/>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>B9.8</t>
+          <t>B9.6</t>
         </is>
       </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
-          <t>Asset Categories</t>
+          <t>Repair Shops</t>
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr">
         <is>
-          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
+          <t>ហាងជួសជុល</t>
         </is>
       </c>
       <c r="G181" s="11" t="inlineStr">
         <is>
-          <t>/asset-categories</t>
+          <t>/repair-shops</t>
         </is>
       </c>
       <c r="H181" s="7" t="n"/>
@@ -8827,22 +8847,22 @@
       <c r="C182" s="8" t="n"/>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>B9.9</t>
+          <t>B9.7</t>
         </is>
       </c>
       <c r="E182" s="10" t="inlineStr">
         <is>
-          <t>Asset Locations</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
+          <t>ការថែទាំ</t>
         </is>
       </c>
       <c r="G182" s="11" t="inlineStr">
         <is>
-          <t>/asset-locations</t>
+          <t>/asset-maintenance</t>
         </is>
       </c>
       <c r="H182" s="7" t="n"/>
@@ -8856,22 +8876,22 @@
       <c r="C183" s="8" t="n"/>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>B9.10</t>
+          <t>B9.8</t>
         </is>
       </c>
       <c r="E183" s="10" t="inlineStr">
         <is>
-          <t>Departments</t>
+          <t>Asset Categories</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>ប្រភេទទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G183" s="11" t="inlineStr">
         <is>
-          <t>/departments</t>
+          <t>/asset-categories</t>
         </is>
       </c>
       <c r="H183" s="7" t="n"/>
@@ -8885,22 +8905,22 @@
       <c r="C184" s="8" t="n"/>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>B9.11</t>
+          <t>B9.9</t>
         </is>
       </c>
       <c r="E184" s="10" t="inlineStr">
         <is>
-          <t>Suppliers</t>
+          <t>Asset Locations</t>
         </is>
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>អ្នកផ្គត់ផ្គង់</t>
+          <t>ទីតាំងទ្រព្យសម្បត្តិ</t>
         </is>
       </c>
       <c r="G184" s="11" t="inlineStr">
         <is>
-          <t>/suppliers</t>
+          <t>/asset-locations</t>
         </is>
       </c>
       <c r="H184" s="7" t="n"/>
@@ -8914,88 +8934,68 @@
       <c r="C185" s="8" t="n"/>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>B9.12</t>
+          <t>B9.10</t>
         </is>
       </c>
       <c r="E185" s="10" t="inlineStr">
         <is>
-          <t>Asset Reports</t>
+          <t>Departments</t>
         </is>
       </c>
       <c r="F185" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="G185" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H185" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I185" s="8" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="J185" s="8" t="inlineStr">
-        <is>
-          <t>ស្តុក</t>
-        </is>
-      </c>
+          <t>/departments</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="n"/>
+      <c r="I185" s="8" t="n"/>
+      <c r="J185" s="8" t="n"/>
       <c r="K185" s="12" t="n"/>
     </row>
     <row r="186" ht="21.6" customHeight="1">
       <c r="A186" s="7" t="n"/>
       <c r="B186" s="8" t="n"/>
       <c r="C186" s="8" t="n"/>
-      <c r="D186" s="7" t="inlineStr">
-        <is>
-          <t>B9.12</t>
-        </is>
-      </c>
-      <c r="E186" s="8" t="inlineStr">
-        <is>
-          <t>Asset Reports</t>
+      <c r="D186" s="9" t="inlineStr">
+        <is>
+          <t>B9.11</t>
+        </is>
+      </c>
+      <c r="E186" s="10" t="inlineStr">
+        <is>
+          <t>Suppliers</t>
         </is>
       </c>
       <c r="F186" s="8" t="inlineStr">
         <is>
-          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+          <t>អ្នកផ្គត់ផ្គង់</t>
         </is>
       </c>
       <c r="G186" s="11" t="inlineStr">
         <is>
-          <t>/asset-reports</t>
-        </is>
-      </c>
-      <c r="H186" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I186" s="8" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="J186" s="8" t="inlineStr">
-        <is>
-          <t>ស្ថានភាព</t>
-        </is>
-      </c>
+          <t>/suppliers</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="n"/>
+      <c r="I186" s="8" t="n"/>
+      <c r="J186" s="8" t="n"/>
       <c r="K186" s="12" t="n"/>
     </row>
     <row r="187" ht="21.6" customHeight="1">
       <c r="A187" s="7" t="n"/>
       <c r="B187" s="8" t="n"/>
       <c r="C187" s="8" t="n"/>
-      <c r="D187" s="7" t="inlineStr">
+      <c r="D187" s="9" t="inlineStr">
         <is>
           <t>B9.12</t>
         </is>
       </c>
-      <c r="E187" s="8" t="inlineStr">
+      <c r="E187" s="10" t="inlineStr">
         <is>
           <t>Asset Reports</t>
         </is>
@@ -9011,16 +9011,16 @@
         </is>
       </c>
       <c r="H187" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I187" s="8" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>ការជួសជុល</t>
+          <t>ស្តុក</t>
         </is>
       </c>
       <c r="K187" s="12" t="n"/>
@@ -9050,16 +9050,16 @@
         </is>
       </c>
       <c r="H188" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I188" s="8" t="inlineStr">
         <is>
-          <t>Repair Cost</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>ថ្លៃជួសជុល</t>
+          <t>ស្ថានភាព</t>
         </is>
       </c>
       <c r="K188" s="12" t="n"/>
@@ -9089,16 +9089,16 @@
         </is>
       </c>
       <c r="H189" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I189" s="8" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>ការថែទាំ</t>
+          <t>ការជួសជុល</t>
         </is>
       </c>
       <c r="K189" s="12" t="n"/>
@@ -9128,16 +9128,16 @@
         </is>
       </c>
       <c r="H190" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I190" s="8" t="inlineStr">
         <is>
-          <t>Assignments</t>
+          <t>Repair Cost</t>
         </is>
       </c>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>ការចាត់ចែង</t>
+          <t>ថ្លៃជួសជុល</t>
         </is>
       </c>
       <c r="K190" s="12" t="n"/>
@@ -9167,266 +9167,286 @@
         </is>
       </c>
       <c r="H191" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I191" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="J191" s="8" t="inlineStr">
+        <is>
+          <t>ការថែទាំ</t>
+        </is>
+      </c>
+      <c r="K191" s="12" t="n"/>
+    </row>
+    <row r="192" ht="21.6" customHeight="1">
+      <c r="A192" s="7" t="n"/>
+      <c r="B192" s="8" t="n"/>
+      <c r="C192" s="8" t="n"/>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E192" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F192" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G192" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H192" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I192" s="8" t="inlineStr">
+        <is>
+          <t>Assignments</t>
+        </is>
+      </c>
+      <c r="J192" s="8" t="inlineStr">
+        <is>
+          <t>ការចាត់ចែង</t>
+        </is>
+      </c>
+      <c r="K192" s="12" t="n"/>
+    </row>
+    <row r="193" ht="21.6" customHeight="1">
+      <c r="A193" s="7" t="n"/>
+      <c r="B193" s="8" t="n"/>
+      <c r="C193" s="8" t="n"/>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>B9.12</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>Asset Reports</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>របាយការណ៍ទ្រព្យសម្បត្តិ</t>
+        </is>
+      </c>
+      <c r="G193" s="11" t="inlineStr">
+        <is>
+          <t>/asset-reports</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="I191" s="8" t="inlineStr">
+      <c r="I193" s="8" t="inlineStr">
         <is>
           <t>History</t>
         </is>
       </c>
-      <c r="J191" s="8" t="inlineStr">
+      <c r="J193" s="8" t="inlineStr">
         <is>
           <t>ប្រវត្តិ</t>
         </is>
       </c>
-      <c r="K191" s="12" t="n"/>
-    </row>
-    <row r="192" ht="21.6" customHeight="1">
-      <c r="A192" s="13" t="inlineStr">
+      <c r="K193" s="12" t="n"/>
+    </row>
+    <row r="194" ht="21.6" customHeight="1">
+      <c r="A194" s="13" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="B192" s="14" t="inlineStr">
+      <c r="B194" s="14" t="inlineStr">
         <is>
           <t>Communication</t>
         </is>
       </c>
-      <c r="C192" s="15" t="inlineStr">
+      <c r="C194" s="15" t="inlineStr">
         <is>
           <t>ការទំនាក់ទំនង</t>
         </is>
       </c>
-      <c r="D192" s="13" t="inlineStr">
+      <c r="D194" s="13" t="inlineStr">
         <is>
           <t>B10.1</t>
         </is>
       </c>
-      <c r="E192" s="14" t="inlineStr">
+      <c r="E194" s="14" t="inlineStr">
         <is>
           <t>Contact Messages</t>
         </is>
       </c>
-      <c r="F192" s="15" t="inlineStr">
+      <c r="F194" s="15" t="inlineStr">
         <is>
           <t>សារទំនាក់ទំនង</t>
         </is>
       </c>
-      <c r="G192" s="16" t="inlineStr">
+      <c r="G194" s="16" t="inlineStr">
         <is>
           <t>/contact-messages</t>
         </is>
       </c>
-      <c r="H192" s="17" t="n"/>
-      <c r="I192" s="15" t="n"/>
-      <c r="J192" s="15" t="n"/>
-      <c r="K192" s="18" t="n"/>
-    </row>
-    <row r="193" ht="21.6" customHeight="1">
-      <c r="A193" s="19" t="n"/>
-      <c r="B193" s="20" t="n"/>
-      <c r="C193" s="20" t="n"/>
-      <c r="D193" s="21" t="inlineStr">
-        <is>
-          <t>B10.2</t>
-        </is>
-      </c>
-      <c r="E193" s="22" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="F193" s="20" t="inlineStr">
-        <is>
-          <t>ការជូនដំណឹង</t>
-        </is>
-      </c>
-      <c r="G193" s="23" t="inlineStr">
-        <is>
-          <t>/notifications</t>
-        </is>
-      </c>
-      <c r="H193" s="19" t="n"/>
-      <c r="I193" s="20" t="n"/>
-      <c r="J193" s="20" t="n"/>
-      <c r="K193" s="24" t="n"/>
-    </row>
-    <row r="194" ht="21.6" customHeight="1">
-      <c r="A194" s="19" t="n"/>
-      <c r="B194" s="20" t="n"/>
-      <c r="C194" s="20" t="n"/>
-      <c r="D194" s="21" t="inlineStr">
-        <is>
-          <t>B10.3</t>
-        </is>
-      </c>
-      <c r="E194" s="22" t="inlineStr">
-        <is>
-          <t>Student Feedback</t>
-        </is>
-      </c>
-      <c r="F194" s="20" t="inlineStr">
-        <is>
-          <t>មតិកែលម្អសិស្ស</t>
-        </is>
-      </c>
-      <c r="G194" s="23" t="inlineStr">
-        <is>
-          <t>/student-feedback</t>
-        </is>
-      </c>
-      <c r="H194" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I194" s="20" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J194" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងបើក</t>
-        </is>
-      </c>
-      <c r="K194" s="24" t="n"/>
+      <c r="H194" s="17" t="n"/>
+      <c r="I194" s="15" t="n"/>
+      <c r="J194" s="15" t="n"/>
+      <c r="K194" s="18" t="n"/>
     </row>
     <row r="195" ht="21.6" customHeight="1">
       <c r="A195" s="19" t="n"/>
       <c r="B195" s="20" t="n"/>
       <c r="C195" s="20" t="n"/>
-      <c r="D195" s="19" t="inlineStr">
+      <c r="D195" s="21" t="inlineStr">
+        <is>
+          <t>B10.2</t>
+        </is>
+      </c>
+      <c r="E195" s="22" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="F195" s="20" t="inlineStr">
+        <is>
+          <t>ការជូនដំណឹង</t>
+        </is>
+      </c>
+      <c r="G195" s="23" t="inlineStr">
+        <is>
+          <t>/notifications</t>
+        </is>
+      </c>
+      <c r="H195" s="19" t="n"/>
+      <c r="I195" s="20" t="n"/>
+      <c r="J195" s="20" t="n"/>
+      <c r="K195" s="24" t="n"/>
+    </row>
+    <row r="196" ht="21.6" customHeight="1">
+      <c r="A196" s="19" t="n"/>
+      <c r="B196" s="20" t="n"/>
+      <c r="C196" s="20" t="n"/>
+      <c r="D196" s="21" t="inlineStr">
         <is>
           <t>B10.3</t>
         </is>
       </c>
-      <c r="E195" s="20" t="inlineStr">
+      <c r="E196" s="22" t="inlineStr">
         <is>
           <t>Student Feedback</t>
         </is>
       </c>
-      <c r="F195" s="20" t="inlineStr">
+      <c r="F196" s="20" t="inlineStr">
         <is>
           <t>មតិកែលម្អសិស្ស</t>
         </is>
       </c>
-      <c r="G195" s="23" t="inlineStr">
+      <c r="G196" s="23" t="inlineStr">
         <is>
           <t>/student-feedback</t>
         </is>
       </c>
-      <c r="H195" s="19" t="n">
+      <c r="H196" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J196" s="20" t="inlineStr">
+        <is>
+          <t>កំពុងបើក</t>
+        </is>
+      </c>
+      <c r="K196" s="24" t="n"/>
+    </row>
+    <row r="197" ht="21.6" customHeight="1">
+      <c r="A197" s="19" t="n"/>
+      <c r="B197" s="20" t="n"/>
+      <c r="C197" s="20" t="n"/>
+      <c r="D197" s="19" t="inlineStr">
+        <is>
+          <t>B10.3</t>
+        </is>
+      </c>
+      <c r="E197" s="20" t="inlineStr">
+        <is>
+          <t>Student Feedback</t>
+        </is>
+      </c>
+      <c r="F197" s="20" t="inlineStr">
+        <is>
+          <t>មតិកែលម្អសិស្ស</t>
+        </is>
+      </c>
+      <c r="G197" s="23" t="inlineStr">
+        <is>
+          <t>/student-feedback</t>
+        </is>
+      </c>
+      <c r="H197" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="I195" s="20" t="inlineStr">
+      <c r="I197" s="20" t="inlineStr">
         <is>
           <t>Replied</t>
         </is>
       </c>
-      <c r="J195" s="20" t="inlineStr">
+      <c r="J197" s="20" t="inlineStr">
         <is>
           <t>បានឆ្លើយតប</t>
         </is>
       </c>
-      <c r="K195" s="24" t="n"/>
-    </row>
-    <row r="196" ht="21.6" customHeight="1">
-      <c r="A196" s="1" t="inlineStr">
+      <c r="K197" s="24" t="n"/>
+    </row>
+    <row r="198" ht="21.6" customHeight="1">
+      <c r="A198" s="1" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C196" s="3" t="inlineStr">
+      <c r="C198" s="3" t="inlineStr">
         <is>
           <t>ការកំណត់</t>
         </is>
       </c>
-      <c r="D196" s="1" t="inlineStr">
+      <c r="D198" s="1" t="inlineStr">
         <is>
           <t>B11.1</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="F196" s="3" t="inlineStr">
+      <c r="F198" s="3" t="inlineStr">
         <is>
           <t>ឯកសារ</t>
         </is>
       </c>
-      <c r="G196" s="4" t="inlineStr">
+      <c r="G198" s="4" t="inlineStr">
         <is>
           <t>/school-documents</t>
         </is>
       </c>
-      <c r="H196" s="5" t="n"/>
-      <c r="I196" s="3" t="n"/>
-      <c r="J196" s="3" t="n"/>
-      <c r="K196" s="6" t="n"/>
-    </row>
-    <row r="197" ht="21.6" customHeight="1">
-      <c r="A197" s="7" t="n"/>
-      <c r="B197" s="8" t="n"/>
-      <c r="C197" s="8" t="n"/>
-      <c r="D197" s="9" t="inlineStr">
-        <is>
-          <t>B11.2</t>
-        </is>
-      </c>
-      <c r="E197" s="10" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F197" s="8" t="inlineStr">
-        <is>
-          <t>ទូទៅ</t>
-        </is>
-      </c>
-      <c r="G197" s="11" t="inlineStr">
-        <is>
-          <t>/settings</t>
-        </is>
-      </c>
-      <c r="H197" s="7" t="n"/>
-      <c r="I197" s="8" t="n"/>
-      <c r="J197" s="8" t="n"/>
-      <c r="K197" s="12" t="n"/>
-    </row>
-    <row r="198" ht="21.6" customHeight="1">
-      <c r="A198" s="7" t="n"/>
-      <c r="B198" s="8" t="n"/>
-      <c r="C198" s="8" t="n"/>
-      <c r="D198" s="9" t="inlineStr">
-        <is>
-          <t>B11.3</t>
-        </is>
-      </c>
-      <c r="E198" s="10" t="inlineStr">
-        <is>
-          <t>Telegram notifications</t>
-        </is>
-      </c>
-      <c r="F198" s="8" t="inlineStr">
-        <is>
-          <t>ការជូនដំណឹង Telegram</t>
-        </is>
-      </c>
-      <c r="G198" s="11" t="inlineStr">
-        <is>
-          <t>/telegram-notifications</t>
-        </is>
-      </c>
-      <c r="H198" s="7" t="n"/>
-      <c r="I198" s="8" t="n"/>
-      <c r="J198" s="8" t="n"/>
-      <c r="K198" s="12" t="n"/>
+      <c r="H198" s="5" t="n"/>
+      <c r="I198" s="3" t="n"/>
+      <c r="J198" s="3" t="n"/>
+      <c r="K198" s="6" t="n"/>
     </row>
     <row r="199" ht="21.6" customHeight="1">
       <c r="A199" s="7" t="n"/>
@@ -9434,22 +9454,22 @@
       <c r="C199" s="8" t="n"/>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>B11.4</t>
+          <t>B11.2</t>
         </is>
       </c>
       <c r="E199" s="10" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr">
         <is>
-          <t>អ្នកប្រើប្រាស់</t>
+          <t>ទូទៅ</t>
         </is>
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/settings</t>
         </is>
       </c>
       <c r="H199" s="7" t="n"/>
@@ -9463,22 +9483,22 @@
       <c r="C200" s="8" t="n"/>
       <c r="D200" s="9" t="inlineStr">
         <is>
-          <t>B11.5</t>
+          <t>B11.3</t>
         </is>
       </c>
       <c r="E200" s="10" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Telegram notifications</t>
         </is>
       </c>
       <c r="F200" s="8" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>ការជូនដំណឹង Telegram</t>
         </is>
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/telegram-notifications</t>
         </is>
       </c>
       <c r="H200" s="7" t="n"/>
@@ -9492,22 +9512,22 @@
       <c r="C201" s="8" t="n"/>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>B11.6</t>
+          <t>B11.4</t>
         </is>
       </c>
       <c r="E201" s="10" t="inlineStr">
         <is>
-          <t>Audit Logs</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr">
         <is>
-          <t>កំណត់ហេតុសវនកម្ម</t>
+          <t>អ្នកប្រើប្រាស់</t>
         </is>
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
-          <t>/audit-logs</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="H201" s="7" t="n"/>
@@ -9521,76 +9541,56 @@
       <c r="C202" s="8" t="n"/>
       <c r="D202" s="9" t="inlineStr">
         <is>
-          <t>B11.7</t>
+          <t>B11.5</t>
         </is>
       </c>
       <c r="E202" s="10" t="inlineStr">
         <is>
-          <t>Languages</t>
+          <t>Roles</t>
         </is>
       </c>
       <c r="F202" s="8" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="H202" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I202" s="8" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="J202" s="8" t="inlineStr">
-        <is>
-          <t>ភាសា</t>
-        </is>
-      </c>
+          <t>/roles</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="n"/>
+      <c r="I202" s="8" t="n"/>
+      <c r="J202" s="8" t="n"/>
       <c r="K202" s="12" t="n"/>
     </row>
     <row r="203" ht="21.6" customHeight="1">
       <c r="A203" s="7" t="n"/>
       <c r="B203" s="8" t="n"/>
       <c r="C203" s="8" t="n"/>
-      <c r="D203" s="7" t="inlineStr">
-        <is>
-          <t>B11.7</t>
-        </is>
-      </c>
-      <c r="E203" s="8" t="inlineStr">
-        <is>
-          <t>Languages</t>
+      <c r="D203" s="9" t="inlineStr">
+        <is>
+          <t>B11.6</t>
+        </is>
+      </c>
+      <c r="E203" s="10" t="inlineStr">
+        <is>
+          <t>Audit Logs</t>
         </is>
       </c>
       <c r="F203" s="8" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>កំណត់ហេតុសវនកម្ម</t>
         </is>
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="H203" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I203" s="8" t="inlineStr">
-        <is>
-          <t>Translation</t>
-        </is>
-      </c>
-      <c r="J203" s="8" t="inlineStr">
-        <is>
-          <t>ការបកប្រែ</t>
-        </is>
-      </c>
+          <t>/audit-logs</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="n"/>
+      <c r="I203" s="8" t="n"/>
+      <c r="J203" s="8" t="n"/>
       <c r="K203" s="12" t="n"/>
     </row>
     <row r="204" ht="21.6" customHeight="1">
@@ -9599,183 +9599,183 @@
       <c r="C204" s="8" t="n"/>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>B11.8</t>
+          <t>B11.7</t>
         </is>
       </c>
       <c r="E204" s="10" t="inlineStr">
         <is>
-          <t>Base Data</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="F204" s="8" t="inlineStr">
         <is>
-          <t>ទិន្នន័យមូលដ្ឋាន</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="G204" s="11" t="inlineStr">
         <is>
-          <t>/lookup-categories</t>
-        </is>
-      </c>
-      <c r="H204" s="7" t="n"/>
-      <c r="I204" s="8" t="n"/>
-      <c r="J204" s="8" t="n"/>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="H204" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" s="8" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="J204" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
       <c r="K204" s="12" t="n"/>
     </row>
     <row r="205" ht="21.6" customHeight="1">
       <c r="A205" s="7" t="n"/>
       <c r="B205" s="8" t="n"/>
       <c r="C205" s="8" t="n"/>
-      <c r="D205" s="9" t="inlineStr">
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>B11.7</t>
+        </is>
+      </c>
+      <c r="E205" s="8" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="G205" s="11" t="inlineStr">
+        <is>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="H205" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I205" s="8" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="J205" s="8" t="inlineStr">
+        <is>
+          <t>ការបកប្រែ</t>
+        </is>
+      </c>
+      <c r="K205" s="12" t="n"/>
+    </row>
+    <row r="206" ht="21.6" customHeight="1">
+      <c r="A206" s="7" t="n"/>
+      <c r="B206" s="8" t="n"/>
+      <c r="C206" s="8" t="n"/>
+      <c r="D206" s="9" t="inlineStr">
+        <is>
+          <t>B11.8</t>
+        </is>
+      </c>
+      <c r="E206" s="10" t="inlineStr">
+        <is>
+          <t>Base Data</t>
+        </is>
+      </c>
+      <c r="F206" s="8" t="inlineStr">
+        <is>
+          <t>ទិន្នន័យមូលដ្ឋាន</t>
+        </is>
+      </c>
+      <c r="G206" s="11" t="inlineStr">
+        <is>
+          <t>/lookup-categories</t>
+        </is>
+      </c>
+      <c r="H206" s="7" t="n"/>
+      <c r="I206" s="8" t="n"/>
+      <c r="J206" s="8" t="n"/>
+      <c r="K206" s="12" t="n"/>
+    </row>
+    <row r="207" ht="21.6" customHeight="1">
+      <c r="A207" s="7" t="n"/>
+      <c r="B207" s="8" t="n"/>
+      <c r="C207" s="8" t="n"/>
+      <c r="D207" s="9" t="inlineStr">
         <is>
           <t>B11.9</t>
         </is>
       </c>
-      <c r="E205" s="10" t="inlineStr">
+      <c r="E207" s="10" t="inlineStr">
         <is>
           <t>Backup</t>
         </is>
       </c>
-      <c r="F205" s="8" t="inlineStr">
+      <c r="F207" s="8" t="inlineStr">
         <is>
           <t>បម្រុងទុក</t>
         </is>
       </c>
-      <c r="G205" s="11" t="inlineStr">
+      <c r="G207" s="11" t="inlineStr">
         <is>
           <t>/database-backups</t>
         </is>
       </c>
-      <c r="H205" s="7" t="n"/>
-      <c r="I205" s="8" t="n"/>
-      <c r="J205" s="8" t="n"/>
-      <c r="K205" s="12" t="n"/>
-    </row>
-    <row r="206" ht="21.6" customHeight="1">
-      <c r="A206" s="13" t="inlineStr">
+      <c r="H207" s="7" t="n"/>
+      <c r="I207" s="8" t="n"/>
+      <c r="J207" s="8" t="n"/>
+      <c r="K207" s="12" t="n"/>
+    </row>
+    <row r="208" ht="21.6" customHeight="1">
+      <c r="A208" s="13" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B206" s="14" t="inlineStr">
+      <c r="B208" s="14" t="inlineStr">
         <is>
           <t>eApprovals</t>
         </is>
       </c>
-      <c r="C206" s="15" t="n"/>
-      <c r="D206" s="13" t="inlineStr">
+      <c r="C208" s="15" t="n"/>
+      <c r="D208" s="13" t="inlineStr">
         <is>
           <t>B12.1</t>
         </is>
       </c>
-      <c r="E206" s="14" t="inlineStr">
+      <c r="E208" s="14" t="inlineStr">
         <is>
           <t>Forms</t>
         </is>
       </c>
-      <c r="F206" s="15" t="inlineStr">
+      <c r="F208" s="15" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="G206" s="16" t="inlineStr">
+      <c r="G208" s="16" t="inlineStr">
         <is>
           <t>/approvals/forms</t>
         </is>
       </c>
-      <c r="H206" s="17" t="n"/>
-      <c r="I206" s="15" t="n"/>
-      <c r="J206" s="15" t="n"/>
-      <c r="K206" s="18" t="n"/>
-    </row>
-    <row r="207" ht="21.6" customHeight="1">
-      <c r="A207" s="19" t="n"/>
-      <c r="B207" s="20" t="n"/>
-      <c r="C207" s="20" t="n"/>
-      <c r="D207" s="21" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E207" s="22" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F207" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G207" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H207" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I207" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J207" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
-      <c r="K207" s="24" t="n"/>
-    </row>
-    <row r="208" ht="21.6" customHeight="1">
-      <c r="A208" s="19" t="n"/>
-      <c r="B208" s="20" t="n"/>
-      <c r="C208" s="20" t="n"/>
-      <c r="D208" s="19" t="inlineStr">
-        <is>
-          <t>B12.2</t>
-        </is>
-      </c>
-      <c r="E208" s="20" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="F208" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="G208" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="H208" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I208" s="20" t="inlineStr">
-        <is>
-          <t>Approved to study</t>
-        </is>
-      </c>
-      <c r="J208" s="20" t="inlineStr">
-        <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
-        </is>
-      </c>
-      <c r="K208" s="24" t="n"/>
+      <c r="H208" s="17" t="n"/>
+      <c r="I208" s="15" t="n"/>
+      <c r="J208" s="15" t="n"/>
+      <c r="K208" s="18" t="n"/>
     </row>
     <row r="209" ht="21.6" customHeight="1">
       <c r="A209" s="19" t="n"/>
       <c r="B209" s="20" t="n"/>
       <c r="C209" s="20" t="n"/>
-      <c r="D209" s="19" t="inlineStr">
+      <c r="D209" s="21" t="inlineStr">
         <is>
           <t>B12.2</t>
         </is>
       </c>
-      <c r="E209" s="20" t="inlineStr">
+      <c r="E209" s="22" t="inlineStr">
         <is>
           <t>My Request</t>
         </is>
@@ -9791,16 +9791,16 @@
         </is>
       </c>
       <c r="H209" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I209" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J209" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="K209" s="24" t="n"/>
@@ -9830,16 +9830,16 @@
         </is>
       </c>
       <c r="H210" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I210" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J210" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K210" s="24" t="n"/>
@@ -9869,16 +9869,16 @@
         </is>
       </c>
       <c r="H211" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I211" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J211" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K211" s="24" t="n"/>
@@ -9887,37 +9887,37 @@
       <c r="A212" s="19" t="n"/>
       <c r="B212" s="20" t="n"/>
       <c r="C212" s="20" t="n"/>
-      <c r="D212" s="21" t="inlineStr">
-        <is>
-          <t>B12.3</t>
-        </is>
-      </c>
-      <c r="E212" s="22" t="inlineStr">
-        <is>
-          <t>Approvals</t>
+      <c r="D212" s="19" t="inlineStr">
+        <is>
+          <t>B12.2</t>
+        </is>
+      </c>
+      <c r="E212" s="20" t="inlineStr">
+        <is>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F212" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G212" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H212" s="19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I212" s="20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Rejected</t>
         </is>
       </c>
       <c r="J212" s="20" t="inlineStr">
         <is>
-          <t>ថ្មី</t>
+          <t>បានបដិសេធ</t>
         </is>
       </c>
       <c r="K212" s="24" t="n"/>
@@ -9928,49 +9928,49 @@
       <c r="C213" s="20" t="n"/>
       <c r="D213" s="19" t="inlineStr">
         <is>
-          <t>B12.3</t>
+          <t>B12.2</t>
         </is>
       </c>
       <c r="E213" s="20" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>My Request</t>
         </is>
       </c>
       <c r="F213" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័ត</t>
+          <t>សំណើរបស់ខ្ញុំ</t>
         </is>
       </c>
       <c r="G213" s="23" t="inlineStr">
         <is>
-          <t>/approvals/queue</t>
+          <t>/approvals/my-requests</t>
         </is>
       </c>
       <c r="H213" s="19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I213" s="20" t="inlineStr">
         <is>
-          <t>Approved to study</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="J213" s="20" t="inlineStr">
         <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
+          <t>បានលុបចោល</t>
         </is>
       </c>
       <c r="K213" s="24" t="n"/>
     </row>
-    <row r="214" ht="151.2" customHeight="1">
+    <row r="214" ht="21.6" customHeight="1">
       <c r="A214" s="19" t="n"/>
       <c r="B214" s="20" t="n"/>
       <c r="C214" s="20" t="n"/>
-      <c r="D214" s="19" t="inlineStr">
+      <c r="D214" s="21" t="inlineStr">
         <is>
           <t>B12.3</t>
         </is>
       </c>
-      <c r="E214" s="20" t="inlineStr">
+      <c r="E214" s="22" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
@@ -9986,21 +9986,21 @@
         </is>
       </c>
       <c r="H214" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I214" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>New</t>
         </is>
       </c>
       <c r="J214" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>ថ្មី</t>
         </is>
       </c>
       <c r="K214" s="24" t="n"/>
     </row>
-    <row r="215" ht="194.4" customHeight="1">
+    <row r="215" ht="21.6" customHeight="1">
       <c r="A215" s="19" t="n"/>
       <c r="B215" s="20" t="n"/>
       <c r="C215" s="20" t="n"/>
@@ -10025,21 +10025,21 @@
         </is>
       </c>
       <c r="H215" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I215" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="J215" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="K215" s="24" t="n"/>
     </row>
-    <row r="216" ht="108" customHeight="1">
+    <row r="216" ht="151.2" customHeight="1">
       <c r="A216" s="19" t="n"/>
       <c r="B216" s="20" t="n"/>
       <c r="C216" s="20" t="n"/>
@@ -10064,382 +10064,460 @@
         </is>
       </c>
       <c r="H216" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I216" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="J216" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="K216" s="24" t="n"/>
     </row>
-    <row r="217" ht="86.40000000000001" customHeight="1">
+    <row r="217" ht="194.4" customHeight="1">
       <c r="A217" s="19" t="n"/>
       <c r="B217" s="20" t="n"/>
       <c r="C217" s="20" t="n"/>
-      <c r="D217" s="21" t="inlineStr">
-        <is>
-          <t>B12.4</t>
-        </is>
-      </c>
-      <c r="E217" s="22" t="inlineStr">
-        <is>
-          <t>Form Categories</t>
+      <c r="D217" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E217" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="F217" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទទម្រង់បែបបទ</t>
+          <t>ការអនុម័ត</t>
         </is>
       </c>
       <c r="G217" s="23" t="inlineStr">
         <is>
-          <t>/form-categories</t>
-        </is>
-      </c>
-      <c r="H217" s="19" t="n"/>
-      <c r="I217" s="20" t="n"/>
-      <c r="J217" s="20" t="n"/>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H217" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I217" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="J217" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
       <c r="K217" s="24" t="n"/>
     </row>
-    <row r="218">
+    <row r="218" ht="108" customHeight="1">
       <c r="A218" s="19" t="n"/>
       <c r="B218" s="20" t="n"/>
       <c r="C218" s="20" t="n"/>
-      <c r="D218" s="21" t="inlineStr">
+      <c r="D218" s="19" t="inlineStr">
+        <is>
+          <t>B12.3</t>
+        </is>
+      </c>
+      <c r="E218" s="20" t="inlineStr">
+        <is>
+          <t>Approvals</t>
+        </is>
+      </c>
+      <c r="F218" s="20" t="inlineStr">
+        <is>
+          <t>ការអនុម័ត</t>
+        </is>
+      </c>
+      <c r="G218" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/queue</t>
+        </is>
+      </c>
+      <c r="H218" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I218" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="J218" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="K218" s="24" t="n"/>
+    </row>
+    <row r="219" ht="86.40000000000001" customHeight="1">
+      <c r="A219" s="19" t="n"/>
+      <c r="B219" s="20" t="n"/>
+      <c r="C219" s="20" t="n"/>
+      <c r="D219" s="21" t="inlineStr">
+        <is>
+          <t>B12.4</t>
+        </is>
+      </c>
+      <c r="E219" s="22" t="inlineStr">
+        <is>
+          <t>Form Categories</t>
+        </is>
+      </c>
+      <c r="F219" s="20" t="inlineStr">
+        <is>
+          <t>ប្រភេទទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="G219" s="23" t="inlineStr">
+        <is>
+          <t>/form-categories</t>
+        </is>
+      </c>
+      <c r="H219" s="19" t="n"/>
+      <c r="I219" s="20" t="n"/>
+      <c r="J219" s="20" t="n"/>
+      <c r="K219" s="24" t="n"/>
+    </row>
+    <row r="220" ht="21.6" customHeight="1">
+      <c r="A220" s="19" t="n"/>
+      <c r="B220" s="20" t="n"/>
+      <c r="C220" s="20" t="n"/>
+      <c r="D220" s="21" t="inlineStr">
         <is>
           <t>B12.5</t>
         </is>
       </c>
-      <c r="E218" s="22" t="inlineStr">
+      <c r="E220" s="22" t="inlineStr">
         <is>
           <t>Form Templates</t>
         </is>
       </c>
-      <c r="F218" s="20" t="inlineStr">
+      <c r="F220" s="20" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="G218" s="23" t="inlineStr">
+      <c r="G220" s="23" t="inlineStr">
         <is>
           <t>/form-templates</t>
         </is>
       </c>
-      <c r="H218" s="19" t="n"/>
-      <c r="I218" s="20" t="n"/>
-      <c r="J218" s="20" t="n"/>
-      <c r="K218" s="24" t="n"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="1" t="inlineStr">
+      <c r="H220" s="19" t="n"/>
+      <c r="I220" s="20" t="n"/>
+      <c r="J220" s="20" t="n"/>
+      <c r="K220" s="24" t="n"/>
+    </row>
+    <row r="221" ht="21.6" customHeight="1">
+      <c r="A221" s="1" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C219" s="3" t="inlineStr">
+      <c r="C221" s="3" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D219" s="1" t="inlineStr">
+      <c r="D221" s="1" t="inlineStr">
         <is>
           <t>B13.1</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Groups</t>
         </is>
       </c>
-      <c r="F219" s="3" t="inlineStr">
+      <c r="F221" s="3" t="inlineStr">
         <is>
           <t>ក្រុម</t>
         </is>
       </c>
-      <c r="G219" s="4" t="inlineStr">
+      <c r="G221" s="4" t="inlineStr">
         <is>
           <t>/approval-flow/groups</t>
         </is>
       </c>
-      <c r="H219" s="5" t="n"/>
-      <c r="I219" s="3" t="n"/>
-      <c r="J219" s="3" t="n"/>
-      <c r="K219" s="6" t="n"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="7" t="inlineStr">
+      <c r="H221" s="5" t="n"/>
+      <c r="I221" s="3" t="n"/>
+      <c r="J221" s="3" t="n"/>
+      <c r="K221" s="6" t="n"/>
+    </row>
+    <row r="222" ht="21.6" customHeight="1">
+      <c r="A222" s="7" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B220" s="8" t="inlineStr">
+      <c r="B222" s="8" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C220" s="8" t="inlineStr">
+      <c r="C222" s="8" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D220" s="9" t="inlineStr">
+      <c r="D222" s="9" t="inlineStr">
         <is>
           <t>B13.2</t>
         </is>
       </c>
-      <c r="E220" s="10" t="inlineStr">
+      <c r="E222" s="10" t="inlineStr">
         <is>
           <t>Flow Setting</t>
         </is>
       </c>
-      <c r="F220" s="8" t="inlineStr">
+      <c r="F222" s="8" t="inlineStr">
         <is>
           <t>កំណត់លំហូរ</t>
         </is>
       </c>
-      <c r="G220" s="11" t="inlineStr">
+      <c r="G222" s="11" t="inlineStr">
         <is>
           <t>/approval-flow/settings</t>
         </is>
       </c>
-      <c r="H220" s="7" t="n"/>
-      <c r="I220" s="8" t="n"/>
-      <c r="J220" s="8" t="n"/>
-      <c r="K220" s="12" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="7" t="inlineStr">
+      <c r="H222" s="7" t="n"/>
+      <c r="I222" s="8" t="n"/>
+      <c r="J222" s="8" t="n"/>
+      <c r="K222" s="12" t="n"/>
+    </row>
+    <row r="223" ht="151.2" customHeight="1">
+      <c r="A223" s="7" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="B221" s="8" t="inlineStr">
+      <c r="B223" s="8" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="C221" s="8" t="inlineStr">
+      <c r="C223" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="D221" s="9" t="inlineStr">
+      <c r="D223" s="9" t="inlineStr">
         <is>
           <t>B14.1</t>
         </is>
       </c>
-      <c r="E221" s="10" t="inlineStr">
+      <c r="E223" s="10" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="F221" s="8" t="inlineStr">
+      <c r="F223" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="G221" s="11" t="inlineStr">
+      <c r="G223" s="11" t="inlineStr">
         <is>
           <t>/front-office</t>
         </is>
       </c>
-      <c r="H221" s="7" t="n">
+      <c r="H223" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I221" s="8" t="inlineStr">
+      <c r="I223" s="8" t="inlineStr">
         <is>
           <t>Inquiry</t>
         </is>
       </c>
-      <c r="J221" s="8" t="inlineStr">
+      <c r="J223" s="8" t="inlineStr">
         <is>
           <t>ការសាកសួរ</t>
         </is>
       </c>
-      <c r="K221" s="12" t="inlineStr">
+      <c r="K223" s="12" t="inlineStr">
         <is>
           <t>In the menu after Project Management. People who ask about the school: source, interest, follow-up history, next follow-up date; Register student fills the student form and links it. The website Register form (C4.4) also lands here as source Website, and staff who can update inquiries are notified.</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="7" t="inlineStr">
+    <row r="224" ht="194.4" customHeight="1">
+      <c r="A224" s="7" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="B222" s="8" t="inlineStr">
+      <c r="B224" s="8" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="C222" s="8" t="inlineStr">
+      <c r="C224" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="D222" s="9" t="inlineStr">
+      <c r="D224" s="9" t="inlineStr">
         <is>
           <t>B14.1</t>
         </is>
       </c>
-      <c r="E222" s="10" t="inlineStr">
+      <c r="E224" s="10" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="F222" s="8" t="inlineStr">
+      <c r="F224" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="G222" s="11" t="inlineStr">
+      <c r="G224" s="11" t="inlineStr">
         <is>
           <t>/front-office</t>
         </is>
       </c>
-      <c r="H222" s="7" t="n">
+      <c r="H224" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I222" s="8" t="inlineStr">
+      <c r="I224" s="8" t="inlineStr">
         <is>
           <t>Meeting arrangement</t>
         </is>
       </c>
-      <c r="J222" s="8" t="inlineStr">
+      <c r="J224" s="8" t="inlineStr">
         <is>
           <t>រៀបចំកិច្ចប្រជុំ</t>
         </is>
       </c>
-      <c r="K222" s="12" t="inlineStr">
+      <c r="K224" s="12" t="inlineStr">
         <is>
           <t>Date, start/end time, place, organizer, agenda; participants are staff (notified when invited, moved or cancelled) plus outside guests; meeting note; Scheduled / Completed / Cancelled. Upcoming, Past, All and Only mine. Teachers can view by default. Also shown on School setup &gt; School calendar (not cancelled ones; only to people who can view meetings); a click opens the meeting.</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="7" t="inlineStr">
+    <row r="225" ht="108" customHeight="1">
+      <c r="A225" s="7" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="B223" s="8" t="inlineStr">
+      <c r="B225" s="8" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="C223" s="8" t="inlineStr">
+      <c r="C225" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="D223" s="9" t="inlineStr">
+      <c r="D225" s="9" t="inlineStr">
         <is>
           <t>B14.1</t>
         </is>
       </c>
-      <c r="E223" s="10" t="inlineStr">
+      <c r="E225" s="10" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="F223" s="8" t="inlineStr">
+      <c r="F225" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="G223" s="11" t="inlineStr">
+      <c r="G225" s="11" t="inlineStr">
         <is>
           <t>/front-office</t>
         </is>
       </c>
-      <c r="H223" s="7" t="n">
+      <c r="H225" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I223" s="8" t="inlineStr">
+      <c r="I225" s="8" t="inlineStr">
         <is>
           <t>Appointment</t>
         </is>
       </c>
-      <c r="J223" s="8" t="inlineStr">
+      <c r="J225" s="8" t="inlineStr">
         <is>
           <t>ការណាត់ជួប</t>
         </is>
       </c>
-      <c r="K223" s="12" t="inlineStr">
+      <c r="K225" s="12" t="inlineStr">
         <is>
           <t>Book a visit: visitor, phone, organization, purpose, date and time, Meeting with (staff, notified). Today / Upcoming / Past / All. Check in adds them to the Visitor log and tells the host; No-show, Cancel.</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="7" t="inlineStr">
+    <row r="226" ht="86.40000000000001" customHeight="1">
+      <c r="A226" s="7" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="B224" s="8" t="inlineStr">
+      <c r="B226" s="8" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="C224" s="8" t="inlineStr">
+      <c r="C226" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="D224" s="9" t="inlineStr">
+      <c r="D226" s="9" t="inlineStr">
         <is>
           <t>B14.1</t>
         </is>
       </c>
-      <c r="E224" s="10" t="inlineStr">
+      <c r="E226" s="10" t="inlineStr">
         <is>
           <t>Front Office</t>
         </is>
       </c>
-      <c r="F224" s="8" t="inlineStr">
+      <c r="F226" s="8" t="inlineStr">
         <is>
           <t>ការិយាល័យទទួលភ្ញៀវ</t>
         </is>
       </c>
-      <c r="G224" s="11" t="inlineStr">
+      <c r="G226" s="11" t="inlineStr">
         <is>
           <t>/front-office</t>
         </is>
       </c>
-      <c r="H224" s="7" t="n">
+      <c r="H226" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I224" s="8" t="inlineStr">
+      <c r="I226" s="8" t="inlineStr">
         <is>
           <t>Visitor</t>
         </is>
       </c>
-      <c r="J224" s="8" t="inlineStr">
+      <c r="J226" s="8" t="inlineStr">
         <is>
           <t>ភ្ញៀវ</t>
         </is>
       </c>
-      <c r="K224" s="12" t="inlineStr">
+      <c r="K226" s="12" t="inlineStr">
         <is>
           <t>Visitor log by day: walk-ins checked in here, appointments via Check in; people count, ID no., badge; check-in and check-out times; On site now. Check out completes the appointment.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K216"/>
+  <autoFilter ref="A1:K218"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
 </worksheet>
@@ -10462,8 +10540,8 @@
     <col width="10.5546875" bestFit="1" customWidth="1" style="27" min="8" max="8"/>
     <col width="28" customWidth="1" style="27" min="9" max="10"/>
     <col width="44" customWidth="1" style="27" min="11" max="11"/>
-    <col width="8.88671875" customWidth="1" style="27" min="12" max="13"/>
-    <col width="8.88671875" customWidth="1" style="27" min="14" max="16384"/>
+    <col width="8.88671875" customWidth="1" style="27" min="12" max="14"/>
+    <col width="8.88671875" customWidth="1" style="27" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customFormat="1" customHeight="1" s="28">
@@ -11807,7 +11885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.77734375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -13223,7 +13301,7 @@
       </c>
       <c r="H55" s="20" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="I55" s="20" t="inlineStr">
@@ -13245,12 +13323,12 @@
       </c>
       <c r="H56" s="20" t="inlineStr">
         <is>
-          <t>Previous Work</t>
+          <t>Job experience</t>
         </is>
       </c>
       <c r="I56" s="20" t="inlineStr">
         <is>
-          <t>បទពិសោធន៍ការងារពីមុន</t>
+          <t>បទពិសោធន៍ការងារ</t>
         </is>
       </c>
       <c r="J56" s="24" t="n"/>
@@ -13259,32 +13337,20 @@
       <c r="A57" s="19" t="n"/>
       <c r="B57" s="20" t="n"/>
       <c r="C57" s="20" t="n"/>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>Teachers</t>
-        </is>
-      </c>
-      <c r="E57" s="20" t="inlineStr">
-        <is>
-          <t>គ្រូ</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>/teachers</t>
-        </is>
-      </c>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="23" t="n"/>
       <c r="G57" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="38" t="inlineStr">
-        <is>
-          <t>Qualification</t>
+        <v>7</v>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>Other Skills</t>
         </is>
       </c>
       <c r="I57" s="20" t="inlineStr">
         <is>
-          <t>គុណវុឌ្ឍិ</t>
+          <t>ជំនាញផ្សេងៗ</t>
         </is>
       </c>
       <c r="J57" s="24" t="n"/>
@@ -13297,16 +13363,16 @@
       <c r="E58" s="20" t="n"/>
       <c r="F58" s="23" t="n"/>
       <c r="G58" s="19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H58" s="20" t="inlineStr">
         <is>
-          <t>Assignment</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="I58" s="20" t="inlineStr">
         <is>
-          <t>ការចាត់តាំង</t>
+          <t>ឯកសារ</t>
         </is>
       </c>
       <c r="J58" s="24" t="n"/>
@@ -13315,20 +13381,32 @@
       <c r="A59" s="19" t="n"/>
       <c r="B59" s="20" t="n"/>
       <c r="C59" s="20" t="n"/>
-      <c r="D59" s="20" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="23" t="n"/>
+      <c r="D59" s="22" t="inlineStr">
+        <is>
+          <t>Teachers</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr">
+        <is>
+          <t>គ្រូ</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>/teachers</t>
+        </is>
+      </c>
       <c r="G59" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" s="20" t="inlineStr">
-        <is>
-          <t>Homeroom</t>
-        </is>
-      </c>
-      <c r="I59" s="20" t="inlineStr">
-        <is>
-          <t>គ្រូប្រចាំថ្នាក់</t>
+        <v>1</v>
+      </c>
+      <c r="H59" s="36" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I59" s="36" t="inlineStr">
+        <is>
+          <t>គុណវុឌ្ឍិ</t>
         </is>
       </c>
       <c r="J59" s="24" t="n"/>
@@ -13341,16 +13419,16 @@
       <c r="E60" s="20" t="n"/>
       <c r="F60" s="23" t="n"/>
       <c r="G60" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H60" s="20" t="inlineStr">
-        <is>
-          <t>Teaching load</t>
-        </is>
-      </c>
-      <c r="I60" s="20" t="inlineStr">
-        <is>
-          <t>ម៉ោងបង្រៀន</t>
+        <v>2</v>
+      </c>
+      <c r="H60" s="36" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="I60" s="36" t="inlineStr">
+        <is>
+          <t>ការចាត់តាំង</t>
         </is>
       </c>
       <c r="J60" s="24" t="n"/>
@@ -13363,16 +13441,16 @@
       <c r="E61" s="20" t="n"/>
       <c r="F61" s="23" t="n"/>
       <c r="G61" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H61" s="20" t="inlineStr">
-        <is>
-          <t>Availability</t>
-        </is>
-      </c>
-      <c r="I61" s="20" t="inlineStr">
-        <is>
-          <t>ពេលទំនេរ</t>
+        <v>3</v>
+      </c>
+      <c r="H61" s="36" t="inlineStr">
+        <is>
+          <t>Homeroom</t>
+        </is>
+      </c>
+      <c r="I61" s="36" t="inlineStr">
+        <is>
+          <t>គ្រូប្រចាំថ្នាក់</t>
         </is>
       </c>
       <c r="J61" s="24" t="n"/>
@@ -13385,16 +13463,16 @@
       <c r="E62" s="20" t="n"/>
       <c r="F62" s="23" t="n"/>
       <c r="G62" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="H62" s="20" t="inlineStr">
-        <is>
-          <t>Substitute</t>
-        </is>
-      </c>
-      <c r="I62" s="20" t="inlineStr">
-        <is>
-          <t>គ្រូជំនួស</t>
+        <v>4</v>
+      </c>
+      <c r="H62" s="36" t="inlineStr">
+        <is>
+          <t>Teaching load</t>
+        </is>
+      </c>
+      <c r="I62" s="36" t="inlineStr">
+        <is>
+          <t>ម៉ោងបង្រៀន</t>
         </is>
       </c>
       <c r="J62" s="24" t="n"/>
@@ -13407,16 +13485,16 @@
       <c r="E63" s="20" t="n"/>
       <c r="F63" s="23" t="n"/>
       <c r="G63" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="H63" s="20" t="inlineStr">
-        <is>
-          <t>Documents</t>
-        </is>
-      </c>
-      <c r="I63" s="20" t="inlineStr">
-        <is>
-          <t>ឯកសារ</t>
+        <v>5</v>
+      </c>
+      <c r="H63" s="36" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="I63" s="36" t="inlineStr">
+        <is>
+          <t>ពេលទំនេរ</t>
         </is>
       </c>
       <c r="J63" s="24" t="n"/>
@@ -13425,56 +13503,42 @@
       <c r="A64" s="19" t="n"/>
       <c r="B64" s="20" t="n"/>
       <c r="C64" s="20" t="n"/>
-      <c r="D64" s="22" t="inlineStr">
-        <is>
-          <t>Staff Status History</t>
-        </is>
-      </c>
-      <c r="E64" s="20" t="inlineStr">
-        <is>
-          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
-        </is>
-      </c>
-      <c r="F64" s="23" t="inlineStr">
-        <is>
-          <t>/staff-status-history</t>
-        </is>
-      </c>
-      <c r="G64" s="19" t="n"/>
-      <c r="H64" s="20" t="n"/>
-      <c r="I64" s="20" t="n"/>
+      <c r="D64" s="20" t="n"/>
+      <c r="E64" s="20" t="n"/>
+      <c r="F64" s="23" t="n"/>
+      <c r="G64" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" s="36" t="inlineStr">
+        <is>
+          <t>Substitute</t>
+        </is>
+      </c>
+      <c r="I64" s="36" t="inlineStr">
+        <is>
+          <t>គ្រូជំនួស</t>
+        </is>
+      </c>
       <c r="J64" s="24" t="n"/>
     </row>
     <row r="65" ht="21.6" customHeight="1">
       <c r="A65" s="19" t="n"/>
       <c r="B65" s="20" t="n"/>
       <c r="C65" s="20" t="n"/>
-      <c r="D65" s="22" t="inlineStr">
-        <is>
-          <t>Organization Management</t>
-        </is>
-      </c>
-      <c r="E65" s="20" t="inlineStr">
-        <is>
-          <t>ការគ្រប់គ្រងអង្គភាព</t>
-        </is>
-      </c>
-      <c r="F65" s="23" t="inlineStr">
-        <is>
-          <t>/organization</t>
-        </is>
-      </c>
+      <c r="D65" s="20" t="n"/>
+      <c r="E65" s="20" t="n"/>
+      <c r="F65" s="23" t="n"/>
       <c r="G65" s="19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H65" s="36" t="inlineStr">
         <is>
-          <t>School</t>
-        </is>
-      </c>
-      <c r="I65" s="20" t="inlineStr">
-        <is>
-          <t>សាលា</t>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="I65" s="36" t="inlineStr">
+        <is>
+          <t>ឯកសារ</t>
         </is>
       </c>
       <c r="J65" s="24" t="n"/>
@@ -13483,42 +13547,56 @@
       <c r="A66" s="19" t="n"/>
       <c r="B66" s="20" t="n"/>
       <c r="C66" s="20" t="n"/>
-      <c r="D66" s="20" t="n"/>
-      <c r="E66" s="20" t="n"/>
-      <c r="F66" s="23" t="n"/>
-      <c r="G66" s="19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H66" s="36" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="I66" s="20" t="inlineStr">
-        <is>
-          <t>សាខា</t>
-        </is>
-      </c>
+      <c r="D66" s="22" t="inlineStr">
+        <is>
+          <t>Staff Status History</t>
+        </is>
+      </c>
+      <c r="E66" s="20" t="inlineStr">
+        <is>
+          <t>ប្រវត្តិស្ថានភាពបុគ្គលិក</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>/staff-status-history</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="n"/>
+      <c r="H66" s="20" t="n"/>
+      <c r="I66" s="20" t="n"/>
       <c r="J66" s="24" t="n"/>
     </row>
     <row r="67" ht="21.6" customHeight="1">
       <c r="A67" s="19" t="n"/>
       <c r="B67" s="20" t="n"/>
       <c r="C67" s="20" t="n"/>
-      <c r="D67" s="20" t="n"/>
-      <c r="E67" s="20" t="n"/>
-      <c r="F67" s="23" t="n"/>
+      <c r="D67" s="22" t="inlineStr">
+        <is>
+          <t>Organization Management</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>ការគ្រប់គ្រងអង្គភាព</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>/organization</t>
+        </is>
+      </c>
       <c r="G67" s="19" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="H67" s="36" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>School</t>
         </is>
       </c>
       <c r="I67" s="20" t="inlineStr">
         <is>
-          <t>នាយកដ្ឋាន</t>
+          <t>សាលា</t>
         </is>
       </c>
       <c r="J67" s="24" t="n"/>
@@ -13531,16 +13609,16 @@
       <c r="E68" s="20" t="n"/>
       <c r="F68" s="23" t="n"/>
       <c r="G68" s="19" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="H68" s="36" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Branch</t>
         </is>
       </c>
       <c r="I68" s="20" t="inlineStr">
         <is>
-          <t>ក្រុម</t>
+          <t>សាខា</t>
         </is>
       </c>
       <c r="J68" s="24" t="n"/>
@@ -13553,16 +13631,16 @@
       <c r="E69" s="20" t="n"/>
       <c r="F69" s="23" t="n"/>
       <c r="G69" s="19" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H69" s="36" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="I69" s="20" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>នាយកដ្ឋាន</t>
         </is>
       </c>
       <c r="J69" s="24" t="n"/>
@@ -13575,16 +13653,16 @@
       <c r="E70" s="20" t="n"/>
       <c r="F70" s="23" t="n"/>
       <c r="G70" s="19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H70" s="36" t="inlineStr">
         <is>
-          <t>Job grade</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="I70" s="20" t="inlineStr">
         <is>
-          <t>ថ្នាក់ការងារ</t>
+          <t>ក្រុម</t>
         </is>
       </c>
       <c r="J70" s="24" t="n"/>
@@ -13597,16 +13675,16 @@
       <c r="E71" s="20" t="n"/>
       <c r="F71" s="23" t="n"/>
       <c r="G71" s="19" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H71" s="36" t="inlineStr">
         <is>
-          <t>Job level</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="I71" s="20" t="inlineStr">
         <is>
-          <t>កម្រិតការងារ</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="J71" s="24" t="n"/>
@@ -13618,19 +13696,17 @@
       <c r="D72" s="20" t="n"/>
       <c r="E72" s="20" t="n"/>
       <c r="F72" s="23" t="n"/>
-      <c r="G72" s="19" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
+      <c r="G72" s="19" t="n">
+        <v>4.5</v>
       </c>
       <c r="H72" s="36" t="inlineStr">
         <is>
-          <t>Reporting manager</t>
+          <t>Job grade</t>
         </is>
       </c>
       <c r="I72" s="20" t="inlineStr">
         <is>
-          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
+          <t>ថ្នាក់ការងារ</t>
         </is>
       </c>
       <c r="J72" s="24" t="n"/>
@@ -13642,19 +13718,17 @@
       <c r="D73" s="20" t="n"/>
       <c r="E73" s="20" t="n"/>
       <c r="F73" s="23" t="n"/>
-      <c r="G73" s="19" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
+      <c r="G73" s="19" t="n">
+        <v>4.6</v>
       </c>
       <c r="H73" s="36" t="inlineStr">
         <is>
-          <t>Organization hierarchy</t>
+          <t>Job level</t>
         </is>
       </c>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
+          <t>កម្រិតការងារ</t>
         </is>
       </c>
       <c r="J73" s="24" t="n"/>
@@ -13663,32 +13737,22 @@
       <c r="A74" s="19" t="n"/>
       <c r="B74" s="20" t="n"/>
       <c r="C74" s="20" t="n"/>
-      <c r="D74" s="22" t="inlineStr">
-        <is>
-          <t>Attendance &amp; Time</t>
-        </is>
-      </c>
-      <c r="E74" s="20" t="inlineStr">
-        <is>
-          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
-        </is>
-      </c>
-      <c r="F74" s="23" t="inlineStr">
-        <is>
-          <t>/time-attendance</t>
-        </is>
-      </c>
-      <c r="G74" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="20" t="inlineStr">
-        <is>
-          <t>Employee attendance</t>
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="20" t="n"/>
+      <c r="F74" s="23" t="n"/>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>Reporting manager</t>
         </is>
       </c>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>វត្តមានបុគ្គលិក</t>
+          <t>អ្នកគ្រប់គ្រងផ្ទាល់</t>
         </is>
       </c>
       <c r="J74" s="24" t="n"/>
@@ -13700,17 +13764,19 @@
       <c r="D75" s="20" t="n"/>
       <c r="E75" s="20" t="n"/>
       <c r="F75" s="23" t="n"/>
-      <c r="G75" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H75" s="20" t="inlineStr">
-        <is>
-          <t>Check-in / check-out</t>
+      <c r="G75" s="19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="H75" s="36" t="inlineStr">
+        <is>
+          <t>Organization hierarchy</t>
         </is>
       </c>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
+          <t>រចនាសម្ព័ន្ធអង្គភាព</t>
         </is>
       </c>
       <c r="J75" s="24" t="n"/>
@@ -13719,20 +13785,32 @@
       <c r="A76" s="19" t="n"/>
       <c r="B76" s="20" t="n"/>
       <c r="C76" s="20" t="n"/>
-      <c r="D76" s="20" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="23" t="n"/>
+      <c r="D76" s="22" t="inlineStr">
+        <is>
+          <t>Attendance &amp; Time</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>វត្តមាន និងម៉ោងធ្វើការ</t>
+        </is>
+      </c>
+      <c r="F76" s="23" t="inlineStr">
+        <is>
+          <t>/time-attendance</t>
+        </is>
+      </c>
       <c r="G76" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H76" s="20" t="inlineStr">
         <is>
-          <t>Late</t>
+          <t>Employee attendance</t>
         </is>
       </c>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>មកយឺត</t>
+          <t>វត្តមានបុគ្គលិក</t>
         </is>
       </c>
       <c r="J76" s="24" t="n"/>
@@ -13745,16 +13823,16 @@
       <c r="E77" s="20" t="n"/>
       <c r="F77" s="23" t="n"/>
       <c r="G77" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H77" s="20" t="inlineStr">
         <is>
-          <t>Early leave</t>
+          <t>Check-in / check-out</t>
         </is>
       </c>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>ចេញមុន</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="J77" s="24" t="n"/>
@@ -13767,16 +13845,16 @@
       <c r="E78" s="20" t="n"/>
       <c r="F78" s="23" t="n"/>
       <c r="G78" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H78" s="20" t="inlineStr">
         <is>
-          <t>Absence</t>
+          <t>Late</t>
         </is>
       </c>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>អវត្តមាន</t>
+          <t>មកយឺត</t>
         </is>
       </c>
       <c r="J78" s="24" t="n"/>
@@ -13789,16 +13867,16 @@
       <c r="E79" s="20" t="n"/>
       <c r="F79" s="23" t="n"/>
       <c r="G79" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H79" s="20" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>Early leave</t>
         </is>
       </c>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>ម៉ោងបន្ថែម</t>
+          <t>ចេញមុន</t>
         </is>
       </c>
       <c r="J79" s="24" t="n"/>
@@ -13811,16 +13889,16 @@
       <c r="E80" s="20" t="n"/>
       <c r="F80" s="23" t="n"/>
       <c r="G80" s="19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H80" s="20" t="inlineStr">
         <is>
-          <t>Shift</t>
+          <t>Absence</t>
         </is>
       </c>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>វេនការងារ</t>
+          <t>អវត្តមាន</t>
         </is>
       </c>
       <c r="J80" s="24" t="n"/>
@@ -13833,16 +13911,16 @@
       <c r="E81" s="20" t="n"/>
       <c r="F81" s="23" t="n"/>
       <c r="G81" s="19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H81" s="20" t="inlineStr">
         <is>
-          <t>Staff shift</t>
+          <t>Overtime</t>
         </is>
       </c>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>វេនបុគ្គលិក</t>
+          <t>ម៉ោងបន្ថែម</t>
         </is>
       </c>
       <c r="J81" s="24" t="n"/>
@@ -13855,16 +13933,16 @@
       <c r="E82" s="20" t="n"/>
       <c r="F82" s="23" t="n"/>
       <c r="G82" s="19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H82" s="20" t="inlineStr">
         <is>
-          <t>Holidays</t>
+          <t>Shift</t>
         </is>
       </c>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>ថ្ងៃឈប់សម្រាក</t>
+          <t>វេនការងារ</t>
         </is>
       </c>
       <c r="J82" s="24" t="n"/>
@@ -13877,16 +13955,16 @@
       <c r="E83" s="20" t="n"/>
       <c r="F83" s="23" t="n"/>
       <c r="G83" s="19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H83" s="20" t="inlineStr">
         <is>
-          <t>Attendance correction</t>
+          <t>Staff shift</t>
         </is>
       </c>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>ការកែវត្តមាន</t>
+          <t>វេនបុគ្គលិក</t>
         </is>
       </c>
       <c r="J83" s="24" t="n"/>
@@ -13899,16 +13977,16 @@
       <c r="E84" s="20" t="n"/>
       <c r="F84" s="23" t="n"/>
       <c r="G84" s="19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H84" s="20" t="inlineStr">
         <is>
-          <t>Attendance approval</t>
+          <t>Holidays</t>
         </is>
       </c>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>ការអនុម័តវត្តមាន</t>
+          <t>ថ្ងៃឈប់សម្រាក</t>
         </is>
       </c>
       <c r="J84" s="24" t="n"/>
@@ -13917,32 +13995,20 @@
       <c r="A85" s="19" t="n"/>
       <c r="B85" s="20" t="n"/>
       <c r="C85" s="20" t="n"/>
-      <c r="D85" s="22" t="inlineStr">
-        <is>
-          <t>Leave Management</t>
-        </is>
-      </c>
-      <c r="E85" s="20" t="inlineStr">
-        <is>
-          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
-        </is>
-      </c>
-      <c r="F85" s="23" t="inlineStr">
-        <is>
-          <t>/leave-management</t>
-        </is>
-      </c>
+      <c r="D85" s="20" t="n"/>
+      <c r="E85" s="20" t="n"/>
+      <c r="F85" s="23" t="n"/>
       <c r="G85" s="19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H85" s="20" t="inlineStr">
         <is>
-          <t>Leave types</t>
+          <t>Attendance correction</t>
         </is>
       </c>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
+          <t>ការកែវត្តមាន</t>
         </is>
       </c>
       <c r="J85" s="24" t="n"/>
@@ -13955,16 +14021,16 @@
       <c r="E86" s="20" t="n"/>
       <c r="F86" s="23" t="n"/>
       <c r="G86" s="19" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H86" s="20" t="inlineStr">
         <is>
-          <t>Leave policies</t>
+          <t>Attendance approval</t>
         </is>
       </c>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
+          <t>ការអនុម័តវត្តមាន</t>
         </is>
       </c>
       <c r="J86" s="24" t="n"/>
@@ -13973,20 +14039,32 @@
       <c r="A87" s="19" t="n"/>
       <c r="B87" s="20" t="n"/>
       <c r="C87" s="20" t="n"/>
-      <c r="D87" s="20" t="n"/>
-      <c r="E87" s="20" t="n"/>
-      <c r="F87" s="23" t="n"/>
+      <c r="D87" s="22" t="inlineStr">
+        <is>
+          <t>Leave Management</t>
+        </is>
+      </c>
+      <c r="E87" s="20" t="inlineStr">
+        <is>
+          <t>គ្រប់គ្រងការឈប់សម្រាក</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="inlineStr">
+        <is>
+          <t>/leave-management</t>
+        </is>
+      </c>
       <c r="G87" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H87" s="20" t="inlineStr">
         <is>
-          <t>Leave balance</t>
+          <t>Leave types</t>
         </is>
       </c>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>សមតុល្យច្បាប់</t>
+          <t>ប្រភេទច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="J87" s="24" t="n"/>
@@ -13999,16 +14077,16 @@
       <c r="E88" s="20" t="n"/>
       <c r="F88" s="23" t="n"/>
       <c r="G88" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H88" s="20" t="inlineStr">
         <is>
-          <t>Leave request</t>
+          <t>Leave policies</t>
         </is>
       </c>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>សំណើច្បាប់ឈប់សម្រាក</t>
+          <t>គោលការណ៍ច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="J88" s="24" t="n"/>
@@ -14021,16 +14099,16 @@
       <c r="E89" s="20" t="n"/>
       <c r="F89" s="23" t="n"/>
       <c r="G89" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H89" s="20" t="inlineStr">
         <is>
-          <t>Approval workflow</t>
+          <t>Leave balance</t>
         </is>
       </c>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>លំហូរការអនុម័ត</t>
+          <t>សមតុល្យច្បាប់</t>
         </is>
       </c>
       <c r="J89" s="24" t="n"/>
@@ -14043,16 +14121,16 @@
       <c r="E90" s="20" t="n"/>
       <c r="F90" s="23" t="n"/>
       <c r="G90" s="19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H90" s="20" t="inlineStr">
         <is>
-          <t>Leave calendar</t>
+          <t>Leave request</t>
         </is>
       </c>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>ប្រតិទិនច្បាប់</t>
+          <t>សំណើច្បាប់ឈប់សម្រាក</t>
         </is>
       </c>
       <c r="J90" s="24" t="n"/>
@@ -14065,16 +14143,16 @@
       <c r="E91" s="20" t="n"/>
       <c r="F91" s="23" t="n"/>
       <c r="G91" s="19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H91" s="20" t="inlineStr">
         <is>
-          <t>Carry forward</t>
+          <t>Approval workflow</t>
         </is>
       </c>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>យោងទៅឆ្នាំបន្ទាប់</t>
+          <t>លំហូរការអនុម័ត</t>
         </is>
       </c>
       <c r="J91" s="24" t="n"/>
@@ -14087,16 +14165,16 @@
       <c r="E92" s="20" t="n"/>
       <c r="F92" s="23" t="n"/>
       <c r="G92" s="19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H92" s="20" t="inlineStr">
         <is>
-          <t>Leave reports</t>
+          <t>Leave calendar</t>
         </is>
       </c>
       <c r="I92" s="20" t="inlineStr">
         <is>
-          <t>របាយការណ៍ច្បាប់</t>
+          <t>ប្រតិទិនច្បាប់</t>
         </is>
       </c>
       <c r="J92" s="24" t="n"/>
@@ -14105,56 +14183,42 @@
       <c r="A93" s="19" t="n"/>
       <c r="B93" s="20" t="n"/>
       <c r="C93" s="20" t="n"/>
-      <c r="D93" s="22" t="inlineStr">
-        <is>
-          <t>Check in / Check out</t>
-        </is>
-      </c>
-      <c r="E93" s="20" t="inlineStr">
-        <is>
-          <t>ចុះវត្តមាន ចូល / ចេញ</t>
-        </is>
-      </c>
-      <c r="F93" s="23" t="inlineStr">
-        <is>
-          <t>/my-check-in</t>
-        </is>
-      </c>
-      <c r="G93" s="19" t="n"/>
-      <c r="H93" s="20" t="n"/>
-      <c r="I93" s="20" t="n"/>
+      <c r="D93" s="20" t="n"/>
+      <c r="E93" s="20" t="n"/>
+      <c r="F93" s="23" t="n"/>
+      <c r="G93" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>Carry forward</t>
+        </is>
+      </c>
+      <c r="I93" s="20" t="inlineStr">
+        <is>
+          <t>យោងទៅឆ្នាំបន្ទាប់</t>
+        </is>
+      </c>
       <c r="J93" s="24" t="n"/>
     </row>
     <row r="94" ht="21.6" customHeight="1">
       <c r="A94" s="19" t="n"/>
       <c r="B94" s="20" t="n"/>
       <c r="C94" s="20" t="n"/>
-      <c r="D94" s="22" t="inlineStr">
-        <is>
-          <t>Request Leave</t>
-        </is>
-      </c>
-      <c r="E94" s="20" t="inlineStr">
-        <is>
-          <t>ស្នើសុំច្បាប់</t>
-        </is>
-      </c>
-      <c r="F94" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
+      <c r="D94" s="20" t="n"/>
+      <c r="E94" s="20" t="n"/>
+      <c r="F94" s="23" t="n"/>
       <c r="G94" s="19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H94" s="20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Leave reports</t>
         </is>
       </c>
       <c r="I94" s="20" t="inlineStr">
         <is>
-          <t>កំពុងរង់ចាំ</t>
+          <t>របាយការណ៍ច្បាប់</t>
         </is>
       </c>
       <c r="J94" s="24" t="n"/>
@@ -14163,41 +14227,31 @@
       <c r="A95" s="19" t="n"/>
       <c r="B95" s="20" t="n"/>
       <c r="C95" s="20" t="n"/>
-      <c r="D95" s="20" t="inlineStr">
-        <is>
-          <t>Request Leave</t>
+      <c r="D95" s="22" t="inlineStr">
+        <is>
+          <t>Check in / Check out</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>ស្នើសុំច្បាប់</t>
+          <t>ចុះវត្តមាន ចូល / ចេញ</t>
         </is>
       </c>
       <c r="F95" s="23" t="inlineStr">
         <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="G95" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H95" s="20" t="inlineStr">
-        <is>
-          <t>Approved to study</t>
-        </is>
-      </c>
-      <c r="I95" s="20" t="inlineStr">
-        <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
-        </is>
-      </c>
+          <t>/my-check-in</t>
+        </is>
+      </c>
+      <c r="G95" s="19" t="n"/>
+      <c r="H95" s="20" t="n"/>
+      <c r="I95" s="20" t="n"/>
       <c r="J95" s="24" t="n"/>
     </row>
     <row r="96" ht="21.6" customHeight="1">
       <c r="A96" s="19" t="n"/>
       <c r="B96" s="20" t="n"/>
       <c r="C96" s="20" t="n"/>
-      <c r="D96" s="20" t="inlineStr">
+      <c r="D96" s="22" t="inlineStr">
         <is>
           <t>Request Leave</t>
         </is>
@@ -14213,16 +14267,16 @@
         </is>
       </c>
       <c r="G96" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H96" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="I96" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="J96" s="24" t="n"/>
@@ -14247,16 +14301,16 @@
         </is>
       </c>
       <c r="G97" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H97" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="I97" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="J97" s="24" t="n"/>
@@ -14281,16 +14335,16 @@
         </is>
       </c>
       <c r="G98" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H98" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="I98" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="J98" s="24" t="n"/>
@@ -14299,125 +14353,145 @@
       <c r="A99" s="19" t="n"/>
       <c r="B99" s="20" t="n"/>
       <c r="C99" s="20" t="n"/>
-      <c r="D99" s="22" t="inlineStr">
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="E99" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="F99" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="G99" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H99" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I99" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
+      <c r="J99" s="24" t="n"/>
+    </row>
+    <row r="100" ht="21.6" customHeight="1">
+      <c r="A100" s="19" t="n"/>
+      <c r="B100" s="20" t="n"/>
+      <c r="C100" s="20" t="n"/>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Request Leave</t>
+        </is>
+      </c>
+      <c r="E100" s="20" t="inlineStr">
+        <is>
+          <t>ស្នើសុំច្បាប់</t>
+        </is>
+      </c>
+      <c r="F100" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
+      <c r="G100" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H100" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="I100" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="J100" s="24" t="n"/>
+    </row>
+    <row r="101" ht="21.6" customHeight="1">
+      <c r="A101" s="19" t="n"/>
+      <c r="B101" s="20" t="n"/>
+      <c r="C101" s="20" t="n"/>
+      <c r="D101" s="22" t="inlineStr">
         <is>
           <t>Form</t>
         </is>
       </c>
-      <c r="E99" s="20" t="inlineStr">
+      <c r="E101" s="20" t="inlineStr">
         <is>
           <t>ទម្រង់</t>
         </is>
       </c>
-      <c r="F99" s="23" t="inlineStr">
+      <c r="F101" s="23" t="inlineStr">
         <is>
           <t>/approvals/my-requests?tab=resignation</t>
         </is>
       </c>
-      <c r="G99" s="19" t="n"/>
-      <c r="H99" s="20" t="n"/>
-      <c r="I99" s="20" t="n"/>
-      <c r="J99" s="24" t="inlineStr">
+      <c r="G101" s="19" t="n"/>
+      <c r="H101" s="20" t="n"/>
+      <c r="I101" s="20" t="n"/>
+      <c r="J101" s="24" t="inlineStr">
         <is>
           <t>Resignation form</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="21.6" customHeight="1">
-      <c r="A100" s="1" t="inlineStr">
+    <row r="102" ht="21.6" customHeight="1">
+      <c r="A102" s="1" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Settings</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>ការកំណត់</t>
         </is>
       </c>
-      <c r="D100" s="35" t="n"/>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="5" t="n"/>
-      <c r="H100" s="3" t="n"/>
-      <c r="I100" s="3" t="n"/>
-      <c r="J100" s="6" t="n"/>
-    </row>
-    <row r="101" ht="21.6" customHeight="1">
-      <c r="A101" s="29" t="n"/>
-      <c r="B101" s="30" t="n"/>
-      <c r="C101" s="31" t="n"/>
-      <c r="D101" s="30" t="inlineStr">
+      <c r="D102" s="35" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="3" t="n"/>
+      <c r="I102" s="3" t="n"/>
+      <c r="J102" s="6" t="n"/>
+    </row>
+    <row r="103" ht="21.6" customHeight="1">
+      <c r="A103" s="29" t="n"/>
+      <c r="B103" s="30" t="n"/>
+      <c r="C103" s="31" t="n"/>
+      <c r="D103" s="30" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="E101" s="31" t="inlineStr">
+      <c r="E103" s="31" t="inlineStr">
         <is>
           <t>ឯកសារ</t>
         </is>
       </c>
-      <c r="F101" s="32" t="inlineStr">
+      <c r="F103" s="32" t="inlineStr">
         <is>
           <t>/school-documents</t>
         </is>
       </c>
-      <c r="G101" s="33" t="n"/>
-      <c r="H101" s="31" t="n"/>
-      <c r="I101" s="31" t="n"/>
-      <c r="J101" s="34" t="n"/>
-    </row>
-    <row r="102" ht="21.6" customHeight="1">
-      <c r="A102" s="7" t="n"/>
-      <c r="B102" s="8" t="n"/>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="10" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>ទូទៅ</t>
-        </is>
-      </c>
-      <c r="F102" s="11" t="inlineStr">
-        <is>
-          <t>/settings</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
-      <c r="J102" s="12" t="n"/>
-    </row>
-    <row r="103" ht="21.6" customHeight="1">
-      <c r="A103" s="7" t="n"/>
-      <c r="B103" s="8" t="n"/>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>Telegram notifications</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>ការជូនដំណឹង Telegram</t>
-        </is>
-      </c>
-      <c r="F103" s="11" t="inlineStr">
-        <is>
-          <t>/telegram-notifications</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="n"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="n"/>
-      <c r="J103" s="12" t="n"/>
+      <c r="G103" s="33" t="n"/>
+      <c r="H103" s="31" t="n"/>
+      <c r="I103" s="31" t="n"/>
+      <c r="J103" s="34" t="n"/>
     </row>
     <row r="104" ht="21.6" customHeight="1">
       <c r="A104" s="7" t="n"/>
@@ -14425,17 +14499,17 @@
       <c r="C104" s="8" t="n"/>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Users</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>អ្នកប្រើប្រាស់</t>
+          <t>ទូទៅ</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
         <is>
-          <t>/users</t>
+          <t>/settings</t>
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
@@ -14446,22 +14520,20 @@
     <row r="105" ht="21.6" customHeight="1">
       <c r="A105" s="7" t="n"/>
       <c r="B105" s="8" t="n"/>
-      <c r="C105" s="8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="D105" s="37" t="inlineStr">
-        <is>
-          <t>Roles</t>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>Telegram notifications</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>តួនាទី</t>
+          <t>ការជូនដំណឹង Telegram</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>/roles</t>
+          <t>/telegram-notifications</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
@@ -14475,17 +14547,17 @@
       <c r="C106" s="8" t="n"/>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Audit Logs</t>
+          <t>Users</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>កំណត់ហេតុសវនកម្ម</t>
+          <t>អ្នកប្រើប្រាស់</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
         <is>
-          <t>/audit-logs</t>
+          <t>/users</t>
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
@@ -14496,69 +14568,51 @@
     <row r="107" ht="21.6" customHeight="1">
       <c r="A107" s="7" t="n"/>
       <c r="B107" s="8" t="n"/>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="10" t="inlineStr">
-        <is>
-          <t>Languages</t>
+      <c r="C107" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D107" s="37" t="inlineStr">
+        <is>
+          <t>Roles</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>តួនាទី</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" s="8" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="I107" s="8" t="inlineStr">
-        <is>
-          <t>ភាសា</t>
-        </is>
-      </c>
+          <t>/roles</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="n"/>
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="8" t="n"/>
       <c r="J107" s="12" t="n"/>
     </row>
     <row r="108" ht="21.6" customHeight="1">
       <c r="A108" s="7" t="n"/>
       <c r="B108" s="8" t="n"/>
       <c r="C108" s="8" t="n"/>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t>Languages</t>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Audit Logs</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>ភាសា</t>
+          <t>កំណត់ហេតុសវនកម្ម</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr">
         <is>
-          <t>/languages</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H108" s="8" t="inlineStr">
-        <is>
-          <t>Translation</t>
-        </is>
-      </c>
-      <c r="I108" s="8" t="inlineStr">
-        <is>
-          <t>ការបកប្រែ</t>
-        </is>
-      </c>
+          <t>/audit-logs</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="n"/>
+      <c r="H108" s="8" t="n"/>
+      <c r="I108" s="8" t="n"/>
       <c r="J108" s="12" t="n"/>
     </row>
     <row r="109" ht="21.6" customHeight="1">
@@ -14567,154 +14621,178 @@
       <c r="C109" s="8" t="n"/>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Base Data</t>
+          <t>Languages</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>ទិន្នន័យមូលដ្ឋាន</t>
+          <t>ភាសា</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
-          <t>/lookup-categories</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="8" t="n"/>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
       <c r="J109" s="12" t="n"/>
     </row>
     <row r="110" ht="21.6" customHeight="1">
       <c r="A110" s="7" t="n"/>
       <c r="B110" s="8" t="n"/>
       <c r="C110" s="8" t="n"/>
-      <c r="D110" s="10" t="inlineStr">
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>ភាសា</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>/languages</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>Translation</t>
+        </is>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>ការបកប្រែ</t>
+        </is>
+      </c>
+      <c r="J110" s="12" t="n"/>
+    </row>
+    <row r="111" ht="21.6" customHeight="1">
+      <c r="A111" s="7" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>Base Data</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>ទិន្នន័យមូលដ្ឋាន</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>/lookup-categories</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="n"/>
+      <c r="H111" s="8" t="n"/>
+      <c r="I111" s="8" t="n"/>
+      <c r="J111" s="12" t="n"/>
+    </row>
+    <row r="112" ht="21.6" customHeight="1">
+      <c r="A112" s="7" t="n"/>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="10" t="inlineStr">
         <is>
           <t>Backup</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
+      <c r="E112" s="8" t="inlineStr">
         <is>
           <t>បម្រុងទុក</t>
         </is>
       </c>
-      <c r="F110" s="11" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>/database-backups</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="8" t="n"/>
-      <c r="I110" s="8" t="n"/>
-      <c r="J110" s="12" t="n"/>
-    </row>
-    <row r="111" ht="21.6" customHeight="1">
-      <c r="A111" s="13" t="inlineStr">
+      <c r="G112" s="7" t="n"/>
+      <c r="H112" s="8" t="n"/>
+      <c r="I112" s="8" t="n"/>
+      <c r="J112" s="12" t="n"/>
+    </row>
+    <row r="113" ht="21.6" customHeight="1">
+      <c r="A113" s="13" t="inlineStr">
         <is>
           <t>B12</t>
         </is>
       </c>
-      <c r="B111" s="14" t="inlineStr">
+      <c r="B113" s="14" t="inlineStr">
         <is>
           <t>eApprovals</t>
         </is>
       </c>
-      <c r="C111" s="15" t="n"/>
-      <c r="D111" s="14" t="inlineStr">
+      <c r="C113" s="15" t="n"/>
+      <c r="D113" s="14" t="inlineStr">
         <is>
           <t>Forms</t>
         </is>
       </c>
-      <c r="E111" s="15" t="inlineStr">
+      <c r="E113" s="15" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="F111" s="16" t="inlineStr">
+      <c r="F113" s="16" t="inlineStr">
         <is>
           <t>/approvals/forms</t>
         </is>
       </c>
-      <c r="G111" s="17" t="n"/>
-      <c r="H111" s="15" t="n"/>
-      <c r="I111" s="15" t="n"/>
-      <c r="J111" s="18" t="n"/>
-    </row>
-    <row r="112" ht="21.6" customHeight="1">
-      <c r="A112" s="19" t="n"/>
-      <c r="B112" s="20" t="n"/>
-      <c r="C112" s="20" t="n"/>
-      <c r="D112" s="22" t="inlineStr">
-        <is>
-          <t>My Request</t>
-        </is>
-      </c>
-      <c r="E112" s="20" t="inlineStr">
-        <is>
-          <t>សំណើរបស់ខ្ញុំ</t>
-        </is>
-      </c>
-      <c r="F112" s="23" t="inlineStr">
-        <is>
-          <t>/approvals/my-requests</t>
-        </is>
-      </c>
-      <c r="G112" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H112" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I112" s="20" t="inlineStr">
-        <is>
-          <t>កំពុងរង់ចាំ</t>
-        </is>
-      </c>
-      <c r="J112" s="24" t="n"/>
-    </row>
-    <row r="113" ht="21.6" customHeight="1">
-      <c r="A113" s="19" t="n"/>
-      <c r="B113" s="20" t="n"/>
-      <c r="C113" s="20" t="n"/>
-      <c r="D113" s="20" t="n"/>
-      <c r="E113" s="20" t="n"/>
-      <c r="F113" s="23" t="n"/>
-      <c r="G113" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H113" s="20" t="inlineStr">
-        <is>
-          <t>Approved to study</t>
-        </is>
-      </c>
-      <c r="I113" s="20" t="inlineStr">
-        <is>
-          <t>អនុញ្ញាតឱ្យមករៀន</t>
-        </is>
-      </c>
-      <c r="J113" s="24" t="n"/>
-    </row>
-    <row r="114" ht="22.2" customHeight="1" thickBot="1">
+      <c r="G113" s="17" t="n"/>
+      <c r="H113" s="15" t="n"/>
+      <c r="I113" s="15" t="n"/>
+      <c r="J113" s="18" t="n"/>
+    </row>
+    <row r="114" ht="21.6" customHeight="1" thickBot="1">
       <c r="A114" s="19" t="n"/>
       <c r="B114" s="20" t="n"/>
       <c r="C114" s="20" t="n"/>
-      <c r="D114" s="20" t="n"/>
-      <c r="E114" s="20" t="n"/>
-      <c r="F114" s="23" t="n"/>
+      <c r="D114" s="22" t="inlineStr">
+        <is>
+          <t>My Request</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>សំណើរបស់ខ្ញុំ</t>
+        </is>
+      </c>
+      <c r="F114" s="23" t="inlineStr">
+        <is>
+          <t>/approvals/my-requests</t>
+        </is>
+      </c>
       <c r="G114" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H114" s="20" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="I114" s="20" t="inlineStr">
         <is>
-          <t>បានអនុម័ត</t>
+          <t>កំពុងរង់ចាំ</t>
         </is>
       </c>
       <c r="J114" s="24" t="n"/>
@@ -14727,21 +14805,21 @@
       <c r="E115" s="20" t="n"/>
       <c r="F115" s="23" t="n"/>
       <c r="G115" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H115" s="20" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Approved to study</t>
         </is>
       </c>
       <c r="I115" s="20" t="inlineStr">
         <is>
-          <t>បានបដិសេធ</t>
+          <t>អនុញ្ញាតឱ្យមករៀន</t>
         </is>
       </c>
       <c r="J115" s="24" t="n"/>
     </row>
-    <row r="116" ht="21.6" customHeight="1">
+    <row r="116" ht="22.2" customHeight="1">
       <c r="A116" s="19" t="n"/>
       <c r="B116" s="20" t="n"/>
       <c r="C116" s="20" t="n"/>
@@ -14749,16 +14827,16 @@
       <c r="E116" s="20" t="n"/>
       <c r="F116" s="23" t="n"/>
       <c r="G116" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H116" s="20" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="I116" s="20" t="inlineStr">
         <is>
-          <t>បានលុបចោល</t>
+          <t>បានអនុម័ត</t>
         </is>
       </c>
       <c r="J116" s="24" t="n"/>
@@ -14767,121 +14845,165 @@
       <c r="A117" s="19" t="n"/>
       <c r="B117" s="20" t="n"/>
       <c r="C117" s="20" t="n"/>
-      <c r="D117" s="22" t="inlineStr">
-        <is>
-          <t>Form Categories</t>
-        </is>
-      </c>
-      <c r="E117" s="20" t="inlineStr">
-        <is>
-          <t>ប្រភេទទម្រង់បែបបទ</t>
-        </is>
-      </c>
-      <c r="F117" s="23" t="inlineStr">
-        <is>
-          <t>/form-categories</t>
-        </is>
-      </c>
-      <c r="G117" s="19" t="n"/>
-      <c r="H117" s="20" t="n"/>
-      <c r="I117" s="20" t="n"/>
+      <c r="D117" s="20" t="n"/>
+      <c r="E117" s="20" t="n"/>
+      <c r="F117" s="23" t="n"/>
+      <c r="G117" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H117" s="20" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I117" s="20" t="inlineStr">
+        <is>
+          <t>បានបដិសេធ</t>
+        </is>
+      </c>
       <c r="J117" s="24" t="n"/>
     </row>
     <row r="118" ht="21.6" customHeight="1">
       <c r="A118" s="19" t="n"/>
       <c r="B118" s="20" t="n"/>
       <c r="C118" s="20" t="n"/>
-      <c r="D118" s="22" t="inlineStr">
+      <c r="D118" s="20" t="n"/>
+      <c r="E118" s="20" t="n"/>
+      <c r="F118" s="23" t="n"/>
+      <c r="G118" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H118" s="20" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="I118" s="20" t="inlineStr">
+        <is>
+          <t>បានលុបចោល</t>
+        </is>
+      </c>
+      <c r="J118" s="24" t="n"/>
+    </row>
+    <row r="119" ht="21.6" customHeight="1">
+      <c r="A119" s="19" t="n"/>
+      <c r="B119" s="20" t="n"/>
+      <c r="C119" s="20" t="n"/>
+      <c r="D119" s="22" t="inlineStr">
+        <is>
+          <t>Form Categories</t>
+        </is>
+      </c>
+      <c r="E119" s="20" t="inlineStr">
+        <is>
+          <t>ប្រភេទទម្រង់បែបបទ</t>
+        </is>
+      </c>
+      <c r="F119" s="23" t="inlineStr">
+        <is>
+          <t>/form-categories</t>
+        </is>
+      </c>
+      <c r="G119" s="19" t="n"/>
+      <c r="H119" s="20" t="n"/>
+      <c r="I119" s="20" t="n"/>
+      <c r="J119" s="24" t="n"/>
+    </row>
+    <row r="120" ht="21.6" customHeight="1">
+      <c r="A120" s="19" t="n"/>
+      <c r="B120" s="20" t="n"/>
+      <c r="C120" s="20" t="n"/>
+      <c r="D120" s="22" t="inlineStr">
         <is>
           <t>Form Templates</t>
         </is>
       </c>
-      <c r="E118" s="20" t="inlineStr">
+      <c r="E120" s="20" t="inlineStr">
         <is>
           <t>ទម្រង់បែបបទ</t>
         </is>
       </c>
-      <c r="F118" s="23" t="inlineStr">
+      <c r="F120" s="23" t="inlineStr">
         <is>
           <t>/form-templates</t>
         </is>
       </c>
-      <c r="G118" s="19" t="n"/>
-      <c r="H118" s="20" t="n"/>
-      <c r="I118" s="20" t="n"/>
-      <c r="J118" s="24" t="n"/>
-    </row>
-    <row r="119" ht="21.6" customHeight="1">
-      <c r="A119" s="1" t="inlineStr">
+      <c r="G120" s="19" t="n"/>
+      <c r="H120" s="20" t="n"/>
+      <c r="I120" s="20" t="n"/>
+      <c r="J120" s="24" t="n"/>
+    </row>
+    <row r="121" ht="21.6" customHeight="1">
+      <c r="A121" s="1" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Groups</t>
         </is>
       </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>ក្រុម</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>/approval-flow/groups</t>
         </is>
       </c>
-      <c r="G119" s="5" t="n"/>
-      <c r="H119" s="3" t="n"/>
-      <c r="I119" s="3" t="n"/>
-      <c r="J119" s="6" t="n"/>
-    </row>
-    <row r="120" ht="21.6" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
+      <c r="G121" s="5" t="n"/>
+      <c r="H121" s="3" t="n"/>
+      <c r="I121" s="3" t="n"/>
+      <c r="J121" s="6" t="n"/>
+    </row>
+    <row r="122" ht="21.6" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>Approval Flow</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="C122" s="8" t="inlineStr">
         <is>
           <t>លំហូរអនុម័ត</t>
         </is>
       </c>
-      <c r="D120" s="10" t="inlineStr">
+      <c r="D122" s="10" t="inlineStr">
         <is>
           <t>Flow Setting</t>
         </is>
       </c>
-      <c r="E120" s="8" t="inlineStr">
+      <c r="E122" s="8" t="inlineStr">
         <is>
           <t>កំណត់លំហូរ</t>
         </is>
       </c>
-      <c r="F120" s="11" t="inlineStr">
+      <c r="F122" s="11" t="inlineStr">
         <is>
           <t>/approval-flow/settings</t>
         </is>
       </c>
-      <c r="G120" s="7" t="n"/>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="8" t="n"/>
-      <c r="J120" s="12" t="n"/>
+      <c r="G122" s="7" t="n"/>
+      <c r="H122" s="8" t="n"/>
+      <c r="I122" s="8" t="n"/>
+      <c r="J122" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
